--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F8A432-959D-FD4A-9D01-81F7FCE6E8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5724752-EA23-E148-A973-F7B4213637D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="1060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="1071">
   <si>
     <t>プロジェクト概要</t>
   </si>
@@ -4077,15 +4077,7 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>GET/POST/PUT</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>AttendanceController</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>create/store/update</t>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -4134,10 +4126,6 @@
   <si>
     <t>AttendanceController/
 ApplicationRequestController</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>create/store</t>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -4438,49 +4426,8 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>register.blade.php</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>ログイン画面（一般ユーザー）</t>
     <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>user-login.blade.php</t>
-  </si>
-  <si>
-    <t>attendance-register.blade.php</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>user-attendance-list.blade.php</t>
-  </si>
-  <si>
-    <t>user-detail.blade.php</t>
-  </si>
-  <si>
-    <t>user-application-list.blade.php</t>
-  </si>
-  <si>
-    <t>admin-login.blade.php</t>
-  </si>
-  <si>
-    <t>admin-attendance-list.blade.php</t>
-  </si>
-  <si>
-    <t>admin-detail.blade.php</t>
-  </si>
-  <si>
-    <t>staff-list.blade.php</t>
-  </si>
-  <si>
-    <t>staff-attendance-list.blade.php</t>
-  </si>
-  <si>
-    <t>admin-application-list.blade.php</t>
-  </si>
-  <si>
-    <t>admin-application-detail.blade.php</t>
   </si>
   <si>
     <t>index.blade.php</t>
@@ -4699,61 +4646,7 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>必須</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / date_format:H:i:s / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>before:clock_out</t>
-    </r>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>new_clock_out</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">nullable / date_format:H:i:s / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>after:clock_in</t>
-    </r>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -4804,10 +4697,6 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>UpdateAttendanceRequest.php</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>new_clock_in</t>
   </si>
   <si>
@@ -4815,10 +4704,6 @@
   </si>
   <si>
     <t>new_clock_out</t>
-  </si>
-  <si>
-    <t>nullable / date_format:H:i:s / after:clock_in</t>
-    <phoneticPr fontId="80"/>
   </si>
   <si>
     <t>new_break_in[]</t>
@@ -5110,12 +4995,6 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>break_in</t>
-  </si>
-  <si>
-    <t>break_out</t>
-  </si>
-  <si>
     <r>
       <t>applications</t>
     </r>
@@ -5449,6 +5328,295 @@
     </rPh>
     <phoneticPr fontId="80"/>
   </si>
+  <si>
+    <t>/login</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>UpdateAttendanceRecordRequest.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t xml:space="preserve">AttendanceController@create
+AttendanceController@store
+</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>break_out</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>create/store(
+StoreAttendanceService, 
+UpdateAttendanceService,
+UpdateAttendanceService,
+StoreBreakTimeService,
+UpdateBreakTimeService)</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>break_in</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>user/register.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>user/user-login.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>user/attendance-register.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>user/user-attendance-list.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>user/user-detail.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>user/user-application-list.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>admin/admin-login.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>admin/admin-attendance-list.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>admin/admin-detail.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>admin/staff-list.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>admin/staff-attendance-list.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>admin/admin-application-list.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>admin/admin-application-detail.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>auth/verify-email.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>レイアウト（一般ユーザー）</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>レイアウト（管理者）</t>
+    <rPh sb="6" eb="9">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>layouts/app.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>layouts/admin-app.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>show/store</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+      </rPr>
+      <t>/attendance/detail/{id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+/attendance/{id}</t>
+    </r>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>←</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>元の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>URL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>View</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>の内容と違うため修正</t>
+    </r>
+    <rPh sb="1" eb="2">
+      <t>モトノ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ノナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>必須</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / date_format:H:i:s / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>before:new_clock_out</t>
+    </r>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">nullable / date_format:H:i:s / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>after:new_clock_in</t>
+    </r>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>必須</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / date_format:H:i:s / before:new_clock_out</t>
+    </r>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>nullable / date_format:H:i:s / after:new_clock_in</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>nullable / array / date_format:H:i:s / before:new_clock_out / new_after:clock_in</t>
+    <rPh sb="58" eb="63">
+      <t>イゼnカクニn</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>nullable / array / date_format:H:i:s / before:new_clock_out</t>
+    <rPh sb="52" eb="54">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
 </sst>
 </file>
 
@@ -5458,7 +5626,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm"/>
   </numFmts>
-  <fonts count="90">
+  <fonts count="94">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -6068,8 +6236,36 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS Gothic"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6182,6 +6378,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC0504D"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0504D"/>
+        <bgColor rgb="FFD4DBE4"/>
       </patternFill>
     </fill>
   </fills>
@@ -7142,7 +7344,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18"/>
   </cellStyleXfs>
-  <cellXfs count="477">
+  <cellXfs count="485">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8199,9 +8401,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -8212,9 +8411,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -8310,6 +8506,41 @@
     <xf numFmtId="0" fontId="8" fillId="18" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="19" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="82" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="20" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="79" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8342,17 +8573,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -8880,7 +9100,7 @@
     <row r="3" spans="1:12" ht="36.75" customHeight="1">
       <c r="A3" s="303"/>
       <c r="B3" s="303"/>
-      <c r="C3" s="409" t="s">
+      <c r="C3" s="407" t="s">
         <v>654</v>
       </c>
       <c r="D3" s="305"/>
@@ -8898,44 +9118,44 @@
       <c r="C4" s="374" t="s">
         <v>659</v>
       </c>
-      <c r="D4" s="410"/>
-      <c r="E4" s="411"/>
-      <c r="F4" s="411"/>
-      <c r="G4" s="411"/>
-      <c r="H4" s="411"/>
-      <c r="I4" s="411"/>
-      <c r="J4" s="411"/>
-      <c r="K4" s="411"/>
+      <c r="D4" s="408"/>
+      <c r="E4" s="409"/>
+      <c r="F4" s="409"/>
+      <c r="G4" s="409"/>
+      <c r="H4" s="409"/>
+      <c r="I4" s="409"/>
+      <c r="J4" s="409"/>
+      <c r="K4" s="409"/>
       <c r="L4" s="305"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="303"/>
       <c r="B5" s="303"/>
-      <c r="C5" s="412" t="s">
+      <c r="C5" s="410" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="413" t="s">
+      <c r="D5" s="411" t="s">
         <v>671</v>
       </c>
-      <c r="E5" s="414" t="s">
+      <c r="E5" s="412" t="s">
         <v>675</v>
       </c>
-      <c r="F5" s="414" t="s">
+      <c r="F5" s="412" t="s">
         <v>438</v>
       </c>
-      <c r="G5" s="414" t="s">
+      <c r="G5" s="412" t="s">
         <v>676</v>
       </c>
-      <c r="H5" s="414" t="s">
+      <c r="H5" s="412" t="s">
         <v>677</v>
       </c>
-      <c r="I5" s="414" t="s">
+      <c r="I5" s="412" t="s">
         <v>678</v>
       </c>
-      <c r="J5" s="414" t="s">
+      <c r="J5" s="412" t="s">
         <v>679</v>
       </c>
-      <c r="K5" s="415" t="s">
+      <c r="K5" s="413" t="s">
         <v>681</v>
       </c>
       <c r="L5" s="305"/>
@@ -8943,81 +9163,81 @@
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="367"/>
       <c r="B6" s="367"/>
-      <c r="C6" s="416">
+      <c r="C6" s="414">
         <v>1</v>
       </c>
-      <c r="D6" s="417" t="s">
-        <v>1003</v>
-      </c>
-      <c r="E6" s="418"/>
-      <c r="F6" s="418"/>
-      <c r="G6" s="418"/>
-      <c r="H6" s="418"/>
-      <c r="I6" s="418"/>
-      <c r="J6" s="419"/>
-      <c r="K6" s="420"/>
+      <c r="D6" s="415" t="s">
+        <v>983</v>
+      </c>
+      <c r="E6" s="416"/>
+      <c r="F6" s="416"/>
+      <c r="G6" s="416"/>
+      <c r="H6" s="416"/>
+      <c r="I6" s="416"/>
+      <c r="J6" s="417"/>
+      <c r="K6" s="418"/>
       <c r="L6" s="305"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="303"/>
       <c r="B7" s="303"/>
-      <c r="C7" s="421"/>
-      <c r="E7" s="394" t="s">
+      <c r="C7" s="419"/>
+      <c r="E7" s="393" t="s">
         <v>701</v>
       </c>
-      <c r="F7" s="422" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G7" s="422" t="s">
+      <c r="F7" s="420" t="s">
+        <v>984</v>
+      </c>
+      <c r="G7" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="H7" s="394"/>
-      <c r="I7" s="422" t="s">
+      <c r="H7" s="393"/>
+      <c r="I7" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="J7" s="423"/>
-      <c r="K7" s="420"/>
+      <c r="J7" s="421"/>
+      <c r="K7" s="418"/>
       <c r="L7" s="305"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="375"/>
       <c r="B8" s="375"/>
-      <c r="C8" s="424"/>
+      <c r="C8" s="422"/>
       <c r="D8" s="304"/>
-      <c r="E8" s="394" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F8" s="394" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G8" s="394"/>
-      <c r="H8" s="394"/>
-      <c r="I8" s="422" t="s">
+      <c r="E8" s="393" t="s">
+        <v>985</v>
+      </c>
+      <c r="F8" s="393" t="s">
+        <v>986</v>
+      </c>
+      <c r="G8" s="393"/>
+      <c r="H8" s="393"/>
+      <c r="I8" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="J8" s="423"/>
-      <c r="K8" s="420"/>
+      <c r="J8" s="421"/>
+      <c r="K8" s="418"/>
       <c r="L8" s="305"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
       <c r="A9" s="367"/>
       <c r="B9" s="367"/>
-      <c r="C9" s="421"/>
-      <c r="E9" s="394" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F9" s="394" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G9" s="394"/>
-      <c r="H9" s="422" t="s">
+      <c r="C9" s="419"/>
+      <c r="E9" s="393" t="s">
+        <v>987</v>
+      </c>
+      <c r="F9" s="393" t="s">
+        <v>986</v>
+      </c>
+      <c r="G9" s="393"/>
+      <c r="H9" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="I9" s="422" t="s">
+      <c r="I9" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="J9" s="423"/>
-      <c r="K9" s="425" t="s">
+      <c r="J9" s="421"/>
+      <c r="K9" s="423" t="s">
         <v>764</v>
       </c>
       <c r="L9" s="305"/>
@@ -9025,1269 +9245,1269 @@
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
       <c r="A10" s="367"/>
       <c r="B10" s="367"/>
-      <c r="C10" s="421"/>
-      <c r="E10" s="394" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F10" s="394" t="s">
+      <c r="C10" s="419"/>
+      <c r="E10" s="393" t="s">
+        <v>988</v>
+      </c>
+      <c r="F10" s="393" t="s">
         <v>731</v>
       </c>
-      <c r="G10" s="394"/>
-      <c r="H10" s="394"/>
-      <c r="I10" s="422"/>
-      <c r="J10" s="423"/>
-      <c r="K10" s="420"/>
+      <c r="G10" s="393"/>
+      <c r="H10" s="393"/>
+      <c r="I10" s="420"/>
+      <c r="J10" s="421"/>
+      <c r="K10" s="418"/>
       <c r="L10" s="305"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="367"/>
       <c r="B11" s="367"/>
-      <c r="C11" s="421"/>
-      <c r="E11" s="394" t="s">
-        <v>1009</v>
-      </c>
-      <c r="F11" s="394" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G11" s="394"/>
-      <c r="H11" s="394"/>
-      <c r="I11" s="422" t="s">
+      <c r="C11" s="419"/>
+      <c r="E11" s="393" t="s">
+        <v>989</v>
+      </c>
+      <c r="F11" s="393" t="s">
+        <v>986</v>
+      </c>
+      <c r="G11" s="393"/>
+      <c r="H11" s="393"/>
+      <c r="I11" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="J11" s="423"/>
-      <c r="K11" s="420"/>
+      <c r="J11" s="421"/>
+      <c r="K11" s="418"/>
       <c r="L11" s="305"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="367"/>
       <c r="B12" s="367"/>
-      <c r="C12" s="421"/>
-      <c r="E12" s="394" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F12" s="394" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G12" s="394"/>
-      <c r="H12" s="394"/>
-      <c r="I12" s="394"/>
-      <c r="J12" s="423"/>
-      <c r="K12" s="420"/>
+      <c r="C12" s="419"/>
+      <c r="E12" s="393" t="s">
+        <v>990</v>
+      </c>
+      <c r="F12" s="393" t="s">
+        <v>991</v>
+      </c>
+      <c r="G12" s="393"/>
+      <c r="H12" s="393"/>
+      <c r="I12" s="393"/>
+      <c r="J12" s="421"/>
+      <c r="K12" s="418"/>
       <c r="L12" s="305"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="367"/>
       <c r="B13" s="367"/>
-      <c r="C13" s="421"/>
-      <c r="D13" s="440" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E13" s="451" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F13" s="451" t="s">
-        <v>1028</v>
-      </c>
-      <c r="G13" s="394"/>
-      <c r="H13" s="394"/>
-      <c r="I13" s="452" t="s">
+      <c r="C13" s="419"/>
+      <c r="D13" s="438" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E13" s="449" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F13" s="449" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G13" s="393"/>
+      <c r="H13" s="393"/>
+      <c r="I13" s="450" t="s">
         <v>710</v>
       </c>
-      <c r="J13" s="423"/>
-      <c r="K13" s="420"/>
+      <c r="J13" s="421"/>
+      <c r="K13" s="418"/>
       <c r="L13" s="305"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
       <c r="A14" s="367"/>
       <c r="B14" s="367"/>
-      <c r="C14" s="421"/>
-      <c r="D14" s="440" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E14" s="394" t="s">
-        <v>1050</v>
-      </c>
-      <c r="F14" s="394" t="s">
-        <v>1051</v>
-      </c>
-      <c r="G14" s="394"/>
-      <c r="H14" s="394"/>
-      <c r="I14" s="394"/>
-      <c r="J14" s="423"/>
-      <c r="K14" s="420"/>
+      <c r="C14" s="419"/>
+      <c r="D14" s="438" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E14" s="393" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F14" s="393" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G14" s="393"/>
+      <c r="H14" s="393"/>
+      <c r="I14" s="393"/>
+      <c r="J14" s="421"/>
+      <c r="K14" s="418"/>
       <c r="L14" s="305"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="A15" s="367"/>
       <c r="B15" s="367"/>
-      <c r="C15" s="421"/>
-      <c r="E15" s="394" t="s">
+      <c r="C15" s="419"/>
+      <c r="E15" s="393" t="s">
         <v>730</v>
       </c>
-      <c r="F15" s="394" t="s">
+      <c r="F15" s="393" t="s">
         <v>731</v>
       </c>
-      <c r="G15" s="394"/>
-      <c r="H15" s="394"/>
-      <c r="I15" s="394"/>
-      <c r="J15" s="423"/>
-      <c r="K15" s="420"/>
+      <c r="G15" s="393"/>
+      <c r="H15" s="393"/>
+      <c r="I15" s="393"/>
+      <c r="J15" s="421"/>
+      <c r="K15" s="418"/>
       <c r="L15" s="305"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
       <c r="A16" s="367"/>
       <c r="B16" s="367"/>
-      <c r="C16" s="421"/>
-      <c r="E16" s="394" t="s">
+      <c r="C16" s="419"/>
+      <c r="E16" s="393" t="s">
         <v>739</v>
       </c>
-      <c r="F16" s="394" t="s">
+      <c r="F16" s="393" t="s">
         <v>731</v>
       </c>
-      <c r="G16" s="394"/>
-      <c r="H16" s="394"/>
-      <c r="I16" s="394"/>
-      <c r="J16" s="423"/>
-      <c r="K16" s="420"/>
+      <c r="G16" s="393"/>
+      <c r="H16" s="393"/>
+      <c r="I16" s="393"/>
+      <c r="J16" s="421"/>
+      <c r="K16" s="418"/>
       <c r="L16" s="305"/>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A17" s="398"/>
-      <c r="B17" s="398"/>
-      <c r="C17" s="428">
+      <c r="A17" s="396"/>
+      <c r="B17" s="396"/>
+      <c r="C17" s="426">
         <v>2</v>
       </c>
-      <c r="D17" s="426" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E17" s="418"/>
-      <c r="F17" s="418"/>
-      <c r="G17" s="418"/>
-      <c r="H17" s="418"/>
-      <c r="I17" s="418"/>
-      <c r="J17" s="419"/>
+      <c r="D17" s="424" t="s">
+        <v>992</v>
+      </c>
+      <c r="E17" s="416"/>
+      <c r="F17" s="416"/>
+      <c r="G17" s="416"/>
+      <c r="H17" s="416"/>
+      <c r="I17" s="416"/>
+      <c r="J17" s="417"/>
       <c r="K17" s="305"/>
       <c r="L17" s="305"/>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A18" s="398"/>
-      <c r="B18" s="398"/>
-      <c r="C18" s="427"/>
-      <c r="E18" s="394" t="s">
-        <v>1013</v>
+      <c r="A18" s="396"/>
+      <c r="B18" s="396"/>
+      <c r="C18" s="425"/>
+      <c r="E18" s="393" t="s">
+        <v>993</v>
       </c>
       <c r="F18" s="363" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G18" s="422" t="s">
-        <v>905</v>
-      </c>
-      <c r="H18" s="394"/>
-      <c r="I18" s="422" t="s">
-        <v>905</v>
-      </c>
-      <c r="J18" s="423"/>
+        <v>984</v>
+      </c>
+      <c r="G18" s="420" t="s">
+        <v>903</v>
+      </c>
+      <c r="H18" s="393"/>
+      <c r="I18" s="420" t="s">
+        <v>903</v>
+      </c>
+      <c r="J18" s="421"/>
       <c r="K18" s="305"/>
       <c r="L18" s="305"/>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A19" s="398"/>
-      <c r="B19" s="398"/>
-      <c r="C19" s="427"/>
+      <c r="A19" s="396"/>
+      <c r="B19" s="396"/>
+      <c r="C19" s="425"/>
       <c r="D19" s="312" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E19" s="394" t="s">
-        <v>985</v>
+        <v>994</v>
+      </c>
+      <c r="E19" s="393" t="s">
+        <v>965</v>
       </c>
       <c r="F19" s="363" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G19" s="422"/>
-      <c r="H19" s="394" t="s">
-        <v>905</v>
-      </c>
-      <c r="I19" s="422" t="s">
-        <v>905</v>
-      </c>
-      <c r="J19" s="423" t="s">
-        <v>1016</v>
+        <v>995</v>
+      </c>
+      <c r="G19" s="420"/>
+      <c r="H19" s="393" t="s">
+        <v>903</v>
+      </c>
+      <c r="I19" s="420" t="s">
+        <v>903</v>
+      </c>
+      <c r="J19" s="421" t="s">
+        <v>996</v>
       </c>
       <c r="K19" s="305"/>
       <c r="L19" s="305"/>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A20" s="398"/>
-      <c r="B20" s="398"/>
-      <c r="C20" s="427"/>
+      <c r="A20" s="396"/>
+      <c r="B20" s="396"/>
+      <c r="C20" s="425"/>
       <c r="D20" s="312"/>
-      <c r="E20" s="394" t="s">
-        <v>987</v>
+      <c r="E20" s="393" t="s">
+        <v>967</v>
       </c>
       <c r="F20" s="363" t="s">
-        <v>987</v>
-      </c>
-      <c r="G20" s="422"/>
-      <c r="H20" s="394" t="s">
-        <v>905</v>
-      </c>
-      <c r="I20" s="422"/>
-      <c r="J20" s="423"/>
+        <v>967</v>
+      </c>
+      <c r="G20" s="420"/>
+      <c r="H20" s="393" t="s">
+        <v>903</v>
+      </c>
+      <c r="I20" s="420"/>
+      <c r="J20" s="421"/>
       <c r="K20" s="305"/>
       <c r="L20" s="305"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A21" s="398"/>
-      <c r="B21" s="398"/>
-      <c r="C21" s="427"/>
+      <c r="A21" s="396"/>
+      <c r="B21" s="396"/>
+      <c r="C21" s="425"/>
       <c r="D21" s="304"/>
-      <c r="E21" s="394" t="s">
-        <v>996</v>
+      <c r="E21" s="393" t="s">
+        <v>976</v>
       </c>
       <c r="F21" s="363" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G21" s="394"/>
-      <c r="H21" s="394"/>
-      <c r="I21" s="422" t="s">
-        <v>905</v>
-      </c>
-      <c r="J21" s="423"/>
+        <v>997</v>
+      </c>
+      <c r="G21" s="393"/>
+      <c r="H21" s="393"/>
+      <c r="I21" s="420" t="s">
+        <v>903</v>
+      </c>
+      <c r="J21" s="421"/>
       <c r="K21" s="305"/>
       <c r="L21" s="305"/>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A22" s="398"/>
-      <c r="B22" s="398"/>
-      <c r="C22" s="427"/>
-      <c r="E22" s="394" t="s">
+      <c r="A22" s="396"/>
+      <c r="B22" s="396"/>
+      <c r="C22" s="425"/>
+      <c r="E22" s="393" t="s">
+        <v>977</v>
+      </c>
+      <c r="F22" s="363" t="s">
         <v>997</v>
       </c>
-      <c r="F22" s="363" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G22" s="394"/>
-      <c r="H22" s="394"/>
-      <c r="I22" s="422"/>
-      <c r="J22" s="423"/>
+      <c r="G22" s="393"/>
+      <c r="H22" s="393"/>
+      <c r="I22" s="420"/>
+      <c r="J22" s="421"/>
       <c r="K22" s="305"/>
       <c r="L22" s="305"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A23" s="398"/>
-      <c r="B23" s="398"/>
-      <c r="C23" s="427"/>
-      <c r="E23" s="451" t="s">
-        <v>999</v>
-      </c>
-      <c r="F23" s="451" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G23" s="394"/>
-      <c r="H23" s="394"/>
-      <c r="I23" s="422"/>
-      <c r="J23" s="423"/>
+      <c r="A23" s="396"/>
+      <c r="B23" s="396"/>
+      <c r="C23" s="425"/>
+      <c r="E23" s="449" t="s">
+        <v>979</v>
+      </c>
+      <c r="F23" s="449" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G23" s="393"/>
+      <c r="H23" s="393"/>
+      <c r="I23" s="420"/>
+      <c r="J23" s="421"/>
       <c r="K23" s="305"/>
       <c r="L23" s="305"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A24" s="398"/>
-      <c r="B24" s="398"/>
-      <c r="C24" s="427"/>
-      <c r="D24" s="429"/>
-      <c r="E24" s="430" t="s">
+      <c r="A24" s="396"/>
+      <c r="B24" s="396"/>
+      <c r="C24" s="425"/>
+      <c r="D24" s="427"/>
+      <c r="E24" s="428" t="s">
         <v>730</v>
       </c>
-      <c r="F24" s="430" t="s">
+      <c r="F24" s="428" t="s">
         <v>731</v>
       </c>
-      <c r="G24" s="430"/>
-      <c r="H24" s="430"/>
-      <c r="I24" s="430"/>
-      <c r="J24" s="431"/>
+      <c r="G24" s="428"/>
+      <c r="H24" s="428"/>
+      <c r="I24" s="428"/>
+      <c r="J24" s="429"/>
       <c r="K24" s="305"/>
       <c r="L24" s="305"/>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A25" s="398"/>
-      <c r="B25" s="398"/>
-      <c r="C25" s="427"/>
-      <c r="D25" s="432"/>
-      <c r="E25" s="430" t="s">
+      <c r="A25" s="396"/>
+      <c r="B25" s="396"/>
+      <c r="C25" s="425"/>
+      <c r="D25" s="430"/>
+      <c r="E25" s="428" t="s">
         <v>739</v>
       </c>
-      <c r="F25" s="430" t="s">
+      <c r="F25" s="428" t="s">
         <v>731</v>
       </c>
-      <c r="G25" s="430"/>
-      <c r="H25" s="430"/>
-      <c r="I25" s="430"/>
-      <c r="J25" s="431"/>
+      <c r="G25" s="428"/>
+      <c r="H25" s="428"/>
+      <c r="I25" s="428"/>
+      <c r="J25" s="429"/>
       <c r="K25" s="305"/>
       <c r="L25" s="305"/>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A26" s="398"/>
-      <c r="B26" s="398"/>
-      <c r="C26" s="427"/>
-      <c r="D26" s="433"/>
-      <c r="E26" s="434" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F26" s="435"/>
-      <c r="G26" s="436"/>
-      <c r="H26" s="435" t="s">
-        <v>1019</v>
-      </c>
-      <c r="I26" s="435"/>
-      <c r="J26" s="437"/>
+      <c r="A26" s="396"/>
+      <c r="B26" s="396"/>
+      <c r="C26" s="425"/>
+      <c r="D26" s="431"/>
+      <c r="E26" s="432" t="s">
+        <v>998</v>
+      </c>
+      <c r="F26" s="433"/>
+      <c r="G26" s="434"/>
+      <c r="H26" s="433" t="s">
+        <v>999</v>
+      </c>
+      <c r="I26" s="433"/>
+      <c r="J26" s="435"/>
       <c r="K26" s="305"/>
       <c r="L26" s="305"/>
     </row>
     <row r="27" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A27" s="398"/>
-      <c r="B27" s="398"/>
-      <c r="C27" s="428">
+      <c r="A27" s="396"/>
+      <c r="B27" s="396"/>
+      <c r="C27" s="426">
         <v>3</v>
       </c>
-      <c r="D27" s="426" t="s">
-        <v>1048</v>
-      </c>
-      <c r="E27" s="418"/>
-      <c r="F27" s="418"/>
-      <c r="G27" s="418"/>
-      <c r="H27" s="418"/>
-      <c r="I27" s="418"/>
-      <c r="J27" s="419"/>
+      <c r="D27" s="424" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E27" s="416"/>
+      <c r="F27" s="416"/>
+      <c r="G27" s="416"/>
+      <c r="H27" s="416"/>
+      <c r="I27" s="416"/>
+      <c r="J27" s="417"/>
       <c r="K27" s="305"/>
       <c r="L27" s="305"/>
     </row>
     <row r="28" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A28" s="398"/>
-      <c r="B28" s="398"/>
-      <c r="C28" s="427"/>
-      <c r="E28" s="394" t="s">
+      <c r="A28" s="396"/>
+      <c r="B28" s="396"/>
+      <c r="C28" s="425"/>
+      <c r="E28" s="393" t="s">
         <v>701</v>
       </c>
-      <c r="F28" s="394" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G28" s="422" t="s">
+      <c r="F28" s="393" t="s">
+        <v>984</v>
+      </c>
+      <c r="G28" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="H28" s="394"/>
-      <c r="I28" s="422" t="s">
+      <c r="H28" s="393"/>
+      <c r="I28" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="J28" s="423"/>
+      <c r="J28" s="421"/>
       <c r="K28" s="305"/>
       <c r="L28" s="305"/>
     </row>
     <row r="29" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A29" s="398"/>
-      <c r="B29" s="398"/>
-      <c r="C29" s="427"/>
+      <c r="A29" s="396"/>
+      <c r="B29" s="396"/>
+      <c r="C29" s="425"/>
       <c r="D29" s="312" t="s">
-        <v>1014</v>
-      </c>
-      <c r="E29" s="455" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F29" s="394" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G29" s="422"/>
-      <c r="H29" s="394"/>
-      <c r="I29" s="422" t="s">
+        <v>994</v>
+      </c>
+      <c r="E29" s="453" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F29" s="393" t="s">
+        <v>984</v>
+      </c>
+      <c r="G29" s="420"/>
+      <c r="H29" s="393"/>
+      <c r="I29" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="J29" s="423" t="s">
-        <v>1020</v>
+      <c r="J29" s="421" t="s">
+        <v>1000</v>
       </c>
       <c r="K29" s="305"/>
       <c r="L29" s="305"/>
     </row>
     <row r="30" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A30" s="398"/>
-      <c r="B30" s="398"/>
-      <c r="C30" s="427"/>
+      <c r="A30" s="396"/>
+      <c r="B30" s="396"/>
+      <c r="C30" s="425"/>
       <c r="D30" s="304"/>
-      <c r="E30" s="394" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F30" s="394" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G30" s="394"/>
-      <c r="H30" s="394"/>
-      <c r="I30" s="422"/>
-      <c r="J30" s="438"/>
+      <c r="E30" s="393" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F30" s="393" t="s">
+        <v>997</v>
+      </c>
+      <c r="G30" s="393"/>
+      <c r="H30" s="393"/>
+      <c r="I30" s="420"/>
+      <c r="J30" s="436"/>
       <c r="K30" s="305"/>
       <c r="L30" s="305"/>
     </row>
     <row r="31" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A31" s="398"/>
-      <c r="B31" s="398"/>
-      <c r="C31" s="427"/>
-      <c r="E31" s="394" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F31" s="394" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G31" s="394"/>
-      <c r="H31" s="394"/>
-      <c r="I31" s="422"/>
-      <c r="J31" s="423"/>
+      <c r="A31" s="396"/>
+      <c r="B31" s="396"/>
+      <c r="C31" s="425"/>
+      <c r="E31" s="393" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F31" s="393" t="s">
+        <v>997</v>
+      </c>
+      <c r="G31" s="393"/>
+      <c r="H31" s="393"/>
+      <c r="I31" s="420"/>
+      <c r="J31" s="421"/>
       <c r="K31" s="305"/>
       <c r="L31" s="305"/>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A32" s="398"/>
-      <c r="B32" s="398"/>
-      <c r="C32" s="427"/>
-      <c r="E32" s="394" t="s">
+      <c r="A32" s="396"/>
+      <c r="B32" s="396"/>
+      <c r="C32" s="425"/>
+      <c r="E32" s="393" t="s">
         <v>730</v>
       </c>
-      <c r="F32" s="394" t="s">
+      <c r="F32" s="393" t="s">
         <v>731</v>
       </c>
-      <c r="G32" s="394"/>
-      <c r="H32" s="394"/>
-      <c r="I32" s="394"/>
-      <c r="J32" s="423"/>
+      <c r="G32" s="393"/>
+      <c r="H32" s="393"/>
+      <c r="I32" s="393"/>
+      <c r="J32" s="421"/>
       <c r="K32" s="305"/>
       <c r="L32" s="305"/>
     </row>
     <row r="33" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A33" s="398"/>
-      <c r="B33" s="398"/>
-      <c r="C33" s="427"/>
-      <c r="E33" s="394" t="s">
+      <c r="A33" s="396"/>
+      <c r="B33" s="396"/>
+      <c r="C33" s="425"/>
+      <c r="E33" s="393" t="s">
         <v>739</v>
       </c>
-      <c r="F33" s="394" t="s">
+      <c r="F33" s="393" t="s">
         <v>731</v>
       </c>
-      <c r="G33" s="394"/>
-      <c r="H33" s="394"/>
-      <c r="I33" s="394"/>
-      <c r="J33" s="423"/>
+      <c r="G33" s="393"/>
+      <c r="H33" s="393"/>
+      <c r="I33" s="393"/>
+      <c r="J33" s="421"/>
       <c r="K33" s="305"/>
       <c r="L33" s="305"/>
     </row>
     <row r="34" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A34" s="398"/>
-      <c r="B34" s="398"/>
-      <c r="C34" s="428">
+      <c r="A34" s="396"/>
+      <c r="B34" s="396"/>
+      <c r="C34" s="426">
         <v>4</v>
       </c>
-      <c r="D34" s="472" t="s">
-        <v>1023</v>
-      </c>
-      <c r="E34" s="473"/>
-      <c r="F34" s="473"/>
-      <c r="G34" s="473"/>
-      <c r="H34" s="473"/>
-      <c r="I34" s="418"/>
-      <c r="J34" s="419"/>
+      <c r="D34" s="468" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E34" s="469"/>
+      <c r="F34" s="469"/>
+      <c r="G34" s="469"/>
+      <c r="H34" s="469"/>
+      <c r="I34" s="416"/>
+      <c r="J34" s="417"/>
       <c r="K34" s="305"/>
       <c r="L34" s="305"/>
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A35" s="398"/>
-      <c r="B35" s="398"/>
-      <c r="C35" s="427"/>
-      <c r="E35" s="394" t="s">
-        <v>1013</v>
+      <c r="A35" s="396"/>
+      <c r="B35" s="396"/>
+      <c r="C35" s="425"/>
+      <c r="E35" s="393" t="s">
+        <v>993</v>
       </c>
       <c r="F35" s="363" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G35" s="422" t="s">
-        <v>905</v>
-      </c>
-      <c r="H35" s="394"/>
-      <c r="I35" s="422" t="s">
-        <v>905</v>
-      </c>
-      <c r="J35" s="423"/>
+        <v>984</v>
+      </c>
+      <c r="G35" s="420" t="s">
+        <v>903</v>
+      </c>
+      <c r="H35" s="393"/>
+      <c r="I35" s="420" t="s">
+        <v>903</v>
+      </c>
+      <c r="J35" s="421"/>
       <c r="K35" s="305"/>
       <c r="L35" s="305"/>
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A36" s="398"/>
-      <c r="B36" s="398"/>
-      <c r="C36" s="427"/>
+      <c r="A36" s="396"/>
+      <c r="B36" s="396"/>
+      <c r="C36" s="425"/>
       <c r="D36" s="306" t="s">
-        <v>1024</v>
-      </c>
-      <c r="E36" s="455" t="s">
-        <v>1058</v>
+        <v>1002</v>
+      </c>
+      <c r="E36" s="453" t="s">
+        <v>1036</v>
       </c>
       <c r="F36" s="363" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G36" s="422"/>
-      <c r="H36" s="394"/>
-      <c r="I36" s="422" t="s">
+        <v>984</v>
+      </c>
+      <c r="G36" s="420"/>
+      <c r="H36" s="393"/>
+      <c r="I36" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="J36" s="423" t="s">
-        <v>1020</v>
+      <c r="J36" s="421" t="s">
+        <v>1000</v>
       </c>
       <c r="K36" s="305"/>
       <c r="L36" s="305"/>
     </row>
     <row r="37" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A37" s="398"/>
-      <c r="B37" s="398"/>
-      <c r="C37" s="427"/>
-      <c r="E37" s="394" t="s">
-        <v>968</v>
-      </c>
-      <c r="F37" s="394" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G37" s="394"/>
-      <c r="H37" s="394"/>
-      <c r="I37" s="422" t="s">
+      <c r="A37" s="396"/>
+      <c r="B37" s="396"/>
+      <c r="C37" s="425"/>
+      <c r="E37" s="393" t="s">
+        <v>952</v>
+      </c>
+      <c r="F37" s="393" t="s">
+        <v>997</v>
+      </c>
+      <c r="G37" s="393"/>
+      <c r="H37" s="393"/>
+      <c r="I37" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="J37" s="423"/>
+      <c r="J37" s="421"/>
       <c r="K37" s="305"/>
       <c r="L37" s="305"/>
     </row>
     <row r="38" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A38" s="398"/>
-      <c r="B38" s="398"/>
-      <c r="C38" s="427"/>
-      <c r="E38" s="394" t="s">
-        <v>970</v>
-      </c>
-      <c r="F38" s="439" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G38" s="394"/>
-      <c r="H38" s="394"/>
-      <c r="I38" s="456"/>
-      <c r="J38" s="423"/>
+      <c r="A38" s="396"/>
+      <c r="B38" s="396"/>
+      <c r="C38" s="425"/>
+      <c r="E38" s="393" t="s">
+        <v>953</v>
+      </c>
+      <c r="F38" s="437" t="s">
+        <v>997</v>
+      </c>
+      <c r="G38" s="393"/>
+      <c r="H38" s="393"/>
+      <c r="I38" s="454"/>
+      <c r="J38" s="421"/>
       <c r="K38" s="305"/>
       <c r="L38" s="305"/>
     </row>
     <row r="39" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A39" s="398"/>
-      <c r="B39" s="398"/>
-      <c r="C39" s="427"/>
-      <c r="E39" s="394" t="s">
-        <v>999</v>
-      </c>
-      <c r="F39" s="394" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G39" s="394"/>
-      <c r="H39" s="394"/>
-      <c r="I39" s="422" t="s">
+      <c r="A39" s="396"/>
+      <c r="B39" s="396"/>
+      <c r="C39" s="425"/>
+      <c r="E39" s="393" t="s">
+        <v>979</v>
+      </c>
+      <c r="F39" s="393" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G39" s="393"/>
+      <c r="H39" s="393"/>
+      <c r="I39" s="420" t="s">
         <v>710</v>
       </c>
-      <c r="J39" s="423"/>
+      <c r="J39" s="421"/>
       <c r="K39" s="305"/>
       <c r="L39" s="305"/>
     </row>
     <row r="40" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A40" s="398"/>
-      <c r="B40" s="398"/>
-      <c r="C40" s="427"/>
-      <c r="D40" s="440" t="s">
-        <v>1026</v>
-      </c>
-      <c r="E40" s="394" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F40" s="394" t="s">
-        <v>1028</v>
-      </c>
-      <c r="G40" s="394"/>
-      <c r="H40" s="394"/>
-      <c r="I40" s="394" t="s">
-        <v>905</v>
-      </c>
-      <c r="J40" s="423"/>
+      <c r="A40" s="396"/>
+      <c r="B40" s="396"/>
+      <c r="C40" s="425"/>
+      <c r="D40" s="438" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E40" s="393" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F40" s="393" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G40" s="393"/>
+      <c r="H40" s="393"/>
+      <c r="I40" s="393" t="s">
+        <v>903</v>
+      </c>
+      <c r="J40" s="421"/>
       <c r="K40" s="305"/>
       <c r="L40" s="305"/>
     </row>
     <row r="41" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A41" s="398"/>
-      <c r="B41" s="398"/>
-      <c r="C41" s="427"/>
-      <c r="D41" s="440"/>
-      <c r="E41" s="451" t="s">
-        <v>1055</v>
-      </c>
-      <c r="F41" s="451" t="s">
-        <v>987</v>
-      </c>
-      <c r="G41" s="394"/>
-      <c r="H41" s="394"/>
-      <c r="I41" s="451" t="s">
-        <v>905</v>
-      </c>
-      <c r="J41" s="423"/>
+      <c r="A41" s="396"/>
+      <c r="B41" s="396"/>
+      <c r="C41" s="425"/>
+      <c r="D41" s="438"/>
+      <c r="E41" s="449" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F41" s="449" t="s">
+        <v>967</v>
+      </c>
+      <c r="G41" s="393"/>
+      <c r="H41" s="393"/>
+      <c r="I41" s="449" t="s">
+        <v>903</v>
+      </c>
+      <c r="J41" s="421"/>
       <c r="K41" s="305"/>
       <c r="L41" s="305"/>
     </row>
     <row r="42" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A42" s="398"/>
-      <c r="B42" s="398"/>
-      <c r="C42" s="427"/>
-      <c r="D42" s="429"/>
-      <c r="E42" s="430" t="s">
+      <c r="A42" s="396"/>
+      <c r="B42" s="396"/>
+      <c r="C42" s="425"/>
+      <c r="D42" s="427"/>
+      <c r="E42" s="428" t="s">
         <v>730</v>
       </c>
-      <c r="F42" s="430" t="s">
+      <c r="F42" s="428" t="s">
         <v>731</v>
       </c>
-      <c r="G42" s="430"/>
-      <c r="H42" s="430"/>
-      <c r="I42" s="430"/>
-      <c r="J42" s="431"/>
+      <c r="G42" s="428"/>
+      <c r="H42" s="428"/>
+      <c r="I42" s="428"/>
+      <c r="J42" s="429"/>
       <c r="K42" s="305"/>
       <c r="L42" s="305"/>
     </row>
     <row r="43" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A43" s="398"/>
-      <c r="B43" s="398"/>
-      <c r="C43" s="441"/>
-      <c r="D43" s="433"/>
-      <c r="E43" s="430" t="s">
+      <c r="A43" s="396"/>
+      <c r="B43" s="396"/>
+      <c r="C43" s="439"/>
+      <c r="D43" s="431"/>
+      <c r="E43" s="428" t="s">
         <v>739</v>
       </c>
-      <c r="F43" s="430" t="s">
+      <c r="F43" s="428" t="s">
         <v>731</v>
       </c>
-      <c r="G43" s="430"/>
-      <c r="H43" s="430"/>
-      <c r="I43" s="430"/>
-      <c r="J43" s="431"/>
+      <c r="G43" s="428"/>
+      <c r="H43" s="428"/>
+      <c r="I43" s="428"/>
+      <c r="J43" s="429"/>
       <c r="K43" s="305"/>
       <c r="L43" s="305"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A44" s="398"/>
-      <c r="B44" s="398"/>
-      <c r="C44" s="428">
+      <c r="A44" s="396"/>
+      <c r="B44" s="396"/>
+      <c r="C44" s="426">
         <v>5</v>
       </c>
-      <c r="D44" s="454" t="s">
-        <v>1056</v>
-      </c>
-      <c r="E44" s="418"/>
-      <c r="F44" s="418"/>
-      <c r="G44" s="418"/>
-      <c r="H44" s="418"/>
-      <c r="I44" s="418"/>
-      <c r="J44" s="419"/>
+      <c r="D44" s="452" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E44" s="416"/>
+      <c r="F44" s="416"/>
+      <c r="G44" s="416"/>
+      <c r="H44" s="416"/>
+      <c r="I44" s="416"/>
+      <c r="J44" s="417"/>
       <c r="K44" s="305"/>
       <c r="L44" s="305"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A45" s="398"/>
-      <c r="B45" s="398"/>
-      <c r="C45" s="427"/>
-      <c r="E45" s="394" t="s">
+      <c r="A45" s="396"/>
+      <c r="B45" s="396"/>
+      <c r="C45" s="425"/>
+      <c r="E45" s="393" t="s">
         <v>701</v>
       </c>
-      <c r="F45" s="394" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G45" s="394" t="s">
+      <c r="F45" s="393" t="s">
+        <v>984</v>
+      </c>
+      <c r="G45" s="393" t="s">
         <v>710</v>
       </c>
-      <c r="H45" s="394"/>
-      <c r="I45" s="394" t="s">
+      <c r="H45" s="393"/>
+      <c r="I45" s="393" t="s">
         <v>710</v>
       </c>
-      <c r="J45" s="423"/>
+      <c r="J45" s="421"/>
       <c r="K45" s="305"/>
       <c r="L45" s="305"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A46" s="398"/>
-      <c r="B46" s="398"/>
-      <c r="C46" s="427"/>
+      <c r="A46" s="396"/>
+      <c r="B46" s="396"/>
+      <c r="C46" s="425"/>
       <c r="D46" s="312" t="s">
-        <v>1024</v>
-      </c>
-      <c r="E46" s="394" t="s">
-        <v>1029</v>
-      </c>
-      <c r="F46" s="394" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G46" s="394"/>
-      <c r="H46" s="394"/>
-      <c r="I46" s="394" t="s">
-        <v>905</v>
-      </c>
-      <c r="J46" s="423" t="s">
-        <v>1030</v>
+        <v>1002</v>
+      </c>
+      <c r="E46" s="393" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F46" s="393" t="s">
+        <v>984</v>
+      </c>
+      <c r="G46" s="393"/>
+      <c r="H46" s="393"/>
+      <c r="I46" s="393" t="s">
+        <v>903</v>
+      </c>
+      <c r="J46" s="421" t="s">
+        <v>1008</v>
       </c>
       <c r="K46" s="305"/>
       <c r="L46" s="305"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A47" s="398"/>
-      <c r="B47" s="398"/>
-      <c r="C47" s="427"/>
-      <c r="E47" s="394" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F47" s="394" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G47" s="394"/>
-      <c r="H47" s="394"/>
-      <c r="I47" s="394"/>
-      <c r="J47" s="423"/>
+      <c r="A47" s="396"/>
+      <c r="B47" s="396"/>
+      <c r="C47" s="425"/>
+      <c r="E47" s="393" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F47" s="393" t="s">
+        <v>997</v>
+      </c>
+      <c r="G47" s="393"/>
+      <c r="H47" s="393"/>
+      <c r="I47" s="393"/>
+      <c r="J47" s="421"/>
       <c r="K47" s="305"/>
       <c r="L47" s="305"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A48" s="398"/>
-      <c r="B48" s="398"/>
-      <c r="C48" s="427"/>
-      <c r="E48" s="394" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F48" s="394" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G48" s="394"/>
-      <c r="H48" s="394"/>
-      <c r="I48" s="394"/>
-      <c r="J48" s="423"/>
+      <c r="A48" s="396"/>
+      <c r="B48" s="396"/>
+      <c r="C48" s="425"/>
+      <c r="E48" s="393" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F48" s="393" t="s">
+        <v>997</v>
+      </c>
+      <c r="G48" s="393"/>
+      <c r="H48" s="393"/>
+      <c r="I48" s="393"/>
+      <c r="J48" s="421"/>
       <c r="K48" s="305"/>
       <c r="L48" s="305"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A49" s="398"/>
-      <c r="B49" s="398"/>
-      <c r="C49" s="427"/>
-      <c r="E49" s="394" t="s">
+      <c r="A49" s="396"/>
+      <c r="B49" s="396"/>
+      <c r="C49" s="425"/>
+      <c r="E49" s="393" t="s">
         <v>730</v>
       </c>
-      <c r="F49" s="394" t="s">
+      <c r="F49" s="393" t="s">
         <v>731</v>
       </c>
-      <c r="G49" s="394"/>
-      <c r="H49" s="394"/>
-      <c r="I49" s="394"/>
-      <c r="J49" s="423"/>
+      <c r="G49" s="393"/>
+      <c r="H49" s="393"/>
+      <c r="I49" s="393"/>
+      <c r="J49" s="421"/>
       <c r="K49" s="305"/>
       <c r="L49" s="305"/>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A50" s="398"/>
-      <c r="B50" s="398"/>
-      <c r="C50" s="427"/>
-      <c r="E50" s="394" t="s">
+      <c r="A50" s="396"/>
+      <c r="B50" s="396"/>
+      <c r="C50" s="425"/>
+      <c r="E50" s="393" t="s">
         <v>739</v>
       </c>
-      <c r="F50" s="394" t="s">
+      <c r="F50" s="393" t="s">
         <v>731</v>
       </c>
-      <c r="G50" s="394"/>
-      <c r="H50" s="394"/>
-      <c r="I50" s="394"/>
-      <c r="J50" s="423"/>
+      <c r="G50" s="393"/>
+      <c r="H50" s="393"/>
+      <c r="I50" s="393"/>
+      <c r="J50" s="421"/>
       <c r="K50" s="305"/>
       <c r="L50" s="305"/>
     </row>
     <row r="51" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A51" s="398"/>
-      <c r="B51" s="398"/>
-      <c r="C51" s="428">
+      <c r="A51" s="396"/>
+      <c r="B51" s="396"/>
+      <c r="C51" s="426">
         <v>6</v>
       </c>
-      <c r="D51" s="417" t="s">
+      <c r="D51" s="415" t="s">
         <v>748</v>
       </c>
-      <c r="E51" s="418"/>
-      <c r="F51" s="418"/>
-      <c r="G51" s="418"/>
-      <c r="H51" s="418"/>
-      <c r="I51" s="418"/>
-      <c r="J51" s="419"/>
+      <c r="E51" s="416"/>
+      <c r="F51" s="416"/>
+      <c r="G51" s="416"/>
+      <c r="H51" s="416"/>
+      <c r="I51" s="416"/>
+      <c r="J51" s="417"/>
       <c r="K51" s="305"/>
       <c r="L51" s="305"/>
     </row>
     <row r="52" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A52" s="398"/>
-      <c r="B52" s="398"/>
-      <c r="C52" s="427"/>
-      <c r="E52" s="394"/>
+      <c r="A52" s="396"/>
+      <c r="B52" s="396"/>
+      <c r="C52" s="425"/>
+      <c r="E52" s="393"/>
       <c r="F52" s="363"/>
-      <c r="G52" s="422"/>
-      <c r="H52" s="394"/>
-      <c r="I52" s="422"/>
-      <c r="J52" s="423"/>
+      <c r="G52" s="420"/>
+      <c r="H52" s="393"/>
+      <c r="I52" s="420"/>
+      <c r="J52" s="421"/>
       <c r="K52" s="305"/>
       <c r="L52" s="305"/>
     </row>
     <row r="53" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A53" s="398"/>
-      <c r="B53" s="398"/>
-      <c r="C53" s="427"/>
-      <c r="E53" s="394"/>
+      <c r="A53" s="396"/>
+      <c r="B53" s="396"/>
+      <c r="C53" s="425"/>
+      <c r="E53" s="393"/>
       <c r="F53" s="363"/>
-      <c r="G53" s="394"/>
-      <c r="H53" s="394"/>
-      <c r="I53" s="422"/>
-      <c r="J53" s="423"/>
+      <c r="G53" s="393"/>
+      <c r="H53" s="393"/>
+      <c r="I53" s="420"/>
+      <c r="J53" s="421"/>
       <c r="K53" s="305"/>
       <c r="L53" s="305"/>
     </row>
     <row r="54" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A54" s="398"/>
-      <c r="B54" s="398"/>
-      <c r="C54" s="427"/>
+      <c r="A54" s="396"/>
+      <c r="B54" s="396"/>
+      <c r="C54" s="425"/>
       <c r="D54" s="312"/>
-      <c r="E54" s="394"/>
+      <c r="E54" s="393"/>
       <c r="F54" s="363"/>
-      <c r="G54" s="394"/>
-      <c r="H54" s="422"/>
-      <c r="I54" s="422"/>
-      <c r="J54" s="423"/>
+      <c r="G54" s="393"/>
+      <c r="H54" s="420"/>
+      <c r="I54" s="420"/>
+      <c r="J54" s="421"/>
       <c r="K54" s="305"/>
       <c r="L54" s="305"/>
     </row>
     <row r="55" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A55" s="398"/>
-      <c r="B55" s="398"/>
-      <c r="C55" s="427"/>
-      <c r="E55" s="394"/>
-      <c r="F55" s="394"/>
-      <c r="G55" s="394"/>
-      <c r="H55" s="394"/>
-      <c r="I55" s="394"/>
-      <c r="J55" s="423"/>
+      <c r="A55" s="396"/>
+      <c r="B55" s="396"/>
+      <c r="C55" s="425"/>
+      <c r="E55" s="393"/>
+      <c r="F55" s="393"/>
+      <c r="G55" s="393"/>
+      <c r="H55" s="393"/>
+      <c r="I55" s="393"/>
+      <c r="J55" s="421"/>
       <c r="K55" s="305"/>
       <c r="L55" s="305"/>
     </row>
     <row r="56" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A56" s="398"/>
-      <c r="B56" s="398"/>
-      <c r="C56" s="427"/>
-      <c r="E56" s="394"/>
-      <c r="F56" s="394"/>
-      <c r="G56" s="394"/>
-      <c r="H56" s="394"/>
-      <c r="I56" s="394"/>
-      <c r="J56" s="423"/>
+      <c r="A56" s="396"/>
+      <c r="B56" s="396"/>
+      <c r="C56" s="425"/>
+      <c r="E56" s="393"/>
+      <c r="F56" s="393"/>
+      <c r="G56" s="393"/>
+      <c r="H56" s="393"/>
+      <c r="I56" s="393"/>
+      <c r="J56" s="421"/>
       <c r="K56" s="305"/>
       <c r="L56" s="305"/>
     </row>
     <row r="57" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A57" s="398"/>
-      <c r="B57" s="398"/>
-      <c r="C57" s="427"/>
+      <c r="A57" s="396"/>
+      <c r="B57" s="396"/>
+      <c r="C57" s="425"/>
       <c r="E57" s="364"/>
-      <c r="F57" s="394"/>
-      <c r="G57" s="394"/>
-      <c r="H57" s="394"/>
-      <c r="I57" s="394"/>
-      <c r="J57" s="423"/>
+      <c r="F57" s="393"/>
+      <c r="G57" s="393"/>
+      <c r="H57" s="393"/>
+      <c r="I57" s="393"/>
+      <c r="J57" s="421"/>
       <c r="K57" s="305"/>
       <c r="L57" s="305"/>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A58" s="398"/>
-      <c r="B58" s="398"/>
-      <c r="C58" s="428">
+      <c r="A58" s="396"/>
+      <c r="B58" s="396"/>
+      <c r="C58" s="426">
         <v>7</v>
       </c>
-      <c r="D58" s="417" t="s">
+      <c r="D58" s="415" t="s">
         <v>748</v>
       </c>
-      <c r="E58" s="418"/>
-      <c r="F58" s="418"/>
-      <c r="G58" s="418"/>
-      <c r="H58" s="418"/>
-      <c r="I58" s="418"/>
-      <c r="J58" s="419"/>
+      <c r="E58" s="416"/>
+      <c r="F58" s="416"/>
+      <c r="G58" s="416"/>
+      <c r="H58" s="416"/>
+      <c r="I58" s="416"/>
+      <c r="J58" s="417"/>
       <c r="K58" s="305"/>
       <c r="L58" s="305"/>
     </row>
     <row r="59" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A59" s="398"/>
-      <c r="B59" s="398"/>
-      <c r="C59" s="427"/>
-      <c r="E59" s="394"/>
-      <c r="F59" s="394"/>
-      <c r="G59" s="394"/>
-      <c r="H59" s="394"/>
-      <c r="I59" s="394"/>
-      <c r="J59" s="423"/>
+      <c r="A59" s="396"/>
+      <c r="B59" s="396"/>
+      <c r="C59" s="425"/>
+      <c r="E59" s="393"/>
+      <c r="F59" s="393"/>
+      <c r="G59" s="393"/>
+      <c r="H59" s="393"/>
+      <c r="I59" s="393"/>
+      <c r="J59" s="421"/>
       <c r="K59" s="305"/>
       <c r="L59" s="305"/>
     </row>
     <row r="60" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A60" s="398"/>
-      <c r="B60" s="398"/>
-      <c r="C60" s="427"/>
+      <c r="A60" s="396"/>
+      <c r="B60" s="396"/>
+      <c r="C60" s="425"/>
       <c r="D60" s="304"/>
-      <c r="E60" s="394"/>
-      <c r="F60" s="394"/>
-      <c r="G60" s="394"/>
-      <c r="H60" s="394"/>
-      <c r="I60" s="394"/>
-      <c r="J60" s="423"/>
+      <c r="E60" s="393"/>
+      <c r="F60" s="393"/>
+      <c r="G60" s="393"/>
+      <c r="H60" s="393"/>
+      <c r="I60" s="393"/>
+      <c r="J60" s="421"/>
       <c r="K60" s="305"/>
       <c r="L60" s="305"/>
     </row>
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A61" s="398"/>
-      <c r="B61" s="398"/>
-      <c r="C61" s="427"/>
-      <c r="E61" s="394"/>
-      <c r="F61" s="394"/>
-      <c r="G61" s="394"/>
-      <c r="H61" s="394"/>
-      <c r="I61" s="394"/>
-      <c r="J61" s="423"/>
+      <c r="A61" s="396"/>
+      <c r="B61" s="396"/>
+      <c r="C61" s="425"/>
+      <c r="E61" s="393"/>
+      <c r="F61" s="393"/>
+      <c r="G61" s="393"/>
+      <c r="H61" s="393"/>
+      <c r="I61" s="393"/>
+      <c r="J61" s="421"/>
       <c r="K61" s="305"/>
       <c r="L61" s="305"/>
     </row>
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A62" s="398"/>
-      <c r="B62" s="398"/>
-      <c r="C62" s="427"/>
-      <c r="E62" s="394"/>
-      <c r="F62" s="394"/>
-      <c r="G62" s="394"/>
-      <c r="H62" s="394"/>
-      <c r="I62" s="394"/>
-      <c r="J62" s="423"/>
+      <c r="A62" s="396"/>
+      <c r="B62" s="396"/>
+      <c r="C62" s="425"/>
+      <c r="E62" s="393"/>
+      <c r="F62" s="393"/>
+      <c r="G62" s="393"/>
+      <c r="H62" s="393"/>
+      <c r="I62" s="393"/>
+      <c r="J62" s="421"/>
       <c r="K62" s="305"/>
       <c r="L62" s="305"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A63" s="398"/>
-      <c r="B63" s="398"/>
-      <c r="C63" s="427"/>
-      <c r="E63" s="394"/>
-      <c r="F63" s="394"/>
-      <c r="G63" s="394"/>
-      <c r="H63" s="394"/>
-      <c r="I63" s="394"/>
-      <c r="J63" s="423"/>
+      <c r="A63" s="396"/>
+      <c r="B63" s="396"/>
+      <c r="C63" s="425"/>
+      <c r="E63" s="393"/>
+      <c r="F63" s="393"/>
+      <c r="G63" s="393"/>
+      <c r="H63" s="393"/>
+      <c r="I63" s="393"/>
+      <c r="J63" s="421"/>
       <c r="K63" s="305"/>
       <c r="L63" s="305"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A64" s="398"/>
-      <c r="B64" s="398"/>
-      <c r="C64" s="427"/>
-      <c r="E64" s="394"/>
-      <c r="F64" s="394"/>
-      <c r="G64" s="394"/>
-      <c r="H64" s="394"/>
-      <c r="I64" s="394"/>
-      <c r="J64" s="423"/>
+      <c r="A64" s="396"/>
+      <c r="B64" s="396"/>
+      <c r="C64" s="425"/>
+      <c r="E64" s="393"/>
+      <c r="F64" s="393"/>
+      <c r="G64" s="393"/>
+      <c r="H64" s="393"/>
+      <c r="I64" s="393"/>
+      <c r="J64" s="421"/>
       <c r="K64" s="305"/>
       <c r="L64" s="305"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A65" s="398"/>
-      <c r="B65" s="398"/>
-      <c r="C65" s="427"/>
-      <c r="E65" s="394"/>
-      <c r="F65" s="394"/>
-      <c r="G65" s="394"/>
-      <c r="H65" s="394"/>
-      <c r="I65" s="394"/>
-      <c r="J65" s="423"/>
+      <c r="A65" s="396"/>
+      <c r="B65" s="396"/>
+      <c r="C65" s="425"/>
+      <c r="E65" s="393"/>
+      <c r="F65" s="393"/>
+      <c r="G65" s="393"/>
+      <c r="H65" s="393"/>
+      <c r="I65" s="393"/>
+      <c r="J65" s="421"/>
       <c r="K65" s="305"/>
       <c r="L65" s="305"/>
     </row>
     <row r="66" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A66" s="398"/>
-      <c r="B66" s="398"/>
-      <c r="C66" s="427"/>
-      <c r="E66" s="394"/>
-      <c r="F66" s="394"/>
-      <c r="G66" s="394"/>
-      <c r="H66" s="394"/>
-      <c r="I66" s="394"/>
-      <c r="J66" s="423"/>
+      <c r="A66" s="396"/>
+      <c r="B66" s="396"/>
+      <c r="C66" s="425"/>
+      <c r="E66" s="393"/>
+      <c r="F66" s="393"/>
+      <c r="G66" s="393"/>
+      <c r="H66" s="393"/>
+      <c r="I66" s="393"/>
+      <c r="J66" s="421"/>
       <c r="K66" s="305"/>
       <c r="L66" s="305"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A67" s="398"/>
-      <c r="B67" s="398"/>
-      <c r="C67" s="427"/>
-      <c r="E67" s="394"/>
-      <c r="F67" s="394"/>
-      <c r="G67" s="394"/>
-      <c r="H67" s="394"/>
-      <c r="I67" s="394"/>
-      <c r="J67" s="423"/>
+      <c r="A67" s="396"/>
+      <c r="B67" s="396"/>
+      <c r="C67" s="425"/>
+      <c r="E67" s="393"/>
+      <c r="F67" s="393"/>
+      <c r="G67" s="393"/>
+      <c r="H67" s="393"/>
+      <c r="I67" s="393"/>
+      <c r="J67" s="421"/>
       <c r="K67" s="305"/>
       <c r="L67" s="305"/>
     </row>
     <row r="68" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A68" s="398"/>
-      <c r="B68" s="398"/>
-      <c r="C68" s="427"/>
+      <c r="A68" s="396"/>
+      <c r="B68" s="396"/>
+      <c r="C68" s="425"/>
       <c r="D68" s="303"/>
-      <c r="E68" s="394"/>
-      <c r="F68" s="394"/>
-      <c r="G68" s="394"/>
-      <c r="H68" s="394"/>
-      <c r="I68" s="394"/>
-      <c r="J68" s="423"/>
+      <c r="E68" s="393"/>
+      <c r="F68" s="393"/>
+      <c r="G68" s="393"/>
+      <c r="H68" s="393"/>
+      <c r="I68" s="393"/>
+      <c r="J68" s="421"/>
       <c r="K68" s="305"/>
       <c r="L68" s="305"/>
     </row>
     <row r="69" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A69" s="398"/>
-      <c r="B69" s="398"/>
-      <c r="C69" s="427"/>
-      <c r="D69" s="429"/>
-      <c r="E69" s="442"/>
-      <c r="F69" s="442"/>
-      <c r="G69" s="442"/>
-      <c r="H69" s="442"/>
-      <c r="I69" s="442"/>
-      <c r="J69" s="443"/>
+      <c r="A69" s="396"/>
+      <c r="B69" s="396"/>
+      <c r="C69" s="425"/>
+      <c r="D69" s="427"/>
+      <c r="E69" s="440"/>
+      <c r="F69" s="440"/>
+      <c r="G69" s="440"/>
+      <c r="H69" s="440"/>
+      <c r="I69" s="440"/>
+      <c r="J69" s="441"/>
       <c r="K69" s="305"/>
       <c r="L69" s="305"/>
     </row>
     <row r="70" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A70" s="398"/>
-      <c r="B70" s="398"/>
-      <c r="C70" s="427"/>
-      <c r="D70" s="429"/>
-      <c r="E70" s="430"/>
-      <c r="F70" s="430"/>
-      <c r="G70" s="430"/>
-      <c r="H70" s="430"/>
-      <c r="I70" s="430"/>
-      <c r="J70" s="431"/>
+      <c r="A70" s="396"/>
+      <c r="B70" s="396"/>
+      <c r="C70" s="425"/>
+      <c r="D70" s="427"/>
+      <c r="E70" s="428"/>
+      <c r="F70" s="428"/>
+      <c r="G70" s="428"/>
+      <c r="H70" s="428"/>
+      <c r="I70" s="428"/>
+      <c r="J70" s="429"/>
       <c r="K70" s="305"/>
       <c r="L70" s="305"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A71" s="398"/>
-      <c r="B71" s="398"/>
-      <c r="C71" s="441"/>
-      <c r="D71" s="433"/>
-      <c r="E71" s="430"/>
-      <c r="F71" s="430"/>
-      <c r="G71" s="430"/>
-      <c r="H71" s="430"/>
-      <c r="I71" s="430"/>
-      <c r="J71" s="431"/>
+      <c r="A71" s="396"/>
+      <c r="B71" s="396"/>
+      <c r="C71" s="439"/>
+      <c r="D71" s="431"/>
+      <c r="E71" s="428"/>
+      <c r="F71" s="428"/>
+      <c r="G71" s="428"/>
+      <c r="H71" s="428"/>
+      <c r="I71" s="428"/>
+      <c r="J71" s="429"/>
       <c r="K71" s="305"/>
       <c r="L71" s="305"/>
     </row>
     <row r="72" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A72" s="398"/>
-      <c r="B72" s="398"/>
-      <c r="C72" s="428">
+      <c r="A72" s="396"/>
+      <c r="B72" s="396"/>
+      <c r="C72" s="426">
         <v>8</v>
       </c>
-      <c r="D72" s="417" t="s">
+      <c r="D72" s="415" t="s">
         <v>748</v>
       </c>
-      <c r="E72" s="418"/>
-      <c r="F72" s="418"/>
-      <c r="G72" s="418"/>
-      <c r="H72" s="418"/>
-      <c r="I72" s="418"/>
-      <c r="J72" s="419"/>
+      <c r="E72" s="416"/>
+      <c r="F72" s="416"/>
+      <c r="G72" s="416"/>
+      <c r="H72" s="416"/>
+      <c r="I72" s="416"/>
+      <c r="J72" s="417"/>
       <c r="K72" s="305"/>
       <c r="L72" s="305"/>
     </row>
     <row r="73" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A73" s="398"/>
-      <c r="B73" s="398"/>
-      <c r="C73" s="427"/>
-      <c r="E73" s="394"/>
-      <c r="F73" s="394"/>
-      <c r="G73" s="394"/>
-      <c r="H73" s="394"/>
-      <c r="I73" s="394"/>
-      <c r="J73" s="423"/>
+      <c r="A73" s="396"/>
+      <c r="B73" s="396"/>
+      <c r="C73" s="425"/>
+      <c r="E73" s="393"/>
+      <c r="F73" s="393"/>
+      <c r="G73" s="393"/>
+      <c r="H73" s="393"/>
+      <c r="I73" s="393"/>
+      <c r="J73" s="421"/>
       <c r="K73" s="305"/>
       <c r="L73" s="305"/>
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A74" s="398"/>
-      <c r="B74" s="398"/>
-      <c r="C74" s="427"/>
+      <c r="A74" s="396"/>
+      <c r="B74" s="396"/>
+      <c r="C74" s="425"/>
       <c r="D74" s="304"/>
-      <c r="E74" s="394"/>
-      <c r="F74" s="394"/>
-      <c r="G74" s="394"/>
-      <c r="H74" s="394"/>
-      <c r="I74" s="394"/>
-      <c r="J74" s="423"/>
+      <c r="E74" s="393"/>
+      <c r="F74" s="393"/>
+      <c r="G74" s="393"/>
+      <c r="H74" s="393"/>
+      <c r="I74" s="393"/>
+      <c r="J74" s="421"/>
       <c r="K74" s="305"/>
       <c r="L74" s="305"/>
     </row>
     <row r="75" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A75" s="398"/>
-      <c r="B75" s="398"/>
-      <c r="C75" s="427"/>
-      <c r="E75" s="394"/>
-      <c r="F75" s="394"/>
-      <c r="G75" s="394"/>
-      <c r="H75" s="394"/>
-      <c r="I75" s="394"/>
-      <c r="J75" s="423"/>
+      <c r="A75" s="396"/>
+      <c r="B75" s="396"/>
+      <c r="C75" s="425"/>
+      <c r="E75" s="393"/>
+      <c r="F75" s="393"/>
+      <c r="G75" s="393"/>
+      <c r="H75" s="393"/>
+      <c r="I75" s="393"/>
+      <c r="J75" s="421"/>
       <c r="K75" s="305"/>
       <c r="L75" s="305"/>
     </row>
     <row r="76" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A76" s="398"/>
-      <c r="B76" s="398"/>
-      <c r="C76" s="427"/>
-      <c r="E76" s="394"/>
-      <c r="F76" s="394"/>
-      <c r="G76" s="394"/>
-      <c r="H76" s="394"/>
-      <c r="I76" s="394"/>
-      <c r="J76" s="423"/>
+      <c r="A76" s="396"/>
+      <c r="B76" s="396"/>
+      <c r="C76" s="425"/>
+      <c r="E76" s="393"/>
+      <c r="F76" s="393"/>
+      <c r="G76" s="393"/>
+      <c r="H76" s="393"/>
+      <c r="I76" s="393"/>
+      <c r="J76" s="421"/>
       <c r="K76" s="305"/>
       <c r="L76" s="305"/>
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A77" s="398"/>
-      <c r="B77" s="398"/>
-      <c r="C77" s="427"/>
-      <c r="E77" s="394"/>
-      <c r="F77" s="394"/>
-      <c r="G77" s="394"/>
-      <c r="H77" s="394"/>
-      <c r="I77" s="394"/>
-      <c r="J77" s="423"/>
+      <c r="A77" s="396"/>
+      <c r="B77" s="396"/>
+      <c r="C77" s="425"/>
+      <c r="E77" s="393"/>
+      <c r="F77" s="393"/>
+      <c r="G77" s="393"/>
+      <c r="H77" s="393"/>
+      <c r="I77" s="393"/>
+      <c r="J77" s="421"/>
       <c r="K77" s="305"/>
       <c r="L77" s="305"/>
     </row>
     <row r="78" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A78" s="398"/>
-      <c r="B78" s="398"/>
-      <c r="C78" s="427"/>
-      <c r="E78" s="394"/>
-      <c r="F78" s="394"/>
-      <c r="G78" s="394"/>
-      <c r="H78" s="394"/>
-      <c r="I78" s="394"/>
-      <c r="J78" s="423"/>
+      <c r="A78" s="396"/>
+      <c r="B78" s="396"/>
+      <c r="C78" s="425"/>
+      <c r="E78" s="393"/>
+      <c r="F78" s="393"/>
+      <c r="G78" s="393"/>
+      <c r="H78" s="393"/>
+      <c r="I78" s="393"/>
+      <c r="J78" s="421"/>
       <c r="K78" s="305"/>
       <c r="L78" s="305"/>
     </row>
     <row r="79" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A79" s="398"/>
-      <c r="B79" s="398"/>
-      <c r="C79" s="427"/>
-      <c r="E79" s="394"/>
-      <c r="F79" s="394"/>
-      <c r="G79" s="394"/>
-      <c r="H79" s="394"/>
-      <c r="I79" s="394"/>
-      <c r="J79" s="423"/>
+      <c r="A79" s="396"/>
+      <c r="B79" s="396"/>
+      <c r="C79" s="425"/>
+      <c r="E79" s="393"/>
+      <c r="F79" s="393"/>
+      <c r="G79" s="393"/>
+      <c r="H79" s="393"/>
+      <c r="I79" s="393"/>
+      <c r="J79" s="421"/>
       <c r="K79" s="305"/>
       <c r="L79" s="305"/>
     </row>
     <row r="80" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A80" s="398"/>
-      <c r="B80" s="398"/>
-      <c r="C80" s="427"/>
-      <c r="E80" s="394"/>
-      <c r="F80" s="394"/>
-      <c r="G80" s="394"/>
-      <c r="H80" s="394"/>
-      <c r="I80" s="394"/>
-      <c r="J80" s="423"/>
+      <c r="A80" s="396"/>
+      <c r="B80" s="396"/>
+      <c r="C80" s="425"/>
+      <c r="E80" s="393"/>
+      <c r="F80" s="393"/>
+      <c r="G80" s="393"/>
+      <c r="H80" s="393"/>
+      <c r="I80" s="393"/>
+      <c r="J80" s="421"/>
       <c r="K80" s="305"/>
       <c r="L80" s="305"/>
     </row>
     <row r="81" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A81" s="398"/>
-      <c r="B81" s="398"/>
-      <c r="C81" s="427"/>
-      <c r="E81" s="394"/>
-      <c r="F81" s="394"/>
-      <c r="G81" s="394"/>
-      <c r="H81" s="394"/>
-      <c r="I81" s="394"/>
-      <c r="J81" s="423"/>
+      <c r="A81" s="396"/>
+      <c r="B81" s="396"/>
+      <c r="C81" s="425"/>
+      <c r="E81" s="393"/>
+      <c r="F81" s="393"/>
+      <c r="G81" s="393"/>
+      <c r="H81" s="393"/>
+      <c r="I81" s="393"/>
+      <c r="J81" s="421"/>
       <c r="K81" s="305"/>
       <c r="L81" s="305"/>
     </row>
     <row r="82" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A82" s="398"/>
-      <c r="B82" s="398"/>
-      <c r="C82" s="427"/>
+      <c r="A82" s="396"/>
+      <c r="B82" s="396"/>
+      <c r="C82" s="425"/>
       <c r="D82" s="303"/>
-      <c r="E82" s="394"/>
-      <c r="F82" s="394"/>
-      <c r="G82" s="394"/>
-      <c r="H82" s="394"/>
-      <c r="I82" s="394"/>
-      <c r="J82" s="423"/>
+      <c r="E82" s="393"/>
+      <c r="F82" s="393"/>
+      <c r="G82" s="393"/>
+      <c r="H82" s="393"/>
+      <c r="I82" s="393"/>
+      <c r="J82" s="421"/>
       <c r="K82" s="305"/>
       <c r="L82" s="305"/>
     </row>
     <row r="83" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A83" s="398"/>
-      <c r="B83" s="398"/>
-      <c r="C83" s="427"/>
-      <c r="D83" s="429"/>
-      <c r="E83" s="442"/>
-      <c r="F83" s="442"/>
-      <c r="G83" s="442"/>
-      <c r="H83" s="442"/>
-      <c r="I83" s="442"/>
-      <c r="J83" s="443"/>
+      <c r="A83" s="396"/>
+      <c r="B83" s="396"/>
+      <c r="C83" s="425"/>
+      <c r="D83" s="427"/>
+      <c r="E83" s="440"/>
+      <c r="F83" s="440"/>
+      <c r="G83" s="440"/>
+      <c r="H83" s="440"/>
+      <c r="I83" s="440"/>
+      <c r="J83" s="441"/>
       <c r="K83" s="305"/>
       <c r="L83" s="305"/>
     </row>
     <row r="84" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A84" s="398"/>
-      <c r="B84" s="398"/>
-      <c r="C84" s="427"/>
-      <c r="D84" s="429"/>
-      <c r="E84" s="430"/>
-      <c r="F84" s="430"/>
-      <c r="G84" s="430"/>
-      <c r="H84" s="430"/>
-      <c r="I84" s="430"/>
-      <c r="J84" s="431"/>
+      <c r="A84" s="396"/>
+      <c r="B84" s="396"/>
+      <c r="C84" s="425"/>
+      <c r="D84" s="427"/>
+      <c r="E84" s="428"/>
+      <c r="F84" s="428"/>
+      <c r="G84" s="428"/>
+      <c r="H84" s="428"/>
+      <c r="I84" s="428"/>
+      <c r="J84" s="429"/>
       <c r="K84" s="305"/>
       <c r="L84" s="305"/>
     </row>
     <row r="85" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A85" s="398"/>
-      <c r="B85" s="398"/>
-      <c r="C85" s="441"/>
-      <c r="D85" s="433"/>
-      <c r="E85" s="430"/>
-      <c r="F85" s="430"/>
-      <c r="G85" s="430"/>
-      <c r="H85" s="430"/>
-      <c r="I85" s="430"/>
-      <c r="J85" s="431"/>
+      <c r="A85" s="396"/>
+      <c r="B85" s="396"/>
+      <c r="C85" s="439"/>
+      <c r="D85" s="431"/>
+      <c r="E85" s="428"/>
+      <c r="F85" s="428"/>
+      <c r="G85" s="428"/>
+      <c r="H85" s="428"/>
+      <c r="I85" s="428"/>
+      <c r="J85" s="429"/>
       <c r="K85" s="305"/>
       <c r="L85" s="305"/>
     </row>
     <row r="86" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A86" s="398"/>
-      <c r="B86" s="398"/>
-      <c r="C86" s="444"/>
+      <c r="A86" s="396"/>
+      <c r="B86" s="396"/>
+      <c r="C86" s="442"/>
       <c r="D86" s="305"/>
       <c r="E86" s="305"/>
       <c r="F86" s="305"/>
@@ -10356,11 +10576,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="460" t="s">
+      <c r="C4" s="473" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="461"/>
-      <c r="E4" s="461"/>
+      <c r="D4" s="474"/>
+      <c r="E4" s="474"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10369,13 +10589,13 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
-      <c r="C5" s="466" t="s">
+      <c r="C5" s="479" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="462" t="s">
+      <c r="D5" s="475" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="463"/>
+      <c r="E5" s="476"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10384,11 +10604,11 @@
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="459"/>
-      <c r="D6" s="464" t="s">
+      <c r="C6" s="472"/>
+      <c r="D6" s="477" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="465"/>
+      <c r="E6" s="478"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10397,11 +10617,11 @@
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="459"/>
-      <c r="D7" s="464" t="s">
+      <c r="C7" s="472"/>
+      <c r="D7" s="477" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="465"/>
+      <c r="E7" s="478"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10410,11 +10630,11 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="459"/>
-      <c r="D8" s="464" t="s">
+      <c r="C8" s="472"/>
+      <c r="D8" s="477" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="465"/>
+      <c r="E8" s="478"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10423,11 +10643,11 @@
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="459"/>
-      <c r="D9" s="464" t="s">
+      <c r="C9" s="472"/>
+      <c r="D9" s="477" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="465"/>
+      <c r="E9" s="478"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10436,11 +10656,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="458"/>
-      <c r="D10" s="464" t="s">
+      <c r="C10" s="471"/>
+      <c r="D10" s="477" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="465"/>
+      <c r="E10" s="478"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10449,13 +10669,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="457" t="s">
+      <c r="C11" s="470" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="464" t="s">
+      <c r="D11" s="477" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="465"/>
+      <c r="E11" s="478"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10464,11 +10684,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="458"/>
-      <c r="D12" s="464" t="s">
+      <c r="C12" s="471"/>
+      <c r="D12" s="477" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="465"/>
+      <c r="E12" s="478"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10477,13 +10697,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="457" t="s">
+      <c r="C13" s="470" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="464" t="s">
+      <c r="D13" s="477" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="465"/>
+      <c r="E13" s="478"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10492,11 +10712,11 @@
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="459"/>
-      <c r="D14" s="464" t="s">
+      <c r="C14" s="472"/>
+      <c r="D14" s="477" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="465"/>
+      <c r="E14" s="478"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10505,11 +10725,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="458"/>
-      <c r="D15" s="464" t="s">
+      <c r="C15" s="471"/>
+      <c r="D15" s="477" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="465"/>
+      <c r="E15" s="478"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -10518,13 +10738,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="457" t="s">
+      <c r="C16" s="470" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="469" t="s">
+      <c r="D16" s="482" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="470"/>
+      <c r="E16" s="483"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -10533,8 +10753,8 @@
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="459"/>
-      <c r="D17" s="468" t="s">
+      <c r="C17" s="472"/>
+      <c r="D17" s="481" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="107" t="s">
@@ -10548,8 +10768,8 @@
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="459"/>
-      <c r="D18" s="459"/>
+      <c r="C18" s="472"/>
+      <c r="D18" s="472"/>
       <c r="E18" s="107" t="s">
         <v>134</v>
       </c>
@@ -10561,8 +10781,8 @@
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="459"/>
-      <c r="D19" s="459"/>
+      <c r="C19" s="472"/>
+      <c r="D19" s="472"/>
       <c r="E19" s="107" t="s">
         <v>137</v>
       </c>
@@ -10574,8 +10794,8 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="459"/>
-      <c r="D20" s="459"/>
+      <c r="C20" s="472"/>
+      <c r="D20" s="472"/>
       <c r="E20" s="107" t="s">
         <v>140</v>
       </c>
@@ -10587,8 +10807,8 @@
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="459"/>
-      <c r="D21" s="458"/>
+      <c r="C21" s="472"/>
+      <c r="D21" s="471"/>
       <c r="E21" s="107" t="s">
         <v>145</v>
       </c>
@@ -10600,8 +10820,8 @@
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="459"/>
-      <c r="D22" s="467" t="s">
+      <c r="C22" s="472"/>
+      <c r="D22" s="480" t="s">
         <v>165</v>
       </c>
       <c r="E22" s="127" t="s">
@@ -10615,8 +10835,8 @@
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="459"/>
-      <c r="D23" s="459"/>
+      <c r="C23" s="472"/>
+      <c r="D23" s="472"/>
       <c r="E23" s="127" t="s">
         <v>177</v>
       </c>
@@ -10628,8 +10848,8 @@
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="459"/>
-      <c r="D24" s="459"/>
+      <c r="C24" s="472"/>
+      <c r="D24" s="472"/>
       <c r="E24" s="127" t="s">
         <v>179</v>
       </c>
@@ -10641,8 +10861,8 @@
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="459"/>
-      <c r="D25" s="459"/>
+      <c r="C25" s="472"/>
+      <c r="D25" s="472"/>
       <c r="E25" s="127" t="s">
         <v>185</v>
       </c>
@@ -10654,8 +10874,8 @@
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="459"/>
-      <c r="D26" s="458"/>
+      <c r="C26" s="472"/>
+      <c r="D26" s="471"/>
       <c r="E26" s="127" t="s">
         <v>190</v>
       </c>
@@ -10667,7 +10887,7 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="459"/>
+      <c r="C27" s="472"/>
       <c r="D27" s="127" t="s">
         <v>193</v>
       </c>
@@ -10682,7 +10902,7 @@
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="459"/>
+      <c r="C28" s="472"/>
       <c r="D28" s="105" t="s">
         <v>221</v>
       </c>
@@ -10697,8 +10917,8 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="459"/>
-      <c r="D29" s="468" t="s">
+      <c r="C29" s="472"/>
+      <c r="D29" s="481" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="127" t="s">
@@ -10712,8 +10932,8 @@
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="459"/>
-      <c r="D30" s="459"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
       <c r="E30" s="127" t="s">
         <v>244</v>
       </c>
@@ -10725,8 +10945,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="458"/>
-      <c r="D31" s="458"/>
+      <c r="C31" s="471"/>
+      <c r="D31" s="471"/>
       <c r="E31" s="127" t="s">
         <v>249</v>
       </c>
@@ -10738,13 +10958,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="457" t="s">
+      <c r="C32" s="470" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="464" t="s">
+      <c r="D32" s="477" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="465"/>
+      <c r="E32" s="478"/>
       <c r="F32" s="159" t="s">
         <v>259</v>
       </c>
@@ -10752,11 +10972,11 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="459"/>
-      <c r="D33" s="464" t="s">
+      <c r="C33" s="472"/>
+      <c r="D33" s="477" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="465"/>
+      <c r="E33" s="478"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -10765,11 +10985,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="458"/>
-      <c r="D34" s="464" t="s">
+      <c r="C34" s="471"/>
+      <c r="D34" s="477" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="465"/>
+      <c r="E34" s="478"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -12081,6 +12301,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FFC0504D"/>
+  </sheetPr>
   <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -12220,7 +12443,7 @@
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
     </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1">
+    <row r="10" spans="1:9" ht="28">
       <c r="A10" s="52"/>
       <c r="D10" s="57" t="s">
         <v>57</v>
@@ -12228,13 +12451,15 @@
       <c r="E10" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="72" t="s">
-        <v>60</v>
+      <c r="F10" s="460" t="s">
+        <v>1063</v>
       </c>
       <c r="G10" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="H10" s="10"/>
+      <c r="H10" s="461" t="s">
+        <v>1064</v>
+      </c>
       <c r="I10" s="10"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1">
@@ -12267,7 +12492,7 @@
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
     </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1">
+    <row r="13" spans="1:9">
       <c r="A13" s="52"/>
       <c r="D13" s="57" t="s">
         <v>71</v>
@@ -12282,7 +12507,7 @@
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
     </row>
-    <row r="14" spans="1:9" ht="15.75" customHeight="1">
+    <row r="14" spans="1:9">
       <c r="A14" s="52"/>
       <c r="D14" s="57" t="s">
         <v>79</v>
@@ -12364,7 +12589,7 @@
       <c r="H18" s="68"/>
       <c r="I18" s="10"/>
     </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1">
+    <row r="19" spans="1:9" ht="42">
       <c r="A19" s="52"/>
       <c r="D19" s="89" t="s">
         <v>109</v>
@@ -14122,7 +14347,7 @@
     <row r="71" spans="1:8" ht="26">
       <c r="A71" s="279"/>
       <c r="B71" s="279"/>
-      <c r="C71" s="471">
+      <c r="C71" s="484">
         <v>16</v>
       </c>
       <c r="D71" s="280" t="s">
@@ -14142,7 +14367,7 @@
     <row r="72" spans="1:8" ht="39">
       <c r="A72" s="279"/>
       <c r="B72" s="279"/>
-      <c r="C72" s="459"/>
+      <c r="C72" s="472"/>
       <c r="D72" s="283"/>
       <c r="E72" s="281" t="s">
         <v>742</v>
@@ -14158,7 +14383,7 @@
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="279"/>
       <c r="B73" s="279"/>
-      <c r="C73" s="458"/>
+      <c r="C73" s="471"/>
       <c r="D73" s="284"/>
       <c r="E73" s="281" t="s">
         <v>745</v>
@@ -17185,7 +17410,7 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="2.6640625" style="306" customWidth="1"/>
@@ -17196,7 +17421,7 @@
     <col min="7" max="7" width="13.1640625" style="306" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" style="306" customWidth="1"/>
     <col min="9" max="9" width="19.83203125" style="306" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="476" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="457" customWidth="1"/>
     <col min="11" max="16384" width="12.6640625" style="306"/>
   </cols>
   <sheetData>
@@ -17210,7 +17435,7 @@
       <c r="G1" s="305"/>
       <c r="H1" s="305"/>
       <c r="I1" s="305"/>
-      <c r="J1" s="474"/>
+      <c r="J1" s="455"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="303"/>
@@ -17222,7 +17447,7 @@
       <c r="G2" s="305"/>
       <c r="H2" s="305"/>
       <c r="I2" s="305"/>
-      <c r="J2" s="474"/>
+      <c r="J2" s="455"/>
     </row>
     <row r="3" spans="1:10" ht="27.75" customHeight="1" thickBot="1">
       <c r="A3" s="308"/>
@@ -17236,7 +17461,7 @@
       <c r="G3" s="310"/>
       <c r="H3" s="310"/>
       <c r="I3" s="310"/>
-      <c r="J3" s="475"/>
+      <c r="J3" s="456"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" thickTop="1">
       <c r="A4" s="312"/>
@@ -17250,7 +17475,7 @@
       <c r="G4" s="312"/>
       <c r="H4" s="312"/>
       <c r="I4" s="305"/>
-      <c r="J4" s="474"/>
+      <c r="J4" s="455"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="312"/>
@@ -17276,7 +17501,7 @@
       <c r="I5" s="315" t="s">
         <v>349</v>
       </c>
-      <c r="J5" s="474"/>
+      <c r="J5" s="455"/>
     </row>
     <row r="6" spans="1:10" ht="56">
       <c r="A6" s="312"/>
@@ -17302,7 +17527,7 @@
       <c r="I6" s="322" t="s">
         <v>898</v>
       </c>
-      <c r="J6" s="474"/>
+      <c r="J6" s="455"/>
     </row>
     <row r="7" spans="1:10" ht="56">
       <c r="A7" s="312"/>
@@ -17311,7 +17536,7 @@
         <v>41</v>
       </c>
       <c r="D7" s="324" t="s">
-        <v>42</v>
+        <v>1038</v>
       </c>
       <c r="E7" s="325" t="s">
         <v>899</v>
@@ -17328,9 +17553,9 @@
       <c r="I7" s="329" t="s">
         <v>900</v>
       </c>
-      <c r="J7" s="474"/>
-    </row>
-    <row r="8" spans="1:10" ht="28">
+      <c r="J7" s="455"/>
+    </row>
+    <row r="8" spans="1:10" ht="154">
       <c r="A8" s="312"/>
       <c r="B8" s="304"/>
       <c r="C8" s="330" t="s">
@@ -17340,21 +17565,21 @@
         <v>52</v>
       </c>
       <c r="E8" s="325" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="F8" s="331" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G8" s="332" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H8" s="333" t="s">
         <v>903</v>
       </c>
-      <c r="G8" s="332" t="s">
+      <c r="I8" s="334" t="s">
         <v>904</v>
       </c>
-      <c r="H8" s="333" t="s">
-        <v>905</v>
-      </c>
-      <c r="I8" s="334" t="s">
-        <v>906</v>
-      </c>
-      <c r="J8" s="474"/>
+      <c r="J8" s="455"/>
     </row>
     <row r="9" spans="1:10" ht="45">
       <c r="A9" s="312"/>
@@ -17369,18 +17594,18 @@
         <v>899</v>
       </c>
       <c r="F9" s="331" t="s">
+        <v>902</v>
+      </c>
+      <c r="G9" s="335" t="s">
+        <v>905</v>
+      </c>
+      <c r="H9" s="333" t="s">
         <v>903</v>
       </c>
-      <c r="G9" s="335" t="s">
-        <v>907</v>
-      </c>
-      <c r="H9" s="333" t="s">
-        <v>905</v>
-      </c>
       <c r="I9" s="336" t="s">
-        <v>908</v>
-      </c>
-      <c r="J9" s="474"/>
+        <v>906</v>
+      </c>
+      <c r="J9" s="455"/>
     </row>
     <row r="10" spans="1:10" ht="45">
       <c r="A10" s="312"/>
@@ -17395,18 +17620,18 @@
         <v>895</v>
       </c>
       <c r="F10" s="331" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="G10" s="335" t="s">
-        <v>910</v>
+        <v>1062</v>
       </c>
       <c r="H10" s="333" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="I10" s="336" t="s">
-        <v>911</v>
-      </c>
-      <c r="J10" s="474"/>
+        <v>908</v>
+      </c>
+      <c r="J10" s="455"/>
     </row>
     <row r="11" spans="1:10" ht="45">
       <c r="A11" s="312"/>
@@ -17415,24 +17640,24 @@
         <v>66</v>
       </c>
       <c r="D11" s="324" t="s">
-        <v>67</v>
+        <v>920</v>
       </c>
       <c r="E11" s="325" t="s">
         <v>899</v>
       </c>
       <c r="F11" s="331" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="G11" s="335" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H11" s="333" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="I11" s="336" t="s">
-        <v>913</v>
-      </c>
-      <c r="J11" s="474"/>
+        <v>910</v>
+      </c>
+      <c r="J11" s="455"/>
     </row>
     <row r="12" spans="1:10" ht="42">
       <c r="A12" s="312"/>
@@ -17456,10 +17681,10 @@
         <v>897</v>
       </c>
       <c r="I12" s="340" t="s">
-        <v>914</v>
-      </c>
-      <c r="J12" s="474" t="s">
-        <v>1059</v>
+        <v>911</v>
+      </c>
+      <c r="J12" s="455" t="s">
+        <v>1037</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="56">
@@ -17475,18 +17700,18 @@
         <v>899</v>
       </c>
       <c r="F13" s="326" t="s">
-        <v>915</v>
+        <v>912</v>
       </c>
       <c r="G13" s="335" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H13" s="333" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="I13" s="334" t="s">
-        <v>916</v>
-      </c>
-      <c r="J13" s="474"/>
+        <v>913</v>
+      </c>
+      <c r="J13" s="455"/>
     </row>
     <row r="14" spans="1:10" ht="56">
       <c r="A14" s="312"/>
@@ -17495,24 +17720,24 @@
         <v>80</v>
       </c>
       <c r="D14" s="337" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="E14" s="343" t="s">
         <v>899</v>
       </c>
       <c r="F14" s="326" t="s">
+        <v>912</v>
+      </c>
+      <c r="G14" s="335" t="s">
         <v>915</v>
       </c>
-      <c r="G14" s="335" t="s">
-        <v>918</v>
-      </c>
       <c r="H14" s="333" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="I14" s="334" t="s">
-        <v>919</v>
-      </c>
-      <c r="J14" s="474"/>
+        <v>916</v>
+      </c>
+      <c r="J14" s="455"/>
     </row>
     <row r="15" spans="1:10" ht="42">
       <c r="A15" s="312"/>
@@ -17527,18 +17752,18 @@
         <v>899</v>
       </c>
       <c r="F15" s="331" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="G15" s="335" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H15" s="333" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="I15" s="334" t="s">
-        <v>921</v>
-      </c>
-      <c r="J15" s="474"/>
+        <v>918</v>
+      </c>
+      <c r="J15" s="455"/>
     </row>
     <row r="16" spans="1:10" ht="42">
       <c r="A16" s="312"/>
@@ -17553,18 +17778,18 @@
         <v>899</v>
       </c>
       <c r="F16" s="331" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
       <c r="G16" s="335" t="s">
-        <v>918</v>
+        <v>915</v>
       </c>
       <c r="H16" s="333" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="I16" s="334" t="s">
-        <v>922</v>
-      </c>
-      <c r="J16" s="474"/>
+        <v>919</v>
+      </c>
+      <c r="J16" s="455"/>
     </row>
     <row r="17" spans="1:10" ht="45">
       <c r="A17" s="312"/>
@@ -17573,24 +17798,24 @@
         <v>102</v>
       </c>
       <c r="D17" s="324" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="E17" s="346" t="s">
         <v>899</v>
       </c>
       <c r="F17" s="331" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="G17" s="335" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H17" s="333" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="I17" s="336" t="s">
-        <v>925</v>
-      </c>
-      <c r="J17" s="474"/>
+        <v>922</v>
+      </c>
+      <c r="J17" s="455"/>
     </row>
     <row r="18" spans="1:10" ht="60">
       <c r="A18" s="312"/>
@@ -17602,56 +17827,56 @@
         <v>108</v>
       </c>
       <c r="E18" s="349" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="F18" s="350" t="s">
+        <v>921</v>
+      </c>
+      <c r="G18" s="351" t="s">
         <v>924</v>
       </c>
-      <c r="G18" s="351" t="s">
-        <v>927</v>
-      </c>
       <c r="H18" s="352" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="I18" s="353" t="s">
-        <v>928</v>
-      </c>
-      <c r="J18" s="474"/>
+        <v>925</v>
+      </c>
+      <c r="J18" s="455"/>
     </row>
     <row r="19" spans="1:10" ht="45">
       <c r="A19" s="312"/>
       <c r="B19" s="304"/>
       <c r="C19" s="354" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="D19" s="355" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="E19" s="356" t="s">
         <v>899</v>
       </c>
       <c r="F19" s="357" t="s">
+        <v>902</v>
+      </c>
+      <c r="G19" s="358" t="s">
+        <v>928</v>
+      </c>
+      <c r="H19" s="359" t="s">
         <v>903</v>
       </c>
-      <c r="G19" s="358" t="s">
-        <v>931</v>
-      </c>
-      <c r="H19" s="359" t="s">
-        <v>905</v>
-      </c>
       <c r="I19" s="360" t="s">
-        <v>932</v>
-      </c>
-      <c r="J19" s="474"/>
+        <v>929</v>
+      </c>
+      <c r="J19" s="455"/>
     </row>
     <row r="20" spans="1:10" ht="45">
       <c r="A20" s="312"/>
       <c r="B20" s="304"/>
       <c r="C20" s="354" t="s">
-        <v>1033</v>
+        <v>1011</v>
       </c>
       <c r="D20" s="355" t="s">
-        <v>1034</v>
+        <v>1012</v>
       </c>
       <c r="E20" s="356" t="s">
         <v>897</v>
@@ -17663,12 +17888,12 @@
         <v>897</v>
       </c>
       <c r="H20" s="359" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="I20" s="360" t="s">
-        <v>1035</v>
-      </c>
-      <c r="J20" s="474"/>
+        <v>1013</v>
+      </c>
+      <c r="J20" s="455"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="312"/>
@@ -17680,7 +17905,7 @@
       <c r="G21" s="312"/>
       <c r="H21" s="312"/>
       <c r="I21" s="305"/>
-      <c r="J21" s="474"/>
+      <c r="J21" s="455"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="312"/>
@@ -17694,7 +17919,7 @@
       <c r="G22" s="312"/>
       <c r="H22" s="312"/>
       <c r="I22" s="305"/>
-      <c r="J22" s="474"/>
+      <c r="J22" s="455"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="312"/>
@@ -17710,87 +17935,87 @@
       <c r="G23" s="312"/>
       <c r="H23" s="312"/>
       <c r="I23" s="305"/>
-      <c r="J23" s="474"/>
+      <c r="J23" s="455"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="312"/>
       <c r="B24" s="304"/>
       <c r="C24" s="363" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="D24" s="364" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="E24" s="312"/>
       <c r="F24" s="312"/>
       <c r="G24" s="312"/>
       <c r="H24" s="312"/>
       <c r="I24" s="305"/>
-      <c r="J24" s="474"/>
+      <c r="J24" s="455"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="312"/>
       <c r="B25" s="304"/>
       <c r="C25" s="366" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D25" s="364" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="E25" s="312"/>
       <c r="F25" s="312"/>
       <c r="G25" s="312"/>
       <c r="H25" s="312"/>
       <c r="I25" s="305"/>
-      <c r="J25" s="474"/>
+      <c r="J25" s="455"/>
     </row>
     <row r="26" spans="1:10" ht="16.5" customHeight="1">
       <c r="A26" s="312"/>
       <c r="B26" s="304"/>
       <c r="C26" s="366" t="s">
-        <v>1049</v>
+        <v>1027</v>
       </c>
       <c r="D26" s="365" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="E26" s="312"/>
       <c r="F26" s="312"/>
       <c r="G26" s="312"/>
       <c r="H26" s="312"/>
       <c r="I26" s="305"/>
-      <c r="J26" s="474"/>
+      <c r="J26" s="455"/>
     </row>
     <row r="27" spans="1:10" ht="17.25" customHeight="1">
       <c r="A27" s="312"/>
       <c r="B27" s="304"/>
       <c r="C27" s="366" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D27" s="365" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="E27" s="312"/>
       <c r="F27" s="312"/>
       <c r="G27" s="312"/>
       <c r="H27" s="312"/>
       <c r="I27" s="305"/>
-      <c r="J27" s="474"/>
+      <c r="J27" s="455"/>
     </row>
     <row r="28" spans="1:10" ht="14.25" customHeight="1">
       <c r="A28" s="312"/>
       <c r="B28" s="304"/>
-      <c r="C28" s="453" t="s">
-        <v>1057</v>
+      <c r="C28" s="451" t="s">
+        <v>1035</v>
       </c>
       <c r="D28" s="365" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="E28" s="312"/>
       <c r="F28" s="312"/>
       <c r="G28" s="312"/>
       <c r="H28" s="312"/>
       <c r="I28" s="305"/>
-      <c r="J28" s="474"/>
+      <c r="J28" s="455"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="312"/>
@@ -17802,7 +18027,7 @@
       <c r="G29" s="312"/>
       <c r="H29" s="312"/>
       <c r="I29" s="305"/>
-      <c r="J29" s="474"/>
+      <c r="J29" s="455"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="312"/>
@@ -17816,7 +18041,7 @@
       <c r="G30" s="312"/>
       <c r="H30" s="312"/>
       <c r="I30" s="305"/>
-      <c r="J30" s="474"/>
+      <c r="J30" s="455"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="312"/>
@@ -17832,39 +18057,39 @@
       <c r="G31" s="312"/>
       <c r="H31" s="312"/>
       <c r="I31" s="305"/>
-      <c r="J31" s="474"/>
+      <c r="J31" s="455"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="312"/>
       <c r="B32" s="304"/>
-      <c r="C32" s="445" t="s">
-        <v>1036</v>
+      <c r="C32" s="443" t="s">
+        <v>1014</v>
       </c>
       <c r="D32" s="370" t="s">
-        <v>941</v>
+        <v>1044</v>
       </c>
       <c r="E32" s="312"/>
       <c r="F32" s="312"/>
       <c r="G32" s="312"/>
       <c r="H32" s="312"/>
       <c r="I32" s="305"/>
-      <c r="J32" s="474"/>
+      <c r="J32" s="455"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="312"/>
       <c r="B33" s="304"/>
       <c r="C33" s="371" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="D33" s="370" t="s">
-        <v>943</v>
+        <v>1045</v>
       </c>
       <c r="E33" s="312"/>
       <c r="F33" s="312"/>
       <c r="G33" s="312"/>
       <c r="H33" s="312"/>
       <c r="I33" s="305"/>
-      <c r="J33" s="474"/>
+      <c r="J33" s="455"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="312"/>
@@ -17873,673 +18098,721 @@
         <v>901</v>
       </c>
       <c r="D34" s="370" t="s">
-        <v>944</v>
+        <v>1046</v>
       </c>
       <c r="E34" s="312"/>
       <c r="F34" s="312"/>
       <c r="G34" s="312"/>
       <c r="H34" s="312"/>
       <c r="I34" s="305"/>
-      <c r="J34" s="474"/>
+      <c r="J34" s="455"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="312"/>
       <c r="B35" s="304"/>
       <c r="C35" s="371" t="s">
-        <v>1037</v>
+        <v>1015</v>
       </c>
       <c r="D35" s="370" t="s">
-        <v>945</v>
+        <v>1047</v>
       </c>
       <c r="E35" s="312"/>
       <c r="F35" s="312"/>
       <c r="G35" s="312"/>
       <c r="H35" s="312"/>
       <c r="I35" s="305"/>
-      <c r="J35" s="474"/>
+      <c r="J35" s="455"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
       <c r="A36" s="312"/>
       <c r="B36" s="304"/>
       <c r="C36" s="371" t="s">
-        <v>1038</v>
+        <v>1016</v>
       </c>
       <c r="D36" s="372" t="s">
-        <v>946</v>
+        <v>1048</v>
       </c>
       <c r="E36" s="312"/>
       <c r="F36" s="312"/>
       <c r="G36" s="312"/>
       <c r="H36" s="312"/>
       <c r="I36" s="305"/>
-      <c r="J36" s="474"/>
+      <c r="J36" s="455"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
       <c r="A37" s="312"/>
       <c r="B37" s="304"/>
       <c r="C37" s="371" t="s">
-        <v>1039</v>
+        <v>1017</v>
       </c>
       <c r="D37" s="370" t="s">
-        <v>947</v>
+        <v>1049</v>
       </c>
       <c r="E37" s="312"/>
       <c r="F37" s="312"/>
       <c r="G37" s="312"/>
       <c r="H37" s="312"/>
       <c r="I37" s="305"/>
-      <c r="J37" s="474"/>
+      <c r="J37" s="455"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
       <c r="A38" s="312"/>
       <c r="B38" s="304"/>
       <c r="C38" s="371" t="s">
-        <v>1040</v>
+        <v>1018</v>
       </c>
       <c r="D38" s="370" t="s">
-        <v>948</v>
+        <v>1050</v>
       </c>
       <c r="E38" s="312"/>
       <c r="F38" s="312"/>
       <c r="G38" s="312"/>
       <c r="H38" s="312"/>
       <c r="I38" s="305"/>
-      <c r="J38" s="474"/>
+      <c r="J38" s="455"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
       <c r="A39" s="312"/>
       <c r="B39" s="304"/>
-      <c r="C39" s="446" t="s">
-        <v>1041</v>
+      <c r="C39" s="444" t="s">
+        <v>1019</v>
       </c>
       <c r="D39" s="370" t="s">
-        <v>949</v>
+        <v>1051</v>
       </c>
       <c r="E39" s="312"/>
       <c r="F39" s="312"/>
       <c r="G39" s="312"/>
       <c r="H39" s="312"/>
       <c r="I39" s="305"/>
-      <c r="J39" s="474"/>
+      <c r="J39" s="455"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
       <c r="A40" s="312"/>
       <c r="B40" s="304"/>
       <c r="C40" s="371" t="s">
-        <v>1042</v>
+        <v>1020</v>
       </c>
       <c r="D40" s="372" t="s">
-        <v>950</v>
+        <v>1052</v>
       </c>
       <c r="E40" s="312"/>
       <c r="F40" s="312"/>
       <c r="G40" s="312"/>
       <c r="H40" s="312"/>
       <c r="I40" s="305"/>
-      <c r="J40" s="474"/>
+      <c r="J40" s="455"/>
     </row>
     <row r="41" spans="1:10" ht="15.75" customHeight="1">
       <c r="A41" s="312"/>
       <c r="B41" s="304"/>
       <c r="C41" s="371" t="s">
-        <v>1043</v>
+        <v>1021</v>
       </c>
       <c r="D41" s="370" t="s">
-        <v>951</v>
+        <v>1053</v>
       </c>
       <c r="E41" s="312"/>
       <c r="F41" s="312"/>
       <c r="G41" s="312"/>
       <c r="H41" s="312"/>
       <c r="I41" s="305"/>
-      <c r="J41" s="474"/>
+      <c r="J41" s="455"/>
     </row>
     <row r="42" spans="1:10" ht="15.75" customHeight="1">
       <c r="A42" s="312"/>
       <c r="B42" s="304"/>
-      <c r="C42" s="446" t="s">
-        <v>1044</v>
+      <c r="C42" s="444" t="s">
+        <v>1022</v>
       </c>
       <c r="D42" s="373" t="s">
-        <v>952</v>
+        <v>1054</v>
       </c>
       <c r="E42" s="312"/>
       <c r="F42" s="312"/>
       <c r="G42" s="312"/>
       <c r="H42" s="312"/>
       <c r="I42" s="305"/>
-      <c r="J42" s="474"/>
+      <c r="J42" s="455"/>
     </row>
     <row r="43" spans="1:10" ht="15.75" customHeight="1">
       <c r="A43" s="312"/>
       <c r="B43" s="304"/>
       <c r="C43" s="371" t="s">
-        <v>1045</v>
+        <v>1023</v>
       </c>
       <c r="D43" s="370" t="s">
-        <v>953</v>
+        <v>1055</v>
       </c>
       <c r="E43" s="312"/>
       <c r="F43" s="312"/>
       <c r="G43" s="312"/>
       <c r="H43" s="312"/>
       <c r="I43" s="305"/>
-      <c r="J43" s="474"/>
-    </row>
-    <row r="44" spans="1:10" ht="15.75" customHeight="1">
+      <c r="J43" s="455"/>
+    </row>
+    <row r="44" spans="1:10" ht="28">
       <c r="A44" s="312"/>
       <c r="B44" s="304"/>
       <c r="C44" s="371" t="s">
-        <v>1046</v>
+        <v>1024</v>
       </c>
       <c r="D44" s="370" t="s">
-        <v>954</v>
+        <v>1056</v>
       </c>
       <c r="E44" s="312"/>
       <c r="F44" s="312"/>
       <c r="G44" s="312"/>
       <c r="H44" s="312"/>
       <c r="I44" s="305"/>
-      <c r="J44" s="474"/>
-    </row>
-    <row r="45" spans="1:10" ht="15.75" customHeight="1">
+      <c r="J44" s="455"/>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" s="312"/>
       <c r="B45" s="304"/>
-      <c r="C45" s="447" t="s">
-        <v>929</v>
-      </c>
-      <c r="D45" s="448" t="s">
-        <v>955</v>
+      <c r="C45" s="459" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D45" s="373" t="s">
+        <v>1057</v>
       </c>
       <c r="E45" s="312"/>
       <c r="F45" s="312"/>
       <c r="G45" s="312"/>
       <c r="H45" s="312"/>
       <c r="I45" s="305"/>
-      <c r="J45" s="474"/>
-    </row>
-    <row r="46" spans="1:10" ht="15.75" customHeight="1">
+      <c r="J45" s="455"/>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" s="312"/>
       <c r="B46" s="304"/>
-      <c r="C46" s="449" t="s">
-        <v>1033</v>
-      </c>
-      <c r="D46" s="450" t="s">
-        <v>1047</v>
+      <c r="C46" s="459" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D46" s="373" t="s">
+        <v>1060</v>
       </c>
       <c r="E46" s="312"/>
       <c r="F46" s="312"/>
       <c r="G46" s="312"/>
       <c r="H46" s="312"/>
       <c r="I46" s="305"/>
-      <c r="J46" s="474"/>
-    </row>
-    <row r="47" spans="1:10" ht="15.75" customHeight="1">
+      <c r="J46" s="455"/>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" s="312"/>
       <c r="B47" s="304"/>
-      <c r="C47" s="312"/>
-      <c r="D47" s="312"/>
+      <c r="C47" s="459" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D47" s="373" t="s">
+        <v>1061</v>
+      </c>
       <c r="E47" s="312"/>
-      <c r="F47" s="367"/>
+      <c r="F47" s="312"/>
       <c r="G47" s="312"/>
       <c r="H47" s="312"/>
       <c r="I47" s="305"/>
-      <c r="J47" s="474"/>
+      <c r="J47" s="455"/>
     </row>
     <row r="48" spans="1:10" ht="15.75" customHeight="1">
       <c r="A48" s="312"/>
-      <c r="B48" s="304" t="s">
-        <v>113</v>
-      </c>
-      <c r="C48" s="312"/>
-      <c r="D48" s="312"/>
+      <c r="B48" s="304"/>
+      <c r="C48" s="445" t="s">
+        <v>926</v>
+      </c>
+      <c r="D48" s="446" t="s">
+        <v>939</v>
+      </c>
       <c r="E48" s="312"/>
-      <c r="F48" s="367"/>
+      <c r="F48" s="312"/>
       <c r="G48" s="312"/>
       <c r="H48" s="312"/>
       <c r="I48" s="305"/>
-      <c r="J48" s="474"/>
+      <c r="J48" s="455"/>
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1">
       <c r="A49" s="312"/>
       <c r="B49" s="304"/>
-      <c r="C49" s="374" t="s">
-        <v>732</v>
-      </c>
-      <c r="D49" s="368" t="s">
-        <v>734</v>
-      </c>
-      <c r="E49" s="368" t="s">
-        <v>736</v>
-      </c>
-      <c r="F49" s="375"/>
+      <c r="C49" s="447" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D49" s="448" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E49" s="312"/>
+      <c r="F49" s="312"/>
+      <c r="G49" s="312"/>
       <c r="H49" s="312"/>
       <c r="I49" s="305"/>
-      <c r="J49" s="474"/>
+      <c r="J49" s="455"/>
     </row>
     <row r="50" spans="1:10" ht="15.75" customHeight="1">
       <c r="A50" s="312"/>
       <c r="B50" s="304"/>
-      <c r="C50" s="376" t="s">
-        <v>956</v>
-      </c>
-      <c r="D50" s="377" t="s">
-        <v>957</v>
-      </c>
-      <c r="E50" s="378" t="s">
-        <v>958</v>
-      </c>
-      <c r="F50" s="379"/>
+      <c r="C50" s="312"/>
+      <c r="D50" s="312"/>
+      <c r="E50" s="312"/>
+      <c r="F50" s="367"/>
+      <c r="G50" s="312"/>
       <c r="H50" s="312"/>
       <c r="I50" s="305"/>
-      <c r="J50" s="474"/>
+      <c r="J50" s="455"/>
     </row>
     <row r="51" spans="1:10" ht="15.75" customHeight="1">
       <c r="A51" s="312"/>
-      <c r="B51" s="304"/>
-      <c r="C51" s="380"/>
-      <c r="D51" s="381" t="s">
-        <v>959</v>
-      </c>
-      <c r="E51" s="382" t="s">
-        <v>960</v>
-      </c>
-      <c r="F51" s="383"/>
+      <c r="B51" s="304" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="312"/>
+      <c r="D51" s="312"/>
+      <c r="E51" s="312"/>
+      <c r="F51" s="367"/>
+      <c r="G51" s="312"/>
       <c r="H51" s="312"/>
       <c r="I51" s="305"/>
-      <c r="J51" s="474"/>
+      <c r="J51" s="455"/>
     </row>
     <row r="52" spans="1:10" ht="15.75" customHeight="1">
       <c r="A52" s="312"/>
       <c r="B52" s="304"/>
-      <c r="C52" s="376" t="s">
-        <v>961</v>
-      </c>
-      <c r="D52" s="377" t="s">
-        <v>957</v>
-      </c>
-      <c r="E52" s="378" t="s">
-        <v>958</v>
-      </c>
-      <c r="F52" s="379"/>
+      <c r="C52" s="374" t="s">
+        <v>732</v>
+      </c>
+      <c r="D52" s="368" t="s">
+        <v>734</v>
+      </c>
+      <c r="E52" s="368" t="s">
+        <v>736</v>
+      </c>
+      <c r="F52" s="375"/>
       <c r="H52" s="312"/>
       <c r="I52" s="305"/>
-      <c r="J52" s="474"/>
+      <c r="J52" s="455"/>
     </row>
     <row r="53" spans="1:10" ht="15.75" customHeight="1">
       <c r="A53" s="312"/>
       <c r="B53" s="304"/>
-      <c r="C53" s="380"/>
-      <c r="D53" s="381" t="s">
-        <v>959</v>
-      </c>
-      <c r="E53" s="382" t="s">
-        <v>960</v>
-      </c>
-      <c r="F53" s="383"/>
+      <c r="C53" s="376" t="s">
+        <v>940</v>
+      </c>
+      <c r="D53" s="377" t="s">
+        <v>941</v>
+      </c>
+      <c r="E53" s="378" t="s">
+        <v>942</v>
+      </c>
+      <c r="F53" s="379"/>
       <c r="H53" s="312"/>
       <c r="I53" s="305"/>
-      <c r="J53" s="474"/>
+      <c r="J53" s="455"/>
     </row>
     <row r="54" spans="1:10" ht="15.75" customHeight="1">
       <c r="A54" s="312"/>
       <c r="B54" s="304"/>
-      <c r="C54" s="384" t="s">
-        <v>962</v>
-      </c>
+      <c r="C54" s="380"/>
       <c r="D54" s="381" t="s">
-        <v>963</v>
-      </c>
-      <c r="E54" s="385" t="s">
-        <v>964</v>
+        <v>943</v>
+      </c>
+      <c r="E54" s="382" t="s">
+        <v>944</v>
       </c>
       <c r="F54" s="383"/>
       <c r="H54" s="312"/>
       <c r="I54" s="305"/>
-      <c r="J54" s="474"/>
+      <c r="J54" s="455"/>
     </row>
     <row r="55" spans="1:10" ht="15.75" customHeight="1">
       <c r="A55" s="312"/>
       <c r="B55" s="304"/>
-      <c r="C55" s="376"/>
-      <c r="D55" s="386" t="s">
-        <v>957</v>
-      </c>
-      <c r="E55" s="385" t="s">
-        <v>965</v>
-      </c>
-      <c r="F55" s="383"/>
+      <c r="C55" s="376" t="s">
+        <v>945</v>
+      </c>
+      <c r="D55" s="377" t="s">
+        <v>941</v>
+      </c>
+      <c r="E55" s="378" t="s">
+        <v>942</v>
+      </c>
+      <c r="F55" s="379"/>
       <c r="H55" s="312"/>
       <c r="I55" s="305"/>
-      <c r="J55" s="474"/>
+      <c r="J55" s="455"/>
     </row>
     <row r="56" spans="1:10" ht="15.75" customHeight="1">
       <c r="A56" s="312"/>
       <c r="B56" s="304"/>
-      <c r="C56" s="387"/>
+      <c r="C56" s="380"/>
       <c r="D56" s="381" t="s">
-        <v>959</v>
-      </c>
-      <c r="E56" s="388" t="s">
-        <v>966</v>
+        <v>943</v>
+      </c>
+      <c r="E56" s="382" t="s">
+        <v>944</v>
       </c>
       <c r="F56" s="383"/>
       <c r="H56" s="312"/>
       <c r="I56" s="305"/>
-      <c r="J56" s="474"/>
+      <c r="J56" s="455"/>
     </row>
     <row r="57" spans="1:10" ht="15.75" customHeight="1">
       <c r="A57" s="312"/>
       <c r="B57" s="304"/>
       <c r="C57" s="384" t="s">
-        <v>967</v>
-      </c>
-      <c r="D57" s="377" t="s">
-        <v>968</v>
+        <v>946</v>
+      </c>
+      <c r="D57" s="381" t="s">
+        <v>947</v>
       </c>
       <c r="E57" s="385" t="s">
-        <v>969</v>
+        <v>948</v>
       </c>
       <c r="F57" s="383"/>
       <c r="H57" s="312"/>
       <c r="I57" s="305"/>
-      <c r="J57" s="474"/>
+      <c r="J57" s="455"/>
     </row>
     <row r="58" spans="1:10" ht="15.75" customHeight="1">
       <c r="A58" s="312"/>
       <c r="B58" s="304"/>
       <c r="C58" s="376"/>
       <c r="D58" s="386" t="s">
-        <v>970</v>
-      </c>
-      <c r="E58" s="388" t="s">
-        <v>971</v>
+        <v>941</v>
+      </c>
+      <c r="E58" s="385" t="s">
+        <v>949</v>
       </c>
       <c r="F58" s="383"/>
       <c r="H58" s="312"/>
       <c r="I58" s="305"/>
-      <c r="J58" s="474"/>
+      <c r="J58" s="455"/>
     </row>
     <row r="59" spans="1:10" ht="15.75" customHeight="1">
       <c r="A59" s="312"/>
       <c r="B59" s="304"/>
-      <c r="C59" s="376"/>
-      <c r="D59" s="377" t="s">
-        <v>972</v>
-      </c>
-      <c r="E59" s="376" t="s">
-        <v>973</v>
+      <c r="C59" s="387"/>
+      <c r="D59" s="381" t="s">
+        <v>943</v>
+      </c>
+      <c r="E59" s="388" t="s">
+        <v>950</v>
       </c>
       <c r="F59" s="383"/>
       <c r="H59" s="312"/>
       <c r="I59" s="305"/>
-      <c r="J59" s="474"/>
+      <c r="J59" s="455"/>
     </row>
     <row r="60" spans="1:10" ht="15.75" customHeight="1">
       <c r="A60" s="312"/>
       <c r="B60" s="304"/>
-      <c r="C60" s="376"/>
+      <c r="C60" s="384" t="s">
+        <v>951</v>
+      </c>
       <c r="D60" s="377" t="s">
-        <v>974</v>
-      </c>
-      <c r="E60" s="386" t="s">
-        <v>975</v>
+        <v>952</v>
+      </c>
+      <c r="E60" s="466" t="s">
+        <v>1065</v>
       </c>
       <c r="F60" s="383"/>
       <c r="H60" s="312"/>
       <c r="I60" s="305"/>
-      <c r="J60" s="474"/>
+      <c r="J60" s="455"/>
     </row>
     <row r="61" spans="1:10" ht="15.75" customHeight="1">
       <c r="A61" s="312"/>
       <c r="B61" s="304"/>
-      <c r="C61" s="380"/>
-      <c r="D61" s="377" t="s">
-        <v>716</v>
-      </c>
-      <c r="E61" s="385" t="s">
-        <v>976</v>
-      </c>
-      <c r="F61" s="379"/>
+      <c r="C61" s="376"/>
+      <c r="D61" s="386" t="s">
+        <v>953</v>
+      </c>
+      <c r="E61" s="467" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F61" s="383"/>
       <c r="H61" s="312"/>
       <c r="I61" s="305"/>
-      <c r="J61" s="474"/>
+      <c r="J61" s="455"/>
     </row>
     <row r="62" spans="1:10" ht="15.75" customHeight="1">
       <c r="A62" s="312"/>
       <c r="B62" s="304"/>
-      <c r="C62" s="384" t="s">
-        <v>977</v>
-      </c>
-      <c r="D62" s="389" t="s">
-        <v>978</v>
-      </c>
-      <c r="E62" s="390" t="s">
-        <v>979</v>
+      <c r="C62" s="376"/>
+      <c r="D62" s="377" t="s">
+        <v>954</v>
+      </c>
+      <c r="E62" s="464" t="s">
+        <v>1069</v>
       </c>
       <c r="F62" s="383"/>
       <c r="H62" s="312"/>
       <c r="I62" s="305"/>
-      <c r="J62" s="474"/>
+      <c r="J62" s="455"/>
     </row>
     <row r="63" spans="1:10" ht="15.75" customHeight="1">
       <c r="A63" s="312"/>
       <c r="B63" s="304"/>
       <c r="C63" s="376"/>
-      <c r="D63" s="381" t="s">
-        <v>980</v>
-      </c>
-      <c r="E63" s="391" t="s">
-        <v>981</v>
+      <c r="D63" s="377" t="s">
+        <v>956</v>
+      </c>
+      <c r="E63" s="465" t="s">
+        <v>1070</v>
       </c>
       <c r="F63" s="383"/>
       <c r="H63" s="312"/>
       <c r="I63" s="305"/>
-      <c r="J63" s="474"/>
+      <c r="J63" s="455"/>
     </row>
     <row r="64" spans="1:10" ht="15.75" customHeight="1">
       <c r="A64" s="312"/>
       <c r="B64" s="304"/>
-      <c r="C64" s="392"/>
-      <c r="D64" s="393" t="s">
-        <v>982</v>
-      </c>
-      <c r="E64" s="394" t="s">
-        <v>973</v>
-      </c>
-      <c r="F64" s="383"/>
+      <c r="C64" s="380"/>
+      <c r="D64" s="377" t="s">
+        <v>716</v>
+      </c>
+      <c r="E64" s="385" t="s">
+        <v>958</v>
+      </c>
+      <c r="F64" s="379"/>
       <c r="H64" s="312"/>
       <c r="I64" s="305"/>
-      <c r="J64" s="474"/>
+      <c r="J64" s="455"/>
     </row>
     <row r="65" spans="1:10" ht="15.75" customHeight="1">
       <c r="A65" s="312"/>
       <c r="B65" s="304"/>
-      <c r="C65" s="395"/>
-      <c r="D65" s="381" t="s">
-        <v>983</v>
-      </c>
-      <c r="E65" s="396" t="s">
-        <v>975</v>
+      <c r="C65" s="458" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D65" s="389" t="s">
+        <v>959</v>
+      </c>
+      <c r="E65" s="463" t="s">
+        <v>1067</v>
       </c>
       <c r="F65" s="383"/>
       <c r="H65" s="312"/>
       <c r="I65" s="305"/>
-      <c r="J65" s="474"/>
+      <c r="J65" s="455"/>
     </row>
     <row r="66" spans="1:10" ht="15.75" customHeight="1">
       <c r="A66" s="312"/>
       <c r="B66" s="304"/>
-      <c r="C66" s="397"/>
-      <c r="D66" s="377" t="s">
-        <v>716</v>
-      </c>
-      <c r="E66" s="377" t="s">
-        <v>976</v>
-      </c>
-      <c r="F66" s="398"/>
+      <c r="C66" s="376"/>
+      <c r="D66" s="381" t="s">
+        <v>961</v>
+      </c>
+      <c r="E66" s="390" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F66" s="383"/>
       <c r="H66" s="312"/>
       <c r="I66" s="305"/>
-      <c r="J66" s="474"/>
+      <c r="J66" s="455"/>
     </row>
     <row r="67" spans="1:10" ht="15.75" customHeight="1">
       <c r="A67" s="312"/>
       <c r="B67" s="304"/>
-      <c r="C67" s="399" t="s">
-        <v>984</v>
-      </c>
-      <c r="D67" s="400" t="s">
-        <v>985</v>
-      </c>
-      <c r="E67" s="400" t="s">
-        <v>986</v>
-      </c>
-      <c r="F67" s="398"/>
+      <c r="C67" s="391"/>
+      <c r="D67" s="392" t="s">
+        <v>962</v>
+      </c>
+      <c r="E67" s="393" t="s">
+        <v>955</v>
+      </c>
+      <c r="F67" s="383"/>
       <c r="H67" s="312"/>
       <c r="I67" s="305"/>
-      <c r="J67" s="474"/>
-    </row>
-    <row r="68" spans="1:10" ht="15.75" customHeight="1">
+      <c r="J67" s="455"/>
+    </row>
+    <row r="68" spans="1:10" ht="13">
       <c r="A68" s="312"/>
       <c r="B68" s="304"/>
-      <c r="C68" s="395"/>
-      <c r="D68" s="400" t="s">
-        <v>987</v>
-      </c>
-      <c r="E68" s="400" t="s">
-        <v>988</v>
-      </c>
-      <c r="F68" s="398"/>
+      <c r="C68" s="394"/>
+      <c r="D68" s="381" t="s">
+        <v>963</v>
+      </c>
+      <c r="E68" s="462" t="s">
+        <v>957</v>
+      </c>
+      <c r="F68" s="383"/>
       <c r="H68" s="312"/>
       <c r="I68" s="305"/>
-      <c r="J68" s="474"/>
+      <c r="J68" s="455"/>
     </row>
     <row r="69" spans="1:10" ht="15.75" customHeight="1">
       <c r="A69" s="312"/>
       <c r="B69" s="304"/>
       <c r="C69" s="395"/>
-      <c r="D69" s="400" t="s">
-        <v>989</v>
-      </c>
-      <c r="E69" s="400" t="s">
-        <v>990</v>
-      </c>
-      <c r="F69" s="398"/>
+      <c r="D69" s="377" t="s">
+        <v>716</v>
+      </c>
+      <c r="E69" s="377" t="s">
+        <v>958</v>
+      </c>
+      <c r="F69" s="396"/>
       <c r="H69" s="312"/>
       <c r="I69" s="305"/>
-      <c r="J69" s="474"/>
+      <c r="J69" s="455"/>
     </row>
     <row r="70" spans="1:10" ht="15.75" customHeight="1">
       <c r="A70" s="312"/>
       <c r="B70" s="304"/>
-      <c r="C70" s="395"/>
-      <c r="D70" s="400" t="s">
-        <v>991</v>
-      </c>
-      <c r="E70" s="400" t="s">
-        <v>986</v>
-      </c>
-      <c r="F70" s="398"/>
+      <c r="C70" s="397" t="s">
+        <v>964</v>
+      </c>
+      <c r="D70" s="398" t="s">
+        <v>965</v>
+      </c>
+      <c r="E70" s="398" t="s">
+        <v>966</v>
+      </c>
+      <c r="F70" s="396"/>
       <c r="H70" s="312"/>
       <c r="I70" s="305"/>
-      <c r="J70" s="474"/>
+      <c r="J70" s="455"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1">
       <c r="A71" s="312"/>
       <c r="B71" s="304"/>
-      <c r="C71" s="395"/>
-      <c r="D71" s="401" t="s">
-        <v>992</v>
-      </c>
-      <c r="E71" s="401" t="s">
-        <v>993</v>
-      </c>
-      <c r="F71" s="398"/>
+      <c r="C71" s="394"/>
+      <c r="D71" s="398" t="s">
+        <v>967</v>
+      </c>
+      <c r="E71" s="398" t="s">
+        <v>968</v>
+      </c>
+      <c r="F71" s="396"/>
       <c r="H71" s="312"/>
       <c r="I71" s="305"/>
-      <c r="J71" s="474"/>
+      <c r="J71" s="455"/>
     </row>
     <row r="72" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A72" s="305"/>
-      <c r="B72" s="305"/>
-      <c r="C72" s="402" t="s">
-        <v>994</v>
-      </c>
-      <c r="D72" s="403" t="s">
-        <v>987</v>
-      </c>
-      <c r="E72" s="404" t="s">
-        <v>995</v>
-      </c>
-      <c r="F72" s="398"/>
-      <c r="G72" s="305"/>
-      <c r="H72" s="305"/>
+      <c r="A72" s="312"/>
+      <c r="B72" s="304"/>
+      <c r="C72" s="394"/>
+      <c r="D72" s="398" t="s">
+        <v>969</v>
+      </c>
+      <c r="E72" s="398" t="s">
+        <v>970</v>
+      </c>
+      <c r="F72" s="396"/>
+      <c r="H72" s="312"/>
       <c r="I72" s="305"/>
-      <c r="J72" s="474"/>
-    </row>
-    <row r="73" spans="1:10" ht="15" customHeight="1">
-      <c r="C73" s="405"/>
-      <c r="D73" s="406" t="s">
-        <v>996</v>
-      </c>
-      <c r="E73" s="407" t="s">
+      <c r="J72" s="455"/>
+    </row>
+    <row r="73" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A73" s="312"/>
+      <c r="B73" s="304"/>
+      <c r="C73" s="394"/>
+      <c r="D73" s="398" t="s">
+        <v>971</v>
+      </c>
+      <c r="E73" s="398" t="s">
+        <v>966</v>
+      </c>
+      <c r="F73" s="396"/>
+      <c r="H73" s="312"/>
+      <c r="I73" s="305"/>
+      <c r="J73" s="455"/>
+    </row>
+    <row r="74" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A74" s="312"/>
+      <c r="B74" s="304"/>
+      <c r="C74" s="394"/>
+      <c r="D74" s="399" t="s">
+        <v>972</v>
+      </c>
+      <c r="E74" s="399" t="s">
+        <v>973</v>
+      </c>
+      <c r="F74" s="396"/>
+      <c r="H74" s="312"/>
+      <c r="I74" s="305"/>
+      <c r="J74" s="455"/>
+    </row>
+    <row r="75" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A75" s="305"/>
+      <c r="B75" s="305"/>
+      <c r="C75" s="400" t="s">
+        <v>974</v>
+      </c>
+      <c r="D75" s="401" t="s">
+        <v>967</v>
+      </c>
+      <c r="E75" s="402" t="s">
+        <v>975</v>
+      </c>
+      <c r="F75" s="396"/>
+      <c r="G75" s="305"/>
+      <c r="H75" s="305"/>
+      <c r="I75" s="305"/>
+      <c r="J75" s="455"/>
+    </row>
+    <row r="76" spans="1:10" ht="15" customHeight="1">
+      <c r="C76" s="403"/>
+      <c r="D76" s="404" t="s">
+        <v>976</v>
+      </c>
+      <c r="E76" s="405" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="15" customHeight="1">
+      <c r="C77" s="403"/>
+      <c r="D77" s="404" t="s">
+        <v>977</v>
+      </c>
+      <c r="E77" s="405" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="15" customHeight="1">
+      <c r="C78" s="406"/>
+      <c r="D78" s="404" t="s">
         <v>979</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" ht="15" customHeight="1">
-      <c r="C74" s="405"/>
-      <c r="D74" s="406" t="s">
-        <v>997</v>
-      </c>
-      <c r="E74" s="407" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1">
-      <c r="C75" s="408"/>
-      <c r="D75" s="406" t="s">
-        <v>999</v>
-      </c>
-      <c r="E75" s="404" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" ht="15" customHeight="1">
-      <c r="C76" s="402" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D76" s="403" t="s">
-        <v>987</v>
-      </c>
-      <c r="E76" s="404" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="15" customHeight="1">
-      <c r="C77" s="405"/>
-      <c r="D77" s="406" t="s">
-        <v>996</v>
-      </c>
-      <c r="E77" s="407" t="s">
+      <c r="E78" s="402" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="15" customHeight="1">
+      <c r="C79" s="400" t="s">
+        <v>981</v>
+      </c>
+      <c r="D79" s="401" t="s">
+        <v>967</v>
+      </c>
+      <c r="E79" s="402" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="15" customHeight="1">
+      <c r="C80" s="403"/>
+      <c r="D80" s="404" t="s">
+        <v>976</v>
+      </c>
+      <c r="E80" s="405" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5" ht="15" customHeight="1">
+      <c r="C81" s="403"/>
+      <c r="D81" s="404" t="s">
+        <v>977</v>
+      </c>
+      <c r="E81" s="405" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" ht="15" customHeight="1">
+      <c r="C82" s="406"/>
+      <c r="D82" s="404" t="s">
         <v>979</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1">
-      <c r="C78" s="405"/>
-      <c r="D78" s="406" t="s">
-        <v>997</v>
-      </c>
-      <c r="E78" s="407" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="15" customHeight="1">
-      <c r="C79" s="408"/>
-      <c r="D79" s="406" t="s">
-        <v>999</v>
-      </c>
-      <c r="E79" s="404" t="s">
-        <v>1000</v>
+      <c r="E82" s="402" t="s">
+        <v>980</v>
       </c>
     </row>
   </sheetData>

--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5724752-EA23-E148-A973-F7B4213637D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841624E7-8081-1B4B-9B0B-56BBFA28BB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="1074">
   <si>
     <t>プロジェクト概要</t>
   </si>
@@ -5291,44 +5291,6 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <r>
-      <t>/admin/login</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>web.php</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>に直接記載</t>
-    </r>
-    <rPh sb="21" eb="25">
-      <t>チョク</t>
-    </rPh>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>/login</t>
     <phoneticPr fontId="80"/>
   </si>
@@ -5617,6 +5579,76 @@
     </rPh>
     <phoneticPr fontId="80"/>
   </si>
+  <si>
+    <t>app/Http/Responses/LoginResponse.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>未ログイン時のリダイレクト先はapp/Http/Middleware/Authenticate.php</t>
+  </si>
+  <si>
+    <t xml:space="preserve">app/Providers/FortifyServiceProvider
+</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>未ログイン時のリダイレクト先は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>app/Http/Middleware/Authenticate.php</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>管理者画面へのアクセス制限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>app/Http/Middleware/AdminMiddleware.php</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ミ </t>
+    </rPh>
+    <rPh sb="52" eb="57">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
 </sst>
 </file>
 
@@ -5626,7 +5658,7 @@
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm"/>
   </numFmts>
-  <fonts count="94">
+  <fonts count="95">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -6263,6 +6295,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Tsukushi A Round Gothic Bold"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="21">
@@ -7344,7 +7383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18"/>
   </cellStyleXfs>
-  <cellXfs count="485">
+  <cellXfs count="487">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8282,9 +8321,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="63" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8539,13 +8575,22 @@
     <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8554,25 +8599,25 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9100,7 +9145,7 @@
     <row r="3" spans="1:12" ht="36.75" customHeight="1">
       <c r="A3" s="303"/>
       <c r="B3" s="303"/>
-      <c r="C3" s="407" t="s">
+      <c r="C3" s="406" t="s">
         <v>654</v>
       </c>
       <c r="D3" s="305"/>
@@ -9115,1399 +9160,1399 @@
     <row r="4" spans="1:12" ht="15.75" customHeight="1">
       <c r="A4" s="303"/>
       <c r="B4" s="303"/>
-      <c r="C4" s="374" t="s">
+      <c r="C4" s="373" t="s">
         <v>659</v>
       </c>
-      <c r="D4" s="408"/>
-      <c r="E4" s="409"/>
-      <c r="F4" s="409"/>
-      <c r="G4" s="409"/>
-      <c r="H4" s="409"/>
-      <c r="I4" s="409"/>
-      <c r="J4" s="409"/>
-      <c r="K4" s="409"/>
+      <c r="D4" s="407"/>
+      <c r="E4" s="408"/>
+      <c r="F4" s="408"/>
+      <c r="G4" s="408"/>
+      <c r="H4" s="408"/>
+      <c r="I4" s="408"/>
+      <c r="J4" s="408"/>
+      <c r="K4" s="408"/>
       <c r="L4" s="305"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="303"/>
       <c r="B5" s="303"/>
-      <c r="C5" s="410" t="s">
+      <c r="C5" s="409" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="411" t="s">
+      <c r="D5" s="410" t="s">
         <v>671</v>
       </c>
-      <c r="E5" s="412" t="s">
+      <c r="E5" s="411" t="s">
         <v>675</v>
       </c>
-      <c r="F5" s="412" t="s">
+      <c r="F5" s="411" t="s">
         <v>438</v>
       </c>
-      <c r="G5" s="412" t="s">
+      <c r="G5" s="411" t="s">
         <v>676</v>
       </c>
-      <c r="H5" s="412" t="s">
+      <c r="H5" s="411" t="s">
         <v>677</v>
       </c>
-      <c r="I5" s="412" t="s">
+      <c r="I5" s="411" t="s">
         <v>678</v>
       </c>
-      <c r="J5" s="412" t="s">
+      <c r="J5" s="411" t="s">
         <v>679</v>
       </c>
-      <c r="K5" s="413" t="s">
+      <c r="K5" s="412" t="s">
         <v>681</v>
       </c>
       <c r="L5" s="305"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A6" s="367"/>
-      <c r="B6" s="367"/>
-      <c r="C6" s="414">
+      <c r="A6" s="366"/>
+      <c r="B6" s="366"/>
+      <c r="C6" s="413">
         <v>1</v>
       </c>
-      <c r="D6" s="415" t="s">
+      <c r="D6" s="414" t="s">
         <v>983</v>
       </c>
-      <c r="E6" s="416"/>
-      <c r="F6" s="416"/>
-      <c r="G6" s="416"/>
-      <c r="H6" s="416"/>
-      <c r="I6" s="416"/>
-      <c r="J6" s="417"/>
-      <c r="K6" s="418"/>
+      <c r="E6" s="415"/>
+      <c r="F6" s="415"/>
+      <c r="G6" s="415"/>
+      <c r="H6" s="415"/>
+      <c r="I6" s="415"/>
+      <c r="J6" s="416"/>
+      <c r="K6" s="417"/>
       <c r="L6" s="305"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="303"/>
       <c r="B7" s="303"/>
-      <c r="C7" s="419"/>
-      <c r="E7" s="393" t="s">
+      <c r="C7" s="418"/>
+      <c r="E7" s="392" t="s">
         <v>701</v>
       </c>
-      <c r="F7" s="420" t="s">
+      <c r="F7" s="419" t="s">
         <v>984</v>
       </c>
-      <c r="G7" s="420" t="s">
+      <c r="G7" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="H7" s="393"/>
-      <c r="I7" s="420" t="s">
+      <c r="H7" s="392"/>
+      <c r="I7" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="J7" s="421"/>
-      <c r="K7" s="418"/>
+      <c r="J7" s="420"/>
+      <c r="K7" s="417"/>
       <c r="L7" s="305"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A8" s="375"/>
-      <c r="B8" s="375"/>
-      <c r="C8" s="422"/>
+      <c r="A8" s="374"/>
+      <c r="B8" s="374"/>
+      <c r="C8" s="421"/>
       <c r="D8" s="304"/>
-      <c r="E8" s="393" t="s">
+      <c r="E8" s="392" t="s">
         <v>985</v>
       </c>
-      <c r="F8" s="393" t="s">
+      <c r="F8" s="392" t="s">
         <v>986</v>
       </c>
-      <c r="G8" s="393"/>
-      <c r="H8" s="393"/>
-      <c r="I8" s="420" t="s">
+      <c r="G8" s="392"/>
+      <c r="H8" s="392"/>
+      <c r="I8" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="J8" s="421"/>
-      <c r="K8" s="418"/>
+      <c r="J8" s="420"/>
+      <c r="K8" s="417"/>
       <c r="L8" s="305"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A9" s="367"/>
-      <c r="B9" s="367"/>
-      <c r="C9" s="419"/>
-      <c r="E9" s="393" t="s">
+      <c r="A9" s="366"/>
+      <c r="B9" s="366"/>
+      <c r="C9" s="418"/>
+      <c r="E9" s="392" t="s">
         <v>987</v>
       </c>
-      <c r="F9" s="393" t="s">
+      <c r="F9" s="392" t="s">
         <v>986</v>
       </c>
-      <c r="G9" s="393"/>
-      <c r="H9" s="420" t="s">
+      <c r="G9" s="392"/>
+      <c r="H9" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="I9" s="420" t="s">
+      <c r="I9" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="J9" s="421"/>
-      <c r="K9" s="423" t="s">
+      <c r="J9" s="420"/>
+      <c r="K9" s="422" t="s">
         <v>764</v>
       </c>
       <c r="L9" s="305"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="367"/>
-      <c r="B10" s="367"/>
-      <c r="C10" s="419"/>
-      <c r="E10" s="393" t="s">
+      <c r="A10" s="366"/>
+      <c r="B10" s="366"/>
+      <c r="C10" s="418"/>
+      <c r="E10" s="392" t="s">
         <v>988</v>
       </c>
-      <c r="F10" s="393" t="s">
+      <c r="F10" s="392" t="s">
         <v>731</v>
       </c>
-      <c r="G10" s="393"/>
-      <c r="H10" s="393"/>
-      <c r="I10" s="420"/>
-      <c r="J10" s="421"/>
-      <c r="K10" s="418"/>
+      <c r="G10" s="392"/>
+      <c r="H10" s="392"/>
+      <c r="I10" s="419"/>
+      <c r="J10" s="420"/>
+      <c r="K10" s="417"/>
       <c r="L10" s="305"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" s="367"/>
-      <c r="B11" s="367"/>
-      <c r="C11" s="419"/>
-      <c r="E11" s="393" t="s">
+      <c r="A11" s="366"/>
+      <c r="B11" s="366"/>
+      <c r="C11" s="418"/>
+      <c r="E11" s="392" t="s">
         <v>989</v>
       </c>
-      <c r="F11" s="393" t="s">
+      <c r="F11" s="392" t="s">
         <v>986</v>
       </c>
-      <c r="G11" s="393"/>
-      <c r="H11" s="393"/>
-      <c r="I11" s="420" t="s">
+      <c r="G11" s="392"/>
+      <c r="H11" s="392"/>
+      <c r="I11" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="J11" s="421"/>
-      <c r="K11" s="418"/>
+      <c r="J11" s="420"/>
+      <c r="K11" s="417"/>
       <c r="L11" s="305"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A12" s="367"/>
-      <c r="B12" s="367"/>
-      <c r="C12" s="419"/>
-      <c r="E12" s="393" t="s">
+      <c r="A12" s="366"/>
+      <c r="B12" s="366"/>
+      <c r="C12" s="418"/>
+      <c r="E12" s="392" t="s">
         <v>990</v>
       </c>
-      <c r="F12" s="393" t="s">
+      <c r="F12" s="392" t="s">
         <v>991</v>
       </c>
-      <c r="G12" s="393"/>
-      <c r="H12" s="393"/>
-      <c r="I12" s="393"/>
-      <c r="J12" s="421"/>
-      <c r="K12" s="418"/>
+      <c r="G12" s="392"/>
+      <c r="H12" s="392"/>
+      <c r="I12" s="392"/>
+      <c r="J12" s="420"/>
+      <c r="K12" s="417"/>
       <c r="L12" s="305"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A13" s="367"/>
-      <c r="B13" s="367"/>
-      <c r="C13" s="419"/>
-      <c r="D13" s="438" t="s">
+      <c r="A13" s="366"/>
+      <c r="B13" s="366"/>
+      <c r="C13" s="418"/>
+      <c r="D13" s="437" t="s">
         <v>1032</v>
       </c>
-      <c r="E13" s="449" t="s">
+      <c r="E13" s="448" t="s">
         <v>1031</v>
       </c>
-      <c r="F13" s="449" t="s">
+      <c r="F13" s="448" t="s">
         <v>1006</v>
       </c>
-      <c r="G13" s="393"/>
-      <c r="H13" s="393"/>
-      <c r="I13" s="450" t="s">
+      <c r="G13" s="392"/>
+      <c r="H13" s="392"/>
+      <c r="I13" s="449" t="s">
         <v>710</v>
       </c>
-      <c r="J13" s="421"/>
-      <c r="K13" s="418"/>
+      <c r="J13" s="420"/>
+      <c r="K13" s="417"/>
       <c r="L13" s="305"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A14" s="367"/>
-      <c r="B14" s="367"/>
-      <c r="C14" s="419"/>
-      <c r="D14" s="438" t="s">
+      <c r="A14" s="366"/>
+      <c r="B14" s="366"/>
+      <c r="C14" s="418"/>
+      <c r="D14" s="437" t="s">
         <v>1030</v>
       </c>
-      <c r="E14" s="393" t="s">
+      <c r="E14" s="392" t="s">
         <v>1028</v>
       </c>
-      <c r="F14" s="393" t="s">
+      <c r="F14" s="392" t="s">
         <v>1029</v>
       </c>
-      <c r="G14" s="393"/>
-      <c r="H14" s="393"/>
-      <c r="I14" s="393"/>
-      <c r="J14" s="421"/>
-      <c r="K14" s="418"/>
+      <c r="G14" s="392"/>
+      <c r="H14" s="392"/>
+      <c r="I14" s="392"/>
+      <c r="J14" s="420"/>
+      <c r="K14" s="417"/>
       <c r="L14" s="305"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A15" s="367"/>
-      <c r="B15" s="367"/>
-      <c r="C15" s="419"/>
-      <c r="E15" s="393" t="s">
+      <c r="A15" s="366"/>
+      <c r="B15" s="366"/>
+      <c r="C15" s="418"/>
+      <c r="E15" s="392" t="s">
         <v>730</v>
       </c>
-      <c r="F15" s="393" t="s">
+      <c r="F15" s="392" t="s">
         <v>731</v>
       </c>
-      <c r="G15" s="393"/>
-      <c r="H15" s="393"/>
-      <c r="I15" s="393"/>
-      <c r="J15" s="421"/>
-      <c r="K15" s="418"/>
+      <c r="G15" s="392"/>
+      <c r="H15" s="392"/>
+      <c r="I15" s="392"/>
+      <c r="J15" s="420"/>
+      <c r="K15" s="417"/>
       <c r="L15" s="305"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="367"/>
-      <c r="B16" s="367"/>
-      <c r="C16" s="419"/>
-      <c r="E16" s="393" t="s">
+      <c r="A16" s="366"/>
+      <c r="B16" s="366"/>
+      <c r="C16" s="418"/>
+      <c r="E16" s="392" t="s">
         <v>739</v>
       </c>
-      <c r="F16" s="393" t="s">
+      <c r="F16" s="392" t="s">
         <v>731</v>
       </c>
-      <c r="G16" s="393"/>
-      <c r="H16" s="393"/>
-      <c r="I16" s="393"/>
-      <c r="J16" s="421"/>
-      <c r="K16" s="418"/>
+      <c r="G16" s="392"/>
+      <c r="H16" s="392"/>
+      <c r="I16" s="392"/>
+      <c r="J16" s="420"/>
+      <c r="K16" s="417"/>
       <c r="L16" s="305"/>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A17" s="396"/>
-      <c r="B17" s="396"/>
-      <c r="C17" s="426">
+      <c r="A17" s="395"/>
+      <c r="B17" s="395"/>
+      <c r="C17" s="425">
         <v>2</v>
       </c>
-      <c r="D17" s="424" t="s">
+      <c r="D17" s="423" t="s">
         <v>992</v>
       </c>
-      <c r="E17" s="416"/>
-      <c r="F17" s="416"/>
-      <c r="G17" s="416"/>
-      <c r="H17" s="416"/>
-      <c r="I17" s="416"/>
-      <c r="J17" s="417"/>
+      <c r="E17" s="415"/>
+      <c r="F17" s="415"/>
+      <c r="G17" s="415"/>
+      <c r="H17" s="415"/>
+      <c r="I17" s="415"/>
+      <c r="J17" s="416"/>
       <c r="K17" s="305"/>
       <c r="L17" s="305"/>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A18" s="396"/>
-      <c r="B18" s="396"/>
-      <c r="C18" s="425"/>
-      <c r="E18" s="393" t="s">
+      <c r="A18" s="395"/>
+      <c r="B18" s="395"/>
+      <c r="C18" s="424"/>
+      <c r="E18" s="392" t="s">
         <v>993</v>
       </c>
-      <c r="F18" s="363" t="s">
+      <c r="F18" s="362" t="s">
         <v>984</v>
       </c>
-      <c r="G18" s="420" t="s">
+      <c r="G18" s="419" t="s">
         <v>903</v>
       </c>
-      <c r="H18" s="393"/>
-      <c r="I18" s="420" t="s">
+      <c r="H18" s="392"/>
+      <c r="I18" s="419" t="s">
         <v>903</v>
       </c>
-      <c r="J18" s="421"/>
+      <c r="J18" s="420"/>
       <c r="K18" s="305"/>
       <c r="L18" s="305"/>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A19" s="396"/>
-      <c r="B19" s="396"/>
-      <c r="C19" s="425"/>
+      <c r="A19" s="395"/>
+      <c r="B19" s="395"/>
+      <c r="C19" s="424"/>
       <c r="D19" s="312" t="s">
         <v>994</v>
       </c>
-      <c r="E19" s="393" t="s">
+      <c r="E19" s="392" t="s">
         <v>965</v>
       </c>
-      <c r="F19" s="363" t="s">
+      <c r="F19" s="362" t="s">
         <v>995</v>
       </c>
-      <c r="G19" s="420"/>
-      <c r="H19" s="393" t="s">
+      <c r="G19" s="419"/>
+      <c r="H19" s="392" t="s">
         <v>903</v>
       </c>
-      <c r="I19" s="420" t="s">
+      <c r="I19" s="419" t="s">
         <v>903</v>
       </c>
-      <c r="J19" s="421" t="s">
+      <c r="J19" s="420" t="s">
         <v>996</v>
       </c>
       <c r="K19" s="305"/>
       <c r="L19" s="305"/>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A20" s="396"/>
-      <c r="B20" s="396"/>
-      <c r="C20" s="425"/>
+      <c r="A20" s="395"/>
+      <c r="B20" s="395"/>
+      <c r="C20" s="424"/>
       <c r="D20" s="312"/>
-      <c r="E20" s="393" t="s">
+      <c r="E20" s="392" t="s">
         <v>967</v>
       </c>
-      <c r="F20" s="363" t="s">
+      <c r="F20" s="362" t="s">
         <v>967</v>
       </c>
-      <c r="G20" s="420"/>
-      <c r="H20" s="393" t="s">
+      <c r="G20" s="419"/>
+      <c r="H20" s="392" t="s">
         <v>903</v>
       </c>
-      <c r="I20" s="420"/>
-      <c r="J20" s="421"/>
+      <c r="I20" s="419"/>
+      <c r="J20" s="420"/>
       <c r="K20" s="305"/>
       <c r="L20" s="305"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A21" s="396"/>
-      <c r="B21" s="396"/>
-      <c r="C21" s="425"/>
+      <c r="A21" s="395"/>
+      <c r="B21" s="395"/>
+      <c r="C21" s="424"/>
       <c r="D21" s="304"/>
-      <c r="E21" s="393" t="s">
+      <c r="E21" s="392" t="s">
         <v>976</v>
       </c>
-      <c r="F21" s="363" t="s">
+      <c r="F21" s="362" t="s">
         <v>997</v>
       </c>
-      <c r="G21" s="393"/>
-      <c r="H21" s="393"/>
-      <c r="I21" s="420" t="s">
+      <c r="G21" s="392"/>
+      <c r="H21" s="392"/>
+      <c r="I21" s="419" t="s">
         <v>903</v>
       </c>
-      <c r="J21" s="421"/>
+      <c r="J21" s="420"/>
       <c r="K21" s="305"/>
       <c r="L21" s="305"/>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A22" s="396"/>
-      <c r="B22" s="396"/>
-      <c r="C22" s="425"/>
-      <c r="E22" s="393" t="s">
+      <c r="A22" s="395"/>
+      <c r="B22" s="395"/>
+      <c r="C22" s="424"/>
+      <c r="E22" s="392" t="s">
         <v>977</v>
       </c>
-      <c r="F22" s="363" t="s">
+      <c r="F22" s="362" t="s">
         <v>997</v>
       </c>
-      <c r="G22" s="393"/>
-      <c r="H22" s="393"/>
-      <c r="I22" s="420"/>
-      <c r="J22" s="421"/>
+      <c r="G22" s="392"/>
+      <c r="H22" s="392"/>
+      <c r="I22" s="419"/>
+      <c r="J22" s="420"/>
       <c r="K22" s="305"/>
       <c r="L22" s="305"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A23" s="396"/>
-      <c r="B23" s="396"/>
-      <c r="C23" s="425"/>
-      <c r="E23" s="449" t="s">
+      <c r="A23" s="395"/>
+      <c r="B23" s="395"/>
+      <c r="C23" s="424"/>
+      <c r="E23" s="448" t="s">
         <v>979</v>
       </c>
-      <c r="F23" s="449" t="s">
+      <c r="F23" s="448" t="s">
         <v>1003</v>
       </c>
-      <c r="G23" s="393"/>
-      <c r="H23" s="393"/>
-      <c r="I23" s="420"/>
-      <c r="J23" s="421"/>
+      <c r="G23" s="392"/>
+      <c r="H23" s="392"/>
+      <c r="I23" s="419"/>
+      <c r="J23" s="420"/>
       <c r="K23" s="305"/>
       <c r="L23" s="305"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A24" s="396"/>
-      <c r="B24" s="396"/>
-      <c r="C24" s="425"/>
-      <c r="D24" s="427"/>
-      <c r="E24" s="428" t="s">
+      <c r="A24" s="395"/>
+      <c r="B24" s="395"/>
+      <c r="C24" s="424"/>
+      <c r="D24" s="426"/>
+      <c r="E24" s="427" t="s">
         <v>730</v>
       </c>
-      <c r="F24" s="428" t="s">
+      <c r="F24" s="427" t="s">
         <v>731</v>
       </c>
-      <c r="G24" s="428"/>
-      <c r="H24" s="428"/>
-      <c r="I24" s="428"/>
-      <c r="J24" s="429"/>
+      <c r="G24" s="427"/>
+      <c r="H24" s="427"/>
+      <c r="I24" s="427"/>
+      <c r="J24" s="428"/>
       <c r="K24" s="305"/>
       <c r="L24" s="305"/>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A25" s="396"/>
-      <c r="B25" s="396"/>
-      <c r="C25" s="425"/>
-      <c r="D25" s="430"/>
-      <c r="E25" s="428" t="s">
+      <c r="A25" s="395"/>
+      <c r="B25" s="395"/>
+      <c r="C25" s="424"/>
+      <c r="D25" s="429"/>
+      <c r="E25" s="427" t="s">
         <v>739</v>
       </c>
-      <c r="F25" s="428" t="s">
+      <c r="F25" s="427" t="s">
         <v>731</v>
       </c>
-      <c r="G25" s="428"/>
-      <c r="H25" s="428"/>
-      <c r="I25" s="428"/>
-      <c r="J25" s="429"/>
+      <c r="G25" s="427"/>
+      <c r="H25" s="427"/>
+      <c r="I25" s="427"/>
+      <c r="J25" s="428"/>
       <c r="K25" s="305"/>
       <c r="L25" s="305"/>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A26" s="396"/>
-      <c r="B26" s="396"/>
-      <c r="C26" s="425"/>
-      <c r="D26" s="431"/>
-      <c r="E26" s="432" t="s">
+      <c r="A26" s="395"/>
+      <c r="B26" s="395"/>
+      <c r="C26" s="424"/>
+      <c r="D26" s="430"/>
+      <c r="E26" s="431" t="s">
         <v>998</v>
       </c>
-      <c r="F26" s="433"/>
-      <c r="G26" s="434"/>
-      <c r="H26" s="433" t="s">
+      <c r="F26" s="432"/>
+      <c r="G26" s="433"/>
+      <c r="H26" s="432" t="s">
         <v>999</v>
       </c>
-      <c r="I26" s="433"/>
-      <c r="J26" s="435"/>
+      <c r="I26" s="432"/>
+      <c r="J26" s="434"/>
       <c r="K26" s="305"/>
       <c r="L26" s="305"/>
     </row>
     <row r="27" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A27" s="396"/>
-      <c r="B27" s="396"/>
-      <c r="C27" s="426">
+      <c r="A27" s="395"/>
+      <c r="B27" s="395"/>
+      <c r="C27" s="425">
         <v>3</v>
       </c>
-      <c r="D27" s="424" t="s">
+      <c r="D27" s="423" t="s">
         <v>1026</v>
       </c>
-      <c r="E27" s="416"/>
-      <c r="F27" s="416"/>
-      <c r="G27" s="416"/>
-      <c r="H27" s="416"/>
-      <c r="I27" s="416"/>
-      <c r="J27" s="417"/>
+      <c r="E27" s="415"/>
+      <c r="F27" s="415"/>
+      <c r="G27" s="415"/>
+      <c r="H27" s="415"/>
+      <c r="I27" s="415"/>
+      <c r="J27" s="416"/>
       <c r="K27" s="305"/>
       <c r="L27" s="305"/>
     </row>
     <row r="28" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A28" s="396"/>
-      <c r="B28" s="396"/>
-      <c r="C28" s="425"/>
-      <c r="E28" s="393" t="s">
+      <c r="A28" s="395"/>
+      <c r="B28" s="395"/>
+      <c r="C28" s="424"/>
+      <c r="E28" s="392" t="s">
         <v>701</v>
       </c>
-      <c r="F28" s="393" t="s">
+      <c r="F28" s="392" t="s">
         <v>984</v>
       </c>
-      <c r="G28" s="420" t="s">
+      <c r="G28" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="H28" s="393"/>
-      <c r="I28" s="420" t="s">
+      <c r="H28" s="392"/>
+      <c r="I28" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="J28" s="421"/>
+      <c r="J28" s="420"/>
       <c r="K28" s="305"/>
       <c r="L28" s="305"/>
     </row>
     <row r="29" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A29" s="396"/>
-      <c r="B29" s="396"/>
-      <c r="C29" s="425"/>
+      <c r="A29" s="395"/>
+      <c r="B29" s="395"/>
+      <c r="C29" s="424"/>
       <c r="D29" s="312" t="s">
         <v>994</v>
       </c>
-      <c r="E29" s="453" t="s">
+      <c r="E29" s="452" t="s">
         <v>1036</v>
       </c>
-      <c r="F29" s="393" t="s">
+      <c r="F29" s="392" t="s">
         <v>984</v>
       </c>
-      <c r="G29" s="420"/>
-      <c r="H29" s="393"/>
-      <c r="I29" s="420" t="s">
+      <c r="G29" s="419"/>
+      <c r="H29" s="392"/>
+      <c r="I29" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="J29" s="421" t="s">
+      <c r="J29" s="420" t="s">
         <v>1000</v>
       </c>
       <c r="K29" s="305"/>
       <c r="L29" s="305"/>
     </row>
     <row r="30" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A30" s="396"/>
-      <c r="B30" s="396"/>
-      <c r="C30" s="425"/>
+      <c r="A30" s="395"/>
+      <c r="B30" s="395"/>
+      <c r="C30" s="424"/>
       <c r="D30" s="304"/>
-      <c r="E30" s="393" t="s">
-        <v>1043</v>
-      </c>
-      <c r="F30" s="393" t="s">
+      <c r="E30" s="392" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F30" s="392" t="s">
         <v>997</v>
       </c>
-      <c r="G30" s="393"/>
-      <c r="H30" s="393"/>
-      <c r="I30" s="420"/>
-      <c r="J30" s="436"/>
+      <c r="G30" s="392"/>
+      <c r="H30" s="392"/>
+      <c r="I30" s="419"/>
+      <c r="J30" s="435"/>
       <c r="K30" s="305"/>
       <c r="L30" s="305"/>
     </row>
     <row r="31" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A31" s="396"/>
-      <c r="B31" s="396"/>
-      <c r="C31" s="425"/>
-      <c r="E31" s="393" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F31" s="393" t="s">
+      <c r="A31" s="395"/>
+      <c r="B31" s="395"/>
+      <c r="C31" s="424"/>
+      <c r="E31" s="392" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F31" s="392" t="s">
         <v>997</v>
       </c>
-      <c r="G31" s="393"/>
-      <c r="H31" s="393"/>
-      <c r="I31" s="420"/>
-      <c r="J31" s="421"/>
+      <c r="G31" s="392"/>
+      <c r="H31" s="392"/>
+      <c r="I31" s="419"/>
+      <c r="J31" s="420"/>
       <c r="K31" s="305"/>
       <c r="L31" s="305"/>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A32" s="396"/>
-      <c r="B32" s="396"/>
-      <c r="C32" s="425"/>
-      <c r="E32" s="393" t="s">
+      <c r="A32" s="395"/>
+      <c r="B32" s="395"/>
+      <c r="C32" s="424"/>
+      <c r="E32" s="392" t="s">
         <v>730</v>
       </c>
-      <c r="F32" s="393" t="s">
+      <c r="F32" s="392" t="s">
         <v>731</v>
       </c>
-      <c r="G32" s="393"/>
-      <c r="H32" s="393"/>
-      <c r="I32" s="393"/>
-      <c r="J32" s="421"/>
+      <c r="G32" s="392"/>
+      <c r="H32" s="392"/>
+      <c r="I32" s="392"/>
+      <c r="J32" s="420"/>
       <c r="K32" s="305"/>
       <c r="L32" s="305"/>
     </row>
     <row r="33" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A33" s="396"/>
-      <c r="B33" s="396"/>
-      <c r="C33" s="425"/>
-      <c r="E33" s="393" t="s">
+      <c r="A33" s="395"/>
+      <c r="B33" s="395"/>
+      <c r="C33" s="424"/>
+      <c r="E33" s="392" t="s">
         <v>739</v>
       </c>
-      <c r="F33" s="393" t="s">
+      <c r="F33" s="392" t="s">
         <v>731</v>
       </c>
-      <c r="G33" s="393"/>
-      <c r="H33" s="393"/>
-      <c r="I33" s="393"/>
-      <c r="J33" s="421"/>
+      <c r="G33" s="392"/>
+      <c r="H33" s="392"/>
+      <c r="I33" s="392"/>
+      <c r="J33" s="420"/>
       <c r="K33" s="305"/>
       <c r="L33" s="305"/>
     </row>
     <row r="34" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A34" s="396"/>
-      <c r="B34" s="396"/>
-      <c r="C34" s="426">
+      <c r="A34" s="395"/>
+      <c r="B34" s="395"/>
+      <c r="C34" s="425">
         <v>4</v>
       </c>
-      <c r="D34" s="468" t="s">
+      <c r="D34" s="482" t="s">
         <v>1001</v>
       </c>
-      <c r="E34" s="469"/>
-      <c r="F34" s="469"/>
-      <c r="G34" s="469"/>
-      <c r="H34" s="469"/>
-      <c r="I34" s="416"/>
-      <c r="J34" s="417"/>
+      <c r="E34" s="483"/>
+      <c r="F34" s="483"/>
+      <c r="G34" s="483"/>
+      <c r="H34" s="483"/>
+      <c r="I34" s="415"/>
+      <c r="J34" s="416"/>
       <c r="K34" s="305"/>
       <c r="L34" s="305"/>
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A35" s="396"/>
-      <c r="B35" s="396"/>
-      <c r="C35" s="425"/>
-      <c r="E35" s="393" t="s">
+      <c r="A35" s="395"/>
+      <c r="B35" s="395"/>
+      <c r="C35" s="424"/>
+      <c r="E35" s="392" t="s">
         <v>993</v>
       </c>
-      <c r="F35" s="363" t="s">
+      <c r="F35" s="362" t="s">
         <v>984</v>
       </c>
-      <c r="G35" s="420" t="s">
+      <c r="G35" s="419" t="s">
         <v>903</v>
       </c>
-      <c r="H35" s="393"/>
-      <c r="I35" s="420" t="s">
+      <c r="H35" s="392"/>
+      <c r="I35" s="419" t="s">
         <v>903</v>
       </c>
-      <c r="J35" s="421"/>
+      <c r="J35" s="420"/>
       <c r="K35" s="305"/>
       <c r="L35" s="305"/>
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A36" s="396"/>
-      <c r="B36" s="396"/>
-      <c r="C36" s="425"/>
+      <c r="A36" s="395"/>
+      <c r="B36" s="395"/>
+      <c r="C36" s="424"/>
       <c r="D36" s="306" t="s">
         <v>1002</v>
       </c>
-      <c r="E36" s="453" t="s">
+      <c r="E36" s="452" t="s">
         <v>1036</v>
       </c>
-      <c r="F36" s="363" t="s">
+      <c r="F36" s="362" t="s">
         <v>984</v>
       </c>
-      <c r="G36" s="420"/>
-      <c r="H36" s="393"/>
-      <c r="I36" s="420" t="s">
+      <c r="G36" s="419"/>
+      <c r="H36" s="392"/>
+      <c r="I36" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="J36" s="421" t="s">
+      <c r="J36" s="420" t="s">
         <v>1000</v>
       </c>
       <c r="K36" s="305"/>
       <c r="L36" s="305"/>
     </row>
     <row r="37" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A37" s="396"/>
-      <c r="B37" s="396"/>
-      <c r="C37" s="425"/>
-      <c r="E37" s="393" t="s">
+      <c r="A37" s="395"/>
+      <c r="B37" s="395"/>
+      <c r="C37" s="424"/>
+      <c r="E37" s="392" t="s">
         <v>952</v>
       </c>
-      <c r="F37" s="393" t="s">
+      <c r="F37" s="392" t="s">
         <v>997</v>
       </c>
-      <c r="G37" s="393"/>
-      <c r="H37" s="393"/>
-      <c r="I37" s="420" t="s">
+      <c r="G37" s="392"/>
+      <c r="H37" s="392"/>
+      <c r="I37" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="J37" s="421"/>
+      <c r="J37" s="420"/>
       <c r="K37" s="305"/>
       <c r="L37" s="305"/>
     </row>
     <row r="38" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A38" s="396"/>
-      <c r="B38" s="396"/>
-      <c r="C38" s="425"/>
-      <c r="E38" s="393" t="s">
+      <c r="A38" s="395"/>
+      <c r="B38" s="395"/>
+      <c r="C38" s="424"/>
+      <c r="E38" s="392" t="s">
         <v>953</v>
       </c>
-      <c r="F38" s="437" t="s">
+      <c r="F38" s="436" t="s">
         <v>997</v>
       </c>
-      <c r="G38" s="393"/>
-      <c r="H38" s="393"/>
-      <c r="I38" s="454"/>
-      <c r="J38" s="421"/>
+      <c r="G38" s="392"/>
+      <c r="H38" s="392"/>
+      <c r="I38" s="453"/>
+      <c r="J38" s="420"/>
       <c r="K38" s="305"/>
       <c r="L38" s="305"/>
     </row>
     <row r="39" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A39" s="396"/>
-      <c r="B39" s="396"/>
-      <c r="C39" s="425"/>
-      <c r="E39" s="393" t="s">
+      <c r="A39" s="395"/>
+      <c r="B39" s="395"/>
+      <c r="C39" s="424"/>
+      <c r="E39" s="392" t="s">
         <v>979</v>
       </c>
-      <c r="F39" s="393" t="s">
+      <c r="F39" s="392" t="s">
         <v>1003</v>
       </c>
-      <c r="G39" s="393"/>
-      <c r="H39" s="393"/>
-      <c r="I39" s="420" t="s">
+      <c r="G39" s="392"/>
+      <c r="H39" s="392"/>
+      <c r="I39" s="419" t="s">
         <v>710</v>
       </c>
-      <c r="J39" s="421"/>
+      <c r="J39" s="420"/>
       <c r="K39" s="305"/>
       <c r="L39" s="305"/>
     </row>
     <row r="40" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A40" s="396"/>
-      <c r="B40" s="396"/>
-      <c r="C40" s="425"/>
-      <c r="D40" s="438" t="s">
+      <c r="A40" s="395"/>
+      <c r="B40" s="395"/>
+      <c r="C40" s="424"/>
+      <c r="D40" s="437" t="s">
         <v>1004</v>
       </c>
-      <c r="E40" s="393" t="s">
+      <c r="E40" s="392" t="s">
         <v>1005</v>
       </c>
-      <c r="F40" s="393" t="s">
+      <c r="F40" s="392" t="s">
         <v>1006</v>
       </c>
-      <c r="G40" s="393"/>
-      <c r="H40" s="393"/>
-      <c r="I40" s="393" t="s">
+      <c r="G40" s="392"/>
+      <c r="H40" s="392"/>
+      <c r="I40" s="392" t="s">
         <v>903</v>
       </c>
-      <c r="J40" s="421"/>
+      <c r="J40" s="420"/>
       <c r="K40" s="305"/>
       <c r="L40" s="305"/>
     </row>
     <row r="41" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A41" s="396"/>
-      <c r="B41" s="396"/>
-      <c r="C41" s="425"/>
-      <c r="D41" s="438"/>
-      <c r="E41" s="449" t="s">
+      <c r="A41" s="395"/>
+      <c r="B41" s="395"/>
+      <c r="C41" s="424"/>
+      <c r="D41" s="437"/>
+      <c r="E41" s="448" t="s">
         <v>1033</v>
       </c>
-      <c r="F41" s="449" t="s">
+      <c r="F41" s="448" t="s">
         <v>967</v>
       </c>
-      <c r="G41" s="393"/>
-      <c r="H41" s="393"/>
-      <c r="I41" s="449" t="s">
+      <c r="G41" s="392"/>
+      <c r="H41" s="392"/>
+      <c r="I41" s="448" t="s">
         <v>903</v>
       </c>
-      <c r="J41" s="421"/>
+      <c r="J41" s="420"/>
       <c r="K41" s="305"/>
       <c r="L41" s="305"/>
     </row>
     <row r="42" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A42" s="396"/>
-      <c r="B42" s="396"/>
-      <c r="C42" s="425"/>
-      <c r="D42" s="427"/>
-      <c r="E42" s="428" t="s">
+      <c r="A42" s="395"/>
+      <c r="B42" s="395"/>
+      <c r="C42" s="424"/>
+      <c r="D42" s="426"/>
+      <c r="E42" s="427" t="s">
         <v>730</v>
       </c>
-      <c r="F42" s="428" t="s">
+      <c r="F42" s="427" t="s">
         <v>731</v>
       </c>
-      <c r="G42" s="428"/>
-      <c r="H42" s="428"/>
-      <c r="I42" s="428"/>
-      <c r="J42" s="429"/>
+      <c r="G42" s="427"/>
+      <c r="H42" s="427"/>
+      <c r="I42" s="427"/>
+      <c r="J42" s="428"/>
       <c r="K42" s="305"/>
       <c r="L42" s="305"/>
     </row>
     <row r="43" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A43" s="396"/>
-      <c r="B43" s="396"/>
-      <c r="C43" s="439"/>
-      <c r="D43" s="431"/>
-      <c r="E43" s="428" t="s">
+      <c r="A43" s="395"/>
+      <c r="B43" s="395"/>
+      <c r="C43" s="438"/>
+      <c r="D43" s="430"/>
+      <c r="E43" s="427" t="s">
         <v>739</v>
       </c>
-      <c r="F43" s="428" t="s">
+      <c r="F43" s="427" t="s">
         <v>731</v>
       </c>
-      <c r="G43" s="428"/>
-      <c r="H43" s="428"/>
-      <c r="I43" s="428"/>
-      <c r="J43" s="429"/>
+      <c r="G43" s="427"/>
+      <c r="H43" s="427"/>
+      <c r="I43" s="427"/>
+      <c r="J43" s="428"/>
       <c r="K43" s="305"/>
       <c r="L43" s="305"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A44" s="396"/>
-      <c r="B44" s="396"/>
-      <c r="C44" s="426">
+      <c r="A44" s="395"/>
+      <c r="B44" s="395"/>
+      <c r="C44" s="425">
         <v>5</v>
       </c>
-      <c r="D44" s="452" t="s">
+      <c r="D44" s="451" t="s">
         <v>1034</v>
       </c>
-      <c r="E44" s="416"/>
-      <c r="F44" s="416"/>
-      <c r="G44" s="416"/>
-      <c r="H44" s="416"/>
-      <c r="I44" s="416"/>
-      <c r="J44" s="417"/>
+      <c r="E44" s="415"/>
+      <c r="F44" s="415"/>
+      <c r="G44" s="415"/>
+      <c r="H44" s="415"/>
+      <c r="I44" s="415"/>
+      <c r="J44" s="416"/>
       <c r="K44" s="305"/>
       <c r="L44" s="305"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A45" s="396"/>
-      <c r="B45" s="396"/>
-      <c r="C45" s="425"/>
-      <c r="E45" s="393" t="s">
+      <c r="A45" s="395"/>
+      <c r="B45" s="395"/>
+      <c r="C45" s="424"/>
+      <c r="E45" s="392" t="s">
         <v>701</v>
       </c>
-      <c r="F45" s="393" t="s">
+      <c r="F45" s="392" t="s">
         <v>984</v>
       </c>
-      <c r="G45" s="393" t="s">
+      <c r="G45" s="392" t="s">
         <v>710</v>
       </c>
-      <c r="H45" s="393"/>
-      <c r="I45" s="393" t="s">
+      <c r="H45" s="392"/>
+      <c r="I45" s="392" t="s">
         <v>710</v>
       </c>
-      <c r="J45" s="421"/>
+      <c r="J45" s="420"/>
       <c r="K45" s="305"/>
       <c r="L45" s="305"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A46" s="396"/>
-      <c r="B46" s="396"/>
-      <c r="C46" s="425"/>
+      <c r="A46" s="395"/>
+      <c r="B46" s="395"/>
+      <c r="C46" s="424"/>
       <c r="D46" s="312" t="s">
         <v>1002</v>
       </c>
-      <c r="E46" s="393" t="s">
+      <c r="E46" s="392" t="s">
         <v>1007</v>
       </c>
-      <c r="F46" s="393" t="s">
+      <c r="F46" s="392" t="s">
         <v>984</v>
       </c>
-      <c r="G46" s="393"/>
-      <c r="H46" s="393"/>
-      <c r="I46" s="393" t="s">
+      <c r="G46" s="392"/>
+      <c r="H46" s="392"/>
+      <c r="I46" s="392" t="s">
         <v>903</v>
       </c>
-      <c r="J46" s="421" t="s">
+      <c r="J46" s="420" t="s">
         <v>1008</v>
       </c>
       <c r="K46" s="305"/>
       <c r="L46" s="305"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A47" s="396"/>
-      <c r="B47" s="396"/>
-      <c r="C47" s="425"/>
-      <c r="E47" s="393" t="s">
+      <c r="A47" s="395"/>
+      <c r="B47" s="395"/>
+      <c r="C47" s="424"/>
+      <c r="E47" s="392" t="s">
         <v>1009</v>
       </c>
-      <c r="F47" s="393" t="s">
+      <c r="F47" s="392" t="s">
         <v>997</v>
       </c>
-      <c r="G47" s="393"/>
-      <c r="H47" s="393"/>
-      <c r="I47" s="393"/>
-      <c r="J47" s="421"/>
+      <c r="G47" s="392"/>
+      <c r="H47" s="392"/>
+      <c r="I47" s="392"/>
+      <c r="J47" s="420"/>
       <c r="K47" s="305"/>
       <c r="L47" s="305"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A48" s="396"/>
-      <c r="B48" s="396"/>
-      <c r="C48" s="425"/>
-      <c r="E48" s="393" t="s">
+      <c r="A48" s="395"/>
+      <c r="B48" s="395"/>
+      <c r="C48" s="424"/>
+      <c r="E48" s="392" t="s">
         <v>1010</v>
       </c>
-      <c r="F48" s="393" t="s">
+      <c r="F48" s="392" t="s">
         <v>997</v>
       </c>
-      <c r="G48" s="393"/>
-      <c r="H48" s="393"/>
-      <c r="I48" s="393"/>
-      <c r="J48" s="421"/>
+      <c r="G48" s="392"/>
+      <c r="H48" s="392"/>
+      <c r="I48" s="392"/>
+      <c r="J48" s="420"/>
       <c r="K48" s="305"/>
       <c r="L48" s="305"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A49" s="396"/>
-      <c r="B49" s="396"/>
-      <c r="C49" s="425"/>
-      <c r="E49" s="393" t="s">
+      <c r="A49" s="395"/>
+      <c r="B49" s="395"/>
+      <c r="C49" s="424"/>
+      <c r="E49" s="392" t="s">
         <v>730</v>
       </c>
-      <c r="F49" s="393" t="s">
+      <c r="F49" s="392" t="s">
         <v>731</v>
       </c>
-      <c r="G49" s="393"/>
-      <c r="H49" s="393"/>
-      <c r="I49" s="393"/>
-      <c r="J49" s="421"/>
+      <c r="G49" s="392"/>
+      <c r="H49" s="392"/>
+      <c r="I49" s="392"/>
+      <c r="J49" s="420"/>
       <c r="K49" s="305"/>
       <c r="L49" s="305"/>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A50" s="396"/>
-      <c r="B50" s="396"/>
-      <c r="C50" s="425"/>
-      <c r="E50" s="393" t="s">
+      <c r="A50" s="395"/>
+      <c r="B50" s="395"/>
+      <c r="C50" s="424"/>
+      <c r="E50" s="392" t="s">
         <v>739</v>
       </c>
-      <c r="F50" s="393" t="s">
+      <c r="F50" s="392" t="s">
         <v>731</v>
       </c>
-      <c r="G50" s="393"/>
-      <c r="H50" s="393"/>
-      <c r="I50" s="393"/>
-      <c r="J50" s="421"/>
+      <c r="G50" s="392"/>
+      <c r="H50" s="392"/>
+      <c r="I50" s="392"/>
+      <c r="J50" s="420"/>
       <c r="K50" s="305"/>
       <c r="L50" s="305"/>
     </row>
     <row r="51" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A51" s="396"/>
-      <c r="B51" s="396"/>
-      <c r="C51" s="426">
+      <c r="A51" s="395"/>
+      <c r="B51" s="395"/>
+      <c r="C51" s="425">
         <v>6</v>
       </c>
-      <c r="D51" s="415" t="s">
+      <c r="D51" s="414" t="s">
         <v>748</v>
       </c>
-      <c r="E51" s="416"/>
-      <c r="F51" s="416"/>
-      <c r="G51" s="416"/>
-      <c r="H51" s="416"/>
-      <c r="I51" s="416"/>
-      <c r="J51" s="417"/>
+      <c r="E51" s="415"/>
+      <c r="F51" s="415"/>
+      <c r="G51" s="415"/>
+      <c r="H51" s="415"/>
+      <c r="I51" s="415"/>
+      <c r="J51" s="416"/>
       <c r="K51" s="305"/>
       <c r="L51" s="305"/>
     </row>
     <row r="52" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A52" s="396"/>
-      <c r="B52" s="396"/>
-      <c r="C52" s="425"/>
-      <c r="E52" s="393"/>
-      <c r="F52" s="363"/>
-      <c r="G52" s="420"/>
-      <c r="H52" s="393"/>
-      <c r="I52" s="420"/>
-      <c r="J52" s="421"/>
+      <c r="A52" s="395"/>
+      <c r="B52" s="395"/>
+      <c r="C52" s="424"/>
+      <c r="E52" s="392"/>
+      <c r="F52" s="362"/>
+      <c r="G52" s="419"/>
+      <c r="H52" s="392"/>
+      <c r="I52" s="419"/>
+      <c r="J52" s="420"/>
       <c r="K52" s="305"/>
       <c r="L52" s="305"/>
     </row>
     <row r="53" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A53" s="396"/>
-      <c r="B53" s="396"/>
-      <c r="C53" s="425"/>
-      <c r="E53" s="393"/>
-      <c r="F53" s="363"/>
-      <c r="G53" s="393"/>
-      <c r="H53" s="393"/>
-      <c r="I53" s="420"/>
-      <c r="J53" s="421"/>
+      <c r="A53" s="395"/>
+      <c r="B53" s="395"/>
+      <c r="C53" s="424"/>
+      <c r="E53" s="392"/>
+      <c r="F53" s="362"/>
+      <c r="G53" s="392"/>
+      <c r="H53" s="392"/>
+      <c r="I53" s="419"/>
+      <c r="J53" s="420"/>
       <c r="K53" s="305"/>
       <c r="L53" s="305"/>
     </row>
     <row r="54" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A54" s="396"/>
-      <c r="B54" s="396"/>
-      <c r="C54" s="425"/>
+      <c r="A54" s="395"/>
+      <c r="B54" s="395"/>
+      <c r="C54" s="424"/>
       <c r="D54" s="312"/>
-      <c r="E54" s="393"/>
-      <c r="F54" s="363"/>
-      <c r="G54" s="393"/>
-      <c r="H54" s="420"/>
-      <c r="I54" s="420"/>
-      <c r="J54" s="421"/>
+      <c r="E54" s="392"/>
+      <c r="F54" s="362"/>
+      <c r="G54" s="392"/>
+      <c r="H54" s="419"/>
+      <c r="I54" s="419"/>
+      <c r="J54" s="420"/>
       <c r="K54" s="305"/>
       <c r="L54" s="305"/>
     </row>
     <row r="55" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A55" s="396"/>
-      <c r="B55" s="396"/>
-      <c r="C55" s="425"/>
-      <c r="E55" s="393"/>
-      <c r="F55" s="393"/>
-      <c r="G55" s="393"/>
-      <c r="H55" s="393"/>
-      <c r="I55" s="393"/>
-      <c r="J55" s="421"/>
+      <c r="A55" s="395"/>
+      <c r="B55" s="395"/>
+      <c r="C55" s="424"/>
+      <c r="E55" s="392"/>
+      <c r="F55" s="392"/>
+      <c r="G55" s="392"/>
+      <c r="H55" s="392"/>
+      <c r="I55" s="392"/>
+      <c r="J55" s="420"/>
       <c r="K55" s="305"/>
       <c r="L55" s="305"/>
     </row>
     <row r="56" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A56" s="396"/>
-      <c r="B56" s="396"/>
-      <c r="C56" s="425"/>
-      <c r="E56" s="393"/>
-      <c r="F56" s="393"/>
-      <c r="G56" s="393"/>
-      <c r="H56" s="393"/>
-      <c r="I56" s="393"/>
-      <c r="J56" s="421"/>
+      <c r="A56" s="395"/>
+      <c r="B56" s="395"/>
+      <c r="C56" s="424"/>
+      <c r="E56" s="392"/>
+      <c r="F56" s="392"/>
+      <c r="G56" s="392"/>
+      <c r="H56" s="392"/>
+      <c r="I56" s="392"/>
+      <c r="J56" s="420"/>
       <c r="K56" s="305"/>
       <c r="L56" s="305"/>
     </row>
     <row r="57" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A57" s="396"/>
-      <c r="B57" s="396"/>
-      <c r="C57" s="425"/>
-      <c r="E57" s="364"/>
-      <c r="F57" s="393"/>
-      <c r="G57" s="393"/>
-      <c r="H57" s="393"/>
-      <c r="I57" s="393"/>
-      <c r="J57" s="421"/>
+      <c r="A57" s="395"/>
+      <c r="B57" s="395"/>
+      <c r="C57" s="424"/>
+      <c r="E57" s="363"/>
+      <c r="F57" s="392"/>
+      <c r="G57" s="392"/>
+      <c r="H57" s="392"/>
+      <c r="I57" s="392"/>
+      <c r="J57" s="420"/>
       <c r="K57" s="305"/>
       <c r="L57" s="305"/>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A58" s="396"/>
-      <c r="B58" s="396"/>
-      <c r="C58" s="426">
+      <c r="A58" s="395"/>
+      <c r="B58" s="395"/>
+      <c r="C58" s="425">
         <v>7</v>
       </c>
-      <c r="D58" s="415" t="s">
+      <c r="D58" s="414" t="s">
         <v>748</v>
       </c>
-      <c r="E58" s="416"/>
-      <c r="F58" s="416"/>
-      <c r="G58" s="416"/>
-      <c r="H58" s="416"/>
-      <c r="I58" s="416"/>
-      <c r="J58" s="417"/>
+      <c r="E58" s="415"/>
+      <c r="F58" s="415"/>
+      <c r="G58" s="415"/>
+      <c r="H58" s="415"/>
+      <c r="I58" s="415"/>
+      <c r="J58" s="416"/>
       <c r="K58" s="305"/>
       <c r="L58" s="305"/>
     </row>
     <row r="59" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A59" s="396"/>
-      <c r="B59" s="396"/>
-      <c r="C59" s="425"/>
-      <c r="E59" s="393"/>
-      <c r="F59" s="393"/>
-      <c r="G59" s="393"/>
-      <c r="H59" s="393"/>
-      <c r="I59" s="393"/>
-      <c r="J59" s="421"/>
+      <c r="A59" s="395"/>
+      <c r="B59" s="395"/>
+      <c r="C59" s="424"/>
+      <c r="E59" s="392"/>
+      <c r="F59" s="392"/>
+      <c r="G59" s="392"/>
+      <c r="H59" s="392"/>
+      <c r="I59" s="392"/>
+      <c r="J59" s="420"/>
       <c r="K59" s="305"/>
       <c r="L59" s="305"/>
     </row>
     <row r="60" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A60" s="396"/>
-      <c r="B60" s="396"/>
-      <c r="C60" s="425"/>
+      <c r="A60" s="395"/>
+      <c r="B60" s="395"/>
+      <c r="C60" s="424"/>
       <c r="D60" s="304"/>
-      <c r="E60" s="393"/>
-      <c r="F60" s="393"/>
-      <c r="G60" s="393"/>
-      <c r="H60" s="393"/>
-      <c r="I60" s="393"/>
-      <c r="J60" s="421"/>
+      <c r="E60" s="392"/>
+      <c r="F60" s="392"/>
+      <c r="G60" s="392"/>
+      <c r="H60" s="392"/>
+      <c r="I60" s="392"/>
+      <c r="J60" s="420"/>
       <c r="K60" s="305"/>
       <c r="L60" s="305"/>
     </row>
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A61" s="396"/>
-      <c r="B61" s="396"/>
-      <c r="C61" s="425"/>
-      <c r="E61" s="393"/>
-      <c r="F61" s="393"/>
-      <c r="G61" s="393"/>
-      <c r="H61" s="393"/>
-      <c r="I61" s="393"/>
-      <c r="J61" s="421"/>
+      <c r="A61" s="395"/>
+      <c r="B61" s="395"/>
+      <c r="C61" s="424"/>
+      <c r="E61" s="392"/>
+      <c r="F61" s="392"/>
+      <c r="G61" s="392"/>
+      <c r="H61" s="392"/>
+      <c r="I61" s="392"/>
+      <c r="J61" s="420"/>
       <c r="K61" s="305"/>
       <c r="L61" s="305"/>
     </row>
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A62" s="396"/>
-      <c r="B62" s="396"/>
-      <c r="C62" s="425"/>
-      <c r="E62" s="393"/>
-      <c r="F62" s="393"/>
-      <c r="G62" s="393"/>
-      <c r="H62" s="393"/>
-      <c r="I62" s="393"/>
-      <c r="J62" s="421"/>
+      <c r="A62" s="395"/>
+      <c r="B62" s="395"/>
+      <c r="C62" s="424"/>
+      <c r="E62" s="392"/>
+      <c r="F62" s="392"/>
+      <c r="G62" s="392"/>
+      <c r="H62" s="392"/>
+      <c r="I62" s="392"/>
+      <c r="J62" s="420"/>
       <c r="K62" s="305"/>
       <c r="L62" s="305"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A63" s="396"/>
-      <c r="B63" s="396"/>
-      <c r="C63" s="425"/>
-      <c r="E63" s="393"/>
-      <c r="F63" s="393"/>
-      <c r="G63" s="393"/>
-      <c r="H63" s="393"/>
-      <c r="I63" s="393"/>
-      <c r="J63" s="421"/>
+      <c r="A63" s="395"/>
+      <c r="B63" s="395"/>
+      <c r="C63" s="424"/>
+      <c r="E63" s="392"/>
+      <c r="F63" s="392"/>
+      <c r="G63" s="392"/>
+      <c r="H63" s="392"/>
+      <c r="I63" s="392"/>
+      <c r="J63" s="420"/>
       <c r="K63" s="305"/>
       <c r="L63" s="305"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A64" s="396"/>
-      <c r="B64" s="396"/>
-      <c r="C64" s="425"/>
-      <c r="E64" s="393"/>
-      <c r="F64" s="393"/>
-      <c r="G64" s="393"/>
-      <c r="H64" s="393"/>
-      <c r="I64" s="393"/>
-      <c r="J64" s="421"/>
+      <c r="A64" s="395"/>
+      <c r="B64" s="395"/>
+      <c r="C64" s="424"/>
+      <c r="E64" s="392"/>
+      <c r="F64" s="392"/>
+      <c r="G64" s="392"/>
+      <c r="H64" s="392"/>
+      <c r="I64" s="392"/>
+      <c r="J64" s="420"/>
       <c r="K64" s="305"/>
       <c r="L64" s="305"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A65" s="396"/>
-      <c r="B65" s="396"/>
-      <c r="C65" s="425"/>
-      <c r="E65" s="393"/>
-      <c r="F65" s="393"/>
-      <c r="G65" s="393"/>
-      <c r="H65" s="393"/>
-      <c r="I65" s="393"/>
-      <c r="J65" s="421"/>
+      <c r="A65" s="395"/>
+      <c r="B65" s="395"/>
+      <c r="C65" s="424"/>
+      <c r="E65" s="392"/>
+      <c r="F65" s="392"/>
+      <c r="G65" s="392"/>
+      <c r="H65" s="392"/>
+      <c r="I65" s="392"/>
+      <c r="J65" s="420"/>
       <c r="K65" s="305"/>
       <c r="L65" s="305"/>
     </row>
     <row r="66" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A66" s="396"/>
-      <c r="B66" s="396"/>
-      <c r="C66" s="425"/>
-      <c r="E66" s="393"/>
-      <c r="F66" s="393"/>
-      <c r="G66" s="393"/>
-      <c r="H66" s="393"/>
-      <c r="I66" s="393"/>
-      <c r="J66" s="421"/>
+      <c r="A66" s="395"/>
+      <c r="B66" s="395"/>
+      <c r="C66" s="424"/>
+      <c r="E66" s="392"/>
+      <c r="F66" s="392"/>
+      <c r="G66" s="392"/>
+      <c r="H66" s="392"/>
+      <c r="I66" s="392"/>
+      <c r="J66" s="420"/>
       <c r="K66" s="305"/>
       <c r="L66" s="305"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A67" s="396"/>
-      <c r="B67" s="396"/>
-      <c r="C67" s="425"/>
-      <c r="E67" s="393"/>
-      <c r="F67" s="393"/>
-      <c r="G67" s="393"/>
-      <c r="H67" s="393"/>
-      <c r="I67" s="393"/>
-      <c r="J67" s="421"/>
+      <c r="A67" s="395"/>
+      <c r="B67" s="395"/>
+      <c r="C67" s="424"/>
+      <c r="E67" s="392"/>
+      <c r="F67" s="392"/>
+      <c r="G67" s="392"/>
+      <c r="H67" s="392"/>
+      <c r="I67" s="392"/>
+      <c r="J67" s="420"/>
       <c r="K67" s="305"/>
       <c r="L67" s="305"/>
     </row>
     <row r="68" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A68" s="396"/>
-      <c r="B68" s="396"/>
-      <c r="C68" s="425"/>
+      <c r="A68" s="395"/>
+      <c r="B68" s="395"/>
+      <c r="C68" s="424"/>
       <c r="D68" s="303"/>
-      <c r="E68" s="393"/>
-      <c r="F68" s="393"/>
-      <c r="G68" s="393"/>
-      <c r="H68" s="393"/>
-      <c r="I68" s="393"/>
-      <c r="J68" s="421"/>
+      <c r="E68" s="392"/>
+      <c r="F68" s="392"/>
+      <c r="G68" s="392"/>
+      <c r="H68" s="392"/>
+      <c r="I68" s="392"/>
+      <c r="J68" s="420"/>
       <c r="K68" s="305"/>
       <c r="L68" s="305"/>
     </row>
     <row r="69" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A69" s="396"/>
-      <c r="B69" s="396"/>
-      <c r="C69" s="425"/>
-      <c r="D69" s="427"/>
-      <c r="E69" s="440"/>
-      <c r="F69" s="440"/>
-      <c r="G69" s="440"/>
-      <c r="H69" s="440"/>
-      <c r="I69" s="440"/>
-      <c r="J69" s="441"/>
+      <c r="A69" s="395"/>
+      <c r="B69" s="395"/>
+      <c r="C69" s="424"/>
+      <c r="D69" s="426"/>
+      <c r="E69" s="439"/>
+      <c r="F69" s="439"/>
+      <c r="G69" s="439"/>
+      <c r="H69" s="439"/>
+      <c r="I69" s="439"/>
+      <c r="J69" s="440"/>
       <c r="K69" s="305"/>
       <c r="L69" s="305"/>
     </row>
     <row r="70" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A70" s="396"/>
-      <c r="B70" s="396"/>
-      <c r="C70" s="425"/>
-      <c r="D70" s="427"/>
-      <c r="E70" s="428"/>
-      <c r="F70" s="428"/>
-      <c r="G70" s="428"/>
-      <c r="H70" s="428"/>
-      <c r="I70" s="428"/>
-      <c r="J70" s="429"/>
+      <c r="A70" s="395"/>
+      <c r="B70" s="395"/>
+      <c r="C70" s="424"/>
+      <c r="D70" s="426"/>
+      <c r="E70" s="427"/>
+      <c r="F70" s="427"/>
+      <c r="G70" s="427"/>
+      <c r="H70" s="427"/>
+      <c r="I70" s="427"/>
+      <c r="J70" s="428"/>
       <c r="K70" s="305"/>
       <c r="L70" s="305"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A71" s="396"/>
-      <c r="B71" s="396"/>
-      <c r="C71" s="439"/>
-      <c r="D71" s="431"/>
-      <c r="E71" s="428"/>
-      <c r="F71" s="428"/>
-      <c r="G71" s="428"/>
-      <c r="H71" s="428"/>
-      <c r="I71" s="428"/>
-      <c r="J71" s="429"/>
+      <c r="A71" s="395"/>
+      <c r="B71" s="395"/>
+      <c r="C71" s="438"/>
+      <c r="D71" s="430"/>
+      <c r="E71" s="427"/>
+      <c r="F71" s="427"/>
+      <c r="G71" s="427"/>
+      <c r="H71" s="427"/>
+      <c r="I71" s="427"/>
+      <c r="J71" s="428"/>
       <c r="K71" s="305"/>
       <c r="L71" s="305"/>
     </row>
     <row r="72" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A72" s="396"/>
-      <c r="B72" s="396"/>
-      <c r="C72" s="426">
+      <c r="A72" s="395"/>
+      <c r="B72" s="395"/>
+      <c r="C72" s="425">
         <v>8</v>
       </c>
-      <c r="D72" s="415" t="s">
+      <c r="D72" s="414" t="s">
         <v>748</v>
       </c>
-      <c r="E72" s="416"/>
-      <c r="F72" s="416"/>
-      <c r="G72" s="416"/>
-      <c r="H72" s="416"/>
-      <c r="I72" s="416"/>
-      <c r="J72" s="417"/>
+      <c r="E72" s="415"/>
+      <c r="F72" s="415"/>
+      <c r="G72" s="415"/>
+      <c r="H72" s="415"/>
+      <c r="I72" s="415"/>
+      <c r="J72" s="416"/>
       <c r="K72" s="305"/>
       <c r="L72" s="305"/>
     </row>
     <row r="73" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A73" s="396"/>
-      <c r="B73" s="396"/>
-      <c r="C73" s="425"/>
-      <c r="E73" s="393"/>
-      <c r="F73" s="393"/>
-      <c r="G73" s="393"/>
-      <c r="H73" s="393"/>
-      <c r="I73" s="393"/>
-      <c r="J73" s="421"/>
+      <c r="A73" s="395"/>
+      <c r="B73" s="395"/>
+      <c r="C73" s="424"/>
+      <c r="E73" s="392"/>
+      <c r="F73" s="392"/>
+      <c r="G73" s="392"/>
+      <c r="H73" s="392"/>
+      <c r="I73" s="392"/>
+      <c r="J73" s="420"/>
       <c r="K73" s="305"/>
       <c r="L73" s="305"/>
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A74" s="396"/>
-      <c r="B74" s="396"/>
-      <c r="C74" s="425"/>
+      <c r="A74" s="395"/>
+      <c r="B74" s="395"/>
+      <c r="C74" s="424"/>
       <c r="D74" s="304"/>
-      <c r="E74" s="393"/>
-      <c r="F74" s="393"/>
-      <c r="G74" s="393"/>
-      <c r="H74" s="393"/>
-      <c r="I74" s="393"/>
-      <c r="J74" s="421"/>
+      <c r="E74" s="392"/>
+      <c r="F74" s="392"/>
+      <c r="G74" s="392"/>
+      <c r="H74" s="392"/>
+      <c r="I74" s="392"/>
+      <c r="J74" s="420"/>
       <c r="K74" s="305"/>
       <c r="L74" s="305"/>
     </row>
     <row r="75" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A75" s="396"/>
-      <c r="B75" s="396"/>
-      <c r="C75" s="425"/>
-      <c r="E75" s="393"/>
-      <c r="F75" s="393"/>
-      <c r="G75" s="393"/>
-      <c r="H75" s="393"/>
-      <c r="I75" s="393"/>
-      <c r="J75" s="421"/>
+      <c r="A75" s="395"/>
+      <c r="B75" s="395"/>
+      <c r="C75" s="424"/>
+      <c r="E75" s="392"/>
+      <c r="F75" s="392"/>
+      <c r="G75" s="392"/>
+      <c r="H75" s="392"/>
+      <c r="I75" s="392"/>
+      <c r="J75" s="420"/>
       <c r="K75" s="305"/>
       <c r="L75" s="305"/>
     </row>
     <row r="76" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A76" s="396"/>
-      <c r="B76" s="396"/>
-      <c r="C76" s="425"/>
-      <c r="E76" s="393"/>
-      <c r="F76" s="393"/>
-      <c r="G76" s="393"/>
-      <c r="H76" s="393"/>
-      <c r="I76" s="393"/>
-      <c r="J76" s="421"/>
+      <c r="A76" s="395"/>
+      <c r="B76" s="395"/>
+      <c r="C76" s="424"/>
+      <c r="E76" s="392"/>
+      <c r="F76" s="392"/>
+      <c r="G76" s="392"/>
+      <c r="H76" s="392"/>
+      <c r="I76" s="392"/>
+      <c r="J76" s="420"/>
       <c r="K76" s="305"/>
       <c r="L76" s="305"/>
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A77" s="396"/>
-      <c r="B77" s="396"/>
-      <c r="C77" s="425"/>
-      <c r="E77" s="393"/>
-      <c r="F77" s="393"/>
-      <c r="G77" s="393"/>
-      <c r="H77" s="393"/>
-      <c r="I77" s="393"/>
-      <c r="J77" s="421"/>
+      <c r="A77" s="395"/>
+      <c r="B77" s="395"/>
+      <c r="C77" s="424"/>
+      <c r="E77" s="392"/>
+      <c r="F77" s="392"/>
+      <c r="G77" s="392"/>
+      <c r="H77" s="392"/>
+      <c r="I77" s="392"/>
+      <c r="J77" s="420"/>
       <c r="K77" s="305"/>
       <c r="L77" s="305"/>
     </row>
     <row r="78" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A78" s="396"/>
-      <c r="B78" s="396"/>
-      <c r="C78" s="425"/>
-      <c r="E78" s="393"/>
-      <c r="F78" s="393"/>
-      <c r="G78" s="393"/>
-      <c r="H78" s="393"/>
-      <c r="I78" s="393"/>
-      <c r="J78" s="421"/>
+      <c r="A78" s="395"/>
+      <c r="B78" s="395"/>
+      <c r="C78" s="424"/>
+      <c r="E78" s="392"/>
+      <c r="F78" s="392"/>
+      <c r="G78" s="392"/>
+      <c r="H78" s="392"/>
+      <c r="I78" s="392"/>
+      <c r="J78" s="420"/>
       <c r="K78" s="305"/>
       <c r="L78" s="305"/>
     </row>
     <row r="79" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A79" s="396"/>
-      <c r="B79" s="396"/>
-      <c r="C79" s="425"/>
-      <c r="E79" s="393"/>
-      <c r="F79" s="393"/>
-      <c r="G79" s="393"/>
-      <c r="H79" s="393"/>
-      <c r="I79" s="393"/>
-      <c r="J79" s="421"/>
+      <c r="A79" s="395"/>
+      <c r="B79" s="395"/>
+      <c r="C79" s="424"/>
+      <c r="E79" s="392"/>
+      <c r="F79" s="392"/>
+      <c r="G79" s="392"/>
+      <c r="H79" s="392"/>
+      <c r="I79" s="392"/>
+      <c r="J79" s="420"/>
       <c r="K79" s="305"/>
       <c r="L79" s="305"/>
     </row>
     <row r="80" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A80" s="396"/>
-      <c r="B80" s="396"/>
-      <c r="C80" s="425"/>
-      <c r="E80" s="393"/>
-      <c r="F80" s="393"/>
-      <c r="G80" s="393"/>
-      <c r="H80" s="393"/>
-      <c r="I80" s="393"/>
-      <c r="J80" s="421"/>
+      <c r="A80" s="395"/>
+      <c r="B80" s="395"/>
+      <c r="C80" s="424"/>
+      <c r="E80" s="392"/>
+      <c r="F80" s="392"/>
+      <c r="G80" s="392"/>
+      <c r="H80" s="392"/>
+      <c r="I80" s="392"/>
+      <c r="J80" s="420"/>
       <c r="K80" s="305"/>
       <c r="L80" s="305"/>
     </row>
     <row r="81" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A81" s="396"/>
-      <c r="B81" s="396"/>
-      <c r="C81" s="425"/>
-      <c r="E81" s="393"/>
-      <c r="F81" s="393"/>
-      <c r="G81" s="393"/>
-      <c r="H81" s="393"/>
-      <c r="I81" s="393"/>
-      <c r="J81" s="421"/>
+      <c r="A81" s="395"/>
+      <c r="B81" s="395"/>
+      <c r="C81" s="424"/>
+      <c r="E81" s="392"/>
+      <c r="F81" s="392"/>
+      <c r="G81" s="392"/>
+      <c r="H81" s="392"/>
+      <c r="I81" s="392"/>
+      <c r="J81" s="420"/>
       <c r="K81" s="305"/>
       <c r="L81" s="305"/>
     </row>
     <row r="82" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A82" s="396"/>
-      <c r="B82" s="396"/>
-      <c r="C82" s="425"/>
+      <c r="A82" s="395"/>
+      <c r="B82" s="395"/>
+      <c r="C82" s="424"/>
       <c r="D82" s="303"/>
-      <c r="E82" s="393"/>
-      <c r="F82" s="393"/>
-      <c r="G82" s="393"/>
-      <c r="H82" s="393"/>
-      <c r="I82" s="393"/>
-      <c r="J82" s="421"/>
+      <c r="E82" s="392"/>
+      <c r="F82" s="392"/>
+      <c r="G82" s="392"/>
+      <c r="H82" s="392"/>
+      <c r="I82" s="392"/>
+      <c r="J82" s="420"/>
       <c r="K82" s="305"/>
       <c r="L82" s="305"/>
     </row>
     <row r="83" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A83" s="396"/>
-      <c r="B83" s="396"/>
-      <c r="C83" s="425"/>
-      <c r="D83" s="427"/>
-      <c r="E83" s="440"/>
-      <c r="F83" s="440"/>
-      <c r="G83" s="440"/>
-      <c r="H83" s="440"/>
-      <c r="I83" s="440"/>
-      <c r="J83" s="441"/>
+      <c r="A83" s="395"/>
+      <c r="B83" s="395"/>
+      <c r="C83" s="424"/>
+      <c r="D83" s="426"/>
+      <c r="E83" s="439"/>
+      <c r="F83" s="439"/>
+      <c r="G83" s="439"/>
+      <c r="H83" s="439"/>
+      <c r="I83" s="439"/>
+      <c r="J83" s="440"/>
       <c r="K83" s="305"/>
       <c r="L83" s="305"/>
     </row>
     <row r="84" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A84" s="396"/>
-      <c r="B84" s="396"/>
-      <c r="C84" s="425"/>
-      <c r="D84" s="427"/>
-      <c r="E84" s="428"/>
-      <c r="F84" s="428"/>
-      <c r="G84" s="428"/>
-      <c r="H84" s="428"/>
-      <c r="I84" s="428"/>
-      <c r="J84" s="429"/>
+      <c r="A84" s="395"/>
+      <c r="B84" s="395"/>
+      <c r="C84" s="424"/>
+      <c r="D84" s="426"/>
+      <c r="E84" s="427"/>
+      <c r="F84" s="427"/>
+      <c r="G84" s="427"/>
+      <c r="H84" s="427"/>
+      <c r="I84" s="427"/>
+      <c r="J84" s="428"/>
       <c r="K84" s="305"/>
       <c r="L84" s="305"/>
     </row>
     <row r="85" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A85" s="396"/>
-      <c r="B85" s="396"/>
-      <c r="C85" s="439"/>
-      <c r="D85" s="431"/>
-      <c r="E85" s="428"/>
-      <c r="F85" s="428"/>
-      <c r="G85" s="428"/>
-      <c r="H85" s="428"/>
-      <c r="I85" s="428"/>
-      <c r="J85" s="429"/>
+      <c r="A85" s="395"/>
+      <c r="B85" s="395"/>
+      <c r="C85" s="438"/>
+      <c r="D85" s="430"/>
+      <c r="E85" s="427"/>
+      <c r="F85" s="427"/>
+      <c r="G85" s="427"/>
+      <c r="H85" s="427"/>
+      <c r="I85" s="427"/>
+      <c r="J85" s="428"/>
       <c r="K85" s="305"/>
       <c r="L85" s="305"/>
     </row>
     <row r="86" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A86" s="396"/>
-      <c r="B86" s="396"/>
-      <c r="C86" s="442"/>
+      <c r="A86" s="395"/>
+      <c r="B86" s="395"/>
+      <c r="C86" s="441"/>
       <c r="D86" s="305"/>
       <c r="E86" s="305"/>
       <c r="F86" s="305"/>
@@ -10576,11 +10621,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="473" t="s">
+      <c r="C4" s="475" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="474"/>
-      <c r="E4" s="474"/>
+      <c r="D4" s="476"/>
+      <c r="E4" s="476"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10592,10 +10637,10 @@
       <c r="C5" s="479" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="475" t="s">
+      <c r="D5" s="477" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="476"/>
+      <c r="E5" s="478"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10605,10 +10650,10 @@
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
       <c r="C6" s="472"/>
-      <c r="D6" s="477" t="s">
+      <c r="D6" s="467" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="478"/>
+      <c r="E6" s="468"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10618,10 +10663,10 @@
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
       <c r="C7" s="472"/>
-      <c r="D7" s="477" t="s">
+      <c r="D7" s="467" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="478"/>
+      <c r="E7" s="468"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10631,10 +10676,10 @@
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
       <c r="C8" s="472"/>
-      <c r="D8" s="477" t="s">
+      <c r="D8" s="467" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="478"/>
+      <c r="E8" s="468"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10644,10 +10689,10 @@
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
       <c r="C9" s="472"/>
-      <c r="D9" s="477" t="s">
+      <c r="D9" s="467" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="478"/>
+      <c r="E9" s="468"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10656,11 +10701,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="471"/>
-      <c r="D10" s="477" t="s">
+      <c r="C10" s="473"/>
+      <c r="D10" s="467" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="478"/>
+      <c r="E10" s="468"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10669,13 +10714,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="470" t="s">
+      <c r="C11" s="474" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="477" t="s">
+      <c r="D11" s="467" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="478"/>
+      <c r="E11" s="468"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10684,11 +10729,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="471"/>
-      <c r="D12" s="477" t="s">
+      <c r="C12" s="473"/>
+      <c r="D12" s="467" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="478"/>
+      <c r="E12" s="468"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10697,13 +10742,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="470" t="s">
+      <c r="C13" s="474" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="477" t="s">
+      <c r="D13" s="467" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="478"/>
+      <c r="E13" s="468"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10713,10 +10758,10 @@
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
       <c r="C14" s="472"/>
-      <c r="D14" s="477" t="s">
+      <c r="D14" s="467" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="478"/>
+      <c r="E14" s="468"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10725,11 +10770,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="471"/>
-      <c r="D15" s="477" t="s">
+      <c r="C15" s="473"/>
+      <c r="D15" s="467" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="478"/>
+      <c r="E15" s="468"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -10738,13 +10783,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="470" t="s">
+      <c r="C16" s="474" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="482" t="s">
+      <c r="D16" s="469" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="483"/>
+      <c r="E16" s="470"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -10754,7 +10799,7 @@
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
       <c r="C17" s="472"/>
-      <c r="D17" s="481" t="s">
+      <c r="D17" s="471" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="107" t="s">
@@ -10808,7 +10853,7 @@
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
       <c r="C21" s="472"/>
-      <c r="D21" s="471"/>
+      <c r="D21" s="473"/>
       <c r="E21" s="107" t="s">
         <v>145</v>
       </c>
@@ -10875,7 +10920,7 @@
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
       <c r="C26" s="472"/>
-      <c r="D26" s="471"/>
+      <c r="D26" s="473"/>
       <c r="E26" s="127" t="s">
         <v>190</v>
       </c>
@@ -10918,7 +10963,7 @@
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
       <c r="C29" s="472"/>
-      <c r="D29" s="481" t="s">
+      <c r="D29" s="471" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="127" t="s">
@@ -10945,8 +10990,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="471"/>
-      <c r="D31" s="471"/>
+      <c r="C31" s="473"/>
+      <c r="D31" s="473"/>
       <c r="E31" s="127" t="s">
         <v>249</v>
       </c>
@@ -10958,13 +11003,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="470" t="s">
+      <c r="C32" s="474" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="477" t="s">
+      <c r="D32" s="467" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="478"/>
+      <c r="E32" s="468"/>
       <c r="F32" s="159" t="s">
         <v>259</v>
       </c>
@@ -10973,10 +11018,10 @@
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
       <c r="C33" s="472"/>
-      <c r="D33" s="477" t="s">
+      <c r="D33" s="467" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="478"/>
+      <c r="E33" s="468"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -10985,11 +11030,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="471"/>
-      <c r="D34" s="477" t="s">
+      <c r="C34" s="473"/>
+      <c r="D34" s="467" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="478"/>
+      <c r="E34" s="468"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -11006,14 +11051,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:D21"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="C16:C31"/>
@@ -11030,6 +11067,14 @@
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:D21"/>
   </mergeCells>
   <phoneticPr fontId="80"/>
   <hyperlinks>
@@ -12451,14 +12496,14 @@
       <c r="E10" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="460" t="s">
-        <v>1063</v>
+      <c r="F10" s="459" t="s">
+        <v>1062</v>
       </c>
       <c r="G10" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="H10" s="461" t="s">
-        <v>1064</v>
+      <c r="H10" s="460" t="s">
+        <v>1063</v>
       </c>
       <c r="I10" s="10"/>
     </row>
@@ -14347,7 +14392,7 @@
     <row r="71" spans="1:8" ht="26">
       <c r="A71" s="279"/>
       <c r="B71" s="279"/>
-      <c r="C71" s="484">
+      <c r="C71" s="481">
         <v>16</v>
       </c>
       <c r="D71" s="280" t="s">
@@ -14383,7 +14428,7 @@
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="279"/>
       <c r="B73" s="279"/>
-      <c r="C73" s="471"/>
+      <c r="C73" s="473"/>
       <c r="D73" s="284"/>
       <c r="E73" s="281" t="s">
         <v>745</v>
@@ -17421,7 +17466,7 @@
     <col min="7" max="7" width="13.1640625" style="306" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" style="306" customWidth="1"/>
     <col min="9" max="9" width="19.83203125" style="306" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="457" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="456" customWidth="1"/>
     <col min="11" max="16384" width="12.6640625" style="306"/>
   </cols>
   <sheetData>
@@ -17435,7 +17480,7 @@
       <c r="G1" s="305"/>
       <c r="H1" s="305"/>
       <c r="I1" s="305"/>
-      <c r="J1" s="455"/>
+      <c r="J1" s="454"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="303"/>
@@ -17447,7 +17492,7 @@
       <c r="G2" s="305"/>
       <c r="H2" s="305"/>
       <c r="I2" s="305"/>
-      <c r="J2" s="455"/>
+      <c r="J2" s="454"/>
     </row>
     <row r="3" spans="1:10" ht="27.75" customHeight="1" thickBot="1">
       <c r="A3" s="308"/>
@@ -17461,7 +17506,7 @@
       <c r="G3" s="310"/>
       <c r="H3" s="310"/>
       <c r="I3" s="310"/>
-      <c r="J3" s="456"/>
+      <c r="J3" s="455"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" thickTop="1">
       <c r="A4" s="312"/>
@@ -17475,7 +17520,7 @@
       <c r="G4" s="312"/>
       <c r="H4" s="312"/>
       <c r="I4" s="305"/>
-      <c r="J4" s="455"/>
+      <c r="J4" s="454"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="312"/>
@@ -17501,7 +17546,7 @@
       <c r="I5" s="315" t="s">
         <v>349</v>
       </c>
-      <c r="J5" s="455"/>
+      <c r="J5" s="454"/>
     </row>
     <row r="6" spans="1:10" ht="56">
       <c r="A6" s="312"/>
@@ -17527,7 +17572,7 @@
       <c r="I6" s="322" t="s">
         <v>898</v>
       </c>
-      <c r="J6" s="455"/>
+      <c r="J6" s="454"/>
     </row>
     <row r="7" spans="1:10" ht="56">
       <c r="A7" s="312"/>
@@ -17536,7 +17581,7 @@
         <v>41</v>
       </c>
       <c r="D7" s="324" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E7" s="325" t="s">
         <v>899</v>
@@ -17545,7 +17590,7 @@
         <v>896</v>
       </c>
       <c r="G7" s="327" t="s">
-        <v>897</v>
+        <v>1070</v>
       </c>
       <c r="H7" s="328" t="s">
         <v>897</v>
@@ -17553,7 +17598,9 @@
       <c r="I7" s="329" t="s">
         <v>900</v>
       </c>
-      <c r="J7" s="455"/>
+      <c r="J7" s="486" t="s">
+        <v>1071</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="154">
       <c r="A8" s="312"/>
@@ -17568,10 +17615,10 @@
         <v>895</v>
       </c>
       <c r="F8" s="331" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G8" s="332" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H8" s="333" t="s">
         <v>903</v>
@@ -17579,7 +17626,7 @@
       <c r="I8" s="334" t="s">
         <v>904</v>
       </c>
-      <c r="J8" s="455"/>
+      <c r="J8" s="454"/>
     </row>
     <row r="9" spans="1:10" ht="45">
       <c r="A9" s="312"/>
@@ -17605,7 +17652,7 @@
       <c r="I9" s="336" t="s">
         <v>906</v>
       </c>
-      <c r="J9" s="455"/>
+      <c r="J9" s="454"/>
     </row>
     <row r="10" spans="1:10" ht="45">
       <c r="A10" s="312"/>
@@ -17623,7 +17670,7 @@
         <v>907</v>
       </c>
       <c r="G10" s="335" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="H10" s="333" t="s">
         <v>903</v>
@@ -17631,7 +17678,7 @@
       <c r="I10" s="336" t="s">
         <v>908</v>
       </c>
-      <c r="J10" s="455"/>
+      <c r="J10" s="454"/>
     </row>
     <row r="11" spans="1:10" ht="45">
       <c r="A11" s="312"/>
@@ -17657,7 +17704,7 @@
       <c r="I11" s="336" t="s">
         <v>910</v>
       </c>
-      <c r="J11" s="455"/>
+      <c r="J11" s="454"/>
     </row>
     <row r="12" spans="1:10" ht="42">
       <c r="A12" s="312"/>
@@ -17672,31 +17719,31 @@
         <v>895</v>
       </c>
       <c r="F12" s="331" t="s">
-        <v>896</v>
-      </c>
-      <c r="G12" s="339" t="s">
-        <v>897</v>
+        <v>1072</v>
+      </c>
+      <c r="G12" s="484" t="s">
+        <v>1070</v>
       </c>
       <c r="H12" s="333" t="s">
         <v>897</v>
       </c>
-      <c r="I12" s="340" t="s">
+      <c r="I12" s="339" t="s">
         <v>911</v>
       </c>
-      <c r="J12" s="455" t="s">
-        <v>1037</v>
+      <c r="J12" s="485" t="s">
+        <v>1073</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="56">
       <c r="A13" s="312"/>
       <c r="B13" s="304"/>
-      <c r="C13" s="341" t="s">
+      <c r="C13" s="340" t="s">
         <v>73</v>
       </c>
       <c r="D13" s="324" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="342" t="s">
+      <c r="E13" s="341" t="s">
         <v>899</v>
       </c>
       <c r="F13" s="326" t="s">
@@ -17711,7 +17758,7 @@
       <c r="I13" s="334" t="s">
         <v>913</v>
       </c>
-      <c r="J13" s="455"/>
+      <c r="J13" s="454"/>
     </row>
     <row r="14" spans="1:10" ht="56">
       <c r="A14" s="312"/>
@@ -17722,7 +17769,7 @@
       <c r="D14" s="337" t="s">
         <v>914</v>
       </c>
-      <c r="E14" s="343" t="s">
+      <c r="E14" s="342" t="s">
         <v>899</v>
       </c>
       <c r="F14" s="326" t="s">
@@ -17737,7 +17784,7 @@
       <c r="I14" s="334" t="s">
         <v>916</v>
       </c>
-      <c r="J14" s="455"/>
+      <c r="J14" s="454"/>
     </row>
     <row r="15" spans="1:10" ht="42">
       <c r="A15" s="312"/>
@@ -17748,7 +17795,7 @@
       <c r="D15" s="324" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="344" t="s">
+      <c r="E15" s="343" t="s">
         <v>899</v>
       </c>
       <c r="F15" s="331" t="s">
@@ -17763,18 +17810,18 @@
       <c r="I15" s="334" t="s">
         <v>918</v>
       </c>
-      <c r="J15" s="455"/>
+      <c r="J15" s="454"/>
     </row>
     <row r="16" spans="1:10" ht="42">
       <c r="A16" s="312"/>
       <c r="B16" s="304"/>
-      <c r="C16" s="341" t="s">
+      <c r="C16" s="340" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="345" t="s">
+      <c r="D16" s="344" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="346" t="s">
+      <c r="E16" s="345" t="s">
         <v>899</v>
       </c>
       <c r="F16" s="331" t="s">
@@ -17789,7 +17836,7 @@
       <c r="I16" s="334" t="s">
         <v>919</v>
       </c>
-      <c r="J16" s="455"/>
+      <c r="J16" s="454"/>
     </row>
     <row r="17" spans="1:10" ht="45">
       <c r="A17" s="312"/>
@@ -17800,7 +17847,7 @@
       <c r="D17" s="324" t="s">
         <v>920</v>
       </c>
-      <c r="E17" s="346" t="s">
+      <c r="E17" s="345" t="s">
         <v>899</v>
       </c>
       <c r="F17" s="331" t="s">
@@ -17815,85 +17862,85 @@
       <c r="I17" s="336" t="s">
         <v>922</v>
       </c>
-      <c r="J17" s="455"/>
+      <c r="J17" s="454"/>
     </row>
     <row r="18" spans="1:10" ht="60">
       <c r="A18" s="312"/>
       <c r="B18" s="304"/>
-      <c r="C18" s="347" t="s">
+      <c r="C18" s="346" t="s">
         <v>107</v>
       </c>
-      <c r="D18" s="348" t="s">
+      <c r="D18" s="347" t="s">
         <v>108</v>
       </c>
-      <c r="E18" s="349" t="s">
+      <c r="E18" s="348" t="s">
         <v>923</v>
       </c>
-      <c r="F18" s="350" t="s">
+      <c r="F18" s="349" t="s">
         <v>921</v>
       </c>
-      <c r="G18" s="351" t="s">
+      <c r="G18" s="350" t="s">
         <v>924</v>
       </c>
-      <c r="H18" s="352" t="s">
+      <c r="H18" s="351" t="s">
         <v>903</v>
       </c>
-      <c r="I18" s="353" t="s">
+      <c r="I18" s="352" t="s">
         <v>925</v>
       </c>
-      <c r="J18" s="455"/>
+      <c r="J18" s="454"/>
     </row>
     <row r="19" spans="1:10" ht="45">
       <c r="A19" s="312"/>
       <c r="B19" s="304"/>
-      <c r="C19" s="354" t="s">
+      <c r="C19" s="353" t="s">
         <v>926</v>
       </c>
-      <c r="D19" s="355" t="s">
+      <c r="D19" s="354" t="s">
         <v>927</v>
       </c>
-      <c r="E19" s="356" t="s">
+      <c r="E19" s="355" t="s">
         <v>899</v>
       </c>
-      <c r="F19" s="357" t="s">
+      <c r="F19" s="356" t="s">
         <v>902</v>
       </c>
-      <c r="G19" s="358" t="s">
+      <c r="G19" s="357" t="s">
         <v>928</v>
       </c>
-      <c r="H19" s="359" t="s">
+      <c r="H19" s="358" t="s">
         <v>903</v>
       </c>
-      <c r="I19" s="360" t="s">
+      <c r="I19" s="359" t="s">
         <v>929</v>
       </c>
-      <c r="J19" s="455"/>
+      <c r="J19" s="454"/>
     </row>
     <row r="20" spans="1:10" ht="45">
       <c r="A20" s="312"/>
       <c r="B20" s="304"/>
-      <c r="C20" s="354" t="s">
+      <c r="C20" s="353" t="s">
         <v>1011</v>
       </c>
-      <c r="D20" s="355" t="s">
+      <c r="D20" s="354" t="s">
         <v>1012</v>
       </c>
-      <c r="E20" s="356" t="s">
+      <c r="E20" s="355" t="s">
         <v>897</v>
       </c>
-      <c r="F20" s="357" t="s">
+      <c r="F20" s="356" t="s">
         <v>897</v>
       </c>
-      <c r="G20" s="358" t="s">
+      <c r="G20" s="357" t="s">
         <v>897</v>
       </c>
-      <c r="H20" s="359" t="s">
+      <c r="H20" s="358" t="s">
         <v>903</v>
       </c>
-      <c r="I20" s="360" t="s">
+      <c r="I20" s="359" t="s">
         <v>1013</v>
       </c>
-      <c r="J20" s="455"/>
+      <c r="J20" s="454"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="312"/>
@@ -17905,7 +17952,7 @@
       <c r="G21" s="312"/>
       <c r="H21" s="312"/>
       <c r="I21" s="305"/>
-      <c r="J21" s="455"/>
+      <c r="J21" s="454"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="312"/>
@@ -17919,15 +17966,15 @@
       <c r="G22" s="312"/>
       <c r="H22" s="312"/>
       <c r="I22" s="305"/>
-      <c r="J22" s="455"/>
+      <c r="J22" s="454"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="312"/>
       <c r="B23" s="304"/>
-      <c r="C23" s="361" t="s">
+      <c r="C23" s="360" t="s">
         <v>600</v>
       </c>
-      <c r="D23" s="362" t="s">
+      <c r="D23" s="361" t="s">
         <v>349</v>
       </c>
       <c r="E23" s="312"/>
@@ -17935,15 +17982,15 @@
       <c r="G23" s="312"/>
       <c r="H23" s="312"/>
       <c r="I23" s="305"/>
-      <c r="J23" s="455"/>
+      <c r="J23" s="454"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="312"/>
       <c r="B24" s="304"/>
-      <c r="C24" s="363" t="s">
+      <c r="C24" s="362" t="s">
         <v>930</v>
       </c>
-      <c r="D24" s="364" t="s">
+      <c r="D24" s="363" t="s">
         <v>931</v>
       </c>
       <c r="E24" s="312"/>
@@ -17951,15 +17998,15 @@
       <c r="G24" s="312"/>
       <c r="H24" s="312"/>
       <c r="I24" s="305"/>
-      <c r="J24" s="455"/>
+      <c r="J24" s="454"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="312"/>
       <c r="B25" s="304"/>
-      <c r="C25" s="366" t="s">
+      <c r="C25" s="365" t="s">
         <v>932</v>
       </c>
-      <c r="D25" s="364" t="s">
+      <c r="D25" s="363" t="s">
         <v>933</v>
       </c>
       <c r="E25" s="312"/>
@@ -17967,15 +18014,15 @@
       <c r="G25" s="312"/>
       <c r="H25" s="312"/>
       <c r="I25" s="305"/>
-      <c r="J25" s="455"/>
+      <c r="J25" s="454"/>
     </row>
     <row r="26" spans="1:10" ht="16.5" customHeight="1">
       <c r="A26" s="312"/>
       <c r="B26" s="304"/>
-      <c r="C26" s="366" t="s">
+      <c r="C26" s="365" t="s">
         <v>1027</v>
       </c>
-      <c r="D26" s="365" t="s">
+      <c r="D26" s="364" t="s">
         <v>934</v>
       </c>
       <c r="E26" s="312"/>
@@ -17983,15 +18030,15 @@
       <c r="G26" s="312"/>
       <c r="H26" s="312"/>
       <c r="I26" s="305"/>
-      <c r="J26" s="455"/>
+      <c r="J26" s="454"/>
     </row>
     <row r="27" spans="1:10" ht="17.25" customHeight="1">
       <c r="A27" s="312"/>
       <c r="B27" s="304"/>
-      <c r="C27" s="366" t="s">
+      <c r="C27" s="365" t="s">
         <v>935</v>
       </c>
-      <c r="D27" s="365" t="s">
+      <c r="D27" s="364" t="s">
         <v>936</v>
       </c>
       <c r="E27" s="312"/>
@@ -17999,15 +18046,15 @@
       <c r="G27" s="312"/>
       <c r="H27" s="312"/>
       <c r="I27" s="305"/>
-      <c r="J27" s="455"/>
+      <c r="J27" s="454"/>
     </row>
     <row r="28" spans="1:10" ht="14.25" customHeight="1">
       <c r="A28" s="312"/>
       <c r="B28" s="304"/>
-      <c r="C28" s="451" t="s">
+      <c r="C28" s="450" t="s">
         <v>1035</v>
       </c>
-      <c r="D28" s="365" t="s">
+      <c r="D28" s="364" t="s">
         <v>937</v>
       </c>
       <c r="E28" s="312"/>
@@ -18015,7 +18062,7 @@
       <c r="G28" s="312"/>
       <c r="H28" s="312"/>
       <c r="I28" s="305"/>
-      <c r="J28" s="455"/>
+      <c r="J28" s="454"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="312"/>
@@ -18027,7 +18074,7 @@
       <c r="G29" s="312"/>
       <c r="H29" s="312"/>
       <c r="I29" s="305"/>
-      <c r="J29" s="455"/>
+      <c r="J29" s="454"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="312"/>
@@ -18035,21 +18082,21 @@
         <v>670</v>
       </c>
       <c r="C30" s="312"/>
-      <c r="D30" s="367"/>
+      <c r="D30" s="366"/>
       <c r="E30" s="312"/>
       <c r="F30" s="312"/>
       <c r="G30" s="312"/>
       <c r="H30" s="312"/>
       <c r="I30" s="305"/>
-      <c r="J30" s="455"/>
+      <c r="J30" s="454"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="312"/>
       <c r="B31" s="304"/>
-      <c r="C31" s="368" t="s">
+      <c r="C31" s="367" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="369" t="s">
+      <c r="D31" s="368" t="s">
         <v>682</v>
       </c>
       <c r="E31" s="312"/>
@@ -18057,271 +18104,271 @@
       <c r="G31" s="312"/>
       <c r="H31" s="312"/>
       <c r="I31" s="305"/>
-      <c r="J31" s="455"/>
+      <c r="J31" s="454"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="312"/>
       <c r="B32" s="304"/>
-      <c r="C32" s="443" t="s">
+      <c r="C32" s="442" t="s">
         <v>1014</v>
       </c>
-      <c r="D32" s="370" t="s">
-        <v>1044</v>
+      <c r="D32" s="369" t="s">
+        <v>1043</v>
       </c>
       <c r="E32" s="312"/>
       <c r="F32" s="312"/>
       <c r="G32" s="312"/>
       <c r="H32" s="312"/>
       <c r="I32" s="305"/>
-      <c r="J32" s="455"/>
+      <c r="J32" s="454"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="312"/>
       <c r="B33" s="304"/>
-      <c r="C33" s="371" t="s">
+      <c r="C33" s="370" t="s">
         <v>938</v>
       </c>
-      <c r="D33" s="370" t="s">
-        <v>1045</v>
+      <c r="D33" s="369" t="s">
+        <v>1044</v>
       </c>
       <c r="E33" s="312"/>
       <c r="F33" s="312"/>
       <c r="G33" s="312"/>
       <c r="H33" s="312"/>
       <c r="I33" s="305"/>
-      <c r="J33" s="455"/>
+      <c r="J33" s="454"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="312"/>
       <c r="B34" s="304"/>
-      <c r="C34" s="371" t="s">
+      <c r="C34" s="370" t="s">
         <v>901</v>
       </c>
-      <c r="D34" s="370" t="s">
-        <v>1046</v>
+      <c r="D34" s="369" t="s">
+        <v>1045</v>
       </c>
       <c r="E34" s="312"/>
       <c r="F34" s="312"/>
       <c r="G34" s="312"/>
       <c r="H34" s="312"/>
       <c r="I34" s="305"/>
-      <c r="J34" s="455"/>
+      <c r="J34" s="454"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="312"/>
       <c r="B35" s="304"/>
-      <c r="C35" s="371" t="s">
+      <c r="C35" s="370" t="s">
         <v>1015</v>
       </c>
-      <c r="D35" s="370" t="s">
-        <v>1047</v>
+      <c r="D35" s="369" t="s">
+        <v>1046</v>
       </c>
       <c r="E35" s="312"/>
       <c r="F35" s="312"/>
       <c r="G35" s="312"/>
       <c r="H35" s="312"/>
       <c r="I35" s="305"/>
-      <c r="J35" s="455"/>
+      <c r="J35" s="454"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
       <c r="A36" s="312"/>
       <c r="B36" s="304"/>
-      <c r="C36" s="371" t="s">
+      <c r="C36" s="370" t="s">
         <v>1016</v>
       </c>
-      <c r="D36" s="372" t="s">
-        <v>1048</v>
+      <c r="D36" s="371" t="s">
+        <v>1047</v>
       </c>
       <c r="E36" s="312"/>
       <c r="F36" s="312"/>
       <c r="G36" s="312"/>
       <c r="H36" s="312"/>
       <c r="I36" s="305"/>
-      <c r="J36" s="455"/>
+      <c r="J36" s="454"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
       <c r="A37" s="312"/>
       <c r="B37" s="304"/>
-      <c r="C37" s="371" t="s">
+      <c r="C37" s="370" t="s">
         <v>1017</v>
       </c>
-      <c r="D37" s="370" t="s">
-        <v>1049</v>
+      <c r="D37" s="369" t="s">
+        <v>1048</v>
       </c>
       <c r="E37" s="312"/>
       <c r="F37" s="312"/>
       <c r="G37" s="312"/>
       <c r="H37" s="312"/>
       <c r="I37" s="305"/>
-      <c r="J37" s="455"/>
+      <c r="J37" s="454"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
       <c r="A38" s="312"/>
       <c r="B38" s="304"/>
-      <c r="C38" s="371" t="s">
+      <c r="C38" s="370" t="s">
         <v>1018</v>
       </c>
-      <c r="D38" s="370" t="s">
-        <v>1050</v>
+      <c r="D38" s="369" t="s">
+        <v>1049</v>
       </c>
       <c r="E38" s="312"/>
       <c r="F38" s="312"/>
       <c r="G38" s="312"/>
       <c r="H38" s="312"/>
       <c r="I38" s="305"/>
-      <c r="J38" s="455"/>
+      <c r="J38" s="454"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
       <c r="A39" s="312"/>
       <c r="B39" s="304"/>
-      <c r="C39" s="444" t="s">
+      <c r="C39" s="443" t="s">
         <v>1019</v>
       </c>
-      <c r="D39" s="370" t="s">
-        <v>1051</v>
+      <c r="D39" s="369" t="s">
+        <v>1050</v>
       </c>
       <c r="E39" s="312"/>
       <c r="F39" s="312"/>
       <c r="G39" s="312"/>
       <c r="H39" s="312"/>
       <c r="I39" s="305"/>
-      <c r="J39" s="455"/>
+      <c r="J39" s="454"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
       <c r="A40" s="312"/>
       <c r="B40" s="304"/>
-      <c r="C40" s="371" t="s">
+      <c r="C40" s="370" t="s">
         <v>1020</v>
       </c>
-      <c r="D40" s="372" t="s">
-        <v>1052</v>
+      <c r="D40" s="371" t="s">
+        <v>1051</v>
       </c>
       <c r="E40" s="312"/>
       <c r="F40" s="312"/>
       <c r="G40" s="312"/>
       <c r="H40" s="312"/>
       <c r="I40" s="305"/>
-      <c r="J40" s="455"/>
+      <c r="J40" s="454"/>
     </row>
     <row r="41" spans="1:10" ht="15.75" customHeight="1">
       <c r="A41" s="312"/>
       <c r="B41" s="304"/>
-      <c r="C41" s="371" t="s">
+      <c r="C41" s="370" t="s">
         <v>1021</v>
       </c>
-      <c r="D41" s="370" t="s">
-        <v>1053</v>
+      <c r="D41" s="369" t="s">
+        <v>1052</v>
       </c>
       <c r="E41" s="312"/>
       <c r="F41" s="312"/>
       <c r="G41" s="312"/>
       <c r="H41" s="312"/>
       <c r="I41" s="305"/>
-      <c r="J41" s="455"/>
+      <c r="J41" s="454"/>
     </row>
     <row r="42" spans="1:10" ht="15.75" customHeight="1">
       <c r="A42" s="312"/>
       <c r="B42" s="304"/>
-      <c r="C42" s="444" t="s">
+      <c r="C42" s="443" t="s">
         <v>1022</v>
       </c>
-      <c r="D42" s="373" t="s">
-        <v>1054</v>
+      <c r="D42" s="372" t="s">
+        <v>1053</v>
       </c>
       <c r="E42" s="312"/>
       <c r="F42" s="312"/>
       <c r="G42" s="312"/>
       <c r="H42" s="312"/>
       <c r="I42" s="305"/>
-      <c r="J42" s="455"/>
+      <c r="J42" s="454"/>
     </row>
     <row r="43" spans="1:10" ht="15.75" customHeight="1">
       <c r="A43" s="312"/>
       <c r="B43" s="304"/>
-      <c r="C43" s="371" t="s">
+      <c r="C43" s="370" t="s">
         <v>1023</v>
       </c>
-      <c r="D43" s="370" t="s">
-        <v>1055</v>
+      <c r="D43" s="369" t="s">
+        <v>1054</v>
       </c>
       <c r="E43" s="312"/>
       <c r="F43" s="312"/>
       <c r="G43" s="312"/>
       <c r="H43" s="312"/>
       <c r="I43" s="305"/>
-      <c r="J43" s="455"/>
+      <c r="J43" s="454"/>
     </row>
     <row r="44" spans="1:10" ht="28">
       <c r="A44" s="312"/>
       <c r="B44" s="304"/>
-      <c r="C44" s="371" t="s">
+      <c r="C44" s="370" t="s">
         <v>1024</v>
       </c>
-      <c r="D44" s="370" t="s">
-        <v>1056</v>
+      <c r="D44" s="369" t="s">
+        <v>1055</v>
       </c>
       <c r="E44" s="312"/>
       <c r="F44" s="312"/>
       <c r="G44" s="312"/>
       <c r="H44" s="312"/>
       <c r="I44" s="305"/>
-      <c r="J44" s="455"/>
+      <c r="J44" s="454"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="312"/>
       <c r="B45" s="304"/>
-      <c r="C45" s="459" t="s">
+      <c r="C45" s="458" t="s">
         <v>1011</v>
       </c>
-      <c r="D45" s="373" t="s">
-        <v>1057</v>
+      <c r="D45" s="372" t="s">
+        <v>1056</v>
       </c>
       <c r="E45" s="312"/>
       <c r="F45" s="312"/>
       <c r="G45" s="312"/>
       <c r="H45" s="312"/>
       <c r="I45" s="305"/>
-      <c r="J45" s="455"/>
+      <c r="J45" s="454"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="312"/>
       <c r="B46" s="304"/>
-      <c r="C46" s="459" t="s">
-        <v>1058</v>
-      </c>
-      <c r="D46" s="373" t="s">
-        <v>1060</v>
+      <c r="C46" s="458" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D46" s="372" t="s">
+        <v>1059</v>
       </c>
       <c r="E46" s="312"/>
       <c r="F46" s="312"/>
       <c r="G46" s="312"/>
       <c r="H46" s="312"/>
       <c r="I46" s="305"/>
-      <c r="J46" s="455"/>
+      <c r="J46" s="454"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="312"/>
       <c r="B47" s="304"/>
-      <c r="C47" s="459" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D47" s="373" t="s">
-        <v>1061</v>
+      <c r="C47" s="458" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D47" s="372" t="s">
+        <v>1060</v>
       </c>
       <c r="E47" s="312"/>
       <c r="F47" s="312"/>
       <c r="G47" s="312"/>
       <c r="H47" s="312"/>
       <c r="I47" s="305"/>
-      <c r="J47" s="455"/>
+      <c r="J47" s="454"/>
     </row>
     <row r="48" spans="1:10" ht="15.75" customHeight="1">
       <c r="A48" s="312"/>
       <c r="B48" s="304"/>
-      <c r="C48" s="445" t="s">
+      <c r="C48" s="444" t="s">
         <v>926</v>
       </c>
-      <c r="D48" s="446" t="s">
+      <c r="D48" s="445" t="s">
         <v>939</v>
       </c>
       <c r="E48" s="312"/>
@@ -18329,15 +18376,15 @@
       <c r="G48" s="312"/>
       <c r="H48" s="312"/>
       <c r="I48" s="305"/>
-      <c r="J48" s="455"/>
+      <c r="J48" s="454"/>
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1">
       <c r="A49" s="312"/>
       <c r="B49" s="304"/>
-      <c r="C49" s="447" t="s">
+      <c r="C49" s="446" t="s">
         <v>1011</v>
       </c>
-      <c r="D49" s="448" t="s">
+      <c r="D49" s="447" t="s">
         <v>1025</v>
       </c>
       <c r="E49" s="312"/>
@@ -18345,7 +18392,7 @@
       <c r="G49" s="312"/>
       <c r="H49" s="312"/>
       <c r="I49" s="305"/>
-      <c r="J49" s="455"/>
+      <c r="J49" s="454"/>
     </row>
     <row r="50" spans="1:10" ht="15.75" customHeight="1">
       <c r="A50" s="312"/>
@@ -18353,11 +18400,11 @@
       <c r="C50" s="312"/>
       <c r="D50" s="312"/>
       <c r="E50" s="312"/>
-      <c r="F50" s="367"/>
+      <c r="F50" s="366"/>
       <c r="G50" s="312"/>
       <c r="H50" s="312"/>
       <c r="I50" s="305"/>
-      <c r="J50" s="455"/>
+      <c r="J50" s="454"/>
     </row>
     <row r="51" spans="1:10" ht="15.75" customHeight="1">
       <c r="A51" s="312"/>
@@ -18367,451 +18414,451 @@
       <c r="C51" s="312"/>
       <c r="D51" s="312"/>
       <c r="E51" s="312"/>
-      <c r="F51" s="367"/>
+      <c r="F51" s="366"/>
       <c r="G51" s="312"/>
       <c r="H51" s="312"/>
       <c r="I51" s="305"/>
-      <c r="J51" s="455"/>
+      <c r="J51" s="454"/>
     </row>
     <row r="52" spans="1:10" ht="15.75" customHeight="1">
       <c r="A52" s="312"/>
       <c r="B52" s="304"/>
-      <c r="C52" s="374" t="s">
+      <c r="C52" s="373" t="s">
         <v>732</v>
       </c>
-      <c r="D52" s="368" t="s">
+      <c r="D52" s="367" t="s">
         <v>734</v>
       </c>
-      <c r="E52" s="368" t="s">
+      <c r="E52" s="367" t="s">
         <v>736</v>
       </c>
-      <c r="F52" s="375"/>
+      <c r="F52" s="374"/>
       <c r="H52" s="312"/>
       <c r="I52" s="305"/>
-      <c r="J52" s="455"/>
+      <c r="J52" s="454"/>
     </row>
     <row r="53" spans="1:10" ht="15.75" customHeight="1">
       <c r="A53" s="312"/>
       <c r="B53" s="304"/>
-      <c r="C53" s="376" t="s">
+      <c r="C53" s="375" t="s">
         <v>940</v>
       </c>
-      <c r="D53" s="377" t="s">
+      <c r="D53" s="376" t="s">
         <v>941</v>
       </c>
-      <c r="E53" s="378" t="s">
+      <c r="E53" s="377" t="s">
         <v>942</v>
       </c>
-      <c r="F53" s="379"/>
+      <c r="F53" s="378"/>
       <c r="H53" s="312"/>
       <c r="I53" s="305"/>
-      <c r="J53" s="455"/>
+      <c r="J53" s="454"/>
     </row>
     <row r="54" spans="1:10" ht="15.75" customHeight="1">
       <c r="A54" s="312"/>
       <c r="B54" s="304"/>
-      <c r="C54" s="380"/>
-      <c r="D54" s="381" t="s">
+      <c r="C54" s="379"/>
+      <c r="D54" s="380" t="s">
         <v>943</v>
       </c>
-      <c r="E54" s="382" t="s">
+      <c r="E54" s="381" t="s">
         <v>944</v>
       </c>
-      <c r="F54" s="383"/>
+      <c r="F54" s="382"/>
       <c r="H54" s="312"/>
       <c r="I54" s="305"/>
-      <c r="J54" s="455"/>
+      <c r="J54" s="454"/>
     </row>
     <row r="55" spans="1:10" ht="15.75" customHeight="1">
       <c r="A55" s="312"/>
       <c r="B55" s="304"/>
-      <c r="C55" s="376" t="s">
+      <c r="C55" s="375" t="s">
         <v>945</v>
       </c>
-      <c r="D55" s="377" t="s">
+      <c r="D55" s="376" t="s">
         <v>941</v>
       </c>
-      <c r="E55" s="378" t="s">
+      <c r="E55" s="377" t="s">
         <v>942</v>
       </c>
-      <c r="F55" s="379"/>
+      <c r="F55" s="378"/>
       <c r="H55" s="312"/>
       <c r="I55" s="305"/>
-      <c r="J55" s="455"/>
+      <c r="J55" s="454"/>
     </row>
     <row r="56" spans="1:10" ht="15.75" customHeight="1">
       <c r="A56" s="312"/>
       <c r="B56" s="304"/>
-      <c r="C56" s="380"/>
-      <c r="D56" s="381" t="s">
+      <c r="C56" s="379"/>
+      <c r="D56" s="380" t="s">
         <v>943</v>
       </c>
-      <c r="E56" s="382" t="s">
+      <c r="E56" s="381" t="s">
         <v>944</v>
       </c>
-      <c r="F56" s="383"/>
+      <c r="F56" s="382"/>
       <c r="H56" s="312"/>
       <c r="I56" s="305"/>
-      <c r="J56" s="455"/>
+      <c r="J56" s="454"/>
     </row>
     <row r="57" spans="1:10" ht="15.75" customHeight="1">
       <c r="A57" s="312"/>
       <c r="B57" s="304"/>
-      <c r="C57" s="384" t="s">
+      <c r="C57" s="383" t="s">
         <v>946</v>
       </c>
-      <c r="D57" s="381" t="s">
+      <c r="D57" s="380" t="s">
         <v>947</v>
       </c>
-      <c r="E57" s="385" t="s">
+      <c r="E57" s="384" t="s">
         <v>948</v>
       </c>
-      <c r="F57" s="383"/>
+      <c r="F57" s="382"/>
       <c r="H57" s="312"/>
       <c r="I57" s="305"/>
-      <c r="J57" s="455"/>
+      <c r="J57" s="454"/>
     </row>
     <row r="58" spans="1:10" ht="15.75" customHeight="1">
       <c r="A58" s="312"/>
       <c r="B58" s="304"/>
-      <c r="C58" s="376"/>
-      <c r="D58" s="386" t="s">
+      <c r="C58" s="375"/>
+      <c r="D58" s="385" t="s">
         <v>941</v>
       </c>
-      <c r="E58" s="385" t="s">
+      <c r="E58" s="384" t="s">
         <v>949</v>
       </c>
-      <c r="F58" s="383"/>
+      <c r="F58" s="382"/>
       <c r="H58" s="312"/>
       <c r="I58" s="305"/>
-      <c r="J58" s="455"/>
+      <c r="J58" s="454"/>
     </row>
     <row r="59" spans="1:10" ht="15.75" customHeight="1">
       <c r="A59" s="312"/>
       <c r="B59" s="304"/>
-      <c r="C59" s="387"/>
-      <c r="D59" s="381" t="s">
+      <c r="C59" s="386"/>
+      <c r="D59" s="380" t="s">
         <v>943</v>
       </c>
-      <c r="E59" s="388" t="s">
+      <c r="E59" s="387" t="s">
         <v>950</v>
       </c>
-      <c r="F59" s="383"/>
+      <c r="F59" s="382"/>
       <c r="H59" s="312"/>
       <c r="I59" s="305"/>
-      <c r="J59" s="455"/>
+      <c r="J59" s="454"/>
     </row>
     <row r="60" spans="1:10" ht="15.75" customHeight="1">
       <c r="A60" s="312"/>
       <c r="B60" s="304"/>
-      <c r="C60" s="384" t="s">
+      <c r="C60" s="383" t="s">
         <v>951</v>
       </c>
-      <c r="D60" s="377" t="s">
+      <c r="D60" s="376" t="s">
         <v>952</v>
       </c>
-      <c r="E60" s="466" t="s">
-        <v>1065</v>
-      </c>
-      <c r="F60" s="383"/>
+      <c r="E60" s="465" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F60" s="382"/>
       <c r="H60" s="312"/>
       <c r="I60" s="305"/>
-      <c r="J60" s="455"/>
+      <c r="J60" s="454"/>
     </row>
     <row r="61" spans="1:10" ht="15.75" customHeight="1">
       <c r="A61" s="312"/>
       <c r="B61" s="304"/>
-      <c r="C61" s="376"/>
-      <c r="D61" s="386" t="s">
+      <c r="C61" s="375"/>
+      <c r="D61" s="385" t="s">
         <v>953</v>
       </c>
-      <c r="E61" s="467" t="s">
-        <v>1066</v>
-      </c>
-      <c r="F61" s="383"/>
+      <c r="E61" s="466" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F61" s="382"/>
       <c r="H61" s="312"/>
       <c r="I61" s="305"/>
-      <c r="J61" s="455"/>
+      <c r="J61" s="454"/>
     </row>
     <row r="62" spans="1:10" ht="15.75" customHeight="1">
       <c r="A62" s="312"/>
       <c r="B62" s="304"/>
-      <c r="C62" s="376"/>
-      <c r="D62" s="377" t="s">
+      <c r="C62" s="375"/>
+      <c r="D62" s="376" t="s">
         <v>954</v>
       </c>
-      <c r="E62" s="464" t="s">
-        <v>1069</v>
-      </c>
-      <c r="F62" s="383"/>
+      <c r="E62" s="463" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F62" s="382"/>
       <c r="H62" s="312"/>
       <c r="I62" s="305"/>
-      <c r="J62" s="455"/>
+      <c r="J62" s="454"/>
     </row>
     <row r="63" spans="1:10" ht="15.75" customHeight="1">
       <c r="A63" s="312"/>
       <c r="B63" s="304"/>
-      <c r="C63" s="376"/>
-      <c r="D63" s="377" t="s">
+      <c r="C63" s="375"/>
+      <c r="D63" s="376" t="s">
         <v>956</v>
       </c>
-      <c r="E63" s="465" t="s">
-        <v>1070</v>
-      </c>
-      <c r="F63" s="383"/>
+      <c r="E63" s="464" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F63" s="382"/>
       <c r="H63" s="312"/>
       <c r="I63" s="305"/>
-      <c r="J63" s="455"/>
+      <c r="J63" s="454"/>
     </row>
     <row r="64" spans="1:10" ht="15.75" customHeight="1">
       <c r="A64" s="312"/>
       <c r="B64" s="304"/>
-      <c r="C64" s="380"/>
-      <c r="D64" s="377" t="s">
+      <c r="C64" s="379"/>
+      <c r="D64" s="376" t="s">
         <v>716</v>
       </c>
-      <c r="E64" s="385" t="s">
+      <c r="E64" s="384" t="s">
         <v>958</v>
       </c>
-      <c r="F64" s="379"/>
+      <c r="F64" s="378"/>
       <c r="H64" s="312"/>
       <c r="I64" s="305"/>
-      <c r="J64" s="455"/>
+      <c r="J64" s="454"/>
     </row>
     <row r="65" spans="1:10" ht="15.75" customHeight="1">
       <c r="A65" s="312"/>
       <c r="B65" s="304"/>
-      <c r="C65" s="458" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D65" s="389" t="s">
+      <c r="C65" s="457" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D65" s="388" t="s">
         <v>959</v>
       </c>
-      <c r="E65" s="463" t="s">
-        <v>1067</v>
-      </c>
-      <c r="F65" s="383"/>
+      <c r="E65" s="462" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F65" s="382"/>
       <c r="H65" s="312"/>
       <c r="I65" s="305"/>
-      <c r="J65" s="455"/>
+      <c r="J65" s="454"/>
     </row>
     <row r="66" spans="1:10" ht="15.75" customHeight="1">
       <c r="A66" s="312"/>
       <c r="B66" s="304"/>
-      <c r="C66" s="376"/>
-      <c r="D66" s="381" t="s">
+      <c r="C66" s="375"/>
+      <c r="D66" s="380" t="s">
         <v>961</v>
       </c>
-      <c r="E66" s="390" t="s">
-        <v>1068</v>
-      </c>
-      <c r="F66" s="383"/>
+      <c r="E66" s="389" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F66" s="382"/>
       <c r="H66" s="312"/>
       <c r="I66" s="305"/>
-      <c r="J66" s="455"/>
+      <c r="J66" s="454"/>
     </row>
     <row r="67" spans="1:10" ht="15.75" customHeight="1">
       <c r="A67" s="312"/>
       <c r="B67" s="304"/>
-      <c r="C67" s="391"/>
-      <c r="D67" s="392" t="s">
+      <c r="C67" s="390"/>
+      <c r="D67" s="391" t="s">
         <v>962</v>
       </c>
-      <c r="E67" s="393" t="s">
+      <c r="E67" s="392" t="s">
         <v>955</v>
       </c>
-      <c r="F67" s="383"/>
+      <c r="F67" s="382"/>
       <c r="H67" s="312"/>
       <c r="I67" s="305"/>
-      <c r="J67" s="455"/>
+      <c r="J67" s="454"/>
     </row>
     <row r="68" spans="1:10" ht="13">
       <c r="A68" s="312"/>
       <c r="B68" s="304"/>
-      <c r="C68" s="394"/>
-      <c r="D68" s="381" t="s">
+      <c r="C68" s="393"/>
+      <c r="D68" s="380" t="s">
         <v>963</v>
       </c>
-      <c r="E68" s="462" t="s">
+      <c r="E68" s="461" t="s">
         <v>957</v>
       </c>
-      <c r="F68" s="383"/>
+      <c r="F68" s="382"/>
       <c r="H68" s="312"/>
       <c r="I68" s="305"/>
-      <c r="J68" s="455"/>
+      <c r="J68" s="454"/>
     </row>
     <row r="69" spans="1:10" ht="15.75" customHeight="1">
       <c r="A69" s="312"/>
       <c r="B69" s="304"/>
-      <c r="C69" s="395"/>
-      <c r="D69" s="377" t="s">
+      <c r="C69" s="394"/>
+      <c r="D69" s="376" t="s">
         <v>716</v>
       </c>
-      <c r="E69" s="377" t="s">
+      <c r="E69" s="376" t="s">
         <v>958</v>
       </c>
-      <c r="F69" s="396"/>
+      <c r="F69" s="395"/>
       <c r="H69" s="312"/>
       <c r="I69" s="305"/>
-      <c r="J69" s="455"/>
+      <c r="J69" s="454"/>
     </row>
     <row r="70" spans="1:10" ht="15.75" customHeight="1">
       <c r="A70" s="312"/>
       <c r="B70" s="304"/>
-      <c r="C70" s="397" t="s">
+      <c r="C70" s="396" t="s">
         <v>964</v>
       </c>
-      <c r="D70" s="398" t="s">
+      <c r="D70" s="397" t="s">
         <v>965</v>
       </c>
-      <c r="E70" s="398" t="s">
+      <c r="E70" s="397" t="s">
         <v>966</v>
       </c>
-      <c r="F70" s="396"/>
+      <c r="F70" s="395"/>
       <c r="H70" s="312"/>
       <c r="I70" s="305"/>
-      <c r="J70" s="455"/>
+      <c r="J70" s="454"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1">
       <c r="A71" s="312"/>
       <c r="B71" s="304"/>
-      <c r="C71" s="394"/>
-      <c r="D71" s="398" t="s">
+      <c r="C71" s="393"/>
+      <c r="D71" s="397" t="s">
         <v>967</v>
       </c>
-      <c r="E71" s="398" t="s">
+      <c r="E71" s="397" t="s">
         <v>968</v>
       </c>
-      <c r="F71" s="396"/>
+      <c r="F71" s="395"/>
       <c r="H71" s="312"/>
       <c r="I71" s="305"/>
-      <c r="J71" s="455"/>
+      <c r="J71" s="454"/>
     </row>
     <row r="72" spans="1:10" ht="15.75" customHeight="1">
       <c r="A72" s="312"/>
       <c r="B72" s="304"/>
-      <c r="C72" s="394"/>
-      <c r="D72" s="398" t="s">
+      <c r="C72" s="393"/>
+      <c r="D72" s="397" t="s">
         <v>969</v>
       </c>
-      <c r="E72" s="398" t="s">
+      <c r="E72" s="397" t="s">
         <v>970</v>
       </c>
-      <c r="F72" s="396"/>
+      <c r="F72" s="395"/>
       <c r="H72" s="312"/>
       <c r="I72" s="305"/>
-      <c r="J72" s="455"/>
+      <c r="J72" s="454"/>
     </row>
     <row r="73" spans="1:10" ht="15.75" customHeight="1">
       <c r="A73" s="312"/>
       <c r="B73" s="304"/>
-      <c r="C73" s="394"/>
-      <c r="D73" s="398" t="s">
+      <c r="C73" s="393"/>
+      <c r="D73" s="397" t="s">
         <v>971</v>
       </c>
-      <c r="E73" s="398" t="s">
+      <c r="E73" s="397" t="s">
         <v>966</v>
       </c>
-      <c r="F73" s="396"/>
+      <c r="F73" s="395"/>
       <c r="H73" s="312"/>
       <c r="I73" s="305"/>
-      <c r="J73" s="455"/>
+      <c r="J73" s="454"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" customHeight="1">
       <c r="A74" s="312"/>
       <c r="B74" s="304"/>
-      <c r="C74" s="394"/>
-      <c r="D74" s="399" t="s">
+      <c r="C74" s="393"/>
+      <c r="D74" s="398" t="s">
         <v>972</v>
       </c>
-      <c r="E74" s="399" t="s">
+      <c r="E74" s="398" t="s">
         <v>973</v>
       </c>
-      <c r="F74" s="396"/>
+      <c r="F74" s="395"/>
       <c r="H74" s="312"/>
       <c r="I74" s="305"/>
-      <c r="J74" s="455"/>
+      <c r="J74" s="454"/>
     </row>
     <row r="75" spans="1:10" ht="15.75" customHeight="1">
       <c r="A75" s="305"/>
       <c r="B75" s="305"/>
-      <c r="C75" s="400" t="s">
+      <c r="C75" s="399" t="s">
         <v>974</v>
       </c>
-      <c r="D75" s="401" t="s">
+      <c r="D75" s="400" t="s">
         <v>967</v>
       </c>
-      <c r="E75" s="402" t="s">
+      <c r="E75" s="401" t="s">
         <v>975</v>
       </c>
-      <c r="F75" s="396"/>
+      <c r="F75" s="395"/>
       <c r="G75" s="305"/>
       <c r="H75" s="305"/>
       <c r="I75" s="305"/>
-      <c r="J75" s="455"/>
+      <c r="J75" s="454"/>
     </row>
     <row r="76" spans="1:10" ht="15" customHeight="1">
-      <c r="C76" s="403"/>
-      <c r="D76" s="404" t="s">
+      <c r="C76" s="402"/>
+      <c r="D76" s="403" t="s">
         <v>976</v>
       </c>
-      <c r="E76" s="405" t="s">
+      <c r="E76" s="404" t="s">
         <v>960</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="15" customHeight="1">
-      <c r="C77" s="403"/>
-      <c r="D77" s="404" t="s">
+      <c r="C77" s="402"/>
+      <c r="D77" s="403" t="s">
         <v>977</v>
       </c>
-      <c r="E77" s="405" t="s">
+      <c r="E77" s="404" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1">
-      <c r="C78" s="406"/>
-      <c r="D78" s="404" t="s">
+      <c r="C78" s="405"/>
+      <c r="D78" s="403" t="s">
         <v>979</v>
       </c>
-      <c r="E78" s="402" t="s">
+      <c r="E78" s="401" t="s">
         <v>980</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15" customHeight="1">
-      <c r="C79" s="400" t="s">
+      <c r="C79" s="399" t="s">
         <v>981</v>
       </c>
-      <c r="D79" s="401" t="s">
+      <c r="D79" s="400" t="s">
         <v>967</v>
       </c>
-      <c r="E79" s="402" t="s">
+      <c r="E79" s="401" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15" customHeight="1">
-      <c r="C80" s="403"/>
-      <c r="D80" s="404" t="s">
+      <c r="C80" s="402"/>
+      <c r="D80" s="403" t="s">
         <v>976</v>
       </c>
-      <c r="E80" s="405" t="s">
+      <c r="E80" s="404" t="s">
         <v>960</v>
       </c>
     </row>
     <row r="81" spans="3:5" ht="15" customHeight="1">
-      <c r="C81" s="403"/>
-      <c r="D81" s="404" t="s">
+      <c r="C81" s="402"/>
+      <c r="D81" s="403" t="s">
         <v>977</v>
       </c>
-      <c r="E81" s="405" t="s">
+      <c r="E81" s="404" t="s">
         <v>978</v>
       </c>
     </row>
     <row r="82" spans="3:5" ht="15" customHeight="1">
-      <c r="C82" s="406"/>
-      <c r="D82" s="404" t="s">
+      <c r="C82" s="405"/>
+      <c r="D82" s="403" t="s">
         <v>979</v>
       </c>
-      <c r="E82" s="402" t="s">
+      <c r="E82" s="401" t="s">
         <v>980</v>
       </c>
     </row>

--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841624E7-8081-1B4B-9B0B-56BBFA28BB83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C6EF64C-25CD-D44D-ADCA-D0132415B345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="1074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="1076">
   <si>
     <t>プロジェクト概要</t>
   </si>
@@ -4306,14 +4306,6 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>GET/PUT</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>edit/update</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>管理者ユーザーのみ、個別で一般ユーザーの修正申請(承認待ち)を表示する画面</t>
     <rPh sb="0" eb="3">
       <t>カンリ</t>
@@ -4347,10 +4339,6 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>report</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>一般ユーザーが、自身の勤怠統計を表示できる画面</t>
     <rPh sb="0" eb="2">
       <t>イッパンユ-</t>
@@ -4654,21 +4642,7 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>nullable / array / date_format:H:i:s / before:clock_out / after:clock_in</t>
-    <rPh sb="54" eb="59">
-      <t>イゼnカクニn</t>
-    </rPh>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>new_break_out[]</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>nullable / array / date_format:H:i:s / before:clock_out</t>
-    <rPh sb="52" eb="54">
-      <t>イコウ</t>
-    </rPh>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -5295,10 +5269,6 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>UpdateAttendanceRecordRequest.php</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t xml:space="preserve">AttendanceController@create
 AttendanceController@store
 </t>
@@ -5566,13 +5536,6 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>nullable / array / date_format:H:i:s / before:new_clock_out / new_after:clock_in</t>
-    <rPh sb="58" eb="63">
-      <t>イゼnカクニn</t>
-    </rPh>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>nullable / array / date_format:H:i:s / before:new_clock_out</t>
     <rPh sb="52" eb="54">
       <t>イコウ</t>
@@ -5647,6 +5610,261 @@
     <rPh sb="52" eb="57">
       <t>カンリ</t>
     </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>/attendance</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>/admin/staff/list</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「詳細」ボタンの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>URL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/application/{id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>から</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/attendance/{id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>となるよう修正</t>
+    </r>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>「詳細」ボタンの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>URL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/attendance/{id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>から</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/admin/attendance/{id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>となるよう修正</t>
+    </r>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>postするURLを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/attendance/{id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>から</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/admin/attendance/{id}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>となるよう修正。また、機能要件（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>FN038</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>）を満たすため「承認待ち」状態の場合の処理を追記。</t>
+    </r>
+    <rPh sb="79" eb="81">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>ツイキ</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>nullable / array / date_format:H:i:s / before:new_clock_out / after:new_clock_in</t>
+    <rPh sb="58" eb="63">
+      <t>イゼnカクニn</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>nullable / array / date_format:H:i:s / before:new_clock_out</t>
+    <rPh sb="56" eb="58">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>StoreAttendanceRecordRequest.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>show/update</t>
     <phoneticPr fontId="80"/>
   </si>
 </sst>
@@ -7383,7 +7601,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18"/>
   </cellStyleXfs>
-  <cellXfs count="487">
+  <cellXfs count="489">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8437,9 +8655,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -8551,7 +8766,6 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="82" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8560,12 +8774,6 @@
     </xf>
     <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -8575,6 +8783,29 @@
     <xf numFmtId="0" fontId="4" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="16" borderId="18" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="79" fillId="19" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8610,15 +8841,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -9145,7 +9367,7 @@
     <row r="3" spans="1:12" ht="36.75" customHeight="1">
       <c r="A3" s="303"/>
       <c r="B3" s="303"/>
-      <c r="C3" s="406" t="s">
+      <c r="C3" s="405" t="s">
         <v>654</v>
       </c>
       <c r="D3" s="305"/>
@@ -9163,44 +9385,44 @@
       <c r="C4" s="373" t="s">
         <v>659</v>
       </c>
-      <c r="D4" s="407"/>
-      <c r="E4" s="408"/>
-      <c r="F4" s="408"/>
-      <c r="G4" s="408"/>
-      <c r="H4" s="408"/>
-      <c r="I4" s="408"/>
-      <c r="J4" s="408"/>
-      <c r="K4" s="408"/>
+      <c r="D4" s="406"/>
+      <c r="E4" s="407"/>
+      <c r="F4" s="407"/>
+      <c r="G4" s="407"/>
+      <c r="H4" s="407"/>
+      <c r="I4" s="407"/>
+      <c r="J4" s="407"/>
+      <c r="K4" s="407"/>
       <c r="L4" s="305"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="303"/>
       <c r="B5" s="303"/>
-      <c r="C5" s="409" t="s">
+      <c r="C5" s="408" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="410" t="s">
+      <c r="D5" s="409" t="s">
         <v>671</v>
       </c>
-      <c r="E5" s="411" t="s">
+      <c r="E5" s="410" t="s">
         <v>675</v>
       </c>
-      <c r="F5" s="411" t="s">
+      <c r="F5" s="410" t="s">
         <v>438</v>
       </c>
-      <c r="G5" s="411" t="s">
+      <c r="G5" s="410" t="s">
         <v>676</v>
       </c>
-      <c r="H5" s="411" t="s">
+      <c r="H5" s="410" t="s">
         <v>677</v>
       </c>
-      <c r="I5" s="411" t="s">
+      <c r="I5" s="410" t="s">
         <v>678</v>
       </c>
-      <c r="J5" s="411" t="s">
+      <c r="J5" s="410" t="s">
         <v>679</v>
       </c>
-      <c r="K5" s="412" t="s">
+      <c r="K5" s="411" t="s">
         <v>681</v>
       </c>
       <c r="L5" s="305"/>
@@ -9208,81 +9430,81 @@
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="366"/>
       <c r="B6" s="366"/>
-      <c r="C6" s="413">
+      <c r="C6" s="412">
         <v>1</v>
       </c>
-      <c r="D6" s="414" t="s">
-        <v>983</v>
-      </c>
-      <c r="E6" s="415"/>
-      <c r="F6" s="415"/>
-      <c r="G6" s="415"/>
-      <c r="H6" s="415"/>
-      <c r="I6" s="415"/>
-      <c r="J6" s="416"/>
-      <c r="K6" s="417"/>
+      <c r="D6" s="413" t="s">
+        <v>978</v>
+      </c>
+      <c r="E6" s="414"/>
+      <c r="F6" s="414"/>
+      <c r="G6" s="414"/>
+      <c r="H6" s="414"/>
+      <c r="I6" s="414"/>
+      <c r="J6" s="415"/>
+      <c r="K6" s="416"/>
       <c r="L6" s="305"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="303"/>
       <c r="B7" s="303"/>
-      <c r="C7" s="418"/>
-      <c r="E7" s="392" t="s">
+      <c r="C7" s="417"/>
+      <c r="E7" s="391" t="s">
         <v>701</v>
       </c>
-      <c r="F7" s="419" t="s">
-        <v>984</v>
-      </c>
-      <c r="G7" s="419" t="s">
+      <c r="F7" s="418" t="s">
+        <v>979</v>
+      </c>
+      <c r="G7" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="H7" s="392"/>
-      <c r="I7" s="419" t="s">
+      <c r="H7" s="391"/>
+      <c r="I7" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="J7" s="420"/>
-      <c r="K7" s="417"/>
+      <c r="J7" s="419"/>
+      <c r="K7" s="416"/>
       <c r="L7" s="305"/>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="374"/>
       <c r="B8" s="374"/>
-      <c r="C8" s="421"/>
+      <c r="C8" s="420"/>
       <c r="D8" s="304"/>
-      <c r="E8" s="392" t="s">
-        <v>985</v>
-      </c>
-      <c r="F8" s="392" t="s">
-        <v>986</v>
-      </c>
-      <c r="G8" s="392"/>
-      <c r="H8" s="392"/>
-      <c r="I8" s="419" t="s">
+      <c r="E8" s="391" t="s">
+        <v>980</v>
+      </c>
+      <c r="F8" s="391" t="s">
+        <v>981</v>
+      </c>
+      <c r="G8" s="391"/>
+      <c r="H8" s="391"/>
+      <c r="I8" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="J8" s="420"/>
-      <c r="K8" s="417"/>
+      <c r="J8" s="419"/>
+      <c r="K8" s="416"/>
       <c r="L8" s="305"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
       <c r="A9" s="366"/>
       <c r="B9" s="366"/>
-      <c r="C9" s="418"/>
-      <c r="E9" s="392" t="s">
-        <v>987</v>
-      </c>
-      <c r="F9" s="392" t="s">
-        <v>986</v>
-      </c>
-      <c r="G9" s="392"/>
-      <c r="H9" s="419" t="s">
+      <c r="C9" s="417"/>
+      <c r="E9" s="391" t="s">
+        <v>982</v>
+      </c>
+      <c r="F9" s="391" t="s">
+        <v>981</v>
+      </c>
+      <c r="G9" s="391"/>
+      <c r="H9" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="I9" s="419" t="s">
+      <c r="I9" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="J9" s="420"/>
-      <c r="K9" s="422" t="s">
+      <c r="J9" s="419"/>
+      <c r="K9" s="421" t="s">
         <v>764</v>
       </c>
       <c r="L9" s="305"/>
@@ -9290,1269 +9512,1269 @@
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
       <c r="A10" s="366"/>
       <c r="B10" s="366"/>
-      <c r="C10" s="418"/>
-      <c r="E10" s="392" t="s">
-        <v>988</v>
-      </c>
-      <c r="F10" s="392" t="s">
+      <c r="C10" s="417"/>
+      <c r="E10" s="391" t="s">
+        <v>983</v>
+      </c>
+      <c r="F10" s="391" t="s">
         <v>731</v>
       </c>
-      <c r="G10" s="392"/>
-      <c r="H10" s="392"/>
-      <c r="I10" s="419"/>
-      <c r="J10" s="420"/>
-      <c r="K10" s="417"/>
+      <c r="G10" s="391"/>
+      <c r="H10" s="391"/>
+      <c r="I10" s="418"/>
+      <c r="J10" s="419"/>
+      <c r="K10" s="416"/>
       <c r="L10" s="305"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="366"/>
       <c r="B11" s="366"/>
-      <c r="C11" s="418"/>
-      <c r="E11" s="392" t="s">
-        <v>989</v>
-      </c>
-      <c r="F11" s="392" t="s">
-        <v>986</v>
-      </c>
-      <c r="G11" s="392"/>
-      <c r="H11" s="392"/>
-      <c r="I11" s="419" t="s">
+      <c r="C11" s="417"/>
+      <c r="E11" s="391" t="s">
+        <v>984</v>
+      </c>
+      <c r="F11" s="391" t="s">
+        <v>981</v>
+      </c>
+      <c r="G11" s="391"/>
+      <c r="H11" s="391"/>
+      <c r="I11" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="J11" s="420"/>
-      <c r="K11" s="417"/>
+      <c r="J11" s="419"/>
+      <c r="K11" s="416"/>
       <c r="L11" s="305"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="366"/>
       <c r="B12" s="366"/>
-      <c r="C12" s="418"/>
-      <c r="E12" s="392" t="s">
-        <v>990</v>
-      </c>
-      <c r="F12" s="392" t="s">
-        <v>991</v>
-      </c>
-      <c r="G12" s="392"/>
-      <c r="H12" s="392"/>
-      <c r="I12" s="392"/>
-      <c r="J12" s="420"/>
-      <c r="K12" s="417"/>
+      <c r="C12" s="417"/>
+      <c r="E12" s="391" t="s">
+        <v>985</v>
+      </c>
+      <c r="F12" s="391" t="s">
+        <v>986</v>
+      </c>
+      <c r="G12" s="391"/>
+      <c r="H12" s="391"/>
+      <c r="I12" s="391"/>
+      <c r="J12" s="419"/>
+      <c r="K12" s="416"/>
       <c r="L12" s="305"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="366"/>
       <c r="B13" s="366"/>
-      <c r="C13" s="418"/>
-      <c r="D13" s="437" t="s">
-        <v>1032</v>
-      </c>
-      <c r="E13" s="448" t="s">
-        <v>1031</v>
-      </c>
-      <c r="F13" s="448" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G13" s="392"/>
-      <c r="H13" s="392"/>
-      <c r="I13" s="449" t="s">
+      <c r="C13" s="417"/>
+      <c r="D13" s="436" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E13" s="447" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F13" s="447" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G13" s="391"/>
+      <c r="H13" s="391"/>
+      <c r="I13" s="448" t="s">
         <v>710</v>
       </c>
-      <c r="J13" s="420"/>
-      <c r="K13" s="417"/>
+      <c r="J13" s="419"/>
+      <c r="K13" s="416"/>
       <c r="L13" s="305"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
       <c r="A14" s="366"/>
       <c r="B14" s="366"/>
-      <c r="C14" s="418"/>
-      <c r="D14" s="437" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E14" s="392" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F14" s="392" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G14" s="392"/>
-      <c r="H14" s="392"/>
-      <c r="I14" s="392"/>
-      <c r="J14" s="420"/>
-      <c r="K14" s="417"/>
+      <c r="C14" s="417"/>
+      <c r="D14" s="436" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E14" s="391" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F14" s="391" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G14" s="391"/>
+      <c r="H14" s="391"/>
+      <c r="I14" s="391"/>
+      <c r="J14" s="419"/>
+      <c r="K14" s="416"/>
       <c r="L14" s="305"/>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="A15" s="366"/>
       <c r="B15" s="366"/>
-      <c r="C15" s="418"/>
-      <c r="E15" s="392" t="s">
+      <c r="C15" s="417"/>
+      <c r="E15" s="391" t="s">
         <v>730</v>
       </c>
-      <c r="F15" s="392" t="s">
+      <c r="F15" s="391" t="s">
         <v>731</v>
       </c>
-      <c r="G15" s="392"/>
-      <c r="H15" s="392"/>
-      <c r="I15" s="392"/>
-      <c r="J15" s="420"/>
-      <c r="K15" s="417"/>
+      <c r="G15" s="391"/>
+      <c r="H15" s="391"/>
+      <c r="I15" s="391"/>
+      <c r="J15" s="419"/>
+      <c r="K15" s="416"/>
       <c r="L15" s="305"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
       <c r="A16" s="366"/>
       <c r="B16" s="366"/>
-      <c r="C16" s="418"/>
-      <c r="E16" s="392" t="s">
+      <c r="C16" s="417"/>
+      <c r="E16" s="391" t="s">
         <v>739</v>
       </c>
-      <c r="F16" s="392" t="s">
+      <c r="F16" s="391" t="s">
         <v>731</v>
       </c>
-      <c r="G16" s="392"/>
-      <c r="H16" s="392"/>
-      <c r="I16" s="392"/>
-      <c r="J16" s="420"/>
-      <c r="K16" s="417"/>
+      <c r="G16" s="391"/>
+      <c r="H16" s="391"/>
+      <c r="I16" s="391"/>
+      <c r="J16" s="419"/>
+      <c r="K16" s="416"/>
       <c r="L16" s="305"/>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A17" s="395"/>
-      <c r="B17" s="395"/>
-      <c r="C17" s="425">
+      <c r="A17" s="394"/>
+      <c r="B17" s="394"/>
+      <c r="C17" s="424">
         <v>2</v>
       </c>
-      <c r="D17" s="423" t="s">
-        <v>992</v>
-      </c>
-      <c r="E17" s="415"/>
-      <c r="F17" s="415"/>
-      <c r="G17" s="415"/>
-      <c r="H17" s="415"/>
-      <c r="I17" s="415"/>
-      <c r="J17" s="416"/>
+      <c r="D17" s="422" t="s">
+        <v>987</v>
+      </c>
+      <c r="E17" s="414"/>
+      <c r="F17" s="414"/>
+      <c r="G17" s="414"/>
+      <c r="H17" s="414"/>
+      <c r="I17" s="414"/>
+      <c r="J17" s="415"/>
       <c r="K17" s="305"/>
       <c r="L17" s="305"/>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A18" s="395"/>
-      <c r="B18" s="395"/>
-      <c r="C18" s="424"/>
-      <c r="E18" s="392" t="s">
-        <v>993</v>
+      <c r="A18" s="394"/>
+      <c r="B18" s="394"/>
+      <c r="C18" s="423"/>
+      <c r="E18" s="391" t="s">
+        <v>988</v>
       </c>
       <c r="F18" s="362" t="s">
-        <v>984</v>
-      </c>
-      <c r="G18" s="419" t="s">
+        <v>979</v>
+      </c>
+      <c r="G18" s="418" t="s">
         <v>903</v>
       </c>
-      <c r="H18" s="392"/>
-      <c r="I18" s="419" t="s">
+      <c r="H18" s="391"/>
+      <c r="I18" s="418" t="s">
         <v>903</v>
       </c>
-      <c r="J18" s="420"/>
+      <c r="J18" s="419"/>
       <c r="K18" s="305"/>
       <c r="L18" s="305"/>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A19" s="395"/>
-      <c r="B19" s="395"/>
-      <c r="C19" s="424"/>
+      <c r="A19" s="394"/>
+      <c r="B19" s="394"/>
+      <c r="C19" s="423"/>
       <c r="D19" s="312" t="s">
-        <v>994</v>
-      </c>
-      <c r="E19" s="392" t="s">
-        <v>965</v>
+        <v>989</v>
+      </c>
+      <c r="E19" s="391" t="s">
+        <v>960</v>
       </c>
       <c r="F19" s="362" t="s">
-        <v>995</v>
-      </c>
-      <c r="G19" s="419"/>
-      <c r="H19" s="392" t="s">
+        <v>990</v>
+      </c>
+      <c r="G19" s="418"/>
+      <c r="H19" s="391" t="s">
         <v>903</v>
       </c>
-      <c r="I19" s="419" t="s">
+      <c r="I19" s="418" t="s">
         <v>903</v>
       </c>
-      <c r="J19" s="420" t="s">
-        <v>996</v>
+      <c r="J19" s="419" t="s">
+        <v>991</v>
       </c>
       <c r="K19" s="305"/>
       <c r="L19" s="305"/>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A20" s="395"/>
-      <c r="B20" s="395"/>
-      <c r="C20" s="424"/>
+      <c r="A20" s="394"/>
+      <c r="B20" s="394"/>
+      <c r="C20" s="423"/>
       <c r="D20" s="312"/>
-      <c r="E20" s="392" t="s">
-        <v>967</v>
+      <c r="E20" s="391" t="s">
+        <v>962</v>
       </c>
       <c r="F20" s="362" t="s">
-        <v>967</v>
-      </c>
-      <c r="G20" s="419"/>
-      <c r="H20" s="392" t="s">
+        <v>962</v>
+      </c>
+      <c r="G20" s="418"/>
+      <c r="H20" s="391" t="s">
         <v>903</v>
       </c>
-      <c r="I20" s="419"/>
-      <c r="J20" s="420"/>
+      <c r="I20" s="418"/>
+      <c r="J20" s="419"/>
       <c r="K20" s="305"/>
       <c r="L20" s="305"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A21" s="395"/>
-      <c r="B21" s="395"/>
-      <c r="C21" s="424"/>
+      <c r="A21" s="394"/>
+      <c r="B21" s="394"/>
+      <c r="C21" s="423"/>
       <c r="D21" s="304"/>
-      <c r="E21" s="392" t="s">
-        <v>976</v>
+      <c r="E21" s="391" t="s">
+        <v>971</v>
       </c>
       <c r="F21" s="362" t="s">
-        <v>997</v>
-      </c>
-      <c r="G21" s="392"/>
-      <c r="H21" s="392"/>
-      <c r="I21" s="419" t="s">
+        <v>992</v>
+      </c>
+      <c r="G21" s="391"/>
+      <c r="H21" s="391"/>
+      <c r="I21" s="418" t="s">
         <v>903</v>
       </c>
-      <c r="J21" s="420"/>
+      <c r="J21" s="419"/>
       <c r="K21" s="305"/>
       <c r="L21" s="305"/>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A22" s="395"/>
-      <c r="B22" s="395"/>
-      <c r="C22" s="424"/>
-      <c r="E22" s="392" t="s">
-        <v>977</v>
+      <c r="A22" s="394"/>
+      <c r="B22" s="394"/>
+      <c r="C22" s="423"/>
+      <c r="E22" s="391" t="s">
+        <v>972</v>
       </c>
       <c r="F22" s="362" t="s">
-        <v>997</v>
-      </c>
-      <c r="G22" s="392"/>
-      <c r="H22" s="392"/>
-      <c r="I22" s="419"/>
-      <c r="J22" s="420"/>
+        <v>992</v>
+      </c>
+      <c r="G22" s="391"/>
+      <c r="H22" s="391"/>
+      <c r="I22" s="418"/>
+      <c r="J22" s="419"/>
       <c r="K22" s="305"/>
       <c r="L22" s="305"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A23" s="395"/>
-      <c r="B23" s="395"/>
-      <c r="C23" s="424"/>
-      <c r="E23" s="448" t="s">
-        <v>979</v>
-      </c>
-      <c r="F23" s="448" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G23" s="392"/>
-      <c r="H23" s="392"/>
-      <c r="I23" s="419"/>
-      <c r="J23" s="420"/>
+      <c r="A23" s="394"/>
+      <c r="B23" s="394"/>
+      <c r="C23" s="423"/>
+      <c r="E23" s="447" t="s">
+        <v>974</v>
+      </c>
+      <c r="F23" s="447" t="s">
+        <v>998</v>
+      </c>
+      <c r="G23" s="391"/>
+      <c r="H23" s="391"/>
+      <c r="I23" s="418"/>
+      <c r="J23" s="419"/>
       <c r="K23" s="305"/>
       <c r="L23" s="305"/>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A24" s="395"/>
-      <c r="B24" s="395"/>
-      <c r="C24" s="424"/>
-      <c r="D24" s="426"/>
-      <c r="E24" s="427" t="s">
+      <c r="A24" s="394"/>
+      <c r="B24" s="394"/>
+      <c r="C24" s="423"/>
+      <c r="D24" s="425"/>
+      <c r="E24" s="426" t="s">
         <v>730</v>
       </c>
-      <c r="F24" s="427" t="s">
+      <c r="F24" s="426" t="s">
         <v>731</v>
       </c>
-      <c r="G24" s="427"/>
-      <c r="H24" s="427"/>
-      <c r="I24" s="427"/>
-      <c r="J24" s="428"/>
+      <c r="G24" s="426"/>
+      <c r="H24" s="426"/>
+      <c r="I24" s="426"/>
+      <c r="J24" s="427"/>
       <c r="K24" s="305"/>
       <c r="L24" s="305"/>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A25" s="395"/>
-      <c r="B25" s="395"/>
-      <c r="C25" s="424"/>
-      <c r="D25" s="429"/>
-      <c r="E25" s="427" t="s">
+      <c r="A25" s="394"/>
+      <c r="B25" s="394"/>
+      <c r="C25" s="423"/>
+      <c r="D25" s="428"/>
+      <c r="E25" s="426" t="s">
         <v>739</v>
       </c>
-      <c r="F25" s="427" t="s">
+      <c r="F25" s="426" t="s">
         <v>731</v>
       </c>
-      <c r="G25" s="427"/>
-      <c r="H25" s="427"/>
-      <c r="I25" s="427"/>
-      <c r="J25" s="428"/>
+      <c r="G25" s="426"/>
+      <c r="H25" s="426"/>
+      <c r="I25" s="426"/>
+      <c r="J25" s="427"/>
       <c r="K25" s="305"/>
       <c r="L25" s="305"/>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A26" s="395"/>
-      <c r="B26" s="395"/>
-      <c r="C26" s="424"/>
-      <c r="D26" s="430"/>
-      <c r="E26" s="431" t="s">
-        <v>998</v>
-      </c>
-      <c r="F26" s="432"/>
-      <c r="G26" s="433"/>
-      <c r="H26" s="432" t="s">
-        <v>999</v>
-      </c>
-      <c r="I26" s="432"/>
-      <c r="J26" s="434"/>
+      <c r="A26" s="394"/>
+      <c r="B26" s="394"/>
+      <c r="C26" s="423"/>
+      <c r="D26" s="429"/>
+      <c r="E26" s="430" t="s">
+        <v>993</v>
+      </c>
+      <c r="F26" s="431"/>
+      <c r="G26" s="432"/>
+      <c r="H26" s="431" t="s">
+        <v>994</v>
+      </c>
+      <c r="I26" s="431"/>
+      <c r="J26" s="433"/>
       <c r="K26" s="305"/>
       <c r="L26" s="305"/>
     </row>
     <row r="27" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A27" s="395"/>
-      <c r="B27" s="395"/>
-      <c r="C27" s="425">
+      <c r="A27" s="394"/>
+      <c r="B27" s="394"/>
+      <c r="C27" s="424">
         <v>3</v>
       </c>
-      <c r="D27" s="423" t="s">
-        <v>1026</v>
-      </c>
-      <c r="E27" s="415"/>
-      <c r="F27" s="415"/>
-      <c r="G27" s="415"/>
-      <c r="H27" s="415"/>
-      <c r="I27" s="415"/>
-      <c r="J27" s="416"/>
+      <c r="D27" s="422" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E27" s="414"/>
+      <c r="F27" s="414"/>
+      <c r="G27" s="414"/>
+      <c r="H27" s="414"/>
+      <c r="I27" s="414"/>
+      <c r="J27" s="415"/>
       <c r="K27" s="305"/>
       <c r="L27" s="305"/>
     </row>
     <row r="28" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A28" s="395"/>
-      <c r="B28" s="395"/>
-      <c r="C28" s="424"/>
-      <c r="E28" s="392" t="s">
+      <c r="A28" s="394"/>
+      <c r="B28" s="394"/>
+      <c r="C28" s="423"/>
+      <c r="E28" s="391" t="s">
         <v>701</v>
       </c>
-      <c r="F28" s="392" t="s">
-        <v>984</v>
-      </c>
-      <c r="G28" s="419" t="s">
+      <c r="F28" s="391" t="s">
+        <v>979</v>
+      </c>
+      <c r="G28" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="H28" s="392"/>
-      <c r="I28" s="419" t="s">
+      <c r="H28" s="391"/>
+      <c r="I28" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="J28" s="420"/>
+      <c r="J28" s="419"/>
       <c r="K28" s="305"/>
       <c r="L28" s="305"/>
     </row>
     <row r="29" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A29" s="395"/>
-      <c r="B29" s="395"/>
-      <c r="C29" s="424"/>
+      <c r="A29" s="394"/>
+      <c r="B29" s="394"/>
+      <c r="C29" s="423"/>
       <c r="D29" s="312" t="s">
-        <v>994</v>
-      </c>
-      <c r="E29" s="452" t="s">
-        <v>1036</v>
-      </c>
-      <c r="F29" s="392" t="s">
-        <v>984</v>
-      </c>
-      <c r="G29" s="419"/>
-      <c r="H29" s="392"/>
-      <c r="I29" s="419" t="s">
+        <v>989</v>
+      </c>
+      <c r="E29" s="451" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F29" s="391" t="s">
+        <v>979</v>
+      </c>
+      <c r="G29" s="418"/>
+      <c r="H29" s="391"/>
+      <c r="I29" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="J29" s="420" t="s">
-        <v>1000</v>
+      <c r="J29" s="419" t="s">
+        <v>995</v>
       </c>
       <c r="K29" s="305"/>
       <c r="L29" s="305"/>
     </row>
     <row r="30" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A30" s="395"/>
-      <c r="B30" s="395"/>
-      <c r="C30" s="424"/>
+      <c r="A30" s="394"/>
+      <c r="B30" s="394"/>
+      <c r="C30" s="423"/>
       <c r="D30" s="304"/>
-      <c r="E30" s="392" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F30" s="392" t="s">
-        <v>997</v>
-      </c>
-      <c r="G30" s="392"/>
-      <c r="H30" s="392"/>
-      <c r="I30" s="419"/>
-      <c r="J30" s="435"/>
+      <c r="E30" s="391" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F30" s="391" t="s">
+        <v>992</v>
+      </c>
+      <c r="G30" s="391"/>
+      <c r="H30" s="391"/>
+      <c r="I30" s="418"/>
+      <c r="J30" s="434"/>
       <c r="K30" s="305"/>
       <c r="L30" s="305"/>
     </row>
     <row r="31" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A31" s="395"/>
-      <c r="B31" s="395"/>
-      <c r="C31" s="424"/>
-      <c r="E31" s="392" t="s">
-        <v>1040</v>
-      </c>
-      <c r="F31" s="392" t="s">
-        <v>997</v>
-      </c>
-      <c r="G31" s="392"/>
-      <c r="H31" s="392"/>
-      <c r="I31" s="419"/>
-      <c r="J31" s="420"/>
+      <c r="A31" s="394"/>
+      <c r="B31" s="394"/>
+      <c r="C31" s="423"/>
+      <c r="E31" s="391" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F31" s="391" t="s">
+        <v>992</v>
+      </c>
+      <c r="G31" s="391"/>
+      <c r="H31" s="391"/>
+      <c r="I31" s="418"/>
+      <c r="J31" s="419"/>
       <c r="K31" s="305"/>
       <c r="L31" s="305"/>
     </row>
     <row r="32" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A32" s="395"/>
-      <c r="B32" s="395"/>
-      <c r="C32" s="424"/>
-      <c r="E32" s="392" t="s">
+      <c r="A32" s="394"/>
+      <c r="B32" s="394"/>
+      <c r="C32" s="423"/>
+      <c r="E32" s="391" t="s">
         <v>730</v>
       </c>
-      <c r="F32" s="392" t="s">
+      <c r="F32" s="391" t="s">
         <v>731</v>
       </c>
-      <c r="G32" s="392"/>
-      <c r="H32" s="392"/>
-      <c r="I32" s="392"/>
-      <c r="J32" s="420"/>
+      <c r="G32" s="391"/>
+      <c r="H32" s="391"/>
+      <c r="I32" s="391"/>
+      <c r="J32" s="419"/>
       <c r="K32" s="305"/>
       <c r="L32" s="305"/>
     </row>
     <row r="33" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A33" s="395"/>
-      <c r="B33" s="395"/>
-      <c r="C33" s="424"/>
-      <c r="E33" s="392" t="s">
+      <c r="A33" s="394"/>
+      <c r="B33" s="394"/>
+      <c r="C33" s="423"/>
+      <c r="E33" s="391" t="s">
         <v>739</v>
       </c>
-      <c r="F33" s="392" t="s">
+      <c r="F33" s="391" t="s">
         <v>731</v>
       </c>
-      <c r="G33" s="392"/>
-      <c r="H33" s="392"/>
-      <c r="I33" s="392"/>
-      <c r="J33" s="420"/>
+      <c r="G33" s="391"/>
+      <c r="H33" s="391"/>
+      <c r="I33" s="391"/>
+      <c r="J33" s="419"/>
       <c r="K33" s="305"/>
       <c r="L33" s="305"/>
     </row>
     <row r="34" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A34" s="395"/>
-      <c r="B34" s="395"/>
-      <c r="C34" s="425">
+      <c r="A34" s="394"/>
+      <c r="B34" s="394"/>
+      <c r="C34" s="424">
         <v>4</v>
       </c>
-      <c r="D34" s="482" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E34" s="483"/>
-      <c r="F34" s="483"/>
-      <c r="G34" s="483"/>
-      <c r="H34" s="483"/>
-      <c r="I34" s="415"/>
-      <c r="J34" s="416"/>
+      <c r="D34" s="487" t="s">
+        <v>996</v>
+      </c>
+      <c r="E34" s="488"/>
+      <c r="F34" s="488"/>
+      <c r="G34" s="488"/>
+      <c r="H34" s="488"/>
+      <c r="I34" s="414"/>
+      <c r="J34" s="415"/>
       <c r="K34" s="305"/>
       <c r="L34" s="305"/>
     </row>
     <row r="35" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A35" s="395"/>
-      <c r="B35" s="395"/>
-      <c r="C35" s="424"/>
-      <c r="E35" s="392" t="s">
-        <v>993</v>
+      <c r="A35" s="394"/>
+      <c r="B35" s="394"/>
+      <c r="C35" s="423"/>
+      <c r="E35" s="391" t="s">
+        <v>988</v>
       </c>
       <c r="F35" s="362" t="s">
-        <v>984</v>
-      </c>
-      <c r="G35" s="419" t="s">
+        <v>979</v>
+      </c>
+      <c r="G35" s="418" t="s">
         <v>903</v>
       </c>
-      <c r="H35" s="392"/>
-      <c r="I35" s="419" t="s">
+      <c r="H35" s="391"/>
+      <c r="I35" s="418" t="s">
         <v>903</v>
       </c>
-      <c r="J35" s="420"/>
+      <c r="J35" s="419"/>
       <c r="K35" s="305"/>
       <c r="L35" s="305"/>
     </row>
     <row r="36" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A36" s="395"/>
-      <c r="B36" s="395"/>
-      <c r="C36" s="424"/>
+      <c r="A36" s="394"/>
+      <c r="B36" s="394"/>
+      <c r="C36" s="423"/>
       <c r="D36" s="306" t="s">
-        <v>1002</v>
-      </c>
-      <c r="E36" s="452" t="s">
-        <v>1036</v>
+        <v>997</v>
+      </c>
+      <c r="E36" s="451" t="s">
+        <v>1031</v>
       </c>
       <c r="F36" s="362" t="s">
-        <v>984</v>
-      </c>
-      <c r="G36" s="419"/>
-      <c r="H36" s="392"/>
-      <c r="I36" s="419" t="s">
+        <v>979</v>
+      </c>
+      <c r="G36" s="418"/>
+      <c r="H36" s="391"/>
+      <c r="I36" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="J36" s="420" t="s">
-        <v>1000</v>
+      <c r="J36" s="419" t="s">
+        <v>995</v>
       </c>
       <c r="K36" s="305"/>
       <c r="L36" s="305"/>
     </row>
     <row r="37" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A37" s="395"/>
-      <c r="B37" s="395"/>
-      <c r="C37" s="424"/>
-      <c r="E37" s="392" t="s">
-        <v>952</v>
-      </c>
-      <c r="F37" s="392" t="s">
-        <v>997</v>
-      </c>
-      <c r="G37" s="392"/>
-      <c r="H37" s="392"/>
-      <c r="I37" s="419" t="s">
+      <c r="A37" s="394"/>
+      <c r="B37" s="394"/>
+      <c r="C37" s="423"/>
+      <c r="E37" s="391" t="s">
+        <v>949</v>
+      </c>
+      <c r="F37" s="391" t="s">
+        <v>992</v>
+      </c>
+      <c r="G37" s="391"/>
+      <c r="H37" s="391"/>
+      <c r="I37" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="J37" s="420"/>
+      <c r="J37" s="419"/>
       <c r="K37" s="305"/>
       <c r="L37" s="305"/>
     </row>
     <row r="38" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A38" s="395"/>
-      <c r="B38" s="395"/>
-      <c r="C38" s="424"/>
-      <c r="E38" s="392" t="s">
-        <v>953</v>
-      </c>
-      <c r="F38" s="436" t="s">
-        <v>997</v>
-      </c>
-      <c r="G38" s="392"/>
-      <c r="H38" s="392"/>
-      <c r="I38" s="453"/>
-      <c r="J38" s="420"/>
+      <c r="A38" s="394"/>
+      <c r="B38" s="394"/>
+      <c r="C38" s="423"/>
+      <c r="E38" s="391" t="s">
+        <v>950</v>
+      </c>
+      <c r="F38" s="435" t="s">
+        <v>992</v>
+      </c>
+      <c r="G38" s="391"/>
+      <c r="H38" s="391"/>
+      <c r="I38" s="452"/>
+      <c r="J38" s="419"/>
       <c r="K38" s="305"/>
       <c r="L38" s="305"/>
     </row>
     <row r="39" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A39" s="395"/>
-      <c r="B39" s="395"/>
-      <c r="C39" s="424"/>
-      <c r="E39" s="392" t="s">
-        <v>979</v>
-      </c>
-      <c r="F39" s="392" t="s">
-        <v>1003</v>
-      </c>
-      <c r="G39" s="392"/>
-      <c r="H39" s="392"/>
-      <c r="I39" s="419" t="s">
+      <c r="A39" s="394"/>
+      <c r="B39" s="394"/>
+      <c r="C39" s="423"/>
+      <c r="E39" s="391" t="s">
+        <v>974</v>
+      </c>
+      <c r="F39" s="391" t="s">
+        <v>998</v>
+      </c>
+      <c r="G39" s="391"/>
+      <c r="H39" s="391"/>
+      <c r="I39" s="418" t="s">
         <v>710</v>
       </c>
-      <c r="J39" s="420"/>
+      <c r="J39" s="419"/>
       <c r="K39" s="305"/>
       <c r="L39" s="305"/>
     </row>
     <row r="40" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A40" s="395"/>
-      <c r="B40" s="395"/>
-      <c r="C40" s="424"/>
-      <c r="D40" s="437" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E40" s="392" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F40" s="392" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G40" s="392"/>
-      <c r="H40" s="392"/>
-      <c r="I40" s="392" t="s">
+      <c r="A40" s="394"/>
+      <c r="B40" s="394"/>
+      <c r="C40" s="423"/>
+      <c r="D40" s="436" t="s">
+        <v>999</v>
+      </c>
+      <c r="E40" s="391" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F40" s="391" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G40" s="391"/>
+      <c r="H40" s="391"/>
+      <c r="I40" s="391" t="s">
         <v>903</v>
       </c>
-      <c r="J40" s="420"/>
+      <c r="J40" s="419"/>
       <c r="K40" s="305"/>
       <c r="L40" s="305"/>
     </row>
     <row r="41" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A41" s="395"/>
-      <c r="B41" s="395"/>
-      <c r="C41" s="424"/>
-      <c r="D41" s="437"/>
-      <c r="E41" s="448" t="s">
-        <v>1033</v>
-      </c>
-      <c r="F41" s="448" t="s">
-        <v>967</v>
-      </c>
-      <c r="G41" s="392"/>
-      <c r="H41" s="392"/>
-      <c r="I41" s="448" t="s">
+      <c r="A41" s="394"/>
+      <c r="B41" s="394"/>
+      <c r="C41" s="423"/>
+      <c r="D41" s="436"/>
+      <c r="E41" s="447" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F41" s="447" t="s">
+        <v>962</v>
+      </c>
+      <c r="G41" s="391"/>
+      <c r="H41" s="391"/>
+      <c r="I41" s="447" t="s">
         <v>903</v>
       </c>
-      <c r="J41" s="420"/>
+      <c r="J41" s="419"/>
       <c r="K41" s="305"/>
       <c r="L41" s="305"/>
     </row>
     <row r="42" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A42" s="395"/>
-      <c r="B42" s="395"/>
-      <c r="C42" s="424"/>
-      <c r="D42" s="426"/>
-      <c r="E42" s="427" t="s">
+      <c r="A42" s="394"/>
+      <c r="B42" s="394"/>
+      <c r="C42" s="423"/>
+      <c r="D42" s="425"/>
+      <c r="E42" s="426" t="s">
         <v>730</v>
       </c>
-      <c r="F42" s="427" t="s">
+      <c r="F42" s="426" t="s">
         <v>731</v>
       </c>
-      <c r="G42" s="427"/>
-      <c r="H42" s="427"/>
-      <c r="I42" s="427"/>
-      <c r="J42" s="428"/>
+      <c r="G42" s="426"/>
+      <c r="H42" s="426"/>
+      <c r="I42" s="426"/>
+      <c r="J42" s="427"/>
       <c r="K42" s="305"/>
       <c r="L42" s="305"/>
     </row>
     <row r="43" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A43" s="395"/>
-      <c r="B43" s="395"/>
-      <c r="C43" s="438"/>
-      <c r="D43" s="430"/>
-      <c r="E43" s="427" t="s">
+      <c r="A43" s="394"/>
+      <c r="B43" s="394"/>
+      <c r="C43" s="437"/>
+      <c r="D43" s="429"/>
+      <c r="E43" s="426" t="s">
         <v>739</v>
       </c>
-      <c r="F43" s="427" t="s">
+      <c r="F43" s="426" t="s">
         <v>731</v>
       </c>
-      <c r="G43" s="427"/>
-      <c r="H43" s="427"/>
-      <c r="I43" s="427"/>
-      <c r="J43" s="428"/>
+      <c r="G43" s="426"/>
+      <c r="H43" s="426"/>
+      <c r="I43" s="426"/>
+      <c r="J43" s="427"/>
       <c r="K43" s="305"/>
       <c r="L43" s="305"/>
     </row>
     <row r="44" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A44" s="395"/>
-      <c r="B44" s="395"/>
-      <c r="C44" s="425">
+      <c r="A44" s="394"/>
+      <c r="B44" s="394"/>
+      <c r="C44" s="424">
         <v>5</v>
       </c>
-      <c r="D44" s="451" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E44" s="415"/>
-      <c r="F44" s="415"/>
-      <c r="G44" s="415"/>
-      <c r="H44" s="415"/>
-      <c r="I44" s="415"/>
-      <c r="J44" s="416"/>
+      <c r="D44" s="450" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E44" s="414"/>
+      <c r="F44" s="414"/>
+      <c r="G44" s="414"/>
+      <c r="H44" s="414"/>
+      <c r="I44" s="414"/>
+      <c r="J44" s="415"/>
       <c r="K44" s="305"/>
       <c r="L44" s="305"/>
     </row>
     <row r="45" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A45" s="395"/>
-      <c r="B45" s="395"/>
-      <c r="C45" s="424"/>
-      <c r="E45" s="392" t="s">
+      <c r="A45" s="394"/>
+      <c r="B45" s="394"/>
+      <c r="C45" s="423"/>
+      <c r="E45" s="391" t="s">
         <v>701</v>
       </c>
-      <c r="F45" s="392" t="s">
-        <v>984</v>
-      </c>
-      <c r="G45" s="392" t="s">
+      <c r="F45" s="391" t="s">
+        <v>979</v>
+      </c>
+      <c r="G45" s="391" t="s">
         <v>710</v>
       </c>
-      <c r="H45" s="392"/>
-      <c r="I45" s="392" t="s">
+      <c r="H45" s="391"/>
+      <c r="I45" s="391" t="s">
         <v>710</v>
       </c>
-      <c r="J45" s="420"/>
+      <c r="J45" s="419"/>
       <c r="K45" s="305"/>
       <c r="L45" s="305"/>
     </row>
     <row r="46" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A46" s="395"/>
-      <c r="B46" s="395"/>
-      <c r="C46" s="424"/>
+      <c r="A46" s="394"/>
+      <c r="B46" s="394"/>
+      <c r="C46" s="423"/>
       <c r="D46" s="312" t="s">
+        <v>997</v>
+      </c>
+      <c r="E46" s="391" t="s">
         <v>1002</v>
       </c>
-      <c r="E46" s="392" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F46" s="392" t="s">
-        <v>984</v>
-      </c>
-      <c r="G46" s="392"/>
-      <c r="H46" s="392"/>
-      <c r="I46" s="392" t="s">
+      <c r="F46" s="391" t="s">
+        <v>979</v>
+      </c>
+      <c r="G46" s="391"/>
+      <c r="H46" s="391"/>
+      <c r="I46" s="391" t="s">
         <v>903</v>
       </c>
-      <c r="J46" s="420" t="s">
-        <v>1008</v>
+      <c r="J46" s="419" t="s">
+        <v>1003</v>
       </c>
       <c r="K46" s="305"/>
       <c r="L46" s="305"/>
     </row>
     <row r="47" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A47" s="395"/>
-      <c r="B47" s="395"/>
-      <c r="C47" s="424"/>
-      <c r="E47" s="392" t="s">
-        <v>1009</v>
-      </c>
-      <c r="F47" s="392" t="s">
-        <v>997</v>
-      </c>
-      <c r="G47" s="392"/>
-      <c r="H47" s="392"/>
-      <c r="I47" s="392"/>
-      <c r="J47" s="420"/>
+      <c r="A47" s="394"/>
+      <c r="B47" s="394"/>
+      <c r="C47" s="423"/>
+      <c r="E47" s="391" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F47" s="391" t="s">
+        <v>992</v>
+      </c>
+      <c r="G47" s="391"/>
+      <c r="H47" s="391"/>
+      <c r="I47" s="391"/>
+      <c r="J47" s="419"/>
       <c r="K47" s="305"/>
       <c r="L47" s="305"/>
     </row>
     <row r="48" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A48" s="395"/>
-      <c r="B48" s="395"/>
-      <c r="C48" s="424"/>
-      <c r="E48" s="392" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F48" s="392" t="s">
-        <v>997</v>
-      </c>
-      <c r="G48" s="392"/>
-      <c r="H48" s="392"/>
-      <c r="I48" s="392"/>
-      <c r="J48" s="420"/>
+      <c r="A48" s="394"/>
+      <c r="B48" s="394"/>
+      <c r="C48" s="423"/>
+      <c r="E48" s="391" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F48" s="391" t="s">
+        <v>992</v>
+      </c>
+      <c r="G48" s="391"/>
+      <c r="H48" s="391"/>
+      <c r="I48" s="391"/>
+      <c r="J48" s="419"/>
       <c r="K48" s="305"/>
       <c r="L48" s="305"/>
     </row>
     <row r="49" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A49" s="395"/>
-      <c r="B49" s="395"/>
-      <c r="C49" s="424"/>
-      <c r="E49" s="392" t="s">
+      <c r="A49" s="394"/>
+      <c r="B49" s="394"/>
+      <c r="C49" s="423"/>
+      <c r="E49" s="391" t="s">
         <v>730</v>
       </c>
-      <c r="F49" s="392" t="s">
+      <c r="F49" s="391" t="s">
         <v>731</v>
       </c>
-      <c r="G49" s="392"/>
-      <c r="H49" s="392"/>
-      <c r="I49" s="392"/>
-      <c r="J49" s="420"/>
+      <c r="G49" s="391"/>
+      <c r="H49" s="391"/>
+      <c r="I49" s="391"/>
+      <c r="J49" s="419"/>
       <c r="K49" s="305"/>
       <c r="L49" s="305"/>
     </row>
     <row r="50" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A50" s="395"/>
-      <c r="B50" s="395"/>
-      <c r="C50" s="424"/>
-      <c r="E50" s="392" t="s">
+      <c r="A50" s="394"/>
+      <c r="B50" s="394"/>
+      <c r="C50" s="423"/>
+      <c r="E50" s="391" t="s">
         <v>739</v>
       </c>
-      <c r="F50" s="392" t="s">
+      <c r="F50" s="391" t="s">
         <v>731</v>
       </c>
-      <c r="G50" s="392"/>
-      <c r="H50" s="392"/>
-      <c r="I50" s="392"/>
-      <c r="J50" s="420"/>
+      <c r="G50" s="391"/>
+      <c r="H50" s="391"/>
+      <c r="I50" s="391"/>
+      <c r="J50" s="419"/>
       <c r="K50" s="305"/>
       <c r="L50" s="305"/>
     </row>
     <row r="51" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A51" s="395"/>
-      <c r="B51" s="395"/>
-      <c r="C51" s="425">
+      <c r="A51" s="394"/>
+      <c r="B51" s="394"/>
+      <c r="C51" s="424">
         <v>6</v>
       </c>
-      <c r="D51" s="414" t="s">
+      <c r="D51" s="413" t="s">
         <v>748</v>
       </c>
-      <c r="E51" s="415"/>
-      <c r="F51" s="415"/>
-      <c r="G51" s="415"/>
-      <c r="H51" s="415"/>
-      <c r="I51" s="415"/>
-      <c r="J51" s="416"/>
+      <c r="E51" s="414"/>
+      <c r="F51" s="414"/>
+      <c r="G51" s="414"/>
+      <c r="H51" s="414"/>
+      <c r="I51" s="414"/>
+      <c r="J51" s="415"/>
       <c r="K51" s="305"/>
       <c r="L51" s="305"/>
     </row>
     <row r="52" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A52" s="395"/>
-      <c r="B52" s="395"/>
-      <c r="C52" s="424"/>
-      <c r="E52" s="392"/>
+      <c r="A52" s="394"/>
+      <c r="B52" s="394"/>
+      <c r="C52" s="423"/>
+      <c r="E52" s="391"/>
       <c r="F52" s="362"/>
-      <c r="G52" s="419"/>
-      <c r="H52" s="392"/>
-      <c r="I52" s="419"/>
-      <c r="J52" s="420"/>
+      <c r="G52" s="418"/>
+      <c r="H52" s="391"/>
+      <c r="I52" s="418"/>
+      <c r="J52" s="419"/>
       <c r="K52" s="305"/>
       <c r="L52" s="305"/>
     </row>
     <row r="53" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A53" s="395"/>
-      <c r="B53" s="395"/>
-      <c r="C53" s="424"/>
-      <c r="E53" s="392"/>
+      <c r="A53" s="394"/>
+      <c r="B53" s="394"/>
+      <c r="C53" s="423"/>
+      <c r="E53" s="391"/>
       <c r="F53" s="362"/>
-      <c r="G53" s="392"/>
-      <c r="H53" s="392"/>
-      <c r="I53" s="419"/>
-      <c r="J53" s="420"/>
+      <c r="G53" s="391"/>
+      <c r="H53" s="391"/>
+      <c r="I53" s="418"/>
+      <c r="J53" s="419"/>
       <c r="K53" s="305"/>
       <c r="L53" s="305"/>
     </row>
     <row r="54" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A54" s="395"/>
-      <c r="B54" s="395"/>
-      <c r="C54" s="424"/>
+      <c r="A54" s="394"/>
+      <c r="B54" s="394"/>
+      <c r="C54" s="423"/>
       <c r="D54" s="312"/>
-      <c r="E54" s="392"/>
+      <c r="E54" s="391"/>
       <c r="F54" s="362"/>
-      <c r="G54" s="392"/>
-      <c r="H54" s="419"/>
-      <c r="I54" s="419"/>
-      <c r="J54" s="420"/>
+      <c r="G54" s="391"/>
+      <c r="H54" s="418"/>
+      <c r="I54" s="418"/>
+      <c r="J54" s="419"/>
       <c r="K54" s="305"/>
       <c r="L54" s="305"/>
     </row>
     <row r="55" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A55" s="395"/>
-      <c r="B55" s="395"/>
-      <c r="C55" s="424"/>
-      <c r="E55" s="392"/>
-      <c r="F55" s="392"/>
-      <c r="G55" s="392"/>
-      <c r="H55" s="392"/>
-      <c r="I55" s="392"/>
-      <c r="J55" s="420"/>
+      <c r="A55" s="394"/>
+      <c r="B55" s="394"/>
+      <c r="C55" s="423"/>
+      <c r="E55" s="391"/>
+      <c r="F55" s="391"/>
+      <c r="G55" s="391"/>
+      <c r="H55" s="391"/>
+      <c r="I55" s="391"/>
+      <c r="J55" s="419"/>
       <c r="K55" s="305"/>
       <c r="L55" s="305"/>
     </row>
     <row r="56" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A56" s="395"/>
-      <c r="B56" s="395"/>
-      <c r="C56" s="424"/>
-      <c r="E56" s="392"/>
-      <c r="F56" s="392"/>
-      <c r="G56" s="392"/>
-      <c r="H56" s="392"/>
-      <c r="I56" s="392"/>
-      <c r="J56" s="420"/>
+      <c r="A56" s="394"/>
+      <c r="B56" s="394"/>
+      <c r="C56" s="423"/>
+      <c r="E56" s="391"/>
+      <c r="F56" s="391"/>
+      <c r="G56" s="391"/>
+      <c r="H56" s="391"/>
+      <c r="I56" s="391"/>
+      <c r="J56" s="419"/>
       <c r="K56" s="305"/>
       <c r="L56" s="305"/>
     </row>
     <row r="57" spans="1:12" ht="16.5" customHeight="1">
-      <c r="A57" s="395"/>
-      <c r="B57" s="395"/>
-      <c r="C57" s="424"/>
+      <c r="A57" s="394"/>
+      <c r="B57" s="394"/>
+      <c r="C57" s="423"/>
       <c r="E57" s="363"/>
-      <c r="F57" s="392"/>
-      <c r="G57" s="392"/>
-      <c r="H57" s="392"/>
-      <c r="I57" s="392"/>
-      <c r="J57" s="420"/>
+      <c r="F57" s="391"/>
+      <c r="G57" s="391"/>
+      <c r="H57" s="391"/>
+      <c r="I57" s="391"/>
+      <c r="J57" s="419"/>
       <c r="K57" s="305"/>
       <c r="L57" s="305"/>
     </row>
     <row r="58" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A58" s="395"/>
-      <c r="B58" s="395"/>
-      <c r="C58" s="425">
+      <c r="A58" s="394"/>
+      <c r="B58" s="394"/>
+      <c r="C58" s="424">
         <v>7</v>
       </c>
-      <c r="D58" s="414" t="s">
+      <c r="D58" s="413" t="s">
         <v>748</v>
       </c>
-      <c r="E58" s="415"/>
-      <c r="F58" s="415"/>
-      <c r="G58" s="415"/>
-      <c r="H58" s="415"/>
-      <c r="I58" s="415"/>
-      <c r="J58" s="416"/>
+      <c r="E58" s="414"/>
+      <c r="F58" s="414"/>
+      <c r="G58" s="414"/>
+      <c r="H58" s="414"/>
+      <c r="I58" s="414"/>
+      <c r="J58" s="415"/>
       <c r="K58" s="305"/>
       <c r="L58" s="305"/>
     </row>
     <row r="59" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A59" s="395"/>
-      <c r="B59" s="395"/>
-      <c r="C59" s="424"/>
-      <c r="E59" s="392"/>
-      <c r="F59" s="392"/>
-      <c r="G59" s="392"/>
-      <c r="H59" s="392"/>
-      <c r="I59" s="392"/>
-      <c r="J59" s="420"/>
+      <c r="A59" s="394"/>
+      <c r="B59" s="394"/>
+      <c r="C59" s="423"/>
+      <c r="E59" s="391"/>
+      <c r="F59" s="391"/>
+      <c r="G59" s="391"/>
+      <c r="H59" s="391"/>
+      <c r="I59" s="391"/>
+      <c r="J59" s="419"/>
       <c r="K59" s="305"/>
       <c r="L59" s="305"/>
     </row>
     <row r="60" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A60" s="395"/>
-      <c r="B60" s="395"/>
-      <c r="C60" s="424"/>
+      <c r="A60" s="394"/>
+      <c r="B60" s="394"/>
+      <c r="C60" s="423"/>
       <c r="D60" s="304"/>
-      <c r="E60" s="392"/>
-      <c r="F60" s="392"/>
-      <c r="G60" s="392"/>
-      <c r="H60" s="392"/>
-      <c r="I60" s="392"/>
-      <c r="J60" s="420"/>
+      <c r="E60" s="391"/>
+      <c r="F60" s="391"/>
+      <c r="G60" s="391"/>
+      <c r="H60" s="391"/>
+      <c r="I60" s="391"/>
+      <c r="J60" s="419"/>
       <c r="K60" s="305"/>
       <c r="L60" s="305"/>
     </row>
     <row r="61" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A61" s="395"/>
-      <c r="B61" s="395"/>
-      <c r="C61" s="424"/>
-      <c r="E61" s="392"/>
-      <c r="F61" s="392"/>
-      <c r="G61" s="392"/>
-      <c r="H61" s="392"/>
-      <c r="I61" s="392"/>
-      <c r="J61" s="420"/>
+      <c r="A61" s="394"/>
+      <c r="B61" s="394"/>
+      <c r="C61" s="423"/>
+      <c r="E61" s="391"/>
+      <c r="F61" s="391"/>
+      <c r="G61" s="391"/>
+      <c r="H61" s="391"/>
+      <c r="I61" s="391"/>
+      <c r="J61" s="419"/>
       <c r="K61" s="305"/>
       <c r="L61" s="305"/>
     </row>
     <row r="62" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A62" s="395"/>
-      <c r="B62" s="395"/>
-      <c r="C62" s="424"/>
-      <c r="E62" s="392"/>
-      <c r="F62" s="392"/>
-      <c r="G62" s="392"/>
-      <c r="H62" s="392"/>
-      <c r="I62" s="392"/>
-      <c r="J62" s="420"/>
+      <c r="A62" s="394"/>
+      <c r="B62" s="394"/>
+      <c r="C62" s="423"/>
+      <c r="E62" s="391"/>
+      <c r="F62" s="391"/>
+      <c r="G62" s="391"/>
+      <c r="H62" s="391"/>
+      <c r="I62" s="391"/>
+      <c r="J62" s="419"/>
       <c r="K62" s="305"/>
       <c r="L62" s="305"/>
     </row>
     <row r="63" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A63" s="395"/>
-      <c r="B63" s="395"/>
-      <c r="C63" s="424"/>
-      <c r="E63" s="392"/>
-      <c r="F63" s="392"/>
-      <c r="G63" s="392"/>
-      <c r="H63" s="392"/>
-      <c r="I63" s="392"/>
-      <c r="J63" s="420"/>
+      <c r="A63" s="394"/>
+      <c r="B63" s="394"/>
+      <c r="C63" s="423"/>
+      <c r="E63" s="391"/>
+      <c r="F63" s="391"/>
+      <c r="G63" s="391"/>
+      <c r="H63" s="391"/>
+      <c r="I63" s="391"/>
+      <c r="J63" s="419"/>
       <c r="K63" s="305"/>
       <c r="L63" s="305"/>
     </row>
     <row r="64" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A64" s="395"/>
-      <c r="B64" s="395"/>
-      <c r="C64" s="424"/>
-      <c r="E64" s="392"/>
-      <c r="F64" s="392"/>
-      <c r="G64" s="392"/>
-      <c r="H64" s="392"/>
-      <c r="I64" s="392"/>
-      <c r="J64" s="420"/>
+      <c r="A64" s="394"/>
+      <c r="B64" s="394"/>
+      <c r="C64" s="423"/>
+      <c r="E64" s="391"/>
+      <c r="F64" s="391"/>
+      <c r="G64" s="391"/>
+      <c r="H64" s="391"/>
+      <c r="I64" s="391"/>
+      <c r="J64" s="419"/>
       <c r="K64" s="305"/>
       <c r="L64" s="305"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A65" s="395"/>
-      <c r="B65" s="395"/>
-      <c r="C65" s="424"/>
-      <c r="E65" s="392"/>
-      <c r="F65" s="392"/>
-      <c r="G65" s="392"/>
-      <c r="H65" s="392"/>
-      <c r="I65" s="392"/>
-      <c r="J65" s="420"/>
+      <c r="A65" s="394"/>
+      <c r="B65" s="394"/>
+      <c r="C65" s="423"/>
+      <c r="E65" s="391"/>
+      <c r="F65" s="391"/>
+      <c r="G65" s="391"/>
+      <c r="H65" s="391"/>
+      <c r="I65" s="391"/>
+      <c r="J65" s="419"/>
       <c r="K65" s="305"/>
       <c r="L65" s="305"/>
     </row>
     <row r="66" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A66" s="395"/>
-      <c r="B66" s="395"/>
-      <c r="C66" s="424"/>
-      <c r="E66" s="392"/>
-      <c r="F66" s="392"/>
-      <c r="G66" s="392"/>
-      <c r="H66" s="392"/>
-      <c r="I66" s="392"/>
-      <c r="J66" s="420"/>
+      <c r="A66" s="394"/>
+      <c r="B66" s="394"/>
+      <c r="C66" s="423"/>
+      <c r="E66" s="391"/>
+      <c r="F66" s="391"/>
+      <c r="G66" s="391"/>
+      <c r="H66" s="391"/>
+      <c r="I66" s="391"/>
+      <c r="J66" s="419"/>
       <c r="K66" s="305"/>
       <c r="L66" s="305"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A67" s="395"/>
-      <c r="B67" s="395"/>
-      <c r="C67" s="424"/>
-      <c r="E67" s="392"/>
-      <c r="F67" s="392"/>
-      <c r="G67" s="392"/>
-      <c r="H67" s="392"/>
-      <c r="I67" s="392"/>
-      <c r="J67" s="420"/>
+      <c r="A67" s="394"/>
+      <c r="B67" s="394"/>
+      <c r="C67" s="423"/>
+      <c r="E67" s="391"/>
+      <c r="F67" s="391"/>
+      <c r="G67" s="391"/>
+      <c r="H67" s="391"/>
+      <c r="I67" s="391"/>
+      <c r="J67" s="419"/>
       <c r="K67" s="305"/>
       <c r="L67" s="305"/>
     </row>
     <row r="68" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A68" s="395"/>
-      <c r="B68" s="395"/>
-      <c r="C68" s="424"/>
+      <c r="A68" s="394"/>
+      <c r="B68" s="394"/>
+      <c r="C68" s="423"/>
       <c r="D68" s="303"/>
-      <c r="E68" s="392"/>
-      <c r="F68" s="392"/>
-      <c r="G68" s="392"/>
-      <c r="H68" s="392"/>
-      <c r="I68" s="392"/>
-      <c r="J68" s="420"/>
+      <c r="E68" s="391"/>
+      <c r="F68" s="391"/>
+      <c r="G68" s="391"/>
+      <c r="H68" s="391"/>
+      <c r="I68" s="391"/>
+      <c r="J68" s="419"/>
       <c r="K68" s="305"/>
       <c r="L68" s="305"/>
     </row>
     <row r="69" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A69" s="395"/>
-      <c r="B69" s="395"/>
-      <c r="C69" s="424"/>
-      <c r="D69" s="426"/>
-      <c r="E69" s="439"/>
-      <c r="F69" s="439"/>
-      <c r="G69" s="439"/>
-      <c r="H69" s="439"/>
-      <c r="I69" s="439"/>
-      <c r="J69" s="440"/>
+      <c r="A69" s="394"/>
+      <c r="B69" s="394"/>
+      <c r="C69" s="423"/>
+      <c r="D69" s="425"/>
+      <c r="E69" s="438"/>
+      <c r="F69" s="438"/>
+      <c r="G69" s="438"/>
+      <c r="H69" s="438"/>
+      <c r="I69" s="438"/>
+      <c r="J69" s="439"/>
       <c r="K69" s="305"/>
       <c r="L69" s="305"/>
     </row>
     <row r="70" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A70" s="395"/>
-      <c r="B70" s="395"/>
-      <c r="C70" s="424"/>
-      <c r="D70" s="426"/>
-      <c r="E70" s="427"/>
-      <c r="F70" s="427"/>
-      <c r="G70" s="427"/>
-      <c r="H70" s="427"/>
-      <c r="I70" s="427"/>
-      <c r="J70" s="428"/>
+      <c r="A70" s="394"/>
+      <c r="B70" s="394"/>
+      <c r="C70" s="423"/>
+      <c r="D70" s="425"/>
+      <c r="E70" s="426"/>
+      <c r="F70" s="426"/>
+      <c r="G70" s="426"/>
+      <c r="H70" s="426"/>
+      <c r="I70" s="426"/>
+      <c r="J70" s="427"/>
       <c r="K70" s="305"/>
       <c r="L70" s="305"/>
     </row>
     <row r="71" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A71" s="395"/>
-      <c r="B71" s="395"/>
-      <c r="C71" s="438"/>
-      <c r="D71" s="430"/>
-      <c r="E71" s="427"/>
-      <c r="F71" s="427"/>
-      <c r="G71" s="427"/>
-      <c r="H71" s="427"/>
-      <c r="I71" s="427"/>
-      <c r="J71" s="428"/>
+      <c r="A71" s="394"/>
+      <c r="B71" s="394"/>
+      <c r="C71" s="437"/>
+      <c r="D71" s="429"/>
+      <c r="E71" s="426"/>
+      <c r="F71" s="426"/>
+      <c r="G71" s="426"/>
+      <c r="H71" s="426"/>
+      <c r="I71" s="426"/>
+      <c r="J71" s="427"/>
       <c r="K71" s="305"/>
       <c r="L71" s="305"/>
     </row>
     <row r="72" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A72" s="395"/>
-      <c r="B72" s="395"/>
-      <c r="C72" s="425">
+      <c r="A72" s="394"/>
+      <c r="B72" s="394"/>
+      <c r="C72" s="424">
         <v>8</v>
       </c>
-      <c r="D72" s="414" t="s">
+      <c r="D72" s="413" t="s">
         <v>748</v>
       </c>
-      <c r="E72" s="415"/>
-      <c r="F72" s="415"/>
-      <c r="G72" s="415"/>
-      <c r="H72" s="415"/>
-      <c r="I72" s="415"/>
-      <c r="J72" s="416"/>
+      <c r="E72" s="414"/>
+      <c r="F72" s="414"/>
+      <c r="G72" s="414"/>
+      <c r="H72" s="414"/>
+      <c r="I72" s="414"/>
+      <c r="J72" s="415"/>
       <c r="K72" s="305"/>
       <c r="L72" s="305"/>
     </row>
     <row r="73" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A73" s="395"/>
-      <c r="B73" s="395"/>
-      <c r="C73" s="424"/>
-      <c r="E73" s="392"/>
-      <c r="F73" s="392"/>
-      <c r="G73" s="392"/>
-      <c r="H73" s="392"/>
-      <c r="I73" s="392"/>
-      <c r="J73" s="420"/>
+      <c r="A73" s="394"/>
+      <c r="B73" s="394"/>
+      <c r="C73" s="423"/>
+      <c r="E73" s="391"/>
+      <c r="F73" s="391"/>
+      <c r="G73" s="391"/>
+      <c r="H73" s="391"/>
+      <c r="I73" s="391"/>
+      <c r="J73" s="419"/>
       <c r="K73" s="305"/>
       <c r="L73" s="305"/>
     </row>
     <row r="74" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A74" s="395"/>
-      <c r="B74" s="395"/>
-      <c r="C74" s="424"/>
+      <c r="A74" s="394"/>
+      <c r="B74" s="394"/>
+      <c r="C74" s="423"/>
       <c r="D74" s="304"/>
-      <c r="E74" s="392"/>
-      <c r="F74" s="392"/>
-      <c r="G74" s="392"/>
-      <c r="H74" s="392"/>
-      <c r="I74" s="392"/>
-      <c r="J74" s="420"/>
+      <c r="E74" s="391"/>
+      <c r="F74" s="391"/>
+      <c r="G74" s="391"/>
+      <c r="H74" s="391"/>
+      <c r="I74" s="391"/>
+      <c r="J74" s="419"/>
       <c r="K74" s="305"/>
       <c r="L74" s="305"/>
     </row>
     <row r="75" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A75" s="395"/>
-      <c r="B75" s="395"/>
-      <c r="C75" s="424"/>
-      <c r="E75" s="392"/>
-      <c r="F75" s="392"/>
-      <c r="G75" s="392"/>
-      <c r="H75" s="392"/>
-      <c r="I75" s="392"/>
-      <c r="J75" s="420"/>
+      <c r="A75" s="394"/>
+      <c r="B75" s="394"/>
+      <c r="C75" s="423"/>
+      <c r="E75" s="391"/>
+      <c r="F75" s="391"/>
+      <c r="G75" s="391"/>
+      <c r="H75" s="391"/>
+      <c r="I75" s="391"/>
+      <c r="J75" s="419"/>
       <c r="K75" s="305"/>
       <c r="L75" s="305"/>
     </row>
     <row r="76" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A76" s="395"/>
-      <c r="B76" s="395"/>
-      <c r="C76" s="424"/>
-      <c r="E76" s="392"/>
-      <c r="F76" s="392"/>
-      <c r="G76" s="392"/>
-      <c r="H76" s="392"/>
-      <c r="I76" s="392"/>
-      <c r="J76" s="420"/>
+      <c r="A76" s="394"/>
+      <c r="B76" s="394"/>
+      <c r="C76" s="423"/>
+      <c r="E76" s="391"/>
+      <c r="F76" s="391"/>
+      <c r="G76" s="391"/>
+      <c r="H76" s="391"/>
+      <c r="I76" s="391"/>
+      <c r="J76" s="419"/>
       <c r="K76" s="305"/>
       <c r="L76" s="305"/>
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A77" s="395"/>
-      <c r="B77" s="395"/>
-      <c r="C77" s="424"/>
-      <c r="E77" s="392"/>
-      <c r="F77" s="392"/>
-      <c r="G77" s="392"/>
-      <c r="H77" s="392"/>
-      <c r="I77" s="392"/>
-      <c r="J77" s="420"/>
+      <c r="A77" s="394"/>
+      <c r="B77" s="394"/>
+      <c r="C77" s="423"/>
+      <c r="E77" s="391"/>
+      <c r="F77" s="391"/>
+      <c r="G77" s="391"/>
+      <c r="H77" s="391"/>
+      <c r="I77" s="391"/>
+      <c r="J77" s="419"/>
       <c r="K77" s="305"/>
       <c r="L77" s="305"/>
     </row>
     <row r="78" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A78" s="395"/>
-      <c r="B78" s="395"/>
-      <c r="C78" s="424"/>
-      <c r="E78" s="392"/>
-      <c r="F78" s="392"/>
-      <c r="G78" s="392"/>
-      <c r="H78" s="392"/>
-      <c r="I78" s="392"/>
-      <c r="J78" s="420"/>
+      <c r="A78" s="394"/>
+      <c r="B78" s="394"/>
+      <c r="C78" s="423"/>
+      <c r="E78" s="391"/>
+      <c r="F78" s="391"/>
+      <c r="G78" s="391"/>
+      <c r="H78" s="391"/>
+      <c r="I78" s="391"/>
+      <c r="J78" s="419"/>
       <c r="K78" s="305"/>
       <c r="L78" s="305"/>
     </row>
     <row r="79" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A79" s="395"/>
-      <c r="B79" s="395"/>
-      <c r="C79" s="424"/>
-      <c r="E79" s="392"/>
-      <c r="F79" s="392"/>
-      <c r="G79" s="392"/>
-      <c r="H79" s="392"/>
-      <c r="I79" s="392"/>
-      <c r="J79" s="420"/>
+      <c r="A79" s="394"/>
+      <c r="B79" s="394"/>
+      <c r="C79" s="423"/>
+      <c r="E79" s="391"/>
+      <c r="F79" s="391"/>
+      <c r="G79" s="391"/>
+      <c r="H79" s="391"/>
+      <c r="I79" s="391"/>
+      <c r="J79" s="419"/>
       <c r="K79" s="305"/>
       <c r="L79" s="305"/>
     </row>
     <row r="80" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A80" s="395"/>
-      <c r="B80" s="395"/>
-      <c r="C80" s="424"/>
-      <c r="E80" s="392"/>
-      <c r="F80" s="392"/>
-      <c r="G80" s="392"/>
-      <c r="H80" s="392"/>
-      <c r="I80" s="392"/>
-      <c r="J80" s="420"/>
+      <c r="A80" s="394"/>
+      <c r="B80" s="394"/>
+      <c r="C80" s="423"/>
+      <c r="E80" s="391"/>
+      <c r="F80" s="391"/>
+      <c r="G80" s="391"/>
+      <c r="H80" s="391"/>
+      <c r="I80" s="391"/>
+      <c r="J80" s="419"/>
       <c r="K80" s="305"/>
       <c r="L80" s="305"/>
     </row>
     <row r="81" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A81" s="395"/>
-      <c r="B81" s="395"/>
-      <c r="C81" s="424"/>
-      <c r="E81" s="392"/>
-      <c r="F81" s="392"/>
-      <c r="G81" s="392"/>
-      <c r="H81" s="392"/>
-      <c r="I81" s="392"/>
-      <c r="J81" s="420"/>
+      <c r="A81" s="394"/>
+      <c r="B81" s="394"/>
+      <c r="C81" s="423"/>
+      <c r="E81" s="391"/>
+      <c r="F81" s="391"/>
+      <c r="G81" s="391"/>
+      <c r="H81" s="391"/>
+      <c r="I81" s="391"/>
+      <c r="J81" s="419"/>
       <c r="K81" s="305"/>
       <c r="L81" s="305"/>
     </row>
     <row r="82" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A82" s="395"/>
-      <c r="B82" s="395"/>
-      <c r="C82" s="424"/>
+      <c r="A82" s="394"/>
+      <c r="B82" s="394"/>
+      <c r="C82" s="423"/>
       <c r="D82" s="303"/>
-      <c r="E82" s="392"/>
-      <c r="F82" s="392"/>
-      <c r="G82" s="392"/>
-      <c r="H82" s="392"/>
-      <c r="I82" s="392"/>
-      <c r="J82" s="420"/>
+      <c r="E82" s="391"/>
+      <c r="F82" s="391"/>
+      <c r="G82" s="391"/>
+      <c r="H82" s="391"/>
+      <c r="I82" s="391"/>
+      <c r="J82" s="419"/>
       <c r="K82" s="305"/>
       <c r="L82" s="305"/>
     </row>
     <row r="83" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A83" s="395"/>
-      <c r="B83" s="395"/>
-      <c r="C83" s="424"/>
-      <c r="D83" s="426"/>
-      <c r="E83" s="439"/>
-      <c r="F83" s="439"/>
-      <c r="G83" s="439"/>
-      <c r="H83" s="439"/>
-      <c r="I83" s="439"/>
-      <c r="J83" s="440"/>
+      <c r="A83" s="394"/>
+      <c r="B83" s="394"/>
+      <c r="C83" s="423"/>
+      <c r="D83" s="425"/>
+      <c r="E83" s="438"/>
+      <c r="F83" s="438"/>
+      <c r="G83" s="438"/>
+      <c r="H83" s="438"/>
+      <c r="I83" s="438"/>
+      <c r="J83" s="439"/>
       <c r="K83" s="305"/>
       <c r="L83" s="305"/>
     </row>
     <row r="84" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A84" s="395"/>
-      <c r="B84" s="395"/>
-      <c r="C84" s="424"/>
-      <c r="D84" s="426"/>
-      <c r="E84" s="427"/>
-      <c r="F84" s="427"/>
-      <c r="G84" s="427"/>
-      <c r="H84" s="427"/>
-      <c r="I84" s="427"/>
-      <c r="J84" s="428"/>
+      <c r="A84" s="394"/>
+      <c r="B84" s="394"/>
+      <c r="C84" s="423"/>
+      <c r="D84" s="425"/>
+      <c r="E84" s="426"/>
+      <c r="F84" s="426"/>
+      <c r="G84" s="426"/>
+      <c r="H84" s="426"/>
+      <c r="I84" s="426"/>
+      <c r="J84" s="427"/>
       <c r="K84" s="305"/>
       <c r="L84" s="305"/>
     </row>
     <row r="85" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A85" s="395"/>
-      <c r="B85" s="395"/>
-      <c r="C85" s="438"/>
-      <c r="D85" s="430"/>
-      <c r="E85" s="427"/>
-      <c r="F85" s="427"/>
-      <c r="G85" s="427"/>
-      <c r="H85" s="427"/>
-      <c r="I85" s="427"/>
-      <c r="J85" s="428"/>
+      <c r="A85" s="394"/>
+      <c r="B85" s="394"/>
+      <c r="C85" s="437"/>
+      <c r="D85" s="429"/>
+      <c r="E85" s="426"/>
+      <c r="F85" s="426"/>
+      <c r="G85" s="426"/>
+      <c r="H85" s="426"/>
+      <c r="I85" s="426"/>
+      <c r="J85" s="427"/>
       <c r="K85" s="305"/>
       <c r="L85" s="305"/>
     </row>
     <row r="86" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A86" s="395"/>
-      <c r="B86" s="395"/>
-      <c r="C86" s="441"/>
+      <c r="A86" s="394"/>
+      <c r="B86" s="394"/>
+      <c r="C86" s="440"/>
       <c r="D86" s="305"/>
       <c r="E86" s="305"/>
       <c r="F86" s="305"/>
@@ -10621,11 +10843,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="475" t="s">
+      <c r="C4" s="480" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="476"/>
-      <c r="E4" s="476"/>
+      <c r="D4" s="481"/>
+      <c r="E4" s="481"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10634,13 +10856,13 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
-      <c r="C5" s="479" t="s">
+      <c r="C5" s="484" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="477" t="s">
+      <c r="D5" s="482" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="478"/>
+      <c r="E5" s="483"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10649,11 +10871,11 @@
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="472"/>
-      <c r="D6" s="467" t="s">
+      <c r="C6" s="477"/>
+      <c r="D6" s="472" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="468"/>
+      <c r="E6" s="473"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10662,11 +10884,11 @@
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="472"/>
-      <c r="D7" s="467" t="s">
+      <c r="C7" s="477"/>
+      <c r="D7" s="472" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="468"/>
+      <c r="E7" s="473"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10675,11 +10897,11 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="472"/>
-      <c r="D8" s="467" t="s">
+      <c r="C8" s="477"/>
+      <c r="D8" s="472" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="468"/>
+      <c r="E8" s="473"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10688,11 +10910,11 @@
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="472"/>
-      <c r="D9" s="467" t="s">
+      <c r="C9" s="477"/>
+      <c r="D9" s="472" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="468"/>
+      <c r="E9" s="473"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10701,11 +10923,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="473"/>
-      <c r="D10" s="467" t="s">
+      <c r="C10" s="478"/>
+      <c r="D10" s="472" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="468"/>
+      <c r="E10" s="473"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10714,13 +10936,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="474" t="s">
+      <c r="C11" s="479" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="467" t="s">
+      <c r="D11" s="472" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="468"/>
+      <c r="E11" s="473"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10729,11 +10951,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="473"/>
-      <c r="D12" s="467" t="s">
+      <c r="C12" s="478"/>
+      <c r="D12" s="472" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="468"/>
+      <c r="E12" s="473"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10742,13 +10964,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="474" t="s">
+      <c r="C13" s="479" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="467" t="s">
+      <c r="D13" s="472" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="468"/>
+      <c r="E13" s="473"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10757,11 +10979,11 @@
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="472"/>
-      <c r="D14" s="467" t="s">
+      <c r="C14" s="477"/>
+      <c r="D14" s="472" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="468"/>
+      <c r="E14" s="473"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10770,11 +10992,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="473"/>
-      <c r="D15" s="467" t="s">
+      <c r="C15" s="478"/>
+      <c r="D15" s="472" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="468"/>
+      <c r="E15" s="473"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -10783,13 +11005,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="474" t="s">
+      <c r="C16" s="479" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="469" t="s">
+      <c r="D16" s="474" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="470"/>
+      <c r="E16" s="475"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -10798,8 +11020,8 @@
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="472"/>
-      <c r="D17" s="471" t="s">
+      <c r="C17" s="477"/>
+      <c r="D17" s="476" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="107" t="s">
@@ -10813,8 +11035,8 @@
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="472"/>
-      <c r="D18" s="472"/>
+      <c r="C18" s="477"/>
+      <c r="D18" s="477"/>
       <c r="E18" s="107" t="s">
         <v>134</v>
       </c>
@@ -10826,8 +11048,8 @@
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="472"/>
-      <c r="D19" s="472"/>
+      <c r="C19" s="477"/>
+      <c r="D19" s="477"/>
       <c r="E19" s="107" t="s">
         <v>137</v>
       </c>
@@ -10839,8 +11061,8 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="472"/>
-      <c r="D20" s="472"/>
+      <c r="C20" s="477"/>
+      <c r="D20" s="477"/>
       <c r="E20" s="107" t="s">
         <v>140</v>
       </c>
@@ -10852,8 +11074,8 @@
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="472"/>
-      <c r="D21" s="473"/>
+      <c r="C21" s="477"/>
+      <c r="D21" s="478"/>
       <c r="E21" s="107" t="s">
         <v>145</v>
       </c>
@@ -10865,8 +11087,8 @@
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="472"/>
-      <c r="D22" s="480" t="s">
+      <c r="C22" s="477"/>
+      <c r="D22" s="485" t="s">
         <v>165</v>
       </c>
       <c r="E22" s="127" t="s">
@@ -10880,8 +11102,8 @@
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="472"/>
-      <c r="D23" s="472"/>
+      <c r="C23" s="477"/>
+      <c r="D23" s="477"/>
       <c r="E23" s="127" t="s">
         <v>177</v>
       </c>
@@ -10893,8 +11115,8 @@
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="472"/>
-      <c r="D24" s="472"/>
+      <c r="C24" s="477"/>
+      <c r="D24" s="477"/>
       <c r="E24" s="127" t="s">
         <v>179</v>
       </c>
@@ -10906,8 +11128,8 @@
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="472"/>
-      <c r="D25" s="472"/>
+      <c r="C25" s="477"/>
+      <c r="D25" s="477"/>
       <c r="E25" s="127" t="s">
         <v>185</v>
       </c>
@@ -10919,8 +11141,8 @@
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="472"/>
-      <c r="D26" s="473"/>
+      <c r="C26" s="477"/>
+      <c r="D26" s="478"/>
       <c r="E26" s="127" t="s">
         <v>190</v>
       </c>
@@ -10932,7 +11154,7 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="472"/>
+      <c r="C27" s="477"/>
       <c r="D27" s="127" t="s">
         <v>193</v>
       </c>
@@ -10947,7 +11169,7 @@
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="472"/>
+      <c r="C28" s="477"/>
       <c r="D28" s="105" t="s">
         <v>221</v>
       </c>
@@ -10962,8 +11184,8 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="472"/>
-      <c r="D29" s="471" t="s">
+      <c r="C29" s="477"/>
+      <c r="D29" s="476" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="127" t="s">
@@ -10977,8 +11199,8 @@
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
       <c r="E30" s="127" t="s">
         <v>244</v>
       </c>
@@ -10990,8 +11212,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="473"/>
-      <c r="D31" s="473"/>
+      <c r="C31" s="478"/>
+      <c r="D31" s="478"/>
       <c r="E31" s="127" t="s">
         <v>249</v>
       </c>
@@ -11003,13 +11225,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="474" t="s">
+      <c r="C32" s="479" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="467" t="s">
+      <c r="D32" s="472" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="468"/>
+      <c r="E32" s="473"/>
       <c r="F32" s="159" t="s">
         <v>259</v>
       </c>
@@ -11017,11 +11239,11 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="472"/>
-      <c r="D33" s="467" t="s">
+      <c r="C33" s="477"/>
+      <c r="D33" s="472" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="468"/>
+      <c r="E33" s="473"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -11030,11 +11252,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="473"/>
-      <c r="D34" s="467" t="s">
+      <c r="C34" s="478"/>
+      <c r="D34" s="472" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="468"/>
+      <c r="E34" s="473"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -12496,14 +12718,14 @@
       <c r="E10" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="F10" s="459" t="s">
-        <v>1062</v>
+      <c r="F10" s="457" t="s">
+        <v>1056</v>
       </c>
       <c r="G10" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="H10" s="460" t="s">
-        <v>1063</v>
+      <c r="H10" s="458" t="s">
+        <v>1057</v>
       </c>
       <c r="I10" s="10"/>
     </row>
@@ -14392,7 +14614,7 @@
     <row r="71" spans="1:8" ht="26">
       <c r="A71" s="279"/>
       <c r="B71" s="279"/>
-      <c r="C71" s="481">
+      <c r="C71" s="486">
         <v>16</v>
       </c>
       <c r="D71" s="280" t="s">
@@ -14412,7 +14634,7 @@
     <row r="72" spans="1:8" ht="39">
       <c r="A72" s="279"/>
       <c r="B72" s="279"/>
-      <c r="C72" s="472"/>
+      <c r="C72" s="477"/>
       <c r="D72" s="283"/>
       <c r="E72" s="281" t="s">
         <v>742</v>
@@ -14428,7 +14650,7 @@
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="279"/>
       <c r="B73" s="279"/>
-      <c r="C73" s="473"/>
+      <c r="C73" s="478"/>
       <c r="D73" s="284"/>
       <c r="E73" s="281" t="s">
         <v>745</v>
@@ -17466,7 +17688,7 @@
     <col min="7" max="7" width="13.1640625" style="306" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" style="306" customWidth="1"/>
     <col min="9" max="9" width="19.83203125" style="306" customWidth="1"/>
-    <col min="10" max="10" width="8.6640625" style="456" customWidth="1"/>
+    <col min="10" max="10" width="8.6640625" style="455" customWidth="1"/>
     <col min="11" max="16384" width="12.6640625" style="306"/>
   </cols>
   <sheetData>
@@ -17480,7 +17702,7 @@
       <c r="G1" s="305"/>
       <c r="H1" s="305"/>
       <c r="I1" s="305"/>
-      <c r="J1" s="454"/>
+      <c r="J1" s="453"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1">
       <c r="A2" s="303"/>
@@ -17492,7 +17714,7 @@
       <c r="G2" s="305"/>
       <c r="H2" s="305"/>
       <c r="I2" s="305"/>
-      <c r="J2" s="454"/>
+      <c r="J2" s="453"/>
     </row>
     <row r="3" spans="1:10" ht="27.75" customHeight="1" thickBot="1">
       <c r="A3" s="308"/>
@@ -17506,7 +17728,7 @@
       <c r="G3" s="310"/>
       <c r="H3" s="310"/>
       <c r="I3" s="310"/>
-      <c r="J3" s="455"/>
+      <c r="J3" s="454"/>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" thickTop="1">
       <c r="A4" s="312"/>
@@ -17520,7 +17742,7 @@
       <c r="G4" s="312"/>
       <c r="H4" s="312"/>
       <c r="I4" s="305"/>
-      <c r="J4" s="454"/>
+      <c r="J4" s="453"/>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1">
       <c r="A5" s="312"/>
@@ -17546,7 +17768,7 @@
       <c r="I5" s="315" t="s">
         <v>349</v>
       </c>
-      <c r="J5" s="454"/>
+      <c r="J5" s="453"/>
     </row>
     <row r="6" spans="1:10" ht="56">
       <c r="A6" s="312"/>
@@ -17572,7 +17794,7 @@
       <c r="I6" s="322" t="s">
         <v>898</v>
       </c>
-      <c r="J6" s="454"/>
+      <c r="J6" s="453"/>
     </row>
     <row r="7" spans="1:10" ht="56">
       <c r="A7" s="312"/>
@@ -17581,7 +17803,7 @@
         <v>41</v>
       </c>
       <c r="D7" s="324" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="E7" s="325" t="s">
         <v>899</v>
@@ -17590,7 +17812,7 @@
         <v>896</v>
       </c>
       <c r="G7" s="327" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="H7" s="328" t="s">
         <v>897</v>
@@ -17598,8 +17820,8 @@
       <c r="I7" s="329" t="s">
         <v>900</v>
       </c>
-      <c r="J7" s="486" t="s">
-        <v>1071</v>
+      <c r="J7" s="465" t="s">
+        <v>1064</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="154">
@@ -17609,16 +17831,16 @@
         <v>901</v>
       </c>
       <c r="D8" s="324" t="s">
-        <v>52</v>
+        <v>1067</v>
       </c>
       <c r="E8" s="325" t="s">
         <v>895</v>
       </c>
       <c r="F8" s="331" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="G8" s="332" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="H8" s="333" t="s">
         <v>903</v>
@@ -17626,7 +17848,7 @@
       <c r="I8" s="334" t="s">
         <v>904</v>
       </c>
-      <c r="J8" s="454"/>
+      <c r="J8" s="453"/>
     </row>
     <row r="9" spans="1:10" ht="45">
       <c r="A9" s="312"/>
@@ -17652,7 +17874,7 @@
       <c r="I9" s="336" t="s">
         <v>906</v>
       </c>
-      <c r="J9" s="454"/>
+      <c r="J9" s="453"/>
     </row>
     <row r="10" spans="1:10" ht="45">
       <c r="A10" s="312"/>
@@ -17670,7 +17892,7 @@
         <v>907</v>
       </c>
       <c r="G10" s="335" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="H10" s="333" t="s">
         <v>903</v>
@@ -17678,7 +17900,7 @@
       <c r="I10" s="336" t="s">
         <v>908</v>
       </c>
-      <c r="J10" s="454"/>
+      <c r="J10" s="453"/>
     </row>
     <row r="11" spans="1:10" ht="45">
       <c r="A11" s="312"/>
@@ -17704,7 +17926,7 @@
       <c r="I11" s="336" t="s">
         <v>910</v>
       </c>
-      <c r="J11" s="454"/>
+      <c r="J11" s="453"/>
     </row>
     <row r="12" spans="1:10" ht="42">
       <c r="A12" s="312"/>
@@ -17719,10 +17941,10 @@
         <v>895</v>
       </c>
       <c r="F12" s="331" t="s">
-        <v>1072</v>
-      </c>
-      <c r="G12" s="484" t="s">
-        <v>1070</v>
+        <v>1065</v>
+      </c>
+      <c r="G12" s="463" t="s">
+        <v>1063</v>
       </c>
       <c r="H12" s="333" t="s">
         <v>897</v>
@@ -17730,8 +17952,8 @@
       <c r="I12" s="339" t="s">
         <v>911</v>
       </c>
-      <c r="J12" s="485" t="s">
-        <v>1073</v>
+      <c r="J12" s="464" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="56">
@@ -17758,7 +17980,7 @@
       <c r="I13" s="334" t="s">
         <v>913</v>
       </c>
-      <c r="J13" s="454"/>
+      <c r="J13" s="453"/>
     </row>
     <row r="14" spans="1:10" ht="56">
       <c r="A14" s="312"/>
@@ -17770,13 +17992,13 @@
         <v>914</v>
       </c>
       <c r="E14" s="342" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="F14" s="326" t="s">
         <v>912</v>
       </c>
-      <c r="G14" s="335" t="s">
-        <v>915</v>
+      <c r="G14" s="466" t="s">
+        <v>1075</v>
       </c>
       <c r="H14" s="333" t="s">
         <v>903</v>
@@ -17784,7 +18006,7 @@
       <c r="I14" s="334" t="s">
         <v>916</v>
       </c>
-      <c r="J14" s="454"/>
+      <c r="J14" s="453"/>
     </row>
     <row r="15" spans="1:10" ht="42">
       <c r="A15" s="312"/>
@@ -17793,7 +18015,7 @@
         <v>84</v>
       </c>
       <c r="D15" s="324" t="s">
-        <v>85</v>
+        <v>1068</v>
       </c>
       <c r="E15" s="343" t="s">
         <v>899</v>
@@ -17810,7 +18032,7 @@
       <c r="I15" s="334" t="s">
         <v>918</v>
       </c>
-      <c r="J15" s="454"/>
+      <c r="J15" s="453"/>
     </row>
     <row r="16" spans="1:10" ht="42">
       <c r="A16" s="312"/>
@@ -17836,7 +18058,7 @@
       <c r="I16" s="334" t="s">
         <v>919</v>
       </c>
-      <c r="J16" s="454"/>
+      <c r="J16" s="453"/>
     </row>
     <row r="17" spans="1:10" ht="45">
       <c r="A17" s="312"/>
@@ -17862,7 +18084,7 @@
       <c r="I17" s="336" t="s">
         <v>922</v>
       </c>
-      <c r="J17" s="454"/>
+      <c r="J17" s="453"/>
     </row>
     <row r="18" spans="1:10" ht="60">
       <c r="A18" s="312"/>
@@ -17874,30 +18096,30 @@
         <v>108</v>
       </c>
       <c r="E18" s="348" t="s">
-        <v>923</v>
+        <v>895</v>
       </c>
       <c r="F18" s="349" t="s">
         <v>921</v>
       </c>
       <c r="G18" s="350" t="s">
-        <v>924</v>
+        <v>1075</v>
       </c>
       <c r="H18" s="351" t="s">
         <v>903</v>
       </c>
       <c r="I18" s="352" t="s">
-        <v>925</v>
-      </c>
-      <c r="J18" s="454"/>
+        <v>923</v>
+      </c>
+      <c r="J18" s="453"/>
     </row>
     <row r="19" spans="1:10" ht="45">
       <c r="A19" s="312"/>
       <c r="B19" s="304"/>
       <c r="C19" s="353" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="D19" s="354" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E19" s="355" t="s">
         <v>899</v>
@@ -17905,25 +18127,23 @@
       <c r="F19" s="356" t="s">
         <v>902</v>
       </c>
-      <c r="G19" s="357" t="s">
-        <v>928</v>
-      </c>
+      <c r="G19" s="357"/>
       <c r="H19" s="358" t="s">
         <v>903</v>
       </c>
       <c r="I19" s="359" t="s">
-        <v>929</v>
-      </c>
-      <c r="J19" s="454"/>
+        <v>926</v>
+      </c>
+      <c r="J19" s="453"/>
     </row>
     <row r="20" spans="1:10" ht="45">
       <c r="A20" s="312"/>
       <c r="B20" s="304"/>
       <c r="C20" s="353" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="D20" s="354" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="E20" s="355" t="s">
         <v>897</v>
@@ -17938,9 +18158,9 @@
         <v>903</v>
       </c>
       <c r="I20" s="359" t="s">
-        <v>1013</v>
-      </c>
-      <c r="J20" s="454"/>
+        <v>1008</v>
+      </c>
+      <c r="J20" s="453"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="312"/>
@@ -17952,7 +18172,7 @@
       <c r="G21" s="312"/>
       <c r="H21" s="312"/>
       <c r="I21" s="305"/>
-      <c r="J21" s="454"/>
+      <c r="J21" s="453"/>
     </row>
     <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="312"/>
@@ -17966,7 +18186,7 @@
       <c r="G22" s="312"/>
       <c r="H22" s="312"/>
       <c r="I22" s="305"/>
-      <c r="J22" s="454"/>
+      <c r="J22" s="453"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="312"/>
@@ -17982,87 +18202,87 @@
       <c r="G23" s="312"/>
       <c r="H23" s="312"/>
       <c r="I23" s="305"/>
-      <c r="J23" s="454"/>
+      <c r="J23" s="453"/>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="312"/>
       <c r="B24" s="304"/>
       <c r="C24" s="362" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="D24" s="363" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
       <c r="E24" s="312"/>
       <c r="F24" s="312"/>
       <c r="G24" s="312"/>
       <c r="H24" s="312"/>
       <c r="I24" s="305"/>
-      <c r="J24" s="454"/>
+      <c r="J24" s="453"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="312"/>
       <c r="B25" s="304"/>
       <c r="C25" s="365" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="D25" s="363" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="E25" s="312"/>
       <c r="F25" s="312"/>
       <c r="G25" s="312"/>
       <c r="H25" s="312"/>
       <c r="I25" s="305"/>
-      <c r="J25" s="454"/>
+      <c r="J25" s="453"/>
     </row>
     <row r="26" spans="1:10" ht="16.5" customHeight="1">
       <c r="A26" s="312"/>
       <c r="B26" s="304"/>
       <c r="C26" s="365" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="D26" s="364" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
       <c r="E26" s="312"/>
       <c r="F26" s="312"/>
       <c r="G26" s="312"/>
       <c r="H26" s="312"/>
       <c r="I26" s="305"/>
-      <c r="J26" s="454"/>
+      <c r="J26" s="453"/>
     </row>
     <row r="27" spans="1:10" ht="17.25" customHeight="1">
       <c r="A27" s="312"/>
       <c r="B27" s="304"/>
       <c r="C27" s="365" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="D27" s="364" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="E27" s="312"/>
       <c r="F27" s="312"/>
       <c r="G27" s="312"/>
       <c r="H27" s="312"/>
       <c r="I27" s="305"/>
-      <c r="J27" s="454"/>
+      <c r="J27" s="453"/>
     </row>
     <row r="28" spans="1:10" ht="14.25" customHeight="1">
       <c r="A28" s="312"/>
       <c r="B28" s="304"/>
-      <c r="C28" s="450" t="s">
-        <v>1035</v>
+      <c r="C28" s="449" t="s">
+        <v>1030</v>
       </c>
       <c r="D28" s="364" t="s">
-        <v>937</v>
+        <v>934</v>
       </c>
       <c r="E28" s="312"/>
       <c r="F28" s="312"/>
       <c r="G28" s="312"/>
       <c r="H28" s="312"/>
       <c r="I28" s="305"/>
-      <c r="J28" s="454"/>
+      <c r="J28" s="453"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1">
       <c r="A29" s="312"/>
@@ -18074,7 +18294,7 @@
       <c r="G29" s="312"/>
       <c r="H29" s="312"/>
       <c r="I29" s="305"/>
-      <c r="J29" s="454"/>
+      <c r="J29" s="453"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="312"/>
@@ -18088,7 +18308,7 @@
       <c r="G30" s="312"/>
       <c r="H30" s="312"/>
       <c r="I30" s="305"/>
-      <c r="J30" s="454"/>
+      <c r="J30" s="453"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="312"/>
@@ -18104,39 +18324,39 @@
       <c r="G31" s="312"/>
       <c r="H31" s="312"/>
       <c r="I31" s="305"/>
-      <c r="J31" s="454"/>
+      <c r="J31" s="453"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="312"/>
       <c r="B32" s="304"/>
-      <c r="C32" s="442" t="s">
-        <v>1014</v>
+      <c r="C32" s="441" t="s">
+        <v>1009</v>
       </c>
       <c r="D32" s="369" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
       <c r="E32" s="312"/>
       <c r="F32" s="312"/>
       <c r="G32" s="312"/>
       <c r="H32" s="312"/>
       <c r="I32" s="305"/>
-      <c r="J32" s="454"/>
+      <c r="J32" s="453"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1">
       <c r="A33" s="312"/>
       <c r="B33" s="304"/>
       <c r="C33" s="370" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="D33" s="369" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="E33" s="312"/>
       <c r="F33" s="312"/>
       <c r="G33" s="312"/>
       <c r="H33" s="312"/>
       <c r="I33" s="305"/>
-      <c r="J33" s="454"/>
+      <c r="J33" s="453"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="312"/>
@@ -18145,254 +18365,262 @@
         <v>901</v>
       </c>
       <c r="D34" s="369" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="E34" s="312"/>
       <c r="F34" s="312"/>
       <c r="G34" s="312"/>
       <c r="H34" s="312"/>
       <c r="I34" s="305"/>
-      <c r="J34" s="454"/>
+      <c r="J34" s="453"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="312"/>
       <c r="B35" s="304"/>
       <c r="C35" s="370" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="D35" s="369" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E35" s="312"/>
+        <v>1040</v>
+      </c>
+      <c r="E35" s="467" t="s">
+        <v>1069</v>
+      </c>
       <c r="F35" s="312"/>
       <c r="G35" s="312"/>
       <c r="H35" s="312"/>
       <c r="I35" s="305"/>
-      <c r="J35" s="454"/>
+      <c r="J35" s="453"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" customHeight="1">
       <c r="A36" s="312"/>
       <c r="B36" s="304"/>
       <c r="C36" s="370" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="D36" s="371" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="E36" s="312"/>
       <c r="F36" s="312"/>
       <c r="G36" s="312"/>
       <c r="H36" s="312"/>
       <c r="I36" s="305"/>
-      <c r="J36" s="454"/>
+      <c r="J36" s="453"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
       <c r="A37" s="312"/>
       <c r="B37" s="304"/>
       <c r="C37" s="370" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="D37" s="369" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="E37" s="312"/>
       <c r="F37" s="312"/>
       <c r="G37" s="312"/>
       <c r="H37" s="312"/>
       <c r="I37" s="305"/>
-      <c r="J37" s="454"/>
+      <c r="J37" s="453"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1">
       <c r="A38" s="312"/>
       <c r="B38" s="304"/>
       <c r="C38" s="370" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="D38" s="369" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="E38" s="312"/>
       <c r="F38" s="312"/>
       <c r="G38" s="312"/>
       <c r="H38" s="312"/>
       <c r="I38" s="305"/>
-      <c r="J38" s="454"/>
+      <c r="J38" s="453"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" customHeight="1">
       <c r="A39" s="312"/>
       <c r="B39" s="304"/>
-      <c r="C39" s="443" t="s">
-        <v>1019</v>
+      <c r="C39" s="442" t="s">
+        <v>1014</v>
       </c>
       <c r="D39" s="369" t="s">
-        <v>1050</v>
-      </c>
-      <c r="E39" s="312"/>
+        <v>1044</v>
+      </c>
+      <c r="E39" s="467" t="s">
+        <v>1070</v>
+      </c>
       <c r="F39" s="312"/>
       <c r="G39" s="312"/>
       <c r="H39" s="312"/>
       <c r="I39" s="305"/>
-      <c r="J39" s="454"/>
+      <c r="J39" s="453"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" customHeight="1">
       <c r="A40" s="312"/>
       <c r="B40" s="304"/>
       <c r="C40" s="370" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="D40" s="371" t="s">
-        <v>1051</v>
-      </c>
-      <c r="E40" s="312"/>
+        <v>1045</v>
+      </c>
+      <c r="E40" s="467" t="s">
+        <v>1071</v>
+      </c>
       <c r="F40" s="312"/>
       <c r="G40" s="312"/>
       <c r="H40" s="312"/>
       <c r="I40" s="305"/>
-      <c r="J40" s="454"/>
+      <c r="J40" s="453"/>
     </row>
     <row r="41" spans="1:10" ht="15.75" customHeight="1">
       <c r="A41" s="312"/>
       <c r="B41" s="304"/>
       <c r="C41" s="370" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="D41" s="369" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="E41" s="312"/>
       <c r="F41" s="312"/>
       <c r="G41" s="312"/>
       <c r="H41" s="312"/>
       <c r="I41" s="305"/>
-      <c r="J41" s="454"/>
+      <c r="J41" s="453"/>
     </row>
     <row r="42" spans="1:10" ht="15.75" customHeight="1">
       <c r="A42" s="312"/>
       <c r="B42" s="304"/>
-      <c r="C42" s="443" t="s">
-        <v>1022</v>
+      <c r="C42" s="442" t="s">
+        <v>1017</v>
       </c>
       <c r="D42" s="372" t="s">
-        <v>1053</v>
-      </c>
-      <c r="E42" s="312"/>
+        <v>1047</v>
+      </c>
+      <c r="E42" s="467" t="s">
+        <v>1070</v>
+      </c>
       <c r="F42" s="312"/>
       <c r="G42" s="312"/>
       <c r="H42" s="312"/>
       <c r="I42" s="305"/>
-      <c r="J42" s="454"/>
+      <c r="J42" s="453"/>
     </row>
     <row r="43" spans="1:10" ht="15.75" customHeight="1">
       <c r="A43" s="312"/>
       <c r="B43" s="304"/>
       <c r="C43" s="370" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="D43" s="369" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="E43" s="312"/>
       <c r="F43" s="312"/>
       <c r="G43" s="312"/>
       <c r="H43" s="312"/>
       <c r="I43" s="305"/>
-      <c r="J43" s="454"/>
+      <c r="J43" s="453"/>
     </row>
     <row r="44" spans="1:10" ht="28">
       <c r="A44" s="312"/>
       <c r="B44" s="304"/>
       <c r="C44" s="370" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="D44" s="369" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="E44" s="312"/>
       <c r="F44" s="312"/>
       <c r="G44" s="312"/>
       <c r="H44" s="312"/>
       <c r="I44" s="305"/>
-      <c r="J44" s="454"/>
+      <c r="J44" s="453"/>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="312"/>
       <c r="B45" s="304"/>
-      <c r="C45" s="458" t="s">
-        <v>1011</v>
+      <c r="C45" s="456" t="s">
+        <v>1006</v>
       </c>
       <c r="D45" s="372" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="E45" s="312"/>
       <c r="F45" s="312"/>
       <c r="G45" s="312"/>
       <c r="H45" s="312"/>
       <c r="I45" s="305"/>
-      <c r="J45" s="454"/>
+      <c r="J45" s="453"/>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="312"/>
       <c r="B46" s="304"/>
-      <c r="C46" s="458" t="s">
-        <v>1057</v>
+      <c r="C46" s="456" t="s">
+        <v>1051</v>
       </c>
       <c r="D46" s="372" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="E46" s="312"/>
       <c r="F46" s="312"/>
       <c r="G46" s="312"/>
       <c r="H46" s="312"/>
       <c r="I46" s="305"/>
-      <c r="J46" s="454"/>
+      <c r="J46" s="453"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="312"/>
       <c r="B47" s="304"/>
-      <c r="C47" s="458" t="s">
-        <v>1058</v>
+      <c r="C47" s="456" t="s">
+        <v>1052</v>
       </c>
       <c r="D47" s="372" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="E47" s="312"/>
       <c r="F47" s="312"/>
       <c r="G47" s="312"/>
       <c r="H47" s="312"/>
       <c r="I47" s="305"/>
-      <c r="J47" s="454"/>
+      <c r="J47" s="453"/>
     </row>
     <row r="48" spans="1:10" ht="15.75" customHeight="1">
       <c r="A48" s="312"/>
       <c r="B48" s="304"/>
-      <c r="C48" s="444" t="s">
-        <v>926</v>
-      </c>
-      <c r="D48" s="445" t="s">
-        <v>939</v>
+      <c r="C48" s="443" t="s">
+        <v>924</v>
+      </c>
+      <c r="D48" s="444" t="s">
+        <v>936</v>
       </c>
       <c r="E48" s="312"/>
       <c r="F48" s="312"/>
       <c r="G48" s="312"/>
       <c r="H48" s="312"/>
       <c r="I48" s="305"/>
-      <c r="J48" s="454"/>
+      <c r="J48" s="453"/>
     </row>
     <row r="49" spans="1:10" ht="15.75" customHeight="1">
       <c r="A49" s="312"/>
       <c r="B49" s="304"/>
-      <c r="C49" s="446" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D49" s="447" t="s">
-        <v>1025</v>
+      <c r="C49" s="445" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D49" s="446" t="s">
+        <v>1020</v>
       </c>
       <c r="E49" s="312"/>
       <c r="F49" s="312"/>
       <c r="G49" s="312"/>
       <c r="H49" s="312"/>
       <c r="I49" s="305"/>
-      <c r="J49" s="454"/>
+      <c r="J49" s="453"/>
     </row>
     <row r="50" spans="1:10" ht="15.75" customHeight="1">
       <c r="A50" s="312"/>
@@ -18404,7 +18632,7 @@
       <c r="G50" s="312"/>
       <c r="H50" s="312"/>
       <c r="I50" s="305"/>
-      <c r="J50" s="454"/>
+      <c r="J50" s="453"/>
     </row>
     <row r="51" spans="1:10" ht="15.75" customHeight="1">
       <c r="A51" s="312"/>
@@ -18418,7 +18646,7 @@
       <c r="G51" s="312"/>
       <c r="H51" s="312"/>
       <c r="I51" s="305"/>
-      <c r="J51" s="454"/>
+      <c r="J51" s="453"/>
     </row>
     <row r="52" spans="1:10" ht="15.75" customHeight="1">
       <c r="A52" s="312"/>
@@ -18435,180 +18663,180 @@
       <c r="F52" s="374"/>
       <c r="H52" s="312"/>
       <c r="I52" s="305"/>
-      <c r="J52" s="454"/>
+      <c r="J52" s="453"/>
     </row>
     <row r="53" spans="1:10" ht="15.75" customHeight="1">
       <c r="A53" s="312"/>
       <c r="B53" s="304"/>
       <c r="C53" s="375" t="s">
-        <v>940</v>
+        <v>937</v>
       </c>
       <c r="D53" s="376" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="E53" s="377" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="F53" s="378"/>
       <c r="H53" s="312"/>
       <c r="I53" s="305"/>
-      <c r="J53" s="454"/>
+      <c r="J53" s="453"/>
     </row>
     <row r="54" spans="1:10" ht="15.75" customHeight="1">
       <c r="A54" s="312"/>
       <c r="B54" s="304"/>
       <c r="C54" s="379"/>
       <c r="D54" s="380" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="E54" s="381" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="F54" s="382"/>
       <c r="H54" s="312"/>
       <c r="I54" s="305"/>
-      <c r="J54" s="454"/>
+      <c r="J54" s="453"/>
     </row>
     <row r="55" spans="1:10" ht="15.75" customHeight="1">
       <c r="A55" s="312"/>
       <c r="B55" s="304"/>
       <c r="C55" s="375" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="D55" s="376" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="E55" s="377" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="F55" s="378"/>
       <c r="H55" s="312"/>
       <c r="I55" s="305"/>
-      <c r="J55" s="454"/>
+      <c r="J55" s="453"/>
     </row>
     <row r="56" spans="1:10" ht="15.75" customHeight="1">
       <c r="A56" s="312"/>
       <c r="B56" s="304"/>
       <c r="C56" s="379"/>
       <c r="D56" s="380" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="E56" s="381" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="F56" s="382"/>
       <c r="H56" s="312"/>
       <c r="I56" s="305"/>
-      <c r="J56" s="454"/>
+      <c r="J56" s="453"/>
     </row>
     <row r="57" spans="1:10" ht="15.75" customHeight="1">
       <c r="A57" s="312"/>
       <c r="B57" s="304"/>
       <c r="C57" s="383" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="D57" s="380" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="E57" s="384" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="F57" s="382"/>
       <c r="H57" s="312"/>
       <c r="I57" s="305"/>
-      <c r="J57" s="454"/>
+      <c r="J57" s="453"/>
     </row>
     <row r="58" spans="1:10" ht="15.75" customHeight="1">
       <c r="A58" s="312"/>
       <c r="B58" s="304"/>
       <c r="C58" s="375"/>
       <c r="D58" s="385" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="E58" s="384" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="F58" s="382"/>
       <c r="H58" s="312"/>
       <c r="I58" s="305"/>
-      <c r="J58" s="454"/>
+      <c r="J58" s="453"/>
     </row>
     <row r="59" spans="1:10" ht="15.75" customHeight="1">
       <c r="A59" s="312"/>
       <c r="B59" s="304"/>
       <c r="C59" s="386"/>
       <c r="D59" s="380" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="E59" s="387" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="F59" s="382"/>
       <c r="H59" s="312"/>
       <c r="I59" s="305"/>
-      <c r="J59" s="454"/>
+      <c r="J59" s="453"/>
     </row>
     <row r="60" spans="1:10" ht="15.75" customHeight="1">
       <c r="A60" s="312"/>
       <c r="B60" s="304"/>
       <c r="C60" s="383" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="D60" s="376" t="s">
-        <v>952</v>
-      </c>
-      <c r="E60" s="465" t="s">
-        <v>1064</v>
+        <v>949</v>
+      </c>
+      <c r="E60" s="461" t="s">
+        <v>1058</v>
       </c>
       <c r="F60" s="382"/>
       <c r="H60" s="312"/>
       <c r="I60" s="305"/>
-      <c r="J60" s="454"/>
+      <c r="J60" s="453"/>
     </row>
     <row r="61" spans="1:10" ht="15.75" customHeight="1">
       <c r="A61" s="312"/>
       <c r="B61" s="304"/>
       <c r="C61" s="375"/>
       <c r="D61" s="385" t="s">
-        <v>953</v>
-      </c>
-      <c r="E61" s="466" t="s">
-        <v>1065</v>
+        <v>950</v>
+      </c>
+      <c r="E61" s="462" t="s">
+        <v>1059</v>
       </c>
       <c r="F61" s="382"/>
       <c r="H61" s="312"/>
       <c r="I61" s="305"/>
-      <c r="J61" s="454"/>
+      <c r="J61" s="453"/>
     </row>
     <row r="62" spans="1:10" ht="15.75" customHeight="1">
       <c r="A62" s="312"/>
       <c r="B62" s="304"/>
       <c r="C62" s="375"/>
       <c r="D62" s="376" t="s">
-        <v>954</v>
-      </c>
-      <c r="E62" s="463" t="s">
-        <v>1068</v>
+        <v>951</v>
+      </c>
+      <c r="E62" s="459" t="s">
+        <v>1072</v>
       </c>
       <c r="F62" s="382"/>
       <c r="H62" s="312"/>
       <c r="I62" s="305"/>
-      <c r="J62" s="454"/>
+      <c r="J62" s="453"/>
     </row>
     <row r="63" spans="1:10" ht="15.75" customHeight="1">
       <c r="A63" s="312"/>
       <c r="B63" s="304"/>
       <c r="C63" s="375"/>
       <c r="D63" s="376" t="s">
-        <v>956</v>
-      </c>
-      <c r="E63" s="464" t="s">
-        <v>1069</v>
+        <v>952</v>
+      </c>
+      <c r="E63" s="460" t="s">
+        <v>1062</v>
       </c>
       <c r="F63" s="382"/>
       <c r="H63" s="312"/>
       <c r="I63" s="305"/>
-      <c r="J63" s="454"/>
+      <c r="J63" s="453"/>
     </row>
     <row r="64" spans="1:10" ht="15.75" customHeight="1">
       <c r="A64" s="312"/>
@@ -18618,248 +18846,248 @@
         <v>716</v>
       </c>
       <c r="E64" s="384" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="F64" s="378"/>
       <c r="H64" s="312"/>
       <c r="I64" s="305"/>
-      <c r="J64" s="454"/>
+      <c r="J64" s="453"/>
     </row>
     <row r="65" spans="1:10" ht="15.75" customHeight="1">
       <c r="A65" s="312"/>
       <c r="B65" s="304"/>
-      <c r="C65" s="457" t="s">
-        <v>1038</v>
+      <c r="C65" s="471" t="s">
+        <v>1074</v>
       </c>
       <c r="D65" s="388" t="s">
-        <v>959</v>
-      </c>
-      <c r="E65" s="462" t="s">
-        <v>1066</v>
+        <v>954</v>
+      </c>
+      <c r="E65" s="468" t="s">
+        <v>1060</v>
       </c>
       <c r="F65" s="382"/>
       <c r="H65" s="312"/>
       <c r="I65" s="305"/>
-      <c r="J65" s="454"/>
+      <c r="J65" s="453"/>
     </row>
     <row r="66" spans="1:10" ht="15.75" customHeight="1">
       <c r="A66" s="312"/>
       <c r="B66" s="304"/>
       <c r="C66" s="375"/>
       <c r="D66" s="380" t="s">
-        <v>961</v>
-      </c>
-      <c r="E66" s="389" t="s">
-        <v>1067</v>
+        <v>956</v>
+      </c>
+      <c r="E66" s="469" t="s">
+        <v>1061</v>
       </c>
       <c r="F66" s="382"/>
       <c r="H66" s="312"/>
       <c r="I66" s="305"/>
-      <c r="J66" s="454"/>
+      <c r="J66" s="453"/>
     </row>
     <row r="67" spans="1:10" ht="15.75" customHeight="1">
       <c r="A67" s="312"/>
       <c r="B67" s="304"/>
-      <c r="C67" s="390"/>
-      <c r="D67" s="391" t="s">
-        <v>962</v>
-      </c>
-      <c r="E67" s="392" t="s">
-        <v>955</v>
+      <c r="C67" s="389"/>
+      <c r="D67" s="390" t="s">
+        <v>957</v>
+      </c>
+      <c r="E67" s="451" t="s">
+        <v>1072</v>
       </c>
       <c r="F67" s="382"/>
       <c r="H67" s="312"/>
       <c r="I67" s="305"/>
-      <c r="J67" s="454"/>
+      <c r="J67" s="453"/>
     </row>
     <row r="68" spans="1:10" ht="13">
       <c r="A68" s="312"/>
       <c r="B68" s="304"/>
-      <c r="C68" s="393"/>
+      <c r="C68" s="392"/>
       <c r="D68" s="380" t="s">
-        <v>963</v>
-      </c>
-      <c r="E68" s="461" t="s">
-        <v>957</v>
+        <v>958</v>
+      </c>
+      <c r="E68" s="470" t="s">
+        <v>1073</v>
       </c>
       <c r="F68" s="382"/>
       <c r="H68" s="312"/>
       <c r="I68" s="305"/>
-      <c r="J68" s="454"/>
+      <c r="J68" s="453"/>
     </row>
     <row r="69" spans="1:10" ht="15.75" customHeight="1">
       <c r="A69" s="312"/>
       <c r="B69" s="304"/>
-      <c r="C69" s="394"/>
+      <c r="C69" s="393"/>
       <c r="D69" s="376" t="s">
         <v>716</v>
       </c>
       <c r="E69" s="376" t="s">
-        <v>958</v>
-      </c>
-      <c r="F69" s="395"/>
+        <v>953</v>
+      </c>
+      <c r="F69" s="394"/>
       <c r="H69" s="312"/>
       <c r="I69" s="305"/>
-      <c r="J69" s="454"/>
+      <c r="J69" s="453"/>
     </row>
     <row r="70" spans="1:10" ht="15.75" customHeight="1">
       <c r="A70" s="312"/>
       <c r="B70" s="304"/>
-      <c r="C70" s="396" t="s">
-        <v>964</v>
-      </c>
-      <c r="D70" s="397" t="s">
-        <v>965</v>
-      </c>
-      <c r="E70" s="397" t="s">
-        <v>966</v>
-      </c>
-      <c r="F70" s="395"/>
+      <c r="C70" s="395" t="s">
+        <v>959</v>
+      </c>
+      <c r="D70" s="396" t="s">
+        <v>960</v>
+      </c>
+      <c r="E70" s="396" t="s">
+        <v>961</v>
+      </c>
+      <c r="F70" s="394"/>
       <c r="H70" s="312"/>
       <c r="I70" s="305"/>
-      <c r="J70" s="454"/>
+      <c r="J70" s="453"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1">
       <c r="A71" s="312"/>
       <c r="B71" s="304"/>
-      <c r="C71" s="393"/>
-      <c r="D71" s="397" t="s">
-        <v>967</v>
-      </c>
-      <c r="E71" s="397" t="s">
-        <v>968</v>
-      </c>
-      <c r="F71" s="395"/>
+      <c r="C71" s="392"/>
+      <c r="D71" s="396" t="s">
+        <v>962</v>
+      </c>
+      <c r="E71" s="396" t="s">
+        <v>963</v>
+      </c>
+      <c r="F71" s="394"/>
       <c r="H71" s="312"/>
       <c r="I71" s="305"/>
-      <c r="J71" s="454"/>
+      <c r="J71" s="453"/>
     </row>
     <row r="72" spans="1:10" ht="15.75" customHeight="1">
       <c r="A72" s="312"/>
       <c r="B72" s="304"/>
-      <c r="C72" s="393"/>
-      <c r="D72" s="397" t="s">
-        <v>969</v>
-      </c>
-      <c r="E72" s="397" t="s">
-        <v>970</v>
-      </c>
-      <c r="F72" s="395"/>
+      <c r="C72" s="392"/>
+      <c r="D72" s="396" t="s">
+        <v>964</v>
+      </c>
+      <c r="E72" s="396" t="s">
+        <v>965</v>
+      </c>
+      <c r="F72" s="394"/>
       <c r="H72" s="312"/>
       <c r="I72" s="305"/>
-      <c r="J72" s="454"/>
+      <c r="J72" s="453"/>
     </row>
     <row r="73" spans="1:10" ht="15.75" customHeight="1">
       <c r="A73" s="312"/>
       <c r="B73" s="304"/>
-      <c r="C73" s="393"/>
-      <c r="D73" s="397" t="s">
-        <v>971</v>
-      </c>
-      <c r="E73" s="397" t="s">
+      <c r="C73" s="392"/>
+      <c r="D73" s="396" t="s">
         <v>966</v>
       </c>
-      <c r="F73" s="395"/>
+      <c r="E73" s="396" t="s">
+        <v>961</v>
+      </c>
+      <c r="F73" s="394"/>
       <c r="H73" s="312"/>
       <c r="I73" s="305"/>
-      <c r="J73" s="454"/>
+      <c r="J73" s="453"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" customHeight="1">
       <c r="A74" s="312"/>
       <c r="B74" s="304"/>
-      <c r="C74" s="393"/>
-      <c r="D74" s="398" t="s">
-        <v>972</v>
-      </c>
-      <c r="E74" s="398" t="s">
-        <v>973</v>
-      </c>
-      <c r="F74" s="395"/>
+      <c r="C74" s="392"/>
+      <c r="D74" s="397" t="s">
+        <v>967</v>
+      </c>
+      <c r="E74" s="397" t="s">
+        <v>968</v>
+      </c>
+      <c r="F74" s="394"/>
       <c r="H74" s="312"/>
       <c r="I74" s="305"/>
-      <c r="J74" s="454"/>
+      <c r="J74" s="453"/>
     </row>
     <row r="75" spans="1:10" ht="15.75" customHeight="1">
       <c r="A75" s="305"/>
       <c r="B75" s="305"/>
-      <c r="C75" s="399" t="s">
-        <v>974</v>
-      </c>
-      <c r="D75" s="400" t="s">
-        <v>967</v>
-      </c>
-      <c r="E75" s="401" t="s">
-        <v>975</v>
-      </c>
-      <c r="F75" s="395"/>
+      <c r="C75" s="398" t="s">
+        <v>969</v>
+      </c>
+      <c r="D75" s="399" t="s">
+        <v>962</v>
+      </c>
+      <c r="E75" s="400" t="s">
+        <v>970</v>
+      </c>
+      <c r="F75" s="394"/>
       <c r="G75" s="305"/>
       <c r="H75" s="305"/>
       <c r="I75" s="305"/>
-      <c r="J75" s="454"/>
+      <c r="J75" s="453"/>
     </row>
     <row r="76" spans="1:10" ht="15" customHeight="1">
-      <c r="C76" s="402"/>
-      <c r="D76" s="403" t="s">
+      <c r="C76" s="401"/>
+      <c r="D76" s="402" t="s">
+        <v>971</v>
+      </c>
+      <c r="E76" s="403" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="15" customHeight="1">
+      <c r="C77" s="401"/>
+      <c r="D77" s="402" t="s">
+        <v>972</v>
+      </c>
+      <c r="E77" s="403" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" ht="15" customHeight="1">
+      <c r="C78" s="404"/>
+      <c r="D78" s="402" t="s">
+        <v>974</v>
+      </c>
+      <c r="E78" s="400" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" ht="15" customHeight="1">
+      <c r="C79" s="398" t="s">
         <v>976</v>
       </c>
-      <c r="E76" s="404" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" ht="15" customHeight="1">
-      <c r="C77" s="402"/>
-      <c r="D77" s="403" t="s">
+      <c r="D79" s="399" t="s">
+        <v>962</v>
+      </c>
+      <c r="E79" s="400" t="s">
         <v>977</v>
       </c>
-      <c r="E77" s="404" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1">
-      <c r="C78" s="405"/>
-      <c r="D78" s="403" t="s">
-        <v>979</v>
-      </c>
-      <c r="E78" s="401" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" ht="15" customHeight="1">
-      <c r="C79" s="399" t="s">
-        <v>981</v>
-      </c>
-      <c r="D79" s="400" t="s">
-        <v>967</v>
-      </c>
-      <c r="E79" s="401" t="s">
-        <v>982</v>
-      </c>
     </row>
     <row r="80" spans="1:10" ht="15" customHeight="1">
-      <c r="C80" s="402"/>
-      <c r="D80" s="403" t="s">
-        <v>976</v>
-      </c>
-      <c r="E80" s="404" t="s">
-        <v>960</v>
+      <c r="C80" s="401"/>
+      <c r="D80" s="402" t="s">
+        <v>971</v>
+      </c>
+      <c r="E80" s="403" t="s">
+        <v>955</v>
       </c>
     </row>
     <row r="81" spans="3:5" ht="15" customHeight="1">
-      <c r="C81" s="402"/>
-      <c r="D81" s="403" t="s">
-        <v>977</v>
-      </c>
-      <c r="E81" s="404" t="s">
-        <v>978</v>
+      <c r="C81" s="401"/>
+      <c r="D81" s="402" t="s">
+        <v>972</v>
+      </c>
+      <c r="E81" s="403" t="s">
+        <v>973</v>
       </c>
     </row>
     <row r="82" spans="3:5" ht="15" customHeight="1">
-      <c r="C82" s="405"/>
-      <c r="D82" s="403" t="s">
-        <v>979</v>
-      </c>
-      <c r="E82" s="401" t="s">
-        <v>980</v>
+      <c r="C82" s="404"/>
+      <c r="D82" s="402" t="s">
+        <v>974</v>
+      </c>
+      <c r="E82" s="400" t="s">
+        <v>975</v>
       </c>
     </row>
   </sheetData>

--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C6EF64C-25CD-D44D-ADCA-D0132415B345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FF3D9F-2A7D-9442-A0E4-E86C529E1A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4214,10 +4214,6 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>show</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>管理者ユーザーのみ、その日になされた一般ユーザの勤怠情報の詳細を個別で確認できる画面</t>
     <rPh sb="0" eb="3">
       <t>カンリ</t>
@@ -5865,6 +5861,10 @@
   </si>
   <si>
     <t>show/update</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>show/export</t>
     <phoneticPr fontId="80"/>
   </si>
 </sst>
@@ -7601,7 +7601,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18"/>
   </cellStyleXfs>
-  <cellXfs count="489">
+  <cellXfs count="490">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8806,22 +8806,11 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8830,17 +8819,31 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -9434,7 +9437,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="413" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="E6" s="414"/>
       <c r="F6" s="414"/>
@@ -9453,7 +9456,7 @@
         <v>701</v>
       </c>
       <c r="F7" s="418" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G7" s="418" t="s">
         <v>710</v>
@@ -9472,10 +9475,10 @@
       <c r="C8" s="420"/>
       <c r="D8" s="304"/>
       <c r="E8" s="391" t="s">
+        <v>979</v>
+      </c>
+      <c r="F8" s="391" t="s">
         <v>980</v>
-      </c>
-      <c r="F8" s="391" t="s">
-        <v>981</v>
       </c>
       <c r="G8" s="391"/>
       <c r="H8" s="391"/>
@@ -9491,10 +9494,10 @@
       <c r="B9" s="366"/>
       <c r="C9" s="417"/>
       <c r="E9" s="391" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F9" s="391" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G9" s="391"/>
       <c r="H9" s="418" t="s">
@@ -9514,7 +9517,7 @@
       <c r="B10" s="366"/>
       <c r="C10" s="417"/>
       <c r="E10" s="391" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F10" s="391" t="s">
         <v>731</v>
@@ -9531,10 +9534,10 @@
       <c r="B11" s="366"/>
       <c r="C11" s="417"/>
       <c r="E11" s="391" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F11" s="391" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G11" s="391"/>
       <c r="H11" s="391"/>
@@ -9550,10 +9553,10 @@
       <c r="B12" s="366"/>
       <c r="C12" s="417"/>
       <c r="E12" s="391" t="s">
+        <v>984</v>
+      </c>
+      <c r="F12" s="391" t="s">
         <v>985</v>
-      </c>
-      <c r="F12" s="391" t="s">
-        <v>986</v>
       </c>
       <c r="G12" s="391"/>
       <c r="H12" s="391"/>
@@ -9567,13 +9570,13 @@
       <c r="B13" s="366"/>
       <c r="C13" s="417"/>
       <c r="D13" s="436" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E13" s="447" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F13" s="447" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G13" s="391"/>
       <c r="H13" s="391"/>
@@ -9589,13 +9592,13 @@
       <c r="B14" s="366"/>
       <c r="C14" s="417"/>
       <c r="D14" s="436" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E14" s="391" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F14" s="391" t="s">
         <v>1023</v>
-      </c>
-      <c r="F14" s="391" t="s">
-        <v>1024</v>
       </c>
       <c r="G14" s="391"/>
       <c r="H14" s="391"/>
@@ -9645,7 +9648,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="422" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E17" s="414"/>
       <c r="F17" s="414"/>
@@ -9661,10 +9664,10 @@
       <c r="B18" s="394"/>
       <c r="C18" s="423"/>
       <c r="E18" s="391" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F18" s="362" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G18" s="418" t="s">
         <v>903</v>
@@ -9682,13 +9685,13 @@
       <c r="B19" s="394"/>
       <c r="C19" s="423"/>
       <c r="D19" s="312" t="s">
+        <v>988</v>
+      </c>
+      <c r="E19" s="391" t="s">
+        <v>959</v>
+      </c>
+      <c r="F19" s="362" t="s">
         <v>989</v>
-      </c>
-      <c r="E19" s="391" t="s">
-        <v>960</v>
-      </c>
-      <c r="F19" s="362" t="s">
-        <v>990</v>
       </c>
       <c r="G19" s="418"/>
       <c r="H19" s="391" t="s">
@@ -9698,7 +9701,7 @@
         <v>903</v>
       </c>
       <c r="J19" s="419" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="K19" s="305"/>
       <c r="L19" s="305"/>
@@ -9709,10 +9712,10 @@
       <c r="C20" s="423"/>
       <c r="D20" s="312"/>
       <c r="E20" s="391" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F20" s="362" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G20" s="418"/>
       <c r="H20" s="391" t="s">
@@ -9729,10 +9732,10 @@
       <c r="C21" s="423"/>
       <c r="D21" s="304"/>
       <c r="E21" s="391" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F21" s="362" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G21" s="391"/>
       <c r="H21" s="391"/>
@@ -9748,10 +9751,10 @@
       <c r="B22" s="394"/>
       <c r="C22" s="423"/>
       <c r="E22" s="391" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F22" s="362" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G22" s="391"/>
       <c r="H22" s="391"/>
@@ -9765,10 +9768,10 @@
       <c r="B23" s="394"/>
       <c r="C23" s="423"/>
       <c r="E23" s="447" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F23" s="447" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G23" s="391"/>
       <c r="H23" s="391"/>
@@ -9819,12 +9822,12 @@
       <c r="C26" s="423"/>
       <c r="D26" s="429"/>
       <c r="E26" s="430" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F26" s="431"/>
       <c r="G26" s="432"/>
       <c r="H26" s="431" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="I26" s="431"/>
       <c r="J26" s="433"/>
@@ -9838,7 +9841,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="422" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E27" s="414"/>
       <c r="F27" s="414"/>
@@ -9857,7 +9860,7 @@
         <v>701</v>
       </c>
       <c r="F28" s="391" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G28" s="418" t="s">
         <v>710</v>
@@ -9875,13 +9878,13 @@
       <c r="B29" s="394"/>
       <c r="C29" s="423"/>
       <c r="D29" s="312" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E29" s="451" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="F29" s="391" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G29" s="418"/>
       <c r="H29" s="391"/>
@@ -9889,7 +9892,7 @@
         <v>710</v>
       </c>
       <c r="J29" s="419" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="K29" s="305"/>
       <c r="L29" s="305"/>
@@ -9900,10 +9903,10 @@
       <c r="C30" s="423"/>
       <c r="D30" s="304"/>
       <c r="E30" s="391" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="F30" s="391" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G30" s="391"/>
       <c r="H30" s="391"/>
@@ -9917,10 +9920,10 @@
       <c r="B31" s="394"/>
       <c r="C31" s="423"/>
       <c r="E31" s="391" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="F31" s="391" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G31" s="391"/>
       <c r="H31" s="391"/>
@@ -9970,7 +9973,7 @@
         <v>4</v>
       </c>
       <c r="D34" s="487" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E34" s="488"/>
       <c r="F34" s="488"/>
@@ -9986,10 +9989,10 @@
       <c r="B35" s="394"/>
       <c r="C35" s="423"/>
       <c r="E35" s="391" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F35" s="362" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G35" s="418" t="s">
         <v>903</v>
@@ -10007,13 +10010,13 @@
       <c r="B36" s="394"/>
       <c r="C36" s="423"/>
       <c r="D36" s="306" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E36" s="451" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="F36" s="362" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G36" s="418"/>
       <c r="H36" s="391"/>
@@ -10021,7 +10024,7 @@
         <v>710</v>
       </c>
       <c r="J36" s="419" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="K36" s="305"/>
       <c r="L36" s="305"/>
@@ -10031,10 +10034,10 @@
       <c r="B37" s="394"/>
       <c r="C37" s="423"/>
       <c r="E37" s="391" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F37" s="391" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G37" s="391"/>
       <c r="H37" s="391"/>
@@ -10050,10 +10053,10 @@
       <c r="B38" s="394"/>
       <c r="C38" s="423"/>
       <c r="E38" s="391" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="F38" s="435" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G38" s="391"/>
       <c r="H38" s="391"/>
@@ -10067,10 +10070,10 @@
       <c r="B39" s="394"/>
       <c r="C39" s="423"/>
       <c r="E39" s="391" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F39" s="391" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G39" s="391"/>
       <c r="H39" s="391"/>
@@ -10086,13 +10089,13 @@
       <c r="B40" s="394"/>
       <c r="C40" s="423"/>
       <c r="D40" s="436" t="s">
+        <v>998</v>
+      </c>
+      <c r="E40" s="391" t="s">
         <v>999</v>
       </c>
-      <c r="E40" s="391" t="s">
+      <c r="F40" s="391" t="s">
         <v>1000</v>
-      </c>
-      <c r="F40" s="391" t="s">
-        <v>1001</v>
       </c>
       <c r="G40" s="391"/>
       <c r="H40" s="391"/>
@@ -10109,10 +10112,10 @@
       <c r="C41" s="423"/>
       <c r="D41" s="436"/>
       <c r="E41" s="447" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="F41" s="447" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G41" s="391"/>
       <c r="H41" s="391"/>
@@ -10166,7 +10169,7 @@
         <v>5</v>
       </c>
       <c r="D44" s="450" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E44" s="414"/>
       <c r="F44" s="414"/>
@@ -10185,7 +10188,7 @@
         <v>701</v>
       </c>
       <c r="F45" s="391" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G45" s="391" t="s">
         <v>710</v>
@@ -10203,13 +10206,13 @@
       <c r="B46" s="394"/>
       <c r="C46" s="423"/>
       <c r="D46" s="312" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E46" s="391" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F46" s="391" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G46" s="391"/>
       <c r="H46" s="391"/>
@@ -10217,7 +10220,7 @@
         <v>903</v>
       </c>
       <c r="J46" s="419" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="K46" s="305"/>
       <c r="L46" s="305"/>
@@ -10227,10 +10230,10 @@
       <c r="B47" s="394"/>
       <c r="C47" s="423"/>
       <c r="E47" s="391" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F47" s="391" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G47" s="391"/>
       <c r="H47" s="391"/>
@@ -10244,10 +10247,10 @@
       <c r="B48" s="394"/>
       <c r="C48" s="423"/>
       <c r="E48" s="391" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F48" s="391" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G48" s="391"/>
       <c r="H48" s="391"/>
@@ -10843,11 +10846,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="480" t="s">
+      <c r="C4" s="475" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="481"/>
-      <c r="E4" s="481"/>
+      <c r="D4" s="476"/>
+      <c r="E4" s="476"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10856,13 +10859,13 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
-      <c r="C5" s="484" t="s">
+      <c r="C5" s="481" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="482" t="s">
+      <c r="D5" s="477" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="483"/>
+      <c r="E5" s="478"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10871,11 +10874,11 @@
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="477"/>
-      <c r="D6" s="472" t="s">
+      <c r="C6" s="474"/>
+      <c r="D6" s="479" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="473"/>
+      <c r="E6" s="480"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10884,11 +10887,11 @@
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="477"/>
-      <c r="D7" s="472" t="s">
+      <c r="C7" s="474"/>
+      <c r="D7" s="479" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="473"/>
+      <c r="E7" s="480"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10897,11 +10900,11 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="477"/>
-      <c r="D8" s="472" t="s">
+      <c r="C8" s="474"/>
+      <c r="D8" s="479" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="473"/>
+      <c r="E8" s="480"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10910,11 +10913,11 @@
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="477"/>
-      <c r="D9" s="472" t="s">
+      <c r="C9" s="474"/>
+      <c r="D9" s="479" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="473"/>
+      <c r="E9" s="480"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10923,11 +10926,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="478"/>
-      <c r="D10" s="472" t="s">
+      <c r="C10" s="473"/>
+      <c r="D10" s="479" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="473"/>
+      <c r="E10" s="480"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10936,13 +10939,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="479" t="s">
+      <c r="C11" s="472" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="472" t="s">
+      <c r="D11" s="479" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="473"/>
+      <c r="E11" s="480"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10951,11 +10954,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="478"/>
-      <c r="D12" s="472" t="s">
+      <c r="C12" s="473"/>
+      <c r="D12" s="479" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="473"/>
+      <c r="E12" s="480"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10964,13 +10967,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="479" t="s">
+      <c r="C13" s="472" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="472" t="s">
+      <c r="D13" s="479" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="473"/>
+      <c r="E13" s="480"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10979,11 +10982,11 @@
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="477"/>
-      <c r="D14" s="472" t="s">
+      <c r="C14" s="474"/>
+      <c r="D14" s="479" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="473"/>
+      <c r="E14" s="480"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10992,11 +10995,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="478"/>
-      <c r="D15" s="472" t="s">
+      <c r="C15" s="473"/>
+      <c r="D15" s="479" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="473"/>
+      <c r="E15" s="480"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -11005,13 +11008,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="479" t="s">
+      <c r="C16" s="472" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="474" t="s">
+      <c r="D16" s="484" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="475"/>
+      <c r="E16" s="485"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -11020,8 +11023,8 @@
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="477"/>
-      <c r="D17" s="476" t="s">
+      <c r="C17" s="474"/>
+      <c r="D17" s="483" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="107" t="s">
@@ -11035,8 +11038,8 @@
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="477"/>
-      <c r="D18" s="477"/>
+      <c r="C18" s="474"/>
+      <c r="D18" s="474"/>
       <c r="E18" s="107" t="s">
         <v>134</v>
       </c>
@@ -11048,8 +11051,8 @@
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="477"/>
-      <c r="D19" s="477"/>
+      <c r="C19" s="474"/>
+      <c r="D19" s="474"/>
       <c r="E19" s="107" t="s">
         <v>137</v>
       </c>
@@ -11061,8 +11064,8 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="477"/>
-      <c r="D20" s="477"/>
+      <c r="C20" s="474"/>
+      <c r="D20" s="474"/>
       <c r="E20" s="107" t="s">
         <v>140</v>
       </c>
@@ -11074,8 +11077,8 @@
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="477"/>
-      <c r="D21" s="478"/>
+      <c r="C21" s="474"/>
+      <c r="D21" s="473"/>
       <c r="E21" s="107" t="s">
         <v>145</v>
       </c>
@@ -11087,8 +11090,8 @@
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="477"/>
-      <c r="D22" s="485" t="s">
+      <c r="C22" s="474"/>
+      <c r="D22" s="482" t="s">
         <v>165</v>
       </c>
       <c r="E22" s="127" t="s">
@@ -11102,8 +11105,8 @@
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="477"/>
-      <c r="D23" s="477"/>
+      <c r="C23" s="474"/>
+      <c r="D23" s="474"/>
       <c r="E23" s="127" t="s">
         <v>177</v>
       </c>
@@ -11115,8 +11118,8 @@
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="477"/>
-      <c r="D24" s="477"/>
+      <c r="C24" s="474"/>
+      <c r="D24" s="474"/>
       <c r="E24" s="127" t="s">
         <v>179</v>
       </c>
@@ -11128,8 +11131,8 @@
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="477"/>
-      <c r="D25" s="477"/>
+      <c r="C25" s="474"/>
+      <c r="D25" s="474"/>
       <c r="E25" s="127" t="s">
         <v>185</v>
       </c>
@@ -11141,8 +11144,8 @@
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="477"/>
-      <c r="D26" s="478"/>
+      <c r="C26" s="474"/>
+      <c r="D26" s="473"/>
       <c r="E26" s="127" t="s">
         <v>190</v>
       </c>
@@ -11154,7 +11157,7 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="477"/>
+      <c r="C27" s="474"/>
       <c r="D27" s="127" t="s">
         <v>193</v>
       </c>
@@ -11169,7 +11172,7 @@
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="477"/>
+      <c r="C28" s="474"/>
       <c r="D28" s="105" t="s">
         <v>221</v>
       </c>
@@ -11184,8 +11187,8 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="477"/>
-      <c r="D29" s="476" t="s">
+      <c r="C29" s="474"/>
+      <c r="D29" s="483" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="127" t="s">
@@ -11199,8 +11202,8 @@
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
+      <c r="C30" s="474"/>
+      <c r="D30" s="474"/>
       <c r="E30" s="127" t="s">
         <v>244</v>
       </c>
@@ -11212,8 +11215,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="478"/>
-      <c r="D31" s="478"/>
+      <c r="C31" s="473"/>
+      <c r="D31" s="473"/>
       <c r="E31" s="127" t="s">
         <v>249</v>
       </c>
@@ -11225,13 +11228,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="479" t="s">
+      <c r="C32" s="472" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="472" t="s">
+      <c r="D32" s="479" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="473"/>
+      <c r="E32" s="480"/>
       <c r="F32" s="159" t="s">
         <v>259</v>
       </c>
@@ -11239,11 +11242,11 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="477"/>
-      <c r="D33" s="472" t="s">
+      <c r="C33" s="474"/>
+      <c r="D33" s="479" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="473"/>
+      <c r="E33" s="480"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -11252,11 +11255,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="478"/>
-      <c r="D34" s="472" t="s">
+      <c r="C34" s="473"/>
+      <c r="D34" s="479" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="473"/>
+      <c r="E34" s="480"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -11273,6 +11276,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:D21"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="C16:C31"/>
@@ -11289,14 +11300,6 @@
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:D21"/>
   </mergeCells>
   <phoneticPr fontId="80"/>
   <hyperlinks>
@@ -12719,13 +12722,13 @@
         <v>58</v>
       </c>
       <c r="F10" s="457" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G10" s="65" t="s">
         <v>64</v>
       </c>
       <c r="H10" s="458" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="I10" s="10"/>
     </row>
@@ -14634,7 +14637,7 @@
     <row r="72" spans="1:8" ht="39">
       <c r="A72" s="279"/>
       <c r="B72" s="279"/>
-      <c r="C72" s="477"/>
+      <c r="C72" s="474"/>
       <c r="D72" s="283"/>
       <c r="E72" s="281" t="s">
         <v>742</v>
@@ -14650,7 +14653,7 @@
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="279"/>
       <c r="B73" s="279"/>
-      <c r="C73" s="478"/>
+      <c r="C73" s="473"/>
       <c r="D73" s="284"/>
       <c r="E73" s="281" t="s">
         <v>745</v>
@@ -17803,7 +17806,7 @@
         <v>41</v>
       </c>
       <c r="D7" s="324" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E7" s="325" t="s">
         <v>899</v>
@@ -17812,7 +17815,7 @@
         <v>896</v>
       </c>
       <c r="G7" s="327" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H7" s="328" t="s">
         <v>897</v>
@@ -17821,7 +17824,7 @@
         <v>900</v>
       </c>
       <c r="J7" s="465" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="154">
@@ -17831,16 +17834,16 @@
         <v>901</v>
       </c>
       <c r="D8" s="324" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E8" s="325" t="s">
         <v>895</v>
       </c>
       <c r="F8" s="331" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="G8" s="332" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H8" s="333" t="s">
         <v>903</v>
@@ -17892,7 +17895,7 @@
         <v>907</v>
       </c>
       <c r="G10" s="335" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="H10" s="333" t="s">
         <v>903</v>
@@ -17909,7 +17912,7 @@
         <v>66</v>
       </c>
       <c r="D11" s="324" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E11" s="325" t="s">
         <v>899</v>
@@ -17941,10 +17944,10 @@
         <v>895</v>
       </c>
       <c r="F12" s="331" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G12" s="463" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="H12" s="333" t="s">
         <v>897</v>
@@ -17953,7 +17956,7 @@
         <v>911</v>
       </c>
       <c r="J12" s="464" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="56">
@@ -17998,13 +18001,13 @@
         <v>912</v>
       </c>
       <c r="G14" s="466" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H14" s="333" t="s">
         <v>903</v>
       </c>
       <c r="I14" s="334" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="J14" s="453"/>
     </row>
@@ -18015,13 +18018,13 @@
         <v>84</v>
       </c>
       <c r="D15" s="324" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="E15" s="343" t="s">
         <v>899</v>
       </c>
       <c r="F15" s="331" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G15" s="335" t="s">
         <v>905</v>
@@ -18030,7 +18033,7 @@
         <v>903</v>
       </c>
       <c r="I15" s="334" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J15" s="453"/>
     </row>
@@ -18047,16 +18050,16 @@
         <v>899</v>
       </c>
       <c r="F16" s="331" t="s">
-        <v>917</v>
-      </c>
-      <c r="G16" s="335" t="s">
-        <v>915</v>
+        <v>916</v>
+      </c>
+      <c r="G16" s="489" t="s">
+        <v>1075</v>
       </c>
       <c r="H16" s="333" t="s">
         <v>903</v>
       </c>
       <c r="I16" s="334" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="J16" s="453"/>
     </row>
@@ -18067,13 +18070,13 @@
         <v>102</v>
       </c>
       <c r="D17" s="324" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E17" s="345" t="s">
         <v>899</v>
       </c>
       <c r="F17" s="331" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G17" s="335" t="s">
         <v>905</v>
@@ -18082,7 +18085,7 @@
         <v>903</v>
       </c>
       <c r="I17" s="336" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="J17" s="453"/>
     </row>
@@ -18099,16 +18102,16 @@
         <v>895</v>
       </c>
       <c r="F18" s="349" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G18" s="350" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H18" s="351" t="s">
         <v>903</v>
       </c>
       <c r="I18" s="352" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="J18" s="453"/>
     </row>
@@ -18116,10 +18119,10 @@
       <c r="A19" s="312"/>
       <c r="B19" s="304"/>
       <c r="C19" s="353" t="s">
+        <v>923</v>
+      </c>
+      <c r="D19" s="354" t="s">
         <v>924</v>
-      </c>
-      <c r="D19" s="354" t="s">
-        <v>925</v>
       </c>
       <c r="E19" s="355" t="s">
         <v>899</v>
@@ -18132,7 +18135,7 @@
         <v>903</v>
       </c>
       <c r="I19" s="359" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="J19" s="453"/>
     </row>
@@ -18140,10 +18143,10 @@
       <c r="A20" s="312"/>
       <c r="B20" s="304"/>
       <c r="C20" s="353" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D20" s="354" t="s">
         <v>1006</v>
-      </c>
-      <c r="D20" s="354" t="s">
-        <v>1007</v>
       </c>
       <c r="E20" s="355" t="s">
         <v>897</v>
@@ -18158,7 +18161,7 @@
         <v>903</v>
       </c>
       <c r="I20" s="359" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="J20" s="453"/>
     </row>
@@ -18208,10 +18211,10 @@
       <c r="A24" s="312"/>
       <c r="B24" s="304"/>
       <c r="C24" s="362" t="s">
+        <v>926</v>
+      </c>
+      <c r="D24" s="363" t="s">
         <v>927</v>
-      </c>
-      <c r="D24" s="363" t="s">
-        <v>928</v>
       </c>
       <c r="E24" s="312"/>
       <c r="F24" s="312"/>
@@ -18224,10 +18227,10 @@
       <c r="A25" s="312"/>
       <c r="B25" s="304"/>
       <c r="C25" s="365" t="s">
+        <v>928</v>
+      </c>
+      <c r="D25" s="363" t="s">
         <v>929</v>
-      </c>
-      <c r="D25" s="363" t="s">
-        <v>930</v>
       </c>
       <c r="E25" s="312"/>
       <c r="F25" s="312"/>
@@ -18240,10 +18243,10 @@
       <c r="A26" s="312"/>
       <c r="B26" s="304"/>
       <c r="C26" s="365" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D26" s="364" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="E26" s="312"/>
       <c r="F26" s="312"/>
@@ -18256,10 +18259,10 @@
       <c r="A27" s="312"/>
       <c r="B27" s="304"/>
       <c r="C27" s="365" t="s">
+        <v>931</v>
+      </c>
+      <c r="D27" s="364" t="s">
         <v>932</v>
-      </c>
-      <c r="D27" s="364" t="s">
-        <v>933</v>
       </c>
       <c r="E27" s="312"/>
       <c r="F27" s="312"/>
@@ -18272,10 +18275,10 @@
       <c r="A28" s="312"/>
       <c r="B28" s="304"/>
       <c r="C28" s="449" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D28" s="364" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="E28" s="312"/>
       <c r="F28" s="312"/>
@@ -18330,10 +18333,10 @@
       <c r="A32" s="312"/>
       <c r="B32" s="304"/>
       <c r="C32" s="441" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D32" s="369" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E32" s="312"/>
       <c r="F32" s="312"/>
@@ -18346,10 +18349,10 @@
       <c r="A33" s="312"/>
       <c r="B33" s="304"/>
       <c r="C33" s="370" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D33" s="369" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E33" s="312"/>
       <c r="F33" s="312"/>
@@ -18365,7 +18368,7 @@
         <v>901</v>
       </c>
       <c r="D34" s="369" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E34" s="312"/>
       <c r="F34" s="312"/>
@@ -18378,13 +18381,13 @@
       <c r="A35" s="312"/>
       <c r="B35" s="304"/>
       <c r="C35" s="370" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="D35" s="369" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E35" s="467" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F35" s="312"/>
       <c r="G35" s="312"/>
@@ -18396,10 +18399,10 @@
       <c r="A36" s="312"/>
       <c r="B36" s="304"/>
       <c r="C36" s="370" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="D36" s="371" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E36" s="312"/>
       <c r="F36" s="312"/>
@@ -18412,10 +18415,10 @@
       <c r="A37" s="312"/>
       <c r="B37" s="304"/>
       <c r="C37" s="370" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D37" s="369" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E37" s="312"/>
       <c r="F37" s="312"/>
@@ -18428,10 +18431,10 @@
       <c r="A38" s="312"/>
       <c r="B38" s="304"/>
       <c r="C38" s="370" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="D38" s="369" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="E38" s="312"/>
       <c r="F38" s="312"/>
@@ -18444,13 +18447,13 @@
       <c r="A39" s="312"/>
       <c r="B39" s="304"/>
       <c r="C39" s="442" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="D39" s="369" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="E39" s="467" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="F39" s="312"/>
       <c r="G39" s="312"/>
@@ -18462,13 +18465,13 @@
       <c r="A40" s="312"/>
       <c r="B40" s="304"/>
       <c r="C40" s="370" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="D40" s="371" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="E40" s="467" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F40" s="312"/>
       <c r="G40" s="312"/>
@@ -18480,10 +18483,10 @@
       <c r="A41" s="312"/>
       <c r="B41" s="304"/>
       <c r="C41" s="370" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D41" s="369" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="E41" s="312"/>
       <c r="F41" s="312"/>
@@ -18496,13 +18499,13 @@
       <c r="A42" s="312"/>
       <c r="B42" s="304"/>
       <c r="C42" s="442" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="D42" s="372" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="E42" s="467" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="F42" s="312"/>
       <c r="G42" s="312"/>
@@ -18514,10 +18517,10 @@
       <c r="A43" s="312"/>
       <c r="B43" s="304"/>
       <c r="C43" s="370" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="D43" s="369" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E43" s="312"/>
       <c r="F43" s="312"/>
@@ -18530,10 +18533,10 @@
       <c r="A44" s="312"/>
       <c r="B44" s="304"/>
       <c r="C44" s="370" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D44" s="369" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E44" s="312"/>
       <c r="F44" s="312"/>
@@ -18546,10 +18549,10 @@
       <c r="A45" s="312"/>
       <c r="B45" s="304"/>
       <c r="C45" s="456" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D45" s="372" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E45" s="312"/>
       <c r="F45" s="312"/>
@@ -18562,10 +18565,10 @@
       <c r="A46" s="312"/>
       <c r="B46" s="304"/>
       <c r="C46" s="456" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D46" s="372" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E46" s="312"/>
       <c r="F46" s="312"/>
@@ -18578,10 +18581,10 @@
       <c r="A47" s="312"/>
       <c r="B47" s="304"/>
       <c r="C47" s="456" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="D47" s="372" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="E47" s="312"/>
       <c r="F47" s="312"/>
@@ -18594,10 +18597,10 @@
       <c r="A48" s="312"/>
       <c r="B48" s="304"/>
       <c r="C48" s="443" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="D48" s="444" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="E48" s="312"/>
       <c r="F48" s="312"/>
@@ -18610,10 +18613,10 @@
       <c r="A49" s="312"/>
       <c r="B49" s="304"/>
       <c r="C49" s="445" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D49" s="446" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E49" s="312"/>
       <c r="F49" s="312"/>
@@ -18669,13 +18672,13 @@
       <c r="A53" s="312"/>
       <c r="B53" s="304"/>
       <c r="C53" s="375" t="s">
+        <v>936</v>
+      </c>
+      <c r="D53" s="376" t="s">
         <v>937</v>
       </c>
-      <c r="D53" s="376" t="s">
+      <c r="E53" s="377" t="s">
         <v>938</v>
-      </c>
-      <c r="E53" s="377" t="s">
-        <v>939</v>
       </c>
       <c r="F53" s="378"/>
       <c r="H53" s="312"/>
@@ -18687,10 +18690,10 @@
       <c r="B54" s="304"/>
       <c r="C54" s="379"/>
       <c r="D54" s="380" t="s">
+        <v>939</v>
+      </c>
+      <c r="E54" s="381" t="s">
         <v>940</v>
-      </c>
-      <c r="E54" s="381" t="s">
-        <v>941</v>
       </c>
       <c r="F54" s="382"/>
       <c r="H54" s="312"/>
@@ -18701,13 +18704,13 @@
       <c r="A55" s="312"/>
       <c r="B55" s="304"/>
       <c r="C55" s="375" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D55" s="376" t="s">
+        <v>937</v>
+      </c>
+      <c r="E55" s="377" t="s">
         <v>938</v>
-      </c>
-      <c r="E55" s="377" t="s">
-        <v>939</v>
       </c>
       <c r="F55" s="378"/>
       <c r="H55" s="312"/>
@@ -18719,10 +18722,10 @@
       <c r="B56" s="304"/>
       <c r="C56" s="379"/>
       <c r="D56" s="380" t="s">
+        <v>939</v>
+      </c>
+      <c r="E56" s="381" t="s">
         <v>940</v>
-      </c>
-      <c r="E56" s="381" t="s">
-        <v>941</v>
       </c>
       <c r="F56" s="382"/>
       <c r="H56" s="312"/>
@@ -18733,13 +18736,13 @@
       <c r="A57" s="312"/>
       <c r="B57" s="304"/>
       <c r="C57" s="383" t="s">
+        <v>942</v>
+      </c>
+      <c r="D57" s="380" t="s">
         <v>943</v>
       </c>
-      <c r="D57" s="380" t="s">
+      <c r="E57" s="384" t="s">
         <v>944</v>
-      </c>
-      <c r="E57" s="384" t="s">
-        <v>945</v>
       </c>
       <c r="F57" s="382"/>
       <c r="H57" s="312"/>
@@ -18751,10 +18754,10 @@
       <c r="B58" s="304"/>
       <c r="C58" s="375"/>
       <c r="D58" s="385" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="E58" s="384" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F58" s="382"/>
       <c r="H58" s="312"/>
@@ -18766,10 +18769,10 @@
       <c r="B59" s="304"/>
       <c r="C59" s="386"/>
       <c r="D59" s="380" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E59" s="387" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F59" s="382"/>
       <c r="H59" s="312"/>
@@ -18780,13 +18783,13 @@
       <c r="A60" s="312"/>
       <c r="B60" s="304"/>
       <c r="C60" s="383" t="s">
+        <v>947</v>
+      </c>
+      <c r="D60" s="376" t="s">
         <v>948</v>
       </c>
-      <c r="D60" s="376" t="s">
-        <v>949</v>
-      </c>
       <c r="E60" s="461" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F60" s="382"/>
       <c r="H60" s="312"/>
@@ -18798,10 +18801,10 @@
       <c r="B61" s="304"/>
       <c r="C61" s="375"/>
       <c r="D61" s="385" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E61" s="462" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="F61" s="382"/>
       <c r="H61" s="312"/>
@@ -18813,10 +18816,10 @@
       <c r="B62" s="304"/>
       <c r="C62" s="375"/>
       <c r="D62" s="376" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E62" s="459" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="F62" s="382"/>
       <c r="H62" s="312"/>
@@ -18828,10 +18831,10 @@
       <c r="B63" s="304"/>
       <c r="C63" s="375"/>
       <c r="D63" s="376" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E63" s="460" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F63" s="382"/>
       <c r="H63" s="312"/>
@@ -18846,7 +18849,7 @@
         <v>716</v>
       </c>
       <c r="E64" s="384" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F64" s="378"/>
       <c r="H64" s="312"/>
@@ -18857,13 +18860,13 @@
       <c r="A65" s="312"/>
       <c r="B65" s="304"/>
       <c r="C65" s="471" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D65" s="388" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E65" s="468" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F65" s="382"/>
       <c r="H65" s="312"/>
@@ -18875,10 +18878,10 @@
       <c r="B66" s="304"/>
       <c r="C66" s="375"/>
       <c r="D66" s="380" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E66" s="469" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="F66" s="382"/>
       <c r="H66" s="312"/>
@@ -18890,10 +18893,10 @@
       <c r="B67" s="304"/>
       <c r="C67" s="389"/>
       <c r="D67" s="390" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E67" s="451" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="F67" s="382"/>
       <c r="H67" s="312"/>
@@ -18905,10 +18908,10 @@
       <c r="B68" s="304"/>
       <c r="C68" s="392"/>
       <c r="D68" s="380" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E68" s="470" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F68" s="382"/>
       <c r="H68" s="312"/>
@@ -18923,7 +18926,7 @@
         <v>716</v>
       </c>
       <c r="E69" s="376" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F69" s="394"/>
       <c r="H69" s="312"/>
@@ -18934,13 +18937,13 @@
       <c r="A70" s="312"/>
       <c r="B70" s="304"/>
       <c r="C70" s="395" t="s">
+        <v>958</v>
+      </c>
+      <c r="D70" s="396" t="s">
         <v>959</v>
       </c>
-      <c r="D70" s="396" t="s">
+      <c r="E70" s="396" t="s">
         <v>960</v>
-      </c>
-      <c r="E70" s="396" t="s">
-        <v>961</v>
       </c>
       <c r="F70" s="394"/>
       <c r="H70" s="312"/>
@@ -18952,10 +18955,10 @@
       <c r="B71" s="304"/>
       <c r="C71" s="392"/>
       <c r="D71" s="396" t="s">
+        <v>961</v>
+      </c>
+      <c r="E71" s="396" t="s">
         <v>962</v>
-      </c>
-      <c r="E71" s="396" t="s">
-        <v>963</v>
       </c>
       <c r="F71" s="394"/>
       <c r="H71" s="312"/>
@@ -18967,10 +18970,10 @@
       <c r="B72" s="304"/>
       <c r="C72" s="392"/>
       <c r="D72" s="396" t="s">
+        <v>963</v>
+      </c>
+      <c r="E72" s="396" t="s">
         <v>964</v>
-      </c>
-      <c r="E72" s="396" t="s">
-        <v>965</v>
       </c>
       <c r="F72" s="394"/>
       <c r="H72" s="312"/>
@@ -18982,10 +18985,10 @@
       <c r="B73" s="304"/>
       <c r="C73" s="392"/>
       <c r="D73" s="396" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E73" s="396" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F73" s="394"/>
       <c r="H73" s="312"/>
@@ -18997,10 +19000,10 @@
       <c r="B74" s="304"/>
       <c r="C74" s="392"/>
       <c r="D74" s="397" t="s">
+        <v>966</v>
+      </c>
+      <c r="E74" s="397" t="s">
         <v>967</v>
-      </c>
-      <c r="E74" s="397" t="s">
-        <v>968</v>
       </c>
       <c r="F74" s="394"/>
       <c r="H74" s="312"/>
@@ -19011,13 +19014,13 @@
       <c r="A75" s="305"/>
       <c r="B75" s="305"/>
       <c r="C75" s="398" t="s">
+        <v>968</v>
+      </c>
+      <c r="D75" s="399" t="s">
+        <v>961</v>
+      </c>
+      <c r="E75" s="400" t="s">
         <v>969</v>
-      </c>
-      <c r="D75" s="399" t="s">
-        <v>962</v>
-      </c>
-      <c r="E75" s="400" t="s">
-        <v>970</v>
       </c>
       <c r="F75" s="394"/>
       <c r="G75" s="305"/>
@@ -19028,66 +19031,66 @@
     <row r="76" spans="1:10" ht="15" customHeight="1">
       <c r="C76" s="401"/>
       <c r="D76" s="402" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E76" s="403" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="15" customHeight="1">
       <c r="C77" s="401"/>
       <c r="D77" s="402" t="s">
+        <v>971</v>
+      </c>
+      <c r="E77" s="403" t="s">
         <v>972</v>
-      </c>
-      <c r="E77" s="403" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1">
       <c r="C78" s="404"/>
       <c r="D78" s="402" t="s">
+        <v>973</v>
+      </c>
+      <c r="E78" s="400" t="s">
         <v>974</v>
-      </c>
-      <c r="E78" s="400" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15" customHeight="1">
       <c r="C79" s="398" t="s">
+        <v>975</v>
+      </c>
+      <c r="D79" s="399" t="s">
+        <v>961</v>
+      </c>
+      <c r="E79" s="400" t="s">
         <v>976</v>
-      </c>
-      <c r="D79" s="399" t="s">
-        <v>962</v>
-      </c>
-      <c r="E79" s="400" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15" customHeight="1">
       <c r="C80" s="401"/>
       <c r="D80" s="402" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E80" s="403" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="81" spans="3:5" ht="15" customHeight="1">
       <c r="C81" s="401"/>
       <c r="D81" s="402" t="s">
+        <v>971</v>
+      </c>
+      <c r="E81" s="403" t="s">
         <v>972</v>
-      </c>
-      <c r="E81" s="403" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="82" spans="3:5" ht="15" customHeight="1">
       <c r="C82" s="404"/>
       <c r="D82" s="402" t="s">
+        <v>973</v>
+      </c>
+      <c r="E82" s="400" t="s">
         <v>974</v>
-      </c>
-      <c r="E82" s="400" t="s">
-        <v>975</v>
       </c>
     </row>
   </sheetData>

--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FF3D9F-2A7D-9442-A0E4-E86C529E1A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57058F2C-0A97-F54A-8F45-1538D65CB40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="1075">
   <si>
     <t>プロジェクト概要</t>
   </si>
@@ -4414,10 +4414,6 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>index.blade.php</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <r>
       <t>Fortify(</t>
     </r>
@@ -5068,10 +5064,6 @@
   </si>
   <si>
     <t>メール認証誘導画面（一般ユーザー）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>redirect</t>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -5129,10 +5121,6 @@
   </si>
   <si>
     <t>修正申請承認画面（管理者）</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <t>verify-email.blade.php</t>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -5865,6 +5853,14 @@
   </si>
   <si>
     <t>show/export</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>/email/verify</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>reports/index.blade.php</t>
     <phoneticPr fontId="80"/>
   </si>
 </sst>
@@ -8806,11 +8802,25 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8819,31 +8829,17 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -9437,7 +9433,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="413" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="E6" s="414"/>
       <c r="F6" s="414"/>
@@ -9456,7 +9452,7 @@
         <v>701</v>
       </c>
       <c r="F7" s="418" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G7" s="418" t="s">
         <v>710</v>
@@ -9475,10 +9471,10 @@
       <c r="C8" s="420"/>
       <c r="D8" s="304"/>
       <c r="E8" s="391" t="s">
+        <v>978</v>
+      </c>
+      <c r="F8" s="391" t="s">
         <v>979</v>
-      </c>
-      <c r="F8" s="391" t="s">
-        <v>980</v>
       </c>
       <c r="G8" s="391"/>
       <c r="H8" s="391"/>
@@ -9494,10 +9490,10 @@
       <c r="B9" s="366"/>
       <c r="C9" s="417"/>
       <c r="E9" s="391" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F9" s="391" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G9" s="391"/>
       <c r="H9" s="418" t="s">
@@ -9517,7 +9513,7 @@
       <c r="B10" s="366"/>
       <c r="C10" s="417"/>
       <c r="E10" s="391" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="F10" s="391" t="s">
         <v>731</v>
@@ -9534,10 +9530,10 @@
       <c r="B11" s="366"/>
       <c r="C11" s="417"/>
       <c r="E11" s="391" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F11" s="391" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G11" s="391"/>
       <c r="H11" s="391"/>
@@ -9553,10 +9549,10 @@
       <c r="B12" s="366"/>
       <c r="C12" s="417"/>
       <c r="E12" s="391" t="s">
+        <v>983</v>
+      </c>
+      <c r="F12" s="391" t="s">
         <v>984</v>
-      </c>
-      <c r="F12" s="391" t="s">
-        <v>985</v>
       </c>
       <c r="G12" s="391"/>
       <c r="H12" s="391"/>
@@ -9570,13 +9566,13 @@
       <c r="B13" s="366"/>
       <c r="C13" s="417"/>
       <c r="D13" s="436" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="E13" s="447" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="F13" s="447" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="G13" s="391"/>
       <c r="H13" s="391"/>
@@ -9592,13 +9588,13 @@
       <c r="B14" s="366"/>
       <c r="C14" s="417"/>
       <c r="D14" s="436" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="E14" s="391" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="F14" s="391" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="G14" s="391"/>
       <c r="H14" s="391"/>
@@ -9648,7 +9644,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="422" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E17" s="414"/>
       <c r="F17" s="414"/>
@@ -9664,10 +9660,10 @@
       <c r="B18" s="394"/>
       <c r="C18" s="423"/>
       <c r="E18" s="391" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="F18" s="362" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G18" s="418" t="s">
         <v>903</v>
@@ -9685,13 +9681,13 @@
       <c r="B19" s="394"/>
       <c r="C19" s="423"/>
       <c r="D19" s="312" t="s">
+        <v>987</v>
+      </c>
+      <c r="E19" s="391" t="s">
+        <v>958</v>
+      </c>
+      <c r="F19" s="362" t="s">
         <v>988</v>
-      </c>
-      <c r="E19" s="391" t="s">
-        <v>959</v>
-      </c>
-      <c r="F19" s="362" t="s">
-        <v>989</v>
       </c>
       <c r="G19" s="418"/>
       <c r="H19" s="391" t="s">
@@ -9701,7 +9697,7 @@
         <v>903</v>
       </c>
       <c r="J19" s="419" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="K19" s="305"/>
       <c r="L19" s="305"/>
@@ -9712,10 +9708,10 @@
       <c r="C20" s="423"/>
       <c r="D20" s="312"/>
       <c r="E20" s="391" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F20" s="362" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G20" s="418"/>
       <c r="H20" s="391" t="s">
@@ -9732,10 +9728,10 @@
       <c r="C21" s="423"/>
       <c r="D21" s="304"/>
       <c r="E21" s="391" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F21" s="362" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G21" s="391"/>
       <c r="H21" s="391"/>
@@ -9751,10 +9747,10 @@
       <c r="B22" s="394"/>
       <c r="C22" s="423"/>
       <c r="E22" s="391" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F22" s="362" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G22" s="391"/>
       <c r="H22" s="391"/>
@@ -9768,10 +9764,10 @@
       <c r="B23" s="394"/>
       <c r="C23" s="423"/>
       <c r="E23" s="447" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F23" s="447" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G23" s="391"/>
       <c r="H23" s="391"/>
@@ -9822,12 +9818,12 @@
       <c r="C26" s="423"/>
       <c r="D26" s="429"/>
       <c r="E26" s="430" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F26" s="431"/>
       <c r="G26" s="432"/>
       <c r="H26" s="431" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="I26" s="431"/>
       <c r="J26" s="433"/>
@@ -9841,7 +9837,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="422" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="E27" s="414"/>
       <c r="F27" s="414"/>
@@ -9860,7 +9856,7 @@
         <v>701</v>
       </c>
       <c r="F28" s="391" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G28" s="418" t="s">
         <v>710</v>
@@ -9878,13 +9874,13 @@
       <c r="B29" s="394"/>
       <c r="C29" s="423"/>
       <c r="D29" s="312" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E29" s="451" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="F29" s="391" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G29" s="418"/>
       <c r="H29" s="391"/>
@@ -9892,7 +9888,7 @@
         <v>710</v>
       </c>
       <c r="J29" s="419" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="K29" s="305"/>
       <c r="L29" s="305"/>
@@ -9903,10 +9899,10 @@
       <c r="C30" s="423"/>
       <c r="D30" s="304"/>
       <c r="E30" s="391" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="F30" s="391" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G30" s="391"/>
       <c r="H30" s="391"/>
@@ -9920,10 +9916,10 @@
       <c r="B31" s="394"/>
       <c r="C31" s="423"/>
       <c r="E31" s="391" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="F31" s="391" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G31" s="391"/>
       <c r="H31" s="391"/>
@@ -9972,13 +9968,13 @@
       <c r="C34" s="424">
         <v>4</v>
       </c>
-      <c r="D34" s="487" t="s">
-        <v>995</v>
-      </c>
-      <c r="E34" s="488"/>
-      <c r="F34" s="488"/>
-      <c r="G34" s="488"/>
-      <c r="H34" s="488"/>
+      <c r="D34" s="488" t="s">
+        <v>994</v>
+      </c>
+      <c r="E34" s="489"/>
+      <c r="F34" s="489"/>
+      <c r="G34" s="489"/>
+      <c r="H34" s="489"/>
       <c r="I34" s="414"/>
       <c r="J34" s="415"/>
       <c r="K34" s="305"/>
@@ -9989,10 +9985,10 @@
       <c r="B35" s="394"/>
       <c r="C35" s="423"/>
       <c r="E35" s="391" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="F35" s="362" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G35" s="418" t="s">
         <v>903</v>
@@ -10010,13 +10006,13 @@
       <c r="B36" s="394"/>
       <c r="C36" s="423"/>
       <c r="D36" s="306" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E36" s="451" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="F36" s="362" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G36" s="418"/>
       <c r="H36" s="391"/>
@@ -10024,7 +10020,7 @@
         <v>710</v>
       </c>
       <c r="J36" s="419" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="K36" s="305"/>
       <c r="L36" s="305"/>
@@ -10034,10 +10030,10 @@
       <c r="B37" s="394"/>
       <c r="C37" s="423"/>
       <c r="E37" s="391" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F37" s="391" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G37" s="391"/>
       <c r="H37" s="391"/>
@@ -10053,10 +10049,10 @@
       <c r="B38" s="394"/>
       <c r="C38" s="423"/>
       <c r="E38" s="391" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="F38" s="435" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G38" s="391"/>
       <c r="H38" s="391"/>
@@ -10070,10 +10066,10 @@
       <c r="B39" s="394"/>
       <c r="C39" s="423"/>
       <c r="E39" s="391" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F39" s="391" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G39" s="391"/>
       <c r="H39" s="391"/>
@@ -10089,13 +10085,13 @@
       <c r="B40" s="394"/>
       <c r="C40" s="423"/>
       <c r="D40" s="436" t="s">
+        <v>997</v>
+      </c>
+      <c r="E40" s="391" t="s">
         <v>998</v>
       </c>
-      <c r="E40" s="391" t="s">
+      <c r="F40" s="391" t="s">
         <v>999</v>
-      </c>
-      <c r="F40" s="391" t="s">
-        <v>1000</v>
       </c>
       <c r="G40" s="391"/>
       <c r="H40" s="391"/>
@@ -10112,10 +10108,10 @@
       <c r="C41" s="423"/>
       <c r="D41" s="436"/>
       <c r="E41" s="447" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="F41" s="447" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G41" s="391"/>
       <c r="H41" s="391"/>
@@ -10169,7 +10165,7 @@
         <v>5</v>
       </c>
       <c r="D44" s="450" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="E44" s="414"/>
       <c r="F44" s="414"/>
@@ -10188,7 +10184,7 @@
         <v>701</v>
       </c>
       <c r="F45" s="391" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G45" s="391" t="s">
         <v>710</v>
@@ -10206,13 +10202,13 @@
       <c r="B46" s="394"/>
       <c r="C46" s="423"/>
       <c r="D46" s="312" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E46" s="391" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F46" s="391" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G46" s="391"/>
       <c r="H46" s="391"/>
@@ -10220,7 +10216,7 @@
         <v>903</v>
       </c>
       <c r="J46" s="419" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="K46" s="305"/>
       <c r="L46" s="305"/>
@@ -10230,10 +10226,10 @@
       <c r="B47" s="394"/>
       <c r="C47" s="423"/>
       <c r="E47" s="391" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F47" s="391" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G47" s="391"/>
       <c r="H47" s="391"/>
@@ -10247,10 +10243,10 @@
       <c r="B48" s="394"/>
       <c r="C48" s="423"/>
       <c r="E48" s="391" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F48" s="391" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G48" s="391"/>
       <c r="H48" s="391"/>
@@ -10846,11 +10842,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="475" t="s">
+      <c r="C4" s="481" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="476"/>
-      <c r="E4" s="476"/>
+      <c r="D4" s="482"/>
+      <c r="E4" s="482"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10859,13 +10855,13 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
-      <c r="C5" s="481" t="s">
+      <c r="C5" s="485" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="477" t="s">
+      <c r="D5" s="483" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="478"/>
+      <c r="E5" s="484"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10874,11 +10870,11 @@
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="474"/>
-      <c r="D6" s="479" t="s">
+      <c r="C6" s="478"/>
+      <c r="D6" s="473" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="480"/>
+      <c r="E6" s="474"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10887,11 +10883,11 @@
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="474"/>
-      <c r="D7" s="479" t="s">
+      <c r="C7" s="478"/>
+      <c r="D7" s="473" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="480"/>
+      <c r="E7" s="474"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10900,11 +10896,11 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="474"/>
-      <c r="D8" s="479" t="s">
+      <c r="C8" s="478"/>
+      <c r="D8" s="473" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="480"/>
+      <c r="E8" s="474"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10913,11 +10909,11 @@
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="474"/>
-      <c r="D9" s="479" t="s">
+      <c r="C9" s="478"/>
+      <c r="D9" s="473" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="480"/>
+      <c r="E9" s="474"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10926,11 +10922,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="473"/>
-      <c r="D10" s="479" t="s">
+      <c r="C10" s="479"/>
+      <c r="D10" s="473" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="480"/>
+      <c r="E10" s="474"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10939,13 +10935,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="472" t="s">
+      <c r="C11" s="480" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="479" t="s">
+      <c r="D11" s="473" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="480"/>
+      <c r="E11" s="474"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10954,11 +10950,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="473"/>
-      <c r="D12" s="479" t="s">
+      <c r="C12" s="479"/>
+      <c r="D12" s="473" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="480"/>
+      <c r="E12" s="474"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10967,13 +10963,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="472" t="s">
+      <c r="C13" s="480" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="479" t="s">
+      <c r="D13" s="473" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="480"/>
+      <c r="E13" s="474"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10982,11 +10978,11 @@
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="474"/>
-      <c r="D14" s="479" t="s">
+      <c r="C14" s="478"/>
+      <c r="D14" s="473" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="480"/>
+      <c r="E14" s="474"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10995,11 +10991,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="473"/>
-      <c r="D15" s="479" t="s">
+      <c r="C15" s="479"/>
+      <c r="D15" s="473" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="480"/>
+      <c r="E15" s="474"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -11008,13 +11004,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="472" t="s">
+      <c r="C16" s="480" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="484" t="s">
+      <c r="D16" s="475" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="485"/>
+      <c r="E16" s="476"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -11023,8 +11019,8 @@
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="474"/>
-      <c r="D17" s="483" t="s">
+      <c r="C17" s="478"/>
+      <c r="D17" s="477" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="107" t="s">
@@ -11038,8 +11034,8 @@
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="474"/>
-      <c r="D18" s="474"/>
+      <c r="C18" s="478"/>
+      <c r="D18" s="478"/>
       <c r="E18" s="107" t="s">
         <v>134</v>
       </c>
@@ -11051,8 +11047,8 @@
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="474"/>
-      <c r="D19" s="474"/>
+      <c r="C19" s="478"/>
+      <c r="D19" s="478"/>
       <c r="E19" s="107" t="s">
         <v>137</v>
       </c>
@@ -11064,8 +11060,8 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="474"/>
-      <c r="D20" s="474"/>
+      <c r="C20" s="478"/>
+      <c r="D20" s="478"/>
       <c r="E20" s="107" t="s">
         <v>140</v>
       </c>
@@ -11077,8 +11073,8 @@
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="474"/>
-      <c r="D21" s="473"/>
+      <c r="C21" s="478"/>
+      <c r="D21" s="479"/>
       <c r="E21" s="107" t="s">
         <v>145</v>
       </c>
@@ -11090,8 +11086,8 @@
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="474"/>
-      <c r="D22" s="482" t="s">
+      <c r="C22" s="478"/>
+      <c r="D22" s="486" t="s">
         <v>165</v>
       </c>
       <c r="E22" s="127" t="s">
@@ -11105,8 +11101,8 @@
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="474"/>
-      <c r="D23" s="474"/>
+      <c r="C23" s="478"/>
+      <c r="D23" s="478"/>
       <c r="E23" s="127" t="s">
         <v>177</v>
       </c>
@@ -11118,8 +11114,8 @@
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="474"/>
-      <c r="D24" s="474"/>
+      <c r="C24" s="478"/>
+      <c r="D24" s="478"/>
       <c r="E24" s="127" t="s">
         <v>179</v>
       </c>
@@ -11131,8 +11127,8 @@
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="474"/>
-      <c r="D25" s="474"/>
+      <c r="C25" s="478"/>
+      <c r="D25" s="478"/>
       <c r="E25" s="127" t="s">
         <v>185</v>
       </c>
@@ -11144,8 +11140,8 @@
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="474"/>
-      <c r="D26" s="473"/>
+      <c r="C26" s="478"/>
+      <c r="D26" s="479"/>
       <c r="E26" s="127" t="s">
         <v>190</v>
       </c>
@@ -11157,7 +11153,7 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="474"/>
+      <c r="C27" s="478"/>
       <c r="D27" s="127" t="s">
         <v>193</v>
       </c>
@@ -11172,7 +11168,7 @@
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="474"/>
+      <c r="C28" s="478"/>
       <c r="D28" s="105" t="s">
         <v>221</v>
       </c>
@@ -11187,8 +11183,8 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="474"/>
-      <c r="D29" s="483" t="s">
+      <c r="C29" s="478"/>
+      <c r="D29" s="477" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="127" t="s">
@@ -11202,8 +11198,8 @@
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="474"/>
-      <c r="D30" s="474"/>
+      <c r="C30" s="478"/>
+      <c r="D30" s="478"/>
       <c r="E30" s="127" t="s">
         <v>244</v>
       </c>
@@ -11215,8 +11211,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="473"/>
-      <c r="D31" s="473"/>
+      <c r="C31" s="479"/>
+      <c r="D31" s="479"/>
       <c r="E31" s="127" t="s">
         <v>249</v>
       </c>
@@ -11228,13 +11224,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="472" t="s">
+      <c r="C32" s="480" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="479" t="s">
+      <c r="D32" s="473" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="480"/>
+      <c r="E32" s="474"/>
       <c r="F32" s="159" t="s">
         <v>259</v>
       </c>
@@ -11242,11 +11238,11 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="474"/>
-      <c r="D33" s="479" t="s">
+      <c r="C33" s="478"/>
+      <c r="D33" s="473" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="480"/>
+      <c r="E33" s="474"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -11255,11 +11251,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="473"/>
-      <c r="D34" s="479" t="s">
+      <c r="C34" s="479"/>
+      <c r="D34" s="473" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="480"/>
+      <c r="E34" s="474"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -11276,14 +11272,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:D21"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="C16:C31"/>
@@ -11300,6 +11288,14 @@
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:D21"/>
   </mergeCells>
   <phoneticPr fontId="80"/>
   <hyperlinks>
@@ -12722,13 +12718,13 @@
         <v>58</v>
       </c>
       <c r="F10" s="457" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="G10" s="65" t="s">
         <v>64</v>
       </c>
       <c r="H10" s="458" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="I10" s="10"/>
     </row>
@@ -14617,7 +14613,7 @@
     <row r="71" spans="1:8" ht="26">
       <c r="A71" s="279"/>
       <c r="B71" s="279"/>
-      <c r="C71" s="486">
+      <c r="C71" s="487">
         <v>16</v>
       </c>
       <c r="D71" s="280" t="s">
@@ -14637,7 +14633,7 @@
     <row r="72" spans="1:8" ht="39">
       <c r="A72" s="279"/>
       <c r="B72" s="279"/>
-      <c r="C72" s="474"/>
+      <c r="C72" s="478"/>
       <c r="D72" s="283"/>
       <c r="E72" s="281" t="s">
         <v>742</v>
@@ -14653,7 +14649,7 @@
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="279"/>
       <c r="B73" s="279"/>
-      <c r="C73" s="473"/>
+      <c r="C73" s="479"/>
       <c r="D73" s="284"/>
       <c r="E73" s="281" t="s">
         <v>745</v>
@@ -17806,7 +17802,7 @@
         <v>41</v>
       </c>
       <c r="D7" s="324" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="E7" s="325" t="s">
         <v>899</v>
@@ -17815,7 +17811,7 @@
         <v>896</v>
       </c>
       <c r="G7" s="327" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="H7" s="328" t="s">
         <v>897</v>
@@ -17824,7 +17820,7 @@
         <v>900</v>
       </c>
       <c r="J7" s="465" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="154">
@@ -17834,16 +17830,16 @@
         <v>901</v>
       </c>
       <c r="D8" s="324" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="E8" s="325" t="s">
         <v>895</v>
       </c>
       <c r="F8" s="331" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="G8" s="332" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="H8" s="333" t="s">
         <v>903</v>
@@ -17895,7 +17891,7 @@
         <v>907</v>
       </c>
       <c r="G10" s="335" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="H10" s="333" t="s">
         <v>903</v>
@@ -17944,10 +17940,10 @@
         <v>895</v>
       </c>
       <c r="F12" s="331" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="G12" s="463" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="H12" s="333" t="s">
         <v>897</v>
@@ -17956,7 +17952,7 @@
         <v>911</v>
       </c>
       <c r="J12" s="464" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="56">
@@ -18001,7 +17997,7 @@
         <v>912</v>
       </c>
       <c r="G14" s="466" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="H14" s="333" t="s">
         <v>903</v>
@@ -18018,7 +18014,7 @@
         <v>84</v>
       </c>
       <c r="D15" s="324" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="E15" s="343" t="s">
         <v>899</v>
@@ -18052,8 +18048,8 @@
       <c r="F16" s="331" t="s">
         <v>916</v>
       </c>
-      <c r="G16" s="489" t="s">
-        <v>1075</v>
+      <c r="G16" s="472" t="s">
+        <v>1072</v>
       </c>
       <c r="H16" s="333" t="s">
         <v>903</v>
@@ -18105,7 +18101,7 @@
         <v>920</v>
       </c>
       <c r="G18" s="350" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="H18" s="351" t="s">
         <v>903</v>
@@ -18143,13 +18139,13 @@
       <c r="A20" s="312"/>
       <c r="B20" s="304"/>
       <c r="C20" s="353" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D20" s="354" t="s">
-        <v>1006</v>
+        <v>1073</v>
       </c>
       <c r="E20" s="355" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="F20" s="356" t="s">
         <v>897</v>
@@ -18161,7 +18157,7 @@
         <v>903</v>
       </c>
       <c r="I20" s="359" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="J20" s="453"/>
     </row>
@@ -18243,7 +18239,7 @@
       <c r="A26" s="312"/>
       <c r="B26" s="304"/>
       <c r="C26" s="365" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="D26" s="364" t="s">
         <v>930</v>
@@ -18275,7 +18271,7 @@
       <c r="A28" s="312"/>
       <c r="B28" s="304"/>
       <c r="C28" s="449" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D28" s="364" t="s">
         <v>933</v>
@@ -18333,10 +18329,10 @@
       <c r="A32" s="312"/>
       <c r="B32" s="304"/>
       <c r="C32" s="441" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="D32" s="369" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="E32" s="312"/>
       <c r="F32" s="312"/>
@@ -18352,7 +18348,7 @@
         <v>934</v>
       </c>
       <c r="D33" s="369" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="E33" s="312"/>
       <c r="F33" s="312"/>
@@ -18368,7 +18364,7 @@
         <v>901</v>
       </c>
       <c r="D34" s="369" t="s">
-        <v>1038</v>
+        <v>1035</v>
       </c>
       <c r="E34" s="312"/>
       <c r="F34" s="312"/>
@@ -18381,13 +18377,13 @@
       <c r="A35" s="312"/>
       <c r="B35" s="304"/>
       <c r="C35" s="370" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D35" s="369" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="E35" s="467" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="F35" s="312"/>
       <c r="G35" s="312"/>
@@ -18399,10 +18395,10 @@
       <c r="A36" s="312"/>
       <c r="B36" s="304"/>
       <c r="C36" s="370" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="D36" s="371" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="E36" s="312"/>
       <c r="F36" s="312"/>
@@ -18415,10 +18411,10 @@
       <c r="A37" s="312"/>
       <c r="B37" s="304"/>
       <c r="C37" s="370" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="D37" s="369" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="E37" s="312"/>
       <c r="F37" s="312"/>
@@ -18431,10 +18427,10 @@
       <c r="A38" s="312"/>
       <c r="B38" s="304"/>
       <c r="C38" s="370" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="D38" s="369" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E38" s="312"/>
       <c r="F38" s="312"/>
@@ -18447,13 +18443,13 @@
       <c r="A39" s="312"/>
       <c r="B39" s="304"/>
       <c r="C39" s="442" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D39" s="369" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="E39" s="467" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F39" s="312"/>
       <c r="G39" s="312"/>
@@ -18465,13 +18461,13 @@
       <c r="A40" s="312"/>
       <c r="B40" s="304"/>
       <c r="C40" s="370" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D40" s="371" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="E40" s="467" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="F40" s="312"/>
       <c r="G40" s="312"/>
@@ -18483,10 +18479,10 @@
       <c r="A41" s="312"/>
       <c r="B41" s="304"/>
       <c r="C41" s="370" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D41" s="369" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="E41" s="312"/>
       <c r="F41" s="312"/>
@@ -18499,13 +18495,13 @@
       <c r="A42" s="312"/>
       <c r="B42" s="304"/>
       <c r="C42" s="442" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D42" s="372" t="s">
-        <v>1046</v>
+        <v>1043</v>
       </c>
       <c r="E42" s="467" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F42" s="312"/>
       <c r="G42" s="312"/>
@@ -18517,10 +18513,10 @@
       <c r="A43" s="312"/>
       <c r="B43" s="304"/>
       <c r="C43" s="370" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="D43" s="369" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="E43" s="312"/>
       <c r="F43" s="312"/>
@@ -18533,10 +18529,10 @@
       <c r="A44" s="312"/>
       <c r="B44" s="304"/>
       <c r="C44" s="370" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="D44" s="369" t="s">
-        <v>1048</v>
+        <v>1045</v>
       </c>
       <c r="E44" s="312"/>
       <c r="F44" s="312"/>
@@ -18549,10 +18545,10 @@
       <c r="A45" s="312"/>
       <c r="B45" s="304"/>
       <c r="C45" s="456" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D45" s="372" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="E45" s="312"/>
       <c r="F45" s="312"/>
@@ -18565,10 +18561,10 @@
       <c r="A46" s="312"/>
       <c r="B46" s="304"/>
       <c r="C46" s="456" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="D46" s="372" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="E46" s="312"/>
       <c r="F46" s="312"/>
@@ -18581,10 +18577,10 @@
       <c r="A47" s="312"/>
       <c r="B47" s="304"/>
       <c r="C47" s="456" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="D47" s="372" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="E47" s="312"/>
       <c r="F47" s="312"/>
@@ -18600,7 +18596,7 @@
         <v>923</v>
       </c>
       <c r="D48" s="444" t="s">
-        <v>935</v>
+        <v>1074</v>
       </c>
       <c r="E48" s="312"/>
       <c r="F48" s="312"/>
@@ -18613,10 +18609,10 @@
       <c r="A49" s="312"/>
       <c r="B49" s="304"/>
       <c r="C49" s="445" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D49" s="446" t="s">
-        <v>1019</v>
+        <v>1046</v>
       </c>
       <c r="E49" s="312"/>
       <c r="F49" s="312"/>
@@ -18672,13 +18668,13 @@
       <c r="A53" s="312"/>
       <c r="B53" s="304"/>
       <c r="C53" s="375" t="s">
+        <v>935</v>
+      </c>
+      <c r="D53" s="376" t="s">
         <v>936</v>
       </c>
-      <c r="D53" s="376" t="s">
+      <c r="E53" s="377" t="s">
         <v>937</v>
-      </c>
-      <c r="E53" s="377" t="s">
-        <v>938</v>
       </c>
       <c r="F53" s="378"/>
       <c r="H53" s="312"/>
@@ -18690,10 +18686,10 @@
       <c r="B54" s="304"/>
       <c r="C54" s="379"/>
       <c r="D54" s="380" t="s">
+        <v>938</v>
+      </c>
+      <c r="E54" s="381" t="s">
         <v>939</v>
-      </c>
-      <c r="E54" s="381" t="s">
-        <v>940</v>
       </c>
       <c r="F54" s="382"/>
       <c r="H54" s="312"/>
@@ -18704,13 +18700,13 @@
       <c r="A55" s="312"/>
       <c r="B55" s="304"/>
       <c r="C55" s="375" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="D55" s="376" t="s">
+        <v>936</v>
+      </c>
+      <c r="E55" s="377" t="s">
         <v>937</v>
-      </c>
-      <c r="E55" s="377" t="s">
-        <v>938</v>
       </c>
       <c r="F55" s="378"/>
       <c r="H55" s="312"/>
@@ -18722,10 +18718,10 @@
       <c r="B56" s="304"/>
       <c r="C56" s="379"/>
       <c r="D56" s="380" t="s">
+        <v>938</v>
+      </c>
+      <c r="E56" s="381" t="s">
         <v>939</v>
-      </c>
-      <c r="E56" s="381" t="s">
-        <v>940</v>
       </c>
       <c r="F56" s="382"/>
       <c r="H56" s="312"/>
@@ -18736,13 +18732,13 @@
       <c r="A57" s="312"/>
       <c r="B57" s="304"/>
       <c r="C57" s="383" t="s">
+        <v>941</v>
+      </c>
+      <c r="D57" s="380" t="s">
         <v>942</v>
       </c>
-      <c r="D57" s="380" t="s">
+      <c r="E57" s="384" t="s">
         <v>943</v>
-      </c>
-      <c r="E57" s="384" t="s">
-        <v>944</v>
       </c>
       <c r="F57" s="382"/>
       <c r="H57" s="312"/>
@@ -18754,10 +18750,10 @@
       <c r="B58" s="304"/>
       <c r="C58" s="375"/>
       <c r="D58" s="385" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E58" s="384" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="F58" s="382"/>
       <c r="H58" s="312"/>
@@ -18769,10 +18765,10 @@
       <c r="B59" s="304"/>
       <c r="C59" s="386"/>
       <c r="D59" s="380" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E59" s="387" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F59" s="382"/>
       <c r="H59" s="312"/>
@@ -18783,13 +18779,13 @@
       <c r="A60" s="312"/>
       <c r="B60" s="304"/>
       <c r="C60" s="383" t="s">
+        <v>946</v>
+      </c>
+      <c r="D60" s="376" t="s">
         <v>947</v>
       </c>
-      <c r="D60" s="376" t="s">
-        <v>948</v>
-      </c>
       <c r="E60" s="461" t="s">
-        <v>1057</v>
+        <v>1054</v>
       </c>
       <c r="F60" s="382"/>
       <c r="H60" s="312"/>
@@ -18801,10 +18797,10 @@
       <c r="B61" s="304"/>
       <c r="C61" s="375"/>
       <c r="D61" s="385" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="E61" s="462" t="s">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="F61" s="382"/>
       <c r="H61" s="312"/>
@@ -18816,10 +18812,10 @@
       <c r="B62" s="304"/>
       <c r="C62" s="375"/>
       <c r="D62" s="376" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E62" s="459" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F62" s="382"/>
       <c r="H62" s="312"/>
@@ -18831,10 +18827,10 @@
       <c r="B63" s="304"/>
       <c r="C63" s="375"/>
       <c r="D63" s="376" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="E63" s="460" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="F63" s="382"/>
       <c r="H63" s="312"/>
@@ -18849,7 +18845,7 @@
         <v>716</v>
       </c>
       <c r="E64" s="384" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F64" s="378"/>
       <c r="H64" s="312"/>
@@ -18860,13 +18856,13 @@
       <c r="A65" s="312"/>
       <c r="B65" s="304"/>
       <c r="C65" s="471" t="s">
-        <v>1073</v>
+        <v>1070</v>
       </c>
       <c r="D65" s="388" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E65" s="468" t="s">
-        <v>1059</v>
+        <v>1056</v>
       </c>
       <c r="F65" s="382"/>
       <c r="H65" s="312"/>
@@ -18878,10 +18874,10 @@
       <c r="B66" s="304"/>
       <c r="C66" s="375"/>
       <c r="D66" s="380" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E66" s="469" t="s">
-        <v>1060</v>
+        <v>1057</v>
       </c>
       <c r="F66" s="382"/>
       <c r="H66" s="312"/>
@@ -18893,10 +18889,10 @@
       <c r="B67" s="304"/>
       <c r="C67" s="389"/>
       <c r="D67" s="390" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E67" s="451" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F67" s="382"/>
       <c r="H67" s="312"/>
@@ -18908,10 +18904,10 @@
       <c r="B68" s="304"/>
       <c r="C68" s="392"/>
       <c r="D68" s="380" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E68" s="470" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F68" s="382"/>
       <c r="H68" s="312"/>
@@ -18926,7 +18922,7 @@
         <v>716</v>
       </c>
       <c r="E69" s="376" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="F69" s="394"/>
       <c r="H69" s="312"/>
@@ -18937,13 +18933,13 @@
       <c r="A70" s="312"/>
       <c r="B70" s="304"/>
       <c r="C70" s="395" t="s">
+        <v>957</v>
+      </c>
+      <c r="D70" s="396" t="s">
         <v>958</v>
       </c>
-      <c r="D70" s="396" t="s">
+      <c r="E70" s="396" t="s">
         <v>959</v>
-      </c>
-      <c r="E70" s="396" t="s">
-        <v>960</v>
       </c>
       <c r="F70" s="394"/>
       <c r="H70" s="312"/>
@@ -18955,10 +18951,10 @@
       <c r="B71" s="304"/>
       <c r="C71" s="392"/>
       <c r="D71" s="396" t="s">
+        <v>960</v>
+      </c>
+      <c r="E71" s="396" t="s">
         <v>961</v>
-      </c>
-      <c r="E71" s="396" t="s">
-        <v>962</v>
       </c>
       <c r="F71" s="394"/>
       <c r="H71" s="312"/>
@@ -18970,10 +18966,10 @@
       <c r="B72" s="304"/>
       <c r="C72" s="392"/>
       <c r="D72" s="396" t="s">
+        <v>962</v>
+      </c>
+      <c r="E72" s="396" t="s">
         <v>963</v>
-      </c>
-      <c r="E72" s="396" t="s">
-        <v>964</v>
       </c>
       <c r="F72" s="394"/>
       <c r="H72" s="312"/>
@@ -18985,10 +18981,10 @@
       <c r="B73" s="304"/>
       <c r="C73" s="392"/>
       <c r="D73" s="396" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="E73" s="396" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F73" s="394"/>
       <c r="H73" s="312"/>
@@ -19000,10 +18996,10 @@
       <c r="B74" s="304"/>
       <c r="C74" s="392"/>
       <c r="D74" s="397" t="s">
+        <v>965</v>
+      </c>
+      <c r="E74" s="397" t="s">
         <v>966</v>
-      </c>
-      <c r="E74" s="397" t="s">
-        <v>967</v>
       </c>
       <c r="F74" s="394"/>
       <c r="H74" s="312"/>
@@ -19014,13 +19010,13 @@
       <c r="A75" s="305"/>
       <c r="B75" s="305"/>
       <c r="C75" s="398" t="s">
+        <v>967</v>
+      </c>
+      <c r="D75" s="399" t="s">
+        <v>960</v>
+      </c>
+      <c r="E75" s="400" t="s">
         <v>968</v>
-      </c>
-      <c r="D75" s="399" t="s">
-        <v>961</v>
-      </c>
-      <c r="E75" s="400" t="s">
-        <v>969</v>
       </c>
       <c r="F75" s="394"/>
       <c r="G75" s="305"/>
@@ -19031,66 +19027,66 @@
     <row r="76" spans="1:10" ht="15" customHeight="1">
       <c r="C76" s="401"/>
       <c r="D76" s="402" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E76" s="403" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="15" customHeight="1">
       <c r="C77" s="401"/>
       <c r="D77" s="402" t="s">
+        <v>970</v>
+      </c>
+      <c r="E77" s="403" t="s">
         <v>971</v>
-      </c>
-      <c r="E77" s="403" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1">
       <c r="C78" s="404"/>
       <c r="D78" s="402" t="s">
+        <v>972</v>
+      </c>
+      <c r="E78" s="400" t="s">
         <v>973</v>
-      </c>
-      <c r="E78" s="400" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15" customHeight="1">
       <c r="C79" s="398" t="s">
+        <v>974</v>
+      </c>
+      <c r="D79" s="399" t="s">
+        <v>960</v>
+      </c>
+      <c r="E79" s="400" t="s">
         <v>975</v>
-      </c>
-      <c r="D79" s="399" t="s">
-        <v>961</v>
-      </c>
-      <c r="E79" s="400" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15" customHeight="1">
       <c r="C80" s="401"/>
       <c r="D80" s="402" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="E80" s="403" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="81" spans="3:5" ht="15" customHeight="1">
       <c r="C81" s="401"/>
       <c r="D81" s="402" t="s">
+        <v>970</v>
+      </c>
+      <c r="E81" s="403" t="s">
         <v>971</v>
-      </c>
-      <c r="E81" s="403" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="82" spans="3:5" ht="15" customHeight="1">
       <c r="C82" s="404"/>
       <c r="D82" s="402" t="s">
+        <v>972</v>
+      </c>
+      <c r="E82" s="400" t="s">
         <v>973</v>
-      </c>
-      <c r="E82" s="400" t="s">
-        <v>974</v>
       </c>
     </row>
   </sheetData>

--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57058F2C-0A97-F54A-8F45-1538D65CB40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A152BBD0-C44B-A546-9762-88E7A2F2FB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="1075">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="1076">
   <si>
     <t>プロジェクト概要</t>
   </si>
@@ -5861,6 +5861,10 @@
   </si>
   <si>
     <t>reports/index.blade.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>report(CalculateWorkMinutesService)</t>
     <phoneticPr fontId="80"/>
   </si>
 </sst>
@@ -7597,7 +7601,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18"/>
   </cellStyleXfs>
-  <cellXfs count="490">
+  <cellXfs count="491">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8805,22 +8809,11 @@
     <xf numFmtId="0" fontId="11" fillId="19" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8829,17 +8822,31 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -10842,11 +10849,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="481" t="s">
+      <c r="C4" s="476" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="482"/>
-      <c r="E4" s="482"/>
+      <c r="D4" s="477"/>
+      <c r="E4" s="477"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10855,13 +10862,13 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
-      <c r="C5" s="485" t="s">
+      <c r="C5" s="482" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="483" t="s">
+      <c r="D5" s="478" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="484"/>
+      <c r="E5" s="479"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10870,11 +10877,11 @@
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="478"/>
-      <c r="D6" s="473" t="s">
+      <c r="C6" s="475"/>
+      <c r="D6" s="480" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="474"/>
+      <c r="E6" s="481"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10883,11 +10890,11 @@
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="478"/>
-      <c r="D7" s="473" t="s">
+      <c r="C7" s="475"/>
+      <c r="D7" s="480" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="474"/>
+      <c r="E7" s="481"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10896,11 +10903,11 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="478"/>
-      <c r="D8" s="473" t="s">
+      <c r="C8" s="475"/>
+      <c r="D8" s="480" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="474"/>
+      <c r="E8" s="481"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10909,11 +10916,11 @@
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="478"/>
-      <c r="D9" s="473" t="s">
+      <c r="C9" s="475"/>
+      <c r="D9" s="480" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="474"/>
+      <c r="E9" s="481"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10922,11 +10929,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="479"/>
-      <c r="D10" s="473" t="s">
+      <c r="C10" s="474"/>
+      <c r="D10" s="480" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="474"/>
+      <c r="E10" s="481"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10935,13 +10942,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="480" t="s">
+      <c r="C11" s="473" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="473" t="s">
+      <c r="D11" s="480" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="474"/>
+      <c r="E11" s="481"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10950,11 +10957,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="479"/>
-      <c r="D12" s="473" t="s">
+      <c r="C12" s="474"/>
+      <c r="D12" s="480" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="474"/>
+      <c r="E12" s="481"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10963,13 +10970,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="480" t="s">
+      <c r="C13" s="473" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="473" t="s">
+      <c r="D13" s="480" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="474"/>
+      <c r="E13" s="481"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10978,11 +10985,11 @@
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="478"/>
-      <c r="D14" s="473" t="s">
+      <c r="C14" s="475"/>
+      <c r="D14" s="480" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="474"/>
+      <c r="E14" s="481"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10991,11 +10998,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="479"/>
-      <c r="D15" s="473" t="s">
+      <c r="C15" s="474"/>
+      <c r="D15" s="480" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="474"/>
+      <c r="E15" s="481"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -11004,13 +11011,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="480" t="s">
+      <c r="C16" s="473" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="475" t="s">
+      <c r="D16" s="485" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="476"/>
+      <c r="E16" s="486"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -11019,8 +11026,8 @@
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="478"/>
-      <c r="D17" s="477" t="s">
+      <c r="C17" s="475"/>
+      <c r="D17" s="484" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="107" t="s">
@@ -11034,8 +11041,8 @@
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="478"/>
-      <c r="D18" s="478"/>
+      <c r="C18" s="475"/>
+      <c r="D18" s="475"/>
       <c r="E18" s="107" t="s">
         <v>134</v>
       </c>
@@ -11047,8 +11054,8 @@
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="478"/>
-      <c r="D19" s="478"/>
+      <c r="C19" s="475"/>
+      <c r="D19" s="475"/>
       <c r="E19" s="107" t="s">
         <v>137</v>
       </c>
@@ -11060,8 +11067,8 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="478"/>
-      <c r="D20" s="478"/>
+      <c r="C20" s="475"/>
+      <c r="D20" s="475"/>
       <c r="E20" s="107" t="s">
         <v>140</v>
       </c>
@@ -11073,8 +11080,8 @@
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="478"/>
-      <c r="D21" s="479"/>
+      <c r="C21" s="475"/>
+      <c r="D21" s="474"/>
       <c r="E21" s="107" t="s">
         <v>145</v>
       </c>
@@ -11086,8 +11093,8 @@
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="478"/>
-      <c r="D22" s="486" t="s">
+      <c r="C22" s="475"/>
+      <c r="D22" s="483" t="s">
         <v>165</v>
       </c>
       <c r="E22" s="127" t="s">
@@ -11101,8 +11108,8 @@
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="478"/>
-      <c r="D23" s="478"/>
+      <c r="C23" s="475"/>
+      <c r="D23" s="475"/>
       <c r="E23" s="127" t="s">
         <v>177</v>
       </c>
@@ -11114,8 +11121,8 @@
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="478"/>
-      <c r="D24" s="478"/>
+      <c r="C24" s="475"/>
+      <c r="D24" s="475"/>
       <c r="E24" s="127" t="s">
         <v>179</v>
       </c>
@@ -11127,8 +11134,8 @@
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="478"/>
-      <c r="D25" s="478"/>
+      <c r="C25" s="475"/>
+      <c r="D25" s="475"/>
       <c r="E25" s="127" t="s">
         <v>185</v>
       </c>
@@ -11140,8 +11147,8 @@
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="478"/>
-      <c r="D26" s="479"/>
+      <c r="C26" s="475"/>
+      <c r="D26" s="474"/>
       <c r="E26" s="127" t="s">
         <v>190</v>
       </c>
@@ -11153,7 +11160,7 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="478"/>
+      <c r="C27" s="475"/>
       <c r="D27" s="127" t="s">
         <v>193</v>
       </c>
@@ -11168,7 +11175,7 @@
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="478"/>
+      <c r="C28" s="475"/>
       <c r="D28" s="105" t="s">
         <v>221</v>
       </c>
@@ -11183,8 +11190,8 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="478"/>
-      <c r="D29" s="477" t="s">
+      <c r="C29" s="475"/>
+      <c r="D29" s="484" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="127" t="s">
@@ -11198,8 +11205,8 @@
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="478"/>
-      <c r="D30" s="478"/>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
       <c r="E30" s="127" t="s">
         <v>244</v>
       </c>
@@ -11211,8 +11218,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="479"/>
-      <c r="D31" s="479"/>
+      <c r="C31" s="474"/>
+      <c r="D31" s="474"/>
       <c r="E31" s="127" t="s">
         <v>249</v>
       </c>
@@ -11224,13 +11231,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="480" t="s">
+      <c r="C32" s="473" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="473" t="s">
+      <c r="D32" s="480" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="474"/>
+      <c r="E32" s="481"/>
       <c r="F32" s="159" t="s">
         <v>259</v>
       </c>
@@ -11238,11 +11245,11 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="478"/>
-      <c r="D33" s="473" t="s">
+      <c r="C33" s="475"/>
+      <c r="D33" s="480" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="474"/>
+      <c r="E33" s="481"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -11251,11 +11258,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="479"/>
-      <c r="D34" s="473" t="s">
+      <c r="C34" s="474"/>
+      <c r="D34" s="480" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="474"/>
+      <c r="E34" s="481"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -11272,6 +11279,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:D21"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="C16:C31"/>
@@ -11288,14 +11303,6 @@
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:D21"/>
   </mergeCells>
   <phoneticPr fontId="80"/>
   <hyperlinks>
@@ -14633,7 +14640,7 @@
     <row r="72" spans="1:8" ht="39">
       <c r="A72" s="279"/>
       <c r="B72" s="279"/>
-      <c r="C72" s="478"/>
+      <c r="C72" s="475"/>
       <c r="D72" s="283"/>
       <c r="E72" s="281" t="s">
         <v>742</v>
@@ -14649,7 +14656,7 @@
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="279"/>
       <c r="B73" s="279"/>
-      <c r="C73" s="479"/>
+      <c r="C73" s="474"/>
       <c r="D73" s="284"/>
       <c r="E73" s="281" t="s">
         <v>745</v>
@@ -18126,7 +18133,9 @@
       <c r="F19" s="356" t="s">
         <v>902</v>
       </c>
-      <c r="G19" s="357"/>
+      <c r="G19" s="490" t="s">
+        <v>1075</v>
+      </c>
       <c r="H19" s="358" t="s">
         <v>903</v>
       </c>

--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A152BBD0-C44B-A546-9762-88E7A2F2FB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA1F8365-1379-934C-9D4B-86716D3E1E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ターム内容" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1475" uniqueCount="1077">
   <si>
     <t>プロジェクト概要</t>
   </si>
@@ -4694,18 +4694,10 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>nullable / date_format:Y:m:d</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>month</t>
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>nullable / date_format:Y:m</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
     <t>page</t>
     <phoneticPr fontId="80"/>
   </si>
@@ -4719,54 +4711,6 @@
   </si>
   <si>
     <t>Api\V1\StoreAttendanceRecordRequest</t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>必須</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / date_format:Y:m:d / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">unique:attendance_records,date,user_id </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>（複合制約）</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="67" eb="68">
-      <t>_x0000__x0000__x0002__x0003_C_x0001__x0005_C_x0001__x0007_C_x0001_</t>
-    </rPh>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -4824,63 +4768,6 @@
   </si>
   <si>
     <t xml:space="preserve">Api\V1\UpdateAttendanceRecordRequest </t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>必須</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / date_format:Y:m:d / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>unique:attendance_records(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>自身を除外</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="50" eb="51">
-      <t>_x0000__x0000__x0002__x0003_2_x0001__x0005_2_x0001__x0007_2_x0001_</t>
-    </rPh>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -5531,69 +5418,8 @@
     <phoneticPr fontId="80"/>
   </si>
   <si>
-    <t>未ログイン時のリダイレクト先はapp/Http/Middleware/Authenticate.php</t>
-  </si>
-  <si>
     <t xml:space="preserve">app/Providers/FortifyServiceProvider
 </t>
-    <phoneticPr fontId="80"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>未ログイン時のリダイレクト先は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>app/Http/Middleware/Authenticate.php</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>管理者画面へのアクセス制限</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>app/Http/Middleware/AdminMiddleware.php</t>
-    </r>
-    <rPh sb="0" eb="1">
-      <t xml:space="preserve">ミ </t>
-    </rPh>
-    <rPh sb="52" eb="57">
-      <t>カンリ</t>
-    </rPh>
     <phoneticPr fontId="80"/>
   </si>
   <si>
@@ -5865,6 +5691,222 @@
   </si>
   <si>
     <t>report(CalculateWorkMinutesService)</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>未ログイン時のリダイレクト先はapp/Http/Middleware/Authenticate.php
+ログイン後のリダイレクト先はLoginResponse.php
+ログアウト後のリダイレクト先はLogoutResponse.php</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>未ログイン時のリダイレクト先は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>app/Http/Middleware/Authenticate.php</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>管理者画面へのアクセス制限は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>app/Http/Middleware/AdminMiddleware.php</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ログイン後のリダイレクト先は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">LoginResponse.php
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>ログアウト後のリダイレクト先は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>LogoutResponse.php</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t xml:space="preserve">ミ </t>
+    </rPh>
+    <rPh sb="52" eb="57">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>nullable / date_format:Y-m-d</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>nullable / date_format:Y-m</t>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>必須 / date_format:Y-m-d / unique(attendance_recordsのdate,user_id （複合制約）)</t>
+    <rPh sb="0" eb="2">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>_x0000__x0000__x0002__x0003_C_x0001__x0005_C_x0001__x0007_C_x0001_</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>sometimes / 必須</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / date_format:Y-m-d / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>unique:attendance_records(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>自身を除外</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="44" eb="45">
+      <t>_x0000__x0000__x0002__x0003_2_x0001__x0005_2_x0001__x0007_2_x0001_</t>
+    </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">sometimes / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="MS Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>必須</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / date_format:H:i:s / before:clock_out</t>
+    </r>
     <phoneticPr fontId="80"/>
   </si>
 </sst>
@@ -7601,7 +7643,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18"/>
   </cellStyleXfs>
-  <cellXfs count="491">
+  <cellXfs count="495">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8809,11 +8851,31 @@
     <xf numFmtId="0" fontId="11" fillId="19" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="19" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="85" fillId="19" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="87" fillId="19" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="86" fillId="19" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8822,31 +8884,17 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="72" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -9440,7 +9488,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="413" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="E6" s="414"/>
       <c r="F6" s="414"/>
@@ -9459,7 +9507,7 @@
         <v>701</v>
       </c>
       <c r="F7" s="418" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="G7" s="418" t="s">
         <v>710</v>
@@ -9478,10 +9526,10 @@
       <c r="C8" s="420"/>
       <c r="D8" s="304"/>
       <c r="E8" s="391" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="F8" s="391" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="G8" s="391"/>
       <c r="H8" s="391"/>
@@ -9497,10 +9545,10 @@
       <c r="B9" s="366"/>
       <c r="C9" s="417"/>
       <c r="E9" s="391" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="F9" s="391" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="G9" s="391"/>
       <c r="H9" s="418" t="s">
@@ -9520,7 +9568,7 @@
       <c r="B10" s="366"/>
       <c r="C10" s="417"/>
       <c r="E10" s="391" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="F10" s="391" t="s">
         <v>731</v>
@@ -9537,10 +9585,10 @@
       <c r="B11" s="366"/>
       <c r="C11" s="417"/>
       <c r="E11" s="391" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="F11" s="391" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="G11" s="391"/>
       <c r="H11" s="391"/>
@@ -9556,10 +9604,10 @@
       <c r="B12" s="366"/>
       <c r="C12" s="417"/>
       <c r="E12" s="391" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="F12" s="391" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="G12" s="391"/>
       <c r="H12" s="391"/>
@@ -9573,13 +9621,13 @@
       <c r="B13" s="366"/>
       <c r="C13" s="417"/>
       <c r="D13" s="436" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="E13" s="447" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="F13" s="447" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G13" s="391"/>
       <c r="H13" s="391"/>
@@ -9595,13 +9643,13 @@
       <c r="B14" s="366"/>
       <c r="C14" s="417"/>
       <c r="D14" s="436" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="E14" s="391" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="F14" s="391" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="G14" s="391"/>
       <c r="H14" s="391"/>
@@ -9651,7 +9699,7 @@
         <v>2</v>
       </c>
       <c r="D17" s="422" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="E17" s="414"/>
       <c r="F17" s="414"/>
@@ -9667,10 +9715,10 @@
       <c r="B18" s="394"/>
       <c r="C18" s="423"/>
       <c r="E18" s="391" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="F18" s="362" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="G18" s="418" t="s">
         <v>903</v>
@@ -9688,13 +9736,13 @@
       <c r="B19" s="394"/>
       <c r="C19" s="423"/>
       <c r="D19" s="312" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="E19" s="391" t="s">
         <v>958</v>
       </c>
       <c r="F19" s="362" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="G19" s="418"/>
       <c r="H19" s="391" t="s">
@@ -9704,7 +9752,7 @@
         <v>903</v>
       </c>
       <c r="J19" s="419" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="K19" s="305"/>
       <c r="L19" s="305"/>
@@ -9735,10 +9783,10 @@
       <c r="C21" s="423"/>
       <c r="D21" s="304"/>
       <c r="E21" s="391" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="F21" s="362" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G21" s="391"/>
       <c r="H21" s="391"/>
@@ -9754,10 +9802,10 @@
       <c r="B22" s="394"/>
       <c r="C22" s="423"/>
       <c r="E22" s="391" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="F22" s="362" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G22" s="391"/>
       <c r="H22" s="391"/>
@@ -9771,10 +9819,10 @@
       <c r="B23" s="394"/>
       <c r="C23" s="423"/>
       <c r="E23" s="447" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="F23" s="447" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="G23" s="391"/>
       <c r="H23" s="391"/>
@@ -9825,12 +9873,12 @@
       <c r="C26" s="423"/>
       <c r="D26" s="429"/>
       <c r="E26" s="430" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="F26" s="431"/>
       <c r="G26" s="432"/>
       <c r="H26" s="431" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="I26" s="431"/>
       <c r="J26" s="433"/>
@@ -9844,7 +9892,7 @@
         <v>3</v>
       </c>
       <c r="D27" s="422" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="E27" s="414"/>
       <c r="F27" s="414"/>
@@ -9863,7 +9911,7 @@
         <v>701</v>
       </c>
       <c r="F28" s="391" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="G28" s="418" t="s">
         <v>710</v>
@@ -9881,13 +9929,13 @@
       <c r="B29" s="394"/>
       <c r="C29" s="423"/>
       <c r="D29" s="312" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="E29" s="451" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="F29" s="391" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="G29" s="418"/>
       <c r="H29" s="391"/>
@@ -9895,7 +9943,7 @@
         <v>710</v>
       </c>
       <c r="J29" s="419" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="K29" s="305"/>
       <c r="L29" s="305"/>
@@ -9906,10 +9954,10 @@
       <c r="C30" s="423"/>
       <c r="D30" s="304"/>
       <c r="E30" s="391" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="F30" s="391" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G30" s="391"/>
       <c r="H30" s="391"/>
@@ -9923,10 +9971,10 @@
       <c r="B31" s="394"/>
       <c r="C31" s="423"/>
       <c r="E31" s="391" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="F31" s="391" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G31" s="391"/>
       <c r="H31" s="391"/>
@@ -9975,13 +10023,13 @@
       <c r="C34" s="424">
         <v>4</v>
       </c>
-      <c r="D34" s="488" t="s">
-        <v>994</v>
-      </c>
-      <c r="E34" s="489"/>
-      <c r="F34" s="489"/>
-      <c r="G34" s="489"/>
-      <c r="H34" s="489"/>
+      <c r="D34" s="493" t="s">
+        <v>990</v>
+      </c>
+      <c r="E34" s="494"/>
+      <c r="F34" s="494"/>
+      <c r="G34" s="494"/>
+      <c r="H34" s="494"/>
       <c r="I34" s="414"/>
       <c r="J34" s="415"/>
       <c r="K34" s="305"/>
@@ -9992,10 +10040,10 @@
       <c r="B35" s="394"/>
       <c r="C35" s="423"/>
       <c r="E35" s="391" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="F35" s="362" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="G35" s="418" t="s">
         <v>903</v>
@@ -10013,13 +10061,13 @@
       <c r="B36" s="394"/>
       <c r="C36" s="423"/>
       <c r="D36" s="306" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="E36" s="451" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="F36" s="362" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="G36" s="418"/>
       <c r="H36" s="391"/>
@@ -10027,7 +10075,7 @@
         <v>710</v>
       </c>
       <c r="J36" s="419" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="K36" s="305"/>
       <c r="L36" s="305"/>
@@ -10040,7 +10088,7 @@
         <v>947</v>
       </c>
       <c r="F37" s="391" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G37" s="391"/>
       <c r="H37" s="391"/>
@@ -10059,7 +10107,7 @@
         <v>948</v>
       </c>
       <c r="F38" s="435" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G38" s="391"/>
       <c r="H38" s="391"/>
@@ -10073,10 +10121,10 @@
       <c r="B39" s="394"/>
       <c r="C39" s="423"/>
       <c r="E39" s="391" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="F39" s="391" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="G39" s="391"/>
       <c r="H39" s="391"/>
@@ -10092,13 +10140,13 @@
       <c r="B40" s="394"/>
       <c r="C40" s="423"/>
       <c r="D40" s="436" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="E40" s="391" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="F40" s="391" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G40" s="391"/>
       <c r="H40" s="391"/>
@@ -10115,7 +10163,7 @@
       <c r="C41" s="423"/>
       <c r="D41" s="436"/>
       <c r="E41" s="447" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="F41" s="447" t="s">
         <v>960</v>
@@ -10172,7 +10220,7 @@
         <v>5</v>
       </c>
       <c r="D44" s="450" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="E44" s="414"/>
       <c r="F44" s="414"/>
@@ -10191,7 +10239,7 @@
         <v>701</v>
       </c>
       <c r="F45" s="391" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="G45" s="391" t="s">
         <v>710</v>
@@ -10209,13 +10257,13 @@
       <c r="B46" s="394"/>
       <c r="C46" s="423"/>
       <c r="D46" s="312" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="E46" s="391" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="F46" s="391" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="G46" s="391"/>
       <c r="H46" s="391"/>
@@ -10223,7 +10271,7 @@
         <v>903</v>
       </c>
       <c r="J46" s="419" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="K46" s="305"/>
       <c r="L46" s="305"/>
@@ -10233,10 +10281,10 @@
       <c r="B47" s="394"/>
       <c r="C47" s="423"/>
       <c r="E47" s="391" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="F47" s="391" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G47" s="391"/>
       <c r="H47" s="391"/>
@@ -10250,10 +10298,10 @@
       <c r="B48" s="394"/>
       <c r="C48" s="423"/>
       <c r="E48" s="391" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="F48" s="391" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="G48" s="391"/>
       <c r="H48" s="391"/>
@@ -10849,11 +10897,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="476" t="s">
+      <c r="C4" s="486" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="477"/>
-      <c r="E4" s="477"/>
+      <c r="D4" s="487"/>
+      <c r="E4" s="487"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10862,13 +10910,13 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
-      <c r="C5" s="482" t="s">
+      <c r="C5" s="490" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="478" t="s">
+      <c r="D5" s="488" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="479"/>
+      <c r="E5" s="489"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10877,11 +10925,11 @@
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="475"/>
-      <c r="D6" s="480" t="s">
+      <c r="C6" s="483"/>
+      <c r="D6" s="478" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="481"/>
+      <c r="E6" s="479"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10890,11 +10938,11 @@
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="475"/>
-      <c r="D7" s="480" t="s">
+      <c r="C7" s="483"/>
+      <c r="D7" s="478" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="481"/>
+      <c r="E7" s="479"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10903,11 +10951,11 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="475"/>
-      <c r="D8" s="480" t="s">
+      <c r="C8" s="483"/>
+      <c r="D8" s="478" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="481"/>
+      <c r="E8" s="479"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10916,11 +10964,11 @@
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="475"/>
-      <c r="D9" s="480" t="s">
+      <c r="C9" s="483"/>
+      <c r="D9" s="478" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="481"/>
+      <c r="E9" s="479"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10929,11 +10977,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="474"/>
-      <c r="D10" s="480" t="s">
+      <c r="C10" s="484"/>
+      <c r="D10" s="478" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="481"/>
+      <c r="E10" s="479"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10942,13 +10990,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="473" t="s">
+      <c r="C11" s="485" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="480" t="s">
+      <c r="D11" s="478" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="481"/>
+      <c r="E11" s="479"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10957,11 +11005,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="474"/>
-      <c r="D12" s="480" t="s">
+      <c r="C12" s="484"/>
+      <c r="D12" s="478" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="481"/>
+      <c r="E12" s="479"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10970,13 +11018,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="473" t="s">
+      <c r="C13" s="485" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="480" t="s">
+      <c r="D13" s="478" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="481"/>
+      <c r="E13" s="479"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10985,11 +11033,11 @@
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="475"/>
-      <c r="D14" s="480" t="s">
+      <c r="C14" s="483"/>
+      <c r="D14" s="478" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="481"/>
+      <c r="E14" s="479"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10998,11 +11046,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="474"/>
-      <c r="D15" s="480" t="s">
+      <c r="C15" s="484"/>
+      <c r="D15" s="478" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="481"/>
+      <c r="E15" s="479"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -11011,13 +11059,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="473" t="s">
+      <c r="C16" s="485" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="485" t="s">
+      <c r="D16" s="480" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="486"/>
+      <c r="E16" s="481"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -11026,8 +11074,8 @@
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="475"/>
-      <c r="D17" s="484" t="s">
+      <c r="C17" s="483"/>
+      <c r="D17" s="482" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="107" t="s">
@@ -11041,8 +11089,8 @@
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="475"/>
-      <c r="D18" s="475"/>
+      <c r="C18" s="483"/>
+      <c r="D18" s="483"/>
       <c r="E18" s="107" t="s">
         <v>134</v>
       </c>
@@ -11054,8 +11102,8 @@
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="475"/>
-      <c r="D19" s="475"/>
+      <c r="C19" s="483"/>
+      <c r="D19" s="483"/>
       <c r="E19" s="107" t="s">
         <v>137</v>
       </c>
@@ -11067,8 +11115,8 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="475"/>
-      <c r="D20" s="475"/>
+      <c r="C20" s="483"/>
+      <c r="D20" s="483"/>
       <c r="E20" s="107" t="s">
         <v>140</v>
       </c>
@@ -11080,8 +11128,8 @@
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="475"/>
-      <c r="D21" s="474"/>
+      <c r="C21" s="483"/>
+      <c r="D21" s="484"/>
       <c r="E21" s="107" t="s">
         <v>145</v>
       </c>
@@ -11093,8 +11141,8 @@
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="475"/>
-      <c r="D22" s="483" t="s">
+      <c r="C22" s="483"/>
+      <c r="D22" s="491" t="s">
         <v>165</v>
       </c>
       <c r="E22" s="127" t="s">
@@ -11108,8 +11156,8 @@
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="475"/>
-      <c r="D23" s="475"/>
+      <c r="C23" s="483"/>
+      <c r="D23" s="483"/>
       <c r="E23" s="127" t="s">
         <v>177</v>
       </c>
@@ -11121,8 +11169,8 @@
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="475"/>
-      <c r="D24" s="475"/>
+      <c r="C24" s="483"/>
+      <c r="D24" s="483"/>
       <c r="E24" s="127" t="s">
         <v>179</v>
       </c>
@@ -11134,8 +11182,8 @@
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="475"/>
-      <c r="D25" s="475"/>
+      <c r="C25" s="483"/>
+      <c r="D25" s="483"/>
       <c r="E25" s="127" t="s">
         <v>185</v>
       </c>
@@ -11147,8 +11195,8 @@
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="475"/>
-      <c r="D26" s="474"/>
+      <c r="C26" s="483"/>
+      <c r="D26" s="484"/>
       <c r="E26" s="127" t="s">
         <v>190</v>
       </c>
@@ -11160,7 +11208,7 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="475"/>
+      <c r="C27" s="483"/>
       <c r="D27" s="127" t="s">
         <v>193</v>
       </c>
@@ -11175,7 +11223,7 @@
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="475"/>
+      <c r="C28" s="483"/>
       <c r="D28" s="105" t="s">
         <v>221</v>
       </c>
@@ -11190,8 +11238,8 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="475"/>
-      <c r="D29" s="484" t="s">
+      <c r="C29" s="483"/>
+      <c r="D29" s="482" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="127" t="s">
@@ -11205,8 +11253,8 @@
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="475"/>
-      <c r="D30" s="475"/>
+      <c r="C30" s="483"/>
+      <c r="D30" s="483"/>
       <c r="E30" s="127" t="s">
         <v>244</v>
       </c>
@@ -11218,8 +11266,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="474"/>
-      <c r="D31" s="474"/>
+      <c r="C31" s="484"/>
+      <c r="D31" s="484"/>
       <c r="E31" s="127" t="s">
         <v>249</v>
       </c>
@@ -11231,13 +11279,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="473" t="s">
+      <c r="C32" s="485" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="480" t="s">
+      <c r="D32" s="478" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="481"/>
+      <c r="E32" s="479"/>
       <c r="F32" s="159" t="s">
         <v>259</v>
       </c>
@@ -11245,11 +11293,11 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="475"/>
-      <c r="D33" s="480" t="s">
+      <c r="C33" s="483"/>
+      <c r="D33" s="478" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="481"/>
+      <c r="E33" s="479"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -11258,11 +11306,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="474"/>
-      <c r="D34" s="480" t="s">
+      <c r="C34" s="484"/>
+      <c r="D34" s="478" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="481"/>
+      <c r="E34" s="479"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -11279,14 +11327,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:D21"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="C16:C31"/>
@@ -11303,6 +11343,14 @@
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:D21"/>
   </mergeCells>
   <phoneticPr fontId="80"/>
   <hyperlinks>
@@ -12725,13 +12773,13 @@
         <v>58</v>
       </c>
       <c r="F10" s="457" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="G10" s="65" t="s">
         <v>64</v>
       </c>
       <c r="H10" s="458" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="I10" s="10"/>
     </row>
@@ -14620,7 +14668,7 @@
     <row r="71" spans="1:8" ht="26">
       <c r="A71" s="279"/>
       <c r="B71" s="279"/>
-      <c r="C71" s="487">
+      <c r="C71" s="492">
         <v>16</v>
       </c>
       <c r="D71" s="280" t="s">
@@ -14640,7 +14688,7 @@
     <row r="72" spans="1:8" ht="39">
       <c r="A72" s="279"/>
       <c r="B72" s="279"/>
-      <c r="C72" s="475"/>
+      <c r="C72" s="483"/>
       <c r="D72" s="283"/>
       <c r="E72" s="281" t="s">
         <v>742</v>
@@ -14656,7 +14704,7 @@
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="279"/>
       <c r="B73" s="279"/>
-      <c r="C73" s="474"/>
+      <c r="C73" s="484"/>
       <c r="D73" s="284"/>
       <c r="E73" s="281" t="s">
         <v>745</v>
@@ -17809,7 +17857,7 @@
         <v>41</v>
       </c>
       <c r="D7" s="324" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="E7" s="325" t="s">
         <v>899</v>
@@ -17818,7 +17866,7 @@
         <v>896</v>
       </c>
       <c r="G7" s="327" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="H7" s="328" t="s">
         <v>897</v>
@@ -17827,7 +17875,7 @@
         <v>900</v>
       </c>
       <c r="J7" s="465" t="s">
-        <v>1060</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="154">
@@ -17837,16 +17885,16 @@
         <v>901</v>
       </c>
       <c r="D8" s="324" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="E8" s="325" t="s">
         <v>895</v>
       </c>
       <c r="F8" s="331" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="G8" s="332" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="H8" s="333" t="s">
         <v>903</v>
@@ -17898,7 +17946,7 @@
         <v>907</v>
       </c>
       <c r="G10" s="335" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="H10" s="333" t="s">
         <v>903</v>
@@ -17947,10 +17995,10 @@
         <v>895</v>
       </c>
       <c r="F12" s="331" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="G12" s="463" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="H12" s="333" t="s">
         <v>897</v>
@@ -17959,7 +18007,7 @@
         <v>911</v>
       </c>
       <c r="J12" s="464" t="s">
-        <v>1062</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="56">
@@ -18004,7 +18052,7 @@
         <v>912</v>
       </c>
       <c r="G14" s="466" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="H14" s="333" t="s">
         <v>903</v>
@@ -18021,7 +18069,7 @@
         <v>84</v>
       </c>
       <c r="D15" s="324" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="E15" s="343" t="s">
         <v>899</v>
@@ -18056,7 +18104,7 @@
         <v>916</v>
       </c>
       <c r="G16" s="472" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="H16" s="333" t="s">
         <v>903</v>
@@ -18108,7 +18156,7 @@
         <v>920</v>
       </c>
       <c r="G18" s="350" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="H18" s="351" t="s">
         <v>903</v>
@@ -18133,8 +18181,8 @@
       <c r="F19" s="356" t="s">
         <v>902</v>
       </c>
-      <c r="G19" s="490" t="s">
-        <v>1075</v>
+      <c r="G19" s="473" t="s">
+        <v>1069</v>
       </c>
       <c r="H19" s="358" t="s">
         <v>903</v>
@@ -18148,10 +18196,10 @@
       <c r="A20" s="312"/>
       <c r="B20" s="304"/>
       <c r="C20" s="353" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="D20" s="354" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="E20" s="355" t="s">
         <v>899</v>
@@ -18166,7 +18214,7 @@
         <v>903</v>
       </c>
       <c r="I20" s="359" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="J20" s="453"/>
     </row>
@@ -18248,7 +18296,7 @@
       <c r="A26" s="312"/>
       <c r="B26" s="304"/>
       <c r="C26" s="365" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="D26" s="364" t="s">
         <v>930</v>
@@ -18280,7 +18328,7 @@
       <c r="A28" s="312"/>
       <c r="B28" s="304"/>
       <c r="C28" s="449" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="D28" s="364" t="s">
         <v>933</v>
@@ -18338,10 +18386,10 @@
       <c r="A32" s="312"/>
       <c r="B32" s="304"/>
       <c r="C32" s="441" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="D32" s="369" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="E32" s="312"/>
       <c r="F32" s="312"/>
@@ -18357,7 +18405,7 @@
         <v>934</v>
       </c>
       <c r="D33" s="369" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="E33" s="312"/>
       <c r="F33" s="312"/>
@@ -18373,7 +18421,7 @@
         <v>901</v>
       </c>
       <c r="D34" s="369" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="E34" s="312"/>
       <c r="F34" s="312"/>
@@ -18386,13 +18434,13 @@
       <c r="A35" s="312"/>
       <c r="B35" s="304"/>
       <c r="C35" s="370" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="D35" s="369" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="E35" s="467" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="F35" s="312"/>
       <c r="G35" s="312"/>
@@ -18404,10 +18452,10 @@
       <c r="A36" s="312"/>
       <c r="B36" s="304"/>
       <c r="C36" s="370" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="D36" s="371" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="E36" s="312"/>
       <c r="F36" s="312"/>
@@ -18420,10 +18468,10 @@
       <c r="A37" s="312"/>
       <c r="B37" s="304"/>
       <c r="C37" s="370" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="D37" s="369" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="E37" s="312"/>
       <c r="F37" s="312"/>
@@ -18436,10 +18484,10 @@
       <c r="A38" s="312"/>
       <c r="B38" s="304"/>
       <c r="C38" s="370" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="D38" s="369" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="E38" s="312"/>
       <c r="F38" s="312"/>
@@ -18452,13 +18500,13 @@
       <c r="A39" s="312"/>
       <c r="B39" s="304"/>
       <c r="C39" s="442" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="D39" s="369" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="E39" s="467" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="F39" s="312"/>
       <c r="G39" s="312"/>
@@ -18470,13 +18518,13 @@
       <c r="A40" s="312"/>
       <c r="B40" s="304"/>
       <c r="C40" s="370" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="D40" s="371" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="E40" s="467" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="F40" s="312"/>
       <c r="G40" s="312"/>
@@ -18488,10 +18536,10 @@
       <c r="A41" s="312"/>
       <c r="B41" s="304"/>
       <c r="C41" s="370" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="D41" s="369" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="E41" s="312"/>
       <c r="F41" s="312"/>
@@ -18504,13 +18552,13 @@
       <c r="A42" s="312"/>
       <c r="B42" s="304"/>
       <c r="C42" s="442" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="D42" s="372" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="E42" s="467" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="F42" s="312"/>
       <c r="G42" s="312"/>
@@ -18522,10 +18570,10 @@
       <c r="A43" s="312"/>
       <c r="B43" s="304"/>
       <c r="C43" s="370" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="D43" s="369" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="E43" s="312"/>
       <c r="F43" s="312"/>
@@ -18538,10 +18586,10 @@
       <c r="A44" s="312"/>
       <c r="B44" s="304"/>
       <c r="C44" s="370" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="D44" s="369" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="E44" s="312"/>
       <c r="F44" s="312"/>
@@ -18554,10 +18602,10 @@
       <c r="A45" s="312"/>
       <c r="B45" s="304"/>
       <c r="C45" s="456" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="D45" s="372" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="E45" s="312"/>
       <c r="F45" s="312"/>
@@ -18570,10 +18618,10 @@
       <c r="A46" s="312"/>
       <c r="B46" s="304"/>
       <c r="C46" s="456" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="D46" s="372" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E46" s="312"/>
       <c r="F46" s="312"/>
@@ -18586,10 +18634,10 @@
       <c r="A47" s="312"/>
       <c r="B47" s="304"/>
       <c r="C47" s="456" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="D47" s="372" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="E47" s="312"/>
       <c r="F47" s="312"/>
@@ -18605,7 +18653,7 @@
         <v>923</v>
       </c>
       <c r="D48" s="444" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="E48" s="312"/>
       <c r="F48" s="312"/>
@@ -18618,10 +18666,10 @@
       <c r="A49" s="312"/>
       <c r="B49" s="304"/>
       <c r="C49" s="445" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="D49" s="446" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="E49" s="312"/>
       <c r="F49" s="312"/>
@@ -18794,7 +18842,7 @@
         <v>947</v>
       </c>
       <c r="E60" s="461" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="F60" s="382"/>
       <c r="H60" s="312"/>
@@ -18809,7 +18857,7 @@
         <v>948</v>
       </c>
       <c r="E61" s="462" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F61" s="382"/>
       <c r="H61" s="312"/>
@@ -18824,7 +18872,7 @@
         <v>949</v>
       </c>
       <c r="E62" s="459" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="F62" s="382"/>
       <c r="H62" s="312"/>
@@ -18839,7 +18887,7 @@
         <v>950</v>
       </c>
       <c r="E63" s="460" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="F63" s="382"/>
       <c r="H63" s="312"/>
@@ -18865,13 +18913,13 @@
       <c r="A65" s="312"/>
       <c r="B65" s="304"/>
       <c r="C65" s="471" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="D65" s="388" t="s">
         <v>952</v>
       </c>
       <c r="E65" s="468" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="F65" s="382"/>
       <c r="H65" s="312"/>
@@ -18886,7 +18934,7 @@
         <v>954</v>
       </c>
       <c r="E66" s="469" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="F66" s="382"/>
       <c r="H66" s="312"/>
@@ -18901,7 +18949,7 @@
         <v>955</v>
       </c>
       <c r="E67" s="451" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="F67" s="382"/>
       <c r="H67" s="312"/>
@@ -18916,7 +18964,7 @@
         <v>956</v>
       </c>
       <c r="E68" s="470" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="F68" s="382"/>
       <c r="H68" s="312"/>
@@ -18962,8 +19010,8 @@
       <c r="D71" s="396" t="s">
         <v>960</v>
       </c>
-      <c r="E71" s="396" t="s">
-        <v>961</v>
+      <c r="E71" s="474" t="s">
+        <v>1072</v>
       </c>
       <c r="F71" s="394"/>
       <c r="H71" s="312"/>
@@ -18975,10 +19023,10 @@
       <c r="B72" s="304"/>
       <c r="C72" s="392"/>
       <c r="D72" s="396" t="s">
-        <v>962</v>
-      </c>
-      <c r="E72" s="396" t="s">
-        <v>963</v>
+        <v>961</v>
+      </c>
+      <c r="E72" s="474" t="s">
+        <v>1073</v>
       </c>
       <c r="F72" s="394"/>
       <c r="H72" s="312"/>
@@ -18990,7 +19038,7 @@
       <c r="B73" s="304"/>
       <c r="C73" s="392"/>
       <c r="D73" s="396" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="E73" s="396" t="s">
         <v>959</v>
@@ -19005,10 +19053,10 @@
       <c r="B74" s="304"/>
       <c r="C74" s="392"/>
       <c r="D74" s="397" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="E74" s="397" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="F74" s="394"/>
       <c r="H74" s="312"/>
@@ -19019,13 +19067,13 @@
       <c r="A75" s="305"/>
       <c r="B75" s="305"/>
       <c r="C75" s="398" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="D75" s="399" t="s">
         <v>960</v>
       </c>
-      <c r="E75" s="400" t="s">
-        <v>968</v>
+      <c r="E75" s="475" t="s">
+        <v>1074</v>
       </c>
       <c r="F75" s="394"/>
       <c r="G75" s="305"/>
@@ -19036,7 +19084,7 @@
     <row r="76" spans="1:10" ht="15" customHeight="1">
       <c r="C76" s="401"/>
       <c r="D76" s="402" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="E76" s="403" t="s">
         <v>953</v>
@@ -19045,57 +19093,57 @@
     <row r="77" spans="1:10" ht="15" customHeight="1">
       <c r="C77" s="401"/>
       <c r="D77" s="402" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="E77" s="403" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1">
       <c r="C78" s="404"/>
       <c r="D78" s="402" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="E78" s="400" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="15" customHeight="1">
       <c r="C79" s="398" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="D79" s="399" t="s">
         <v>960</v>
       </c>
-      <c r="E79" s="400" t="s">
-        <v>975</v>
+      <c r="E79" s="476" t="s">
+        <v>1075</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="15" customHeight="1">
       <c r="C80" s="401"/>
       <c r="D80" s="402" t="s">
-        <v>969</v>
-      </c>
-      <c r="E80" s="403" t="s">
-        <v>953</v>
+        <v>966</v>
+      </c>
+      <c r="E80" s="477" t="s">
+        <v>1076</v>
       </c>
     </row>
     <row r="81" spans="3:5" ht="15" customHeight="1">
       <c r="C81" s="401"/>
       <c r="D81" s="402" t="s">
-        <v>970</v>
+        <v>967</v>
       </c>
       <c r="E81" s="403" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
     </row>
     <row r="82" spans="3:5" ht="15" customHeight="1">
       <c r="C82" s="404"/>
       <c r="D82" s="402" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="E82" s="400" t="s">
-        <v>973</v>
+        <v>970</v>
       </c>
     </row>
   </sheetData>

--- a/docs/各種設計書.xlsx
+++ b/docs/各種設計書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE22397B-6459-134D-B7C1-F8075CED38A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B68CBE42-49B8-384B-88A3-66F91B3DBA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ターム内容" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="1077">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1473" uniqueCount="1078">
   <si>
     <t>プロジェクト概要</t>
   </si>
@@ -5930,6 +5930,10 @@
     <rPh sb="1" eb="3">
       <t>ツイカ</t>
     </rPh>
+    <phoneticPr fontId="80"/>
+  </si>
+  <si>
+    <t>AttendanceReportController</t>
     <phoneticPr fontId="80"/>
   </si>
 </sst>
@@ -7657,7 +7661,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="18"/>
   </cellStyleXfs>
-  <cellXfs count="500">
+  <cellXfs count="485">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -8809,11 +8813,77 @@
     </xf>
     <xf numFmtId="0" fontId="95" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="69" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="75" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="75" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="76" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="75" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="75" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="77" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="75" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -8822,99 +8892,14 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="18" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="69" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="74" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="57" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="76" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="77" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="87" fillId="0" borderId="75" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -9644,15 +9629,15 @@
       <c r="D13" s="415" t="s">
         <v>1018</v>
       </c>
-      <c r="E13" s="458" t="s">
+      <c r="E13" s="383" t="s">
         <v>1017</v>
       </c>
-      <c r="F13" s="458" t="s">
+      <c r="F13" s="383" t="s">
         <v>994</v>
       </c>
-      <c r="G13" s="458"/>
-      <c r="H13" s="458"/>
-      <c r="I13" s="459" t="s">
+      <c r="G13" s="383"/>
+      <c r="H13" s="383"/>
+      <c r="I13" s="398" t="s">
         <v>710</v>
       </c>
       <c r="J13" s="399"/>
@@ -9666,15 +9651,15 @@
       <c r="D14" s="415" t="s">
         <v>1016</v>
       </c>
-      <c r="E14" s="458" t="s">
+      <c r="E14" s="383" t="s">
         <v>1014</v>
       </c>
-      <c r="F14" s="458" t="s">
+      <c r="F14" s="383" t="s">
         <v>1015</v>
       </c>
-      <c r="G14" s="458"/>
-      <c r="H14" s="458"/>
-      <c r="I14" s="458"/>
+      <c r="G14" s="383"/>
+      <c r="H14" s="383"/>
+      <c r="I14" s="383"/>
       <c r="J14" s="399"/>
       <c r="K14" s="396"/>
       <c r="L14" s="303"/>
@@ -9839,10 +9824,10 @@
       <c r="A23" s="384"/>
       <c r="B23" s="384"/>
       <c r="C23" s="403"/>
-      <c r="E23" s="458" t="s">
+      <c r="E23" s="383" t="s">
         <v>968</v>
       </c>
-      <c r="F23" s="458" t="s">
+      <c r="F23" s="383" t="s">
         <v>991</v>
       </c>
       <c r="G23" s="383"/>
@@ -9952,7 +9937,7 @@
       <c r="D29" s="310" t="s">
         <v>982</v>
       </c>
-      <c r="E29" s="458" t="s">
+      <c r="E29" s="383" t="s">
         <v>1022</v>
       </c>
       <c r="F29" s="383" t="s">
@@ -10044,13 +10029,13 @@
       <c r="C34" s="404">
         <v>4</v>
       </c>
-      <c r="D34" s="456" t="s">
+      <c r="D34" s="468" t="s">
         <v>989</v>
       </c>
-      <c r="E34" s="457"/>
-      <c r="F34" s="457"/>
-      <c r="G34" s="457"/>
-      <c r="H34" s="457"/>
+      <c r="E34" s="469"/>
+      <c r="F34" s="469"/>
+      <c r="G34" s="469"/>
+      <c r="H34" s="469"/>
       <c r="I34" s="394"/>
       <c r="J34" s="395"/>
       <c r="K34" s="303"/>
@@ -10084,15 +10069,15 @@
       <c r="D36" s="304" t="s">
         <v>990</v>
       </c>
-      <c r="E36" s="458" t="s">
+      <c r="E36" s="383" t="s">
         <v>1022</v>
       </c>
-      <c r="F36" s="460" t="s">
+      <c r="F36" s="360" t="s">
         <v>972</v>
       </c>
-      <c r="G36" s="459"/>
-      <c r="H36" s="458"/>
-      <c r="I36" s="459" t="s">
+      <c r="G36" s="398"/>
+      <c r="H36" s="383"/>
+      <c r="I36" s="398" t="s">
         <v>710</v>
       </c>
       <c r="J36" s="399" t="s">
@@ -10105,15 +10090,15 @@
       <c r="A37" s="384"/>
       <c r="B37" s="384"/>
       <c r="C37" s="403"/>
-      <c r="E37" s="458" t="s">
+      <c r="E37" s="383" t="s">
         <v>946</v>
       </c>
-      <c r="F37" s="458" t="s">
+      <c r="F37" s="383" t="s">
         <v>985</v>
       </c>
-      <c r="G37" s="458"/>
-      <c r="H37" s="458"/>
-      <c r="I37" s="459" t="s">
+      <c r="G37" s="383"/>
+      <c r="H37" s="383"/>
+      <c r="I37" s="398" t="s">
         <v>710</v>
       </c>
       <c r="J37" s="399"/>
@@ -10124,15 +10109,15 @@
       <c r="A38" s="384"/>
       <c r="B38" s="384"/>
       <c r="C38" s="403"/>
-      <c r="E38" s="458" t="s">
+      <c r="E38" s="383" t="s">
         <v>947</v>
       </c>
-      <c r="F38" s="461" t="s">
+      <c r="F38" s="441" t="s">
         <v>985</v>
       </c>
-      <c r="G38" s="458"/>
-      <c r="H38" s="458"/>
-      <c r="I38" s="459"/>
+      <c r="G38" s="383"/>
+      <c r="H38" s="383"/>
+      <c r="I38" s="398"/>
       <c r="J38" s="399"/>
       <c r="K38" s="303"/>
       <c r="L38" s="303"/>
@@ -10141,15 +10126,15 @@
       <c r="A39" s="384"/>
       <c r="B39" s="384"/>
       <c r="C39" s="403"/>
-      <c r="E39" s="458" t="s">
+      <c r="E39" s="383" t="s">
         <v>968</v>
       </c>
-      <c r="F39" s="458" t="s">
+      <c r="F39" s="383" t="s">
         <v>991</v>
       </c>
-      <c r="G39" s="458"/>
-      <c r="H39" s="458"/>
-      <c r="I39" s="459" t="s">
+      <c r="G39" s="383"/>
+      <c r="H39" s="383"/>
+      <c r="I39" s="398" t="s">
         <v>710</v>
       </c>
       <c r="J39" s="399"/>
@@ -10163,15 +10148,15 @@
       <c r="D40" s="415" t="s">
         <v>992</v>
       </c>
-      <c r="E40" s="458" t="s">
+      <c r="E40" s="383" t="s">
         <v>993</v>
       </c>
-      <c r="F40" s="458" t="s">
+      <c r="F40" s="383" t="s">
         <v>994</v>
       </c>
-      <c r="G40" s="458"/>
-      <c r="H40" s="458"/>
-      <c r="I40" s="458" t="s">
+      <c r="G40" s="383"/>
+      <c r="H40" s="383"/>
+      <c r="I40" s="383" t="s">
         <v>902</v>
       </c>
       <c r="J40" s="399"/>
@@ -10183,15 +10168,15 @@
       <c r="B41" s="384"/>
       <c r="C41" s="403"/>
       <c r="D41" s="415"/>
-      <c r="E41" s="458" t="s">
+      <c r="E41" s="383" t="s">
         <v>1019</v>
       </c>
-      <c r="F41" s="458" t="s">
+      <c r="F41" s="383" t="s">
         <v>959</v>
       </c>
-      <c r="G41" s="458"/>
-      <c r="H41" s="458"/>
-      <c r="I41" s="458" t="s">
+      <c r="G41" s="383"/>
+      <c r="H41" s="383"/>
+      <c r="I41" s="383" t="s">
         <v>902</v>
       </c>
       <c r="J41" s="399"/>
@@ -10203,15 +10188,15 @@
       <c r="B42" s="384"/>
       <c r="C42" s="403"/>
       <c r="D42" s="405"/>
-      <c r="E42" s="458" t="s">
+      <c r="E42" s="383" t="s">
         <v>730</v>
       </c>
-      <c r="F42" s="458" t="s">
+      <c r="F42" s="383" t="s">
         <v>731</v>
       </c>
-      <c r="G42" s="458"/>
-      <c r="H42" s="458"/>
-      <c r="I42" s="458"/>
+      <c r="G42" s="383"/>
+      <c r="H42" s="383"/>
+      <c r="I42" s="383"/>
       <c r="J42" s="407"/>
       <c r="K42" s="303"/>
       <c r="L42" s="303"/>
@@ -10221,15 +10206,15 @@
       <c r="B43" s="384"/>
       <c r="C43" s="416"/>
       <c r="D43" s="409"/>
-      <c r="E43" s="458" t="s">
+      <c r="E43" s="383" t="s">
         <v>739</v>
       </c>
-      <c r="F43" s="458" t="s">
+      <c r="F43" s="383" t="s">
         <v>731</v>
       </c>
-      <c r="G43" s="458"/>
-      <c r="H43" s="458"/>
-      <c r="I43" s="458"/>
+      <c r="G43" s="383"/>
+      <c r="H43" s="383"/>
+      <c r="I43" s="383"/>
       <c r="J43" s="407"/>
       <c r="K43" s="303"/>
       <c r="L43" s="303"/>
@@ -10240,14 +10225,14 @@
       <c r="C44" s="404">
         <v>5</v>
       </c>
-      <c r="D44" s="463" t="s">
+      <c r="D44" s="443" t="s">
         <v>1020</v>
       </c>
-      <c r="E44" s="462"/>
-      <c r="F44" s="462"/>
-      <c r="G44" s="462"/>
-      <c r="H44" s="462"/>
-      <c r="I44" s="462"/>
+      <c r="E44" s="442"/>
+      <c r="F44" s="442"/>
+      <c r="G44" s="442"/>
+      <c r="H44" s="442"/>
+      <c r="I44" s="442"/>
       <c r="J44" s="395"/>
       <c r="K44" s="303"/>
       <c r="L44" s="303"/>
@@ -10256,7 +10241,6 @@
       <c r="A45" s="384"/>
       <c r="B45" s="384"/>
       <c r="C45" s="403"/>
-      <c r="D45" s="464"/>
       <c r="E45" s="383" t="s">
         <v>701</v>
       </c>
@@ -10438,11 +10422,11 @@
     <row r="4" spans="1:7" ht="15.75" customHeight="1">
       <c r="A4" s="16"/>
       <c r="B4" s="16"/>
-      <c r="C4" s="444" t="s">
+      <c r="C4" s="478" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="445"/>
-      <c r="E4" s="445"/>
+      <c r="D4" s="479"/>
+      <c r="E4" s="479"/>
       <c r="F4" s="19" t="s">
         <v>8</v>
       </c>
@@ -10451,13 +10435,13 @@
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
-      <c r="C5" s="450" t="s">
+      <c r="C5" s="482" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="446" t="s">
+      <c r="D5" s="480" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="447"/>
+      <c r="E5" s="481"/>
       <c r="F5" s="43" t="s">
         <v>20</v>
       </c>
@@ -10466,11 +10450,11 @@
     <row r="6" spans="1:7" ht="15.75" customHeight="1">
       <c r="A6" s="27"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="443"/>
-      <c r="D6" s="448" t="s">
+      <c r="C6" s="475"/>
+      <c r="D6" s="470" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="449"/>
+      <c r="E6" s="471"/>
       <c r="F6" s="54" t="s">
         <v>29</v>
       </c>
@@ -10479,11 +10463,11 @@
     <row r="7" spans="1:7" ht="15.75" customHeight="1">
       <c r="A7" s="27"/>
       <c r="B7" s="27"/>
-      <c r="C7" s="443"/>
-      <c r="D7" s="448" t="s">
+      <c r="C7" s="475"/>
+      <c r="D7" s="470" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="449"/>
+      <c r="E7" s="471"/>
       <c r="F7" s="54" t="s">
         <v>38</v>
       </c>
@@ -10492,11 +10476,11 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="27"/>
       <c r="B8" s="27"/>
-      <c r="C8" s="443"/>
-      <c r="D8" s="448" t="s">
+      <c r="C8" s="475"/>
+      <c r="D8" s="470" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="449"/>
+      <c r="E8" s="471"/>
       <c r="F8" s="54" t="s">
         <v>43</v>
       </c>
@@ -10505,11 +10489,11 @@
     <row r="9" spans="1:7" ht="15.75" customHeight="1">
       <c r="A9" s="27"/>
       <c r="B9" s="27"/>
-      <c r="C9" s="443"/>
-      <c r="D9" s="448" t="s">
+      <c r="C9" s="475"/>
+      <c r="D9" s="470" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="449"/>
+      <c r="E9" s="471"/>
       <c r="F9" s="54" t="s">
         <v>25</v>
       </c>
@@ -10518,11 +10502,11 @@
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="27"/>
       <c r="B10" s="27"/>
-      <c r="C10" s="442"/>
-      <c r="D10" s="448" t="s">
+      <c r="C10" s="476"/>
+      <c r="D10" s="470" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="449"/>
+      <c r="E10" s="471"/>
       <c r="F10" s="54" t="s">
         <v>59</v>
       </c>
@@ -10531,13 +10515,13 @@
     <row r="11" spans="1:7" ht="15.75" customHeight="1">
       <c r="A11" s="27"/>
       <c r="B11" s="27"/>
-      <c r="C11" s="441" t="s">
+      <c r="C11" s="477" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="448" t="s">
+      <c r="D11" s="470" t="s">
         <v>75</v>
       </c>
-      <c r="E11" s="449"/>
+      <c r="E11" s="471"/>
       <c r="F11" s="54" t="s">
         <v>76</v>
       </c>
@@ -10546,11 +10530,11 @@
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
       <c r="A12" s="27"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="442"/>
-      <c r="D12" s="448" t="s">
+      <c r="C12" s="476"/>
+      <c r="D12" s="470" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="449"/>
+      <c r="E12" s="471"/>
       <c r="F12" s="54" t="s">
         <v>86</v>
       </c>
@@ -10559,13 +10543,13 @@
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="27"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="441" t="s">
+      <c r="C13" s="477" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="448" t="s">
+      <c r="D13" s="470" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="449"/>
+      <c r="E13" s="471"/>
       <c r="F13" s="54" t="s">
         <v>89</v>
       </c>
@@ -10574,11 +10558,11 @@
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="443"/>
-      <c r="D14" s="448" t="s">
+      <c r="C14" s="475"/>
+      <c r="D14" s="470" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="449"/>
+      <c r="E14" s="471"/>
       <c r="F14" s="54" t="s">
         <v>91</v>
       </c>
@@ -10587,11 +10571,11 @@
     <row r="15" spans="1:7" ht="15.75" customHeight="1">
       <c r="A15" s="27"/>
       <c r="B15" s="27"/>
-      <c r="C15" s="442"/>
-      <c r="D15" s="448" t="s">
+      <c r="C15" s="476"/>
+      <c r="D15" s="470" t="s">
         <v>92</v>
       </c>
-      <c r="E15" s="449"/>
+      <c r="E15" s="471"/>
       <c r="F15" s="87" t="s">
         <v>94</v>
       </c>
@@ -10600,13 +10584,13 @@
     <row r="16" spans="1:7" ht="15.75" customHeight="1">
       <c r="A16" s="27"/>
       <c r="B16" s="27"/>
-      <c r="C16" s="441" t="s">
+      <c r="C16" s="477" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="453" t="s">
+      <c r="D16" s="472" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="454"/>
+      <c r="E16" s="473"/>
       <c r="F16" s="87" t="s">
         <v>124</v>
       </c>
@@ -10615,8 +10599,8 @@
     <row r="17" spans="1:7" ht="15.75" customHeight="1">
       <c r="A17" s="27"/>
       <c r="B17" s="27"/>
-      <c r="C17" s="443"/>
-      <c r="D17" s="452" t="s">
+      <c r="C17" s="475"/>
+      <c r="D17" s="474" t="s">
         <v>129</v>
       </c>
       <c r="E17" s="105" t="s">
@@ -10630,8 +10614,8 @@
     <row r="18" spans="1:7" ht="15.75" customHeight="1">
       <c r="A18" s="27"/>
       <c r="B18" s="27"/>
-      <c r="C18" s="443"/>
-      <c r="D18" s="443"/>
+      <c r="C18" s="475"/>
+      <c r="D18" s="475"/>
       <c r="E18" s="105" t="s">
         <v>134</v>
       </c>
@@ -10643,8 +10627,8 @@
     <row r="19" spans="1:7" ht="15.75" customHeight="1">
       <c r="A19" s="27"/>
       <c r="B19" s="27"/>
-      <c r="C19" s="443"/>
-      <c r="D19" s="443"/>
+      <c r="C19" s="475"/>
+      <c r="D19" s="475"/>
       <c r="E19" s="105" t="s">
         <v>137</v>
       </c>
@@ -10656,8 +10640,8 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="27"/>
       <c r="B20" s="27"/>
-      <c r="C20" s="443"/>
-      <c r="D20" s="443"/>
+      <c r="C20" s="475"/>
+      <c r="D20" s="475"/>
       <c r="E20" s="105" t="s">
         <v>140</v>
       </c>
@@ -10669,8 +10653,8 @@
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
-      <c r="C21" s="443"/>
-      <c r="D21" s="442"/>
+      <c r="C21" s="475"/>
+      <c r="D21" s="476"/>
       <c r="E21" s="105" t="s">
         <v>145</v>
       </c>
@@ -10682,8 +10666,8 @@
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
       <c r="A22" s="27"/>
       <c r="B22" s="27"/>
-      <c r="C22" s="443"/>
-      <c r="D22" s="451" t="s">
+      <c r="C22" s="475"/>
+      <c r="D22" s="483" t="s">
         <v>165</v>
       </c>
       <c r="E22" s="125" t="s">
@@ -10697,8 +10681,8 @@
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
       <c r="A23" s="27"/>
       <c r="B23" s="27"/>
-      <c r="C23" s="443"/>
-      <c r="D23" s="443"/>
+      <c r="C23" s="475"/>
+      <c r="D23" s="475"/>
       <c r="E23" s="125" t="s">
         <v>177</v>
       </c>
@@ -10710,8 +10694,8 @@
     <row r="24" spans="1:7" ht="15.75" customHeight="1">
       <c r="A24" s="27"/>
       <c r="B24" s="27"/>
-      <c r="C24" s="443"/>
-      <c r="D24" s="443"/>
+      <c r="C24" s="475"/>
+      <c r="D24" s="475"/>
       <c r="E24" s="125" t="s">
         <v>179</v>
       </c>
@@ -10723,8 +10707,8 @@
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="27"/>
       <c r="B25" s="27"/>
-      <c r="C25" s="443"/>
-      <c r="D25" s="443"/>
+      <c r="C25" s="475"/>
+      <c r="D25" s="475"/>
       <c r="E25" s="125" t="s">
         <v>185</v>
       </c>
@@ -10736,8 +10720,8 @@
     <row r="26" spans="1:7" ht="15.75" customHeight="1">
       <c r="A26" s="27"/>
       <c r="B26" s="27"/>
-      <c r="C26" s="443"/>
-      <c r="D26" s="442"/>
+      <c r="C26" s="475"/>
+      <c r="D26" s="476"/>
       <c r="E26" s="125" t="s">
         <v>190</v>
       </c>
@@ -10749,7 +10733,7 @@
     <row r="27" spans="1:7" ht="15.75" customHeight="1">
       <c r="A27" s="27"/>
       <c r="B27" s="27"/>
-      <c r="C27" s="443"/>
+      <c r="C27" s="475"/>
       <c r="D27" s="125" t="s">
         <v>193</v>
       </c>
@@ -10764,7 +10748,7 @@
     <row r="28" spans="1:7" ht="15.75" customHeight="1">
       <c r="A28" s="27"/>
       <c r="B28" s="27"/>
-      <c r="C28" s="443"/>
+      <c r="C28" s="475"/>
       <c r="D28" s="103" t="s">
         <v>221</v>
       </c>
@@ -10779,8 +10763,8 @@
     <row r="29" spans="1:7" ht="15.75" customHeight="1">
       <c r="A29" s="27"/>
       <c r="B29" s="27"/>
-      <c r="C29" s="443"/>
-      <c r="D29" s="452" t="s">
+      <c r="C29" s="475"/>
+      <c r="D29" s="474" t="s">
         <v>235</v>
       </c>
       <c r="E29" s="125" t="s">
@@ -10794,8 +10778,8 @@
     <row r="30" spans="1:7" ht="15.75" customHeight="1">
       <c r="A30" s="27"/>
       <c r="B30" s="27"/>
-      <c r="C30" s="443"/>
-      <c r="D30" s="443"/>
+      <c r="C30" s="475"/>
+      <c r="D30" s="475"/>
       <c r="E30" s="125" t="s">
         <v>244</v>
       </c>
@@ -10807,8 +10791,8 @@
     <row r="31" spans="1:7" ht="15.75" customHeight="1">
       <c r="A31" s="27"/>
       <c r="B31" s="27"/>
-      <c r="C31" s="442"/>
-      <c r="D31" s="442"/>
+      <c r="C31" s="476"/>
+      <c r="D31" s="476"/>
       <c r="E31" s="125" t="s">
         <v>249</v>
       </c>
@@ -10820,13 +10804,13 @@
     <row r="32" spans="1:7" ht="15.75" customHeight="1">
       <c r="A32" s="27"/>
       <c r="B32" s="27"/>
-      <c r="C32" s="441" t="s">
+      <c r="C32" s="477" t="s">
         <v>252</v>
       </c>
-      <c r="D32" s="448" t="s">
+      <c r="D32" s="470" t="s">
         <v>257</v>
       </c>
-      <c r="E32" s="449"/>
+      <c r="E32" s="471"/>
       <c r="F32" s="157" t="s">
         <v>259</v>
       </c>
@@ -10834,11 +10818,11 @@
     <row r="33" spans="1:7" ht="15.75" customHeight="1">
       <c r="A33" s="27"/>
       <c r="B33" s="27"/>
-      <c r="C33" s="443"/>
-      <c r="D33" s="448" t="s">
+      <c r="C33" s="475"/>
+      <c r="D33" s="470" t="s">
         <v>266</v>
       </c>
-      <c r="E33" s="449"/>
+      <c r="E33" s="471"/>
       <c r="F33" s="54" t="s">
         <v>271</v>
       </c>
@@ -10847,11 +10831,11 @@
     <row r="34" spans="1:7" ht="15.75" customHeight="1">
       <c r="A34" s="27"/>
       <c r="B34" s="27"/>
-      <c r="C34" s="442"/>
-      <c r="D34" s="448" t="s">
+      <c r="C34" s="476"/>
+      <c r="D34" s="470" t="s">
         <v>275</v>
       </c>
-      <c r="E34" s="449"/>
+      <c r="E34" s="471"/>
       <c r="F34" s="54" t="s">
         <v>278</v>
       </c>
@@ -10868,14 +10852,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="D17:D21"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="C16:C31"/>
@@ -10892,6 +10868,14 @@
     <mergeCell ref="D29:D31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="D33:E33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="D17:D21"/>
   </mergeCells>
   <phoneticPr fontId="80"/>
   <hyperlinks>
@@ -14222,7 +14206,7 @@
     <row r="71" spans="1:8" ht="26">
       <c r="A71" s="277"/>
       <c r="B71" s="277"/>
-      <c r="C71" s="455">
+      <c r="C71" s="484">
         <v>16</v>
       </c>
       <c r="D71" s="278" t="s">
@@ -14242,7 +14226,7 @@
     <row r="72" spans="1:8" ht="39">
       <c r="A72" s="277"/>
       <c r="B72" s="277"/>
-      <c r="C72" s="443"/>
+      <c r="C72" s="475"/>
       <c r="D72" s="281"/>
       <c r="E72" s="279" t="s">
         <v>742</v>
@@ -14258,7 +14242,7 @@
     <row r="73" spans="1:8" ht="26">
       <c r="A73" s="277"/>
       <c r="B73" s="277"/>
-      <c r="C73" s="442"/>
+      <c r="C73" s="476"/>
       <c r="D73" s="282"/>
       <c r="E73" s="279" t="s">
         <v>745</v>
@@ -17285,7 +17269,7 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="2.6640625" style="304" customWidth="1"/>
@@ -17605,7 +17589,7 @@
       <c r="F14" s="324" t="s">
         <v>911</v>
       </c>
-      <c r="G14" s="499" t="s">
+      <c r="G14" s="333" t="s">
         <v>1064</v>
       </c>
       <c r="H14" s="331" t="s">
@@ -17631,7 +17615,7 @@
       <c r="F15" s="329" t="s">
         <v>915</v>
       </c>
-      <c r="G15" s="499" t="s">
+      <c r="G15" s="333" t="s">
         <v>904</v>
       </c>
       <c r="H15" s="331" t="s">
@@ -17657,7 +17641,7 @@
       <c r="F16" s="329" t="s">
         <v>915</v>
       </c>
-      <c r="G16" s="499" t="s">
+      <c r="G16" s="333" t="s">
         <v>1065</v>
       </c>
       <c r="H16" s="331" t="s">
@@ -17733,7 +17717,7 @@
         <v>898</v>
       </c>
       <c r="F19" s="354" t="s">
-        <v>901</v>
+        <v>1077</v>
       </c>
       <c r="G19" s="433" t="s">
         <v>1068</v>
@@ -17881,7 +17865,7 @@
     <row r="28" spans="1:10" ht="14.25" customHeight="1">
       <c r="A28" s="310"/>
       <c r="B28" s="302"/>
-      <c r="C28" s="467" t="s">
+      <c r="C28" s="363" t="s">
         <v>1021</v>
       </c>
       <c r="D28" s="362" t="s">
@@ -17993,7 +17977,7 @@
       <c r="D35" s="367" t="s">
         <v>1031</v>
       </c>
-      <c r="E35" s="465" t="s">
+      <c r="E35" s="415" t="s">
         <v>1058</v>
       </c>
       <c r="F35" s="310"/>
@@ -18011,7 +17995,7 @@
       <c r="D36" s="369" t="s">
         <v>1032</v>
       </c>
-      <c r="E36" s="466"/>
+      <c r="E36" s="310"/>
       <c r="F36" s="310"/>
       <c r="G36" s="310"/>
       <c r="H36" s="310"/>
@@ -18027,7 +18011,7 @@
       <c r="D37" s="367" t="s">
         <v>1033</v>
       </c>
-      <c r="E37" s="466"/>
+      <c r="E37" s="310"/>
       <c r="F37" s="310"/>
       <c r="G37" s="310"/>
       <c r="H37" s="310"/>
@@ -18043,7 +18027,7 @@
       <c r="D38" s="367" t="s">
         <v>1034</v>
       </c>
-      <c r="E38" s="466"/>
+      <c r="E38" s="310"/>
       <c r="F38" s="310"/>
       <c r="G38" s="310"/>
       <c r="H38" s="310"/>
@@ -18059,7 +18043,7 @@
       <c r="D39" s="367" t="s">
         <v>1035</v>
       </c>
-      <c r="E39" s="465" t="s">
+      <c r="E39" s="415" t="s">
         <v>1059</v>
       </c>
       <c r="F39" s="310"/>
@@ -18077,7 +18061,7 @@
       <c r="D40" s="369" t="s">
         <v>1036</v>
       </c>
-      <c r="E40" s="465" t="s">
+      <c r="E40" s="415" t="s">
         <v>1060</v>
       </c>
       <c r="F40" s="310"/>
@@ -18095,7 +18079,7 @@
       <c r="D41" s="367" t="s">
         <v>1037</v>
       </c>
-      <c r="E41" s="466"/>
+      <c r="E41" s="310"/>
       <c r="F41" s="310"/>
       <c r="G41" s="310"/>
       <c r="H41" s="310"/>
@@ -18111,7 +18095,7 @@
       <c r="D42" s="370" t="s">
         <v>1038</v>
       </c>
-      <c r="E42" s="465" t="s">
+      <c r="E42" s="415" t="s">
         <v>1059</v>
       </c>
       <c r="F42" s="310"/>
@@ -18343,14 +18327,14 @@
     <row r="57" spans="1:10" ht="15.75" customHeight="1">
       <c r="A57" s="310"/>
       <c r="B57" s="302"/>
-      <c r="C57" s="468"/>
-      <c r="D57" s="469" t="s">
+      <c r="C57" s="373"/>
+      <c r="D57" s="444" t="s">
         <v>935</v>
       </c>
-      <c r="E57" s="470" t="s">
+      <c r="E57" s="382" t="s">
         <v>943</v>
       </c>
-      <c r="F57" s="471"/>
+      <c r="F57" s="445"/>
       <c r="H57" s="310"/>
       <c r="I57" s="303"/>
       <c r="J57" s="424"/>
@@ -18358,14 +18342,14 @@
     <row r="58" spans="1:10" ht="15.75" customHeight="1">
       <c r="A58" s="310"/>
       <c r="B58" s="302"/>
-      <c r="C58" s="472"/>
-      <c r="D58" s="473" t="s">
+      <c r="C58" s="446"/>
+      <c r="D58" s="378" t="s">
         <v>937</v>
       </c>
-      <c r="E58" s="474" t="s">
+      <c r="E58" s="447" t="s">
         <v>944</v>
       </c>
-      <c r="F58" s="471"/>
+      <c r="F58" s="445"/>
       <c r="H58" s="310"/>
       <c r="I58" s="303"/>
       <c r="J58" s="424"/>
@@ -18373,16 +18357,16 @@
     <row r="59" spans="1:10" ht="15.75" customHeight="1">
       <c r="A59" s="310"/>
       <c r="B59" s="302"/>
-      <c r="C59" s="475" t="s">
+      <c r="C59" s="381" t="s">
         <v>945</v>
       </c>
-      <c r="D59" s="476" t="s">
+      <c r="D59" s="374" t="s">
         <v>946</v>
       </c>
-      <c r="E59" s="470" t="s">
+      <c r="E59" s="382" t="s">
         <v>1049</v>
       </c>
-      <c r="F59" s="471"/>
+      <c r="F59" s="445"/>
       <c r="H59" s="310"/>
       <c r="I59" s="303"/>
       <c r="J59" s="424"/>
@@ -18390,14 +18374,14 @@
     <row r="60" spans="1:10" ht="15.75" customHeight="1">
       <c r="A60" s="310"/>
       <c r="B60" s="302"/>
-      <c r="C60" s="468"/>
-      <c r="D60" s="469" t="s">
+      <c r="C60" s="373"/>
+      <c r="D60" s="444" t="s">
         <v>947</v>
       </c>
-      <c r="E60" s="474" t="s">
+      <c r="E60" s="447" t="s">
         <v>1050</v>
       </c>
-      <c r="F60" s="471"/>
+      <c r="F60" s="445"/>
       <c r="H60" s="310"/>
       <c r="I60" s="303"/>
       <c r="J60" s="424"/>
@@ -18405,14 +18389,14 @@
     <row r="61" spans="1:10" ht="15.75" customHeight="1">
       <c r="A61" s="310"/>
       <c r="B61" s="302"/>
-      <c r="C61" s="468"/>
-      <c r="D61" s="476" t="s">
+      <c r="C61" s="373"/>
+      <c r="D61" s="374" t="s">
         <v>948</v>
       </c>
-      <c r="E61" s="468" t="s">
+      <c r="E61" s="373" t="s">
         <v>1061</v>
       </c>
-      <c r="F61" s="471"/>
+      <c r="F61" s="445"/>
       <c r="H61" s="310"/>
       <c r="I61" s="303"/>
       <c r="J61" s="424"/>
@@ -18420,14 +18404,14 @@
     <row r="62" spans="1:10" ht="15.75" customHeight="1">
       <c r="A62" s="310"/>
       <c r="B62" s="302"/>
-      <c r="C62" s="468"/>
-      <c r="D62" s="476" t="s">
+      <c r="C62" s="373"/>
+      <c r="D62" s="374" t="s">
         <v>949</v>
       </c>
-      <c r="E62" s="469" t="s">
+      <c r="E62" s="444" t="s">
         <v>1053</v>
       </c>
-      <c r="F62" s="471"/>
+      <c r="F62" s="445"/>
       <c r="H62" s="310"/>
       <c r="I62" s="303"/>
       <c r="J62" s="424"/>
@@ -18435,14 +18419,14 @@
     <row r="63" spans="1:10" ht="15.75" customHeight="1">
       <c r="A63" s="310"/>
       <c r="B63" s="302"/>
-      <c r="C63" s="477"/>
-      <c r="D63" s="476" t="s">
+      <c r="C63" s="377"/>
+      <c r="D63" s="374" t="s">
         <v>716</v>
       </c>
-      <c r="E63" s="470" t="s">
+      <c r="E63" s="382" t="s">
         <v>950</v>
       </c>
-      <c r="F63" s="478"/>
+      <c r="F63" s="448"/>
       <c r="H63" s="310"/>
       <c r="I63" s="303"/>
       <c r="J63" s="424"/>
@@ -18450,16 +18434,16 @@
     <row r="64" spans="1:10" ht="15.75" customHeight="1">
       <c r="A64" s="310"/>
       <c r="B64" s="302"/>
-      <c r="C64" s="475" t="s">
+      <c r="C64" s="381" t="s">
         <v>1063</v>
       </c>
-      <c r="D64" s="479" t="s">
+      <c r="D64" s="449" t="s">
         <v>951</v>
       </c>
-      <c r="E64" s="480" t="s">
+      <c r="E64" s="450" t="s">
         <v>1051</v>
       </c>
-      <c r="F64" s="471"/>
+      <c r="F64" s="445"/>
       <c r="H64" s="310"/>
       <c r="I64" s="303"/>
       <c r="J64" s="424"/>
@@ -18467,14 +18451,14 @@
     <row r="65" spans="1:10" ht="15.75" customHeight="1">
       <c r="A65" s="310"/>
       <c r="B65" s="302"/>
-      <c r="C65" s="468"/>
-      <c r="D65" s="473" t="s">
+      <c r="C65" s="373"/>
+      <c r="D65" s="378" t="s">
         <v>953</v>
       </c>
-      <c r="E65" s="481" t="s">
+      <c r="E65" s="451" t="s">
         <v>1052</v>
       </c>
-      <c r="F65" s="471"/>
+      <c r="F65" s="445"/>
       <c r="H65" s="310"/>
       <c r="I65" s="303"/>
       <c r="J65" s="424"/>
@@ -18482,14 +18466,14 @@
     <row r="66" spans="1:10" ht="15.75" customHeight="1">
       <c r="A66" s="310"/>
       <c r="B66" s="302"/>
-      <c r="C66" s="482"/>
-      <c r="D66" s="483" t="s">
+      <c r="C66" s="452"/>
+      <c r="D66" s="453" t="s">
         <v>954</v>
       </c>
-      <c r="E66" s="458" t="s">
+      <c r="E66" s="383" t="s">
         <v>1061</v>
       </c>
-      <c r="F66" s="471"/>
+      <c r="F66" s="445"/>
       <c r="H66" s="310"/>
       <c r="I66" s="303"/>
       <c r="J66" s="424"/>
@@ -18497,14 +18481,14 @@
     <row r="67" spans="1:10" ht="13">
       <c r="A67" s="310"/>
       <c r="B67" s="302"/>
-      <c r="C67" s="484"/>
-      <c r="D67" s="473" t="s">
+      <c r="C67" s="454"/>
+      <c r="D67" s="378" t="s">
         <v>955</v>
       </c>
-      <c r="E67" s="485" t="s">
+      <c r="E67" s="455" t="s">
         <v>1062</v>
       </c>
-      <c r="F67" s="471"/>
+      <c r="F67" s="445"/>
       <c r="H67" s="310"/>
       <c r="I67" s="303"/>
       <c r="J67" s="424"/>
@@ -18512,14 +18496,14 @@
     <row r="68" spans="1:10" ht="15.75" customHeight="1">
       <c r="A68" s="310"/>
       <c r="B68" s="302"/>
-      <c r="C68" s="486"/>
-      <c r="D68" s="476" t="s">
+      <c r="C68" s="456"/>
+      <c r="D68" s="374" t="s">
         <v>716</v>
       </c>
-      <c r="E68" s="476" t="s">
+      <c r="E68" s="374" t="s">
         <v>950</v>
       </c>
-      <c r="F68" s="487"/>
+      <c r="F68" s="303"/>
       <c r="H68" s="310"/>
       <c r="I68" s="303"/>
       <c r="J68" s="424"/>
@@ -18527,16 +18511,16 @@
     <row r="69" spans="1:10" ht="15.75" customHeight="1">
       <c r="A69" s="310"/>
       <c r="B69" s="302"/>
-      <c r="C69" s="488" t="s">
+      <c r="C69" s="457" t="s">
         <v>956</v>
       </c>
-      <c r="D69" s="489" t="s">
+      <c r="D69" s="458" t="s">
         <v>957</v>
       </c>
-      <c r="E69" s="489" t="s">
+      <c r="E69" s="458" t="s">
         <v>958</v>
       </c>
-      <c r="F69" s="487"/>
+      <c r="F69" s="303"/>
       <c r="H69" s="310"/>
       <c r="I69" s="303"/>
       <c r="J69" s="424"/>
@@ -18544,14 +18528,14 @@
     <row r="70" spans="1:10" ht="15.75" customHeight="1">
       <c r="A70" s="310"/>
       <c r="B70" s="302"/>
-      <c r="C70" s="484"/>
-      <c r="D70" s="489" t="s">
+      <c r="C70" s="454"/>
+      <c r="D70" s="458" t="s">
         <v>959</v>
       </c>
-      <c r="E70" s="489" t="s">
+      <c r="E70" s="458" t="s">
         <v>1071</v>
       </c>
-      <c r="F70" s="487"/>
+      <c r="F70" s="303"/>
       <c r="H70" s="310"/>
       <c r="I70" s="303"/>
       <c r="J70" s="424"/>
@@ -18559,14 +18543,14 @@
     <row r="71" spans="1:10" ht="15.75" customHeight="1">
       <c r="A71" s="310"/>
       <c r="B71" s="302"/>
-      <c r="C71" s="484"/>
-      <c r="D71" s="489" t="s">
+      <c r="C71" s="454"/>
+      <c r="D71" s="458" t="s">
         <v>960</v>
       </c>
-      <c r="E71" s="489" t="s">
+      <c r="E71" s="458" t="s">
         <v>1072</v>
       </c>
-      <c r="F71" s="487"/>
+      <c r="F71" s="303"/>
       <c r="H71" s="310"/>
       <c r="I71" s="303"/>
       <c r="J71" s="424"/>
@@ -18574,14 +18558,14 @@
     <row r="72" spans="1:10" ht="15.75" customHeight="1">
       <c r="A72" s="310"/>
       <c r="B72" s="302"/>
-      <c r="C72" s="484"/>
-      <c r="D72" s="489" t="s">
+      <c r="C72" s="454"/>
+      <c r="D72" s="458" t="s">
         <v>961</v>
       </c>
-      <c r="E72" s="489" t="s">
+      <c r="E72" s="458" t="s">
         <v>958</v>
       </c>
-      <c r="F72" s="487"/>
+      <c r="F72" s="303"/>
       <c r="H72" s="310"/>
       <c r="I72" s="303"/>
       <c r="J72" s="424"/>
@@ -18589,14 +18573,14 @@
     <row r="73" spans="1:10" ht="15.75" customHeight="1">
       <c r="A73" s="310"/>
       <c r="B73" s="302"/>
-      <c r="C73" s="484"/>
-      <c r="D73" s="490" t="s">
+      <c r="C73" s="454"/>
+      <c r="D73" s="459" t="s">
         <v>962</v>
       </c>
-      <c r="E73" s="490" t="s">
+      <c r="E73" s="459" t="s">
         <v>963</v>
       </c>
-      <c r="F73" s="487"/>
+      <c r="F73" s="303"/>
       <c r="H73" s="310"/>
       <c r="I73" s="303"/>
       <c r="J73" s="424"/>
@@ -18604,104 +18588,85 @@
     <row r="74" spans="1:10" ht="15.75" customHeight="1">
       <c r="A74" s="303"/>
       <c r="B74" s="303"/>
-      <c r="C74" s="491" t="s">
+      <c r="C74" s="460" t="s">
         <v>964</v>
       </c>
-      <c r="D74" s="492" t="s">
+      <c r="D74" s="461" t="s">
         <v>959</v>
       </c>
-      <c r="E74" s="493" t="s">
+      <c r="E74" s="462" t="s">
         <v>1073</v>
       </c>
-      <c r="F74" s="487"/>
+      <c r="F74" s="303"/>
       <c r="G74" s="303"/>
       <c r="H74" s="303"/>
       <c r="I74" s="303"/>
       <c r="J74" s="424"/>
     </row>
     <row r="75" spans="1:10" ht="15" customHeight="1">
-      <c r="C75" s="494"/>
-      <c r="D75" s="495" t="s">
+      <c r="C75" s="463"/>
+      <c r="D75" s="464" t="s">
         <v>965</v>
       </c>
-      <c r="E75" s="496" t="s">
+      <c r="E75" s="465" t="s">
         <v>952</v>
       </c>
-      <c r="F75" s="464"/>
     </row>
     <row r="76" spans="1:10" ht="15" customHeight="1">
-      <c r="C76" s="494"/>
-      <c r="D76" s="495" t="s">
+      <c r="C76" s="463"/>
+      <c r="D76" s="464" t="s">
         <v>966</v>
       </c>
-      <c r="E76" s="496" t="s">
+      <c r="E76" s="465" t="s">
         <v>967</v>
       </c>
-      <c r="F76" s="464"/>
     </row>
     <row r="77" spans="1:10" ht="15" customHeight="1">
-      <c r="C77" s="497"/>
-      <c r="D77" s="495" t="s">
+      <c r="C77" s="466"/>
+      <c r="D77" s="464" t="s">
         <v>968</v>
       </c>
-      <c r="E77" s="498" t="s">
+      <c r="E77" s="467" t="s">
         <v>969</v>
       </c>
-      <c r="F77" s="464"/>
     </row>
     <row r="78" spans="1:10" ht="15" customHeight="1">
-      <c r="C78" s="491" t="s">
+      <c r="C78" s="460" t="s">
         <v>970</v>
       </c>
-      <c r="D78" s="492" t="s">
+      <c r="D78" s="461" t="s">
         <v>959</v>
       </c>
-      <c r="E78" s="498" t="s">
+      <c r="E78" s="467" t="s">
         <v>1074</v>
       </c>
-      <c r="F78" s="464"/>
     </row>
     <row r="79" spans="1:10" ht="15" customHeight="1">
-      <c r="C79" s="494"/>
-      <c r="D79" s="495" t="s">
+      <c r="C79" s="463"/>
+      <c r="D79" s="464" t="s">
         <v>965</v>
       </c>
-      <c r="E79" s="496" t="s">
+      <c r="E79" s="465" t="s">
         <v>1075</v>
       </c>
-      <c r="F79" s="464"/>
     </row>
     <row r="80" spans="1:10" ht="15" customHeight="1">
-      <c r="C80" s="494"/>
-      <c r="D80" s="495" t="s">
+      <c r="C80" s="463"/>
+      <c r="D80" s="464" t="s">
         <v>966</v>
       </c>
-      <c r="E80" s="496" t="s">
+      <c r="E80" s="465" t="s">
         <v>967</v>
       </c>
-      <c r="F80" s="464"/>
-    </row>
-    <row r="81" spans="3:6" ht="15" customHeight="1">
-      <c r="C81" s="497"/>
-      <c r="D81" s="495" t="s">
+    </row>
+    <row r="81" spans="3:5" ht="15" customHeight="1">
+      <c r="C81" s="466"/>
+      <c r="D81" s="464" t="s">
         <v>968</v>
       </c>
-      <c r="E81" s="498" t="s">
+      <c r="E81" s="467" t="s">
         <v>969</v>
       </c>
-      <c r="F81" s="464"/>
-    </row>
-    <row r="82" spans="3:6" ht="15" customHeight="1">
-      <c r="C82" s="464"/>
-      <c r="D82" s="464"/>
-      <c r="E82" s="464"/>
-      <c r="F82" s="464"/>
-    </row>
-    <row r="83" spans="3:6" ht="15" customHeight="1">
-      <c r="C83" s="464"/>
-      <c r="D83" s="464"/>
-      <c r="E83" s="464"/>
-      <c r="F83" s="464"/>
     </row>
   </sheetData>
   <phoneticPr fontId="80"/>
